--- a/resumo_busca_ativa_consolidado.xlsx
+++ b/resumo_busca_ativa_consolidado.xlsx
@@ -862,16 +862,16 @@
         <v>19133</v>
       </c>
       <c r="C2">
-        <v>1142</v>
+        <v>1158</v>
       </c>
       <c r="D2">
-        <v>1762</v>
+        <v>1688</v>
       </c>
       <c r="E2">
-        <v>16229</v>
+        <v>16286</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -885,10 +885,10 @@
         <v>874</v>
       </c>
       <c r="D3">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="E3">
-        <v>14274</v>
+        <v>14275</v>
       </c>
       <c r="F3">
         <v>79</v>
@@ -902,13 +902,13 @@
         <v>9446</v>
       </c>
       <c r="C4">
-        <v>567</v>
+        <v>552</v>
       </c>
       <c r="D4">
-        <v>1360</v>
+        <v>1349</v>
       </c>
       <c r="E4">
-        <v>7352</v>
+        <v>7378</v>
       </c>
       <c r="F4">
         <v>167</v>
@@ -952,13 +952,13 @@
         <v>9670</v>
       </c>
       <c r="C2">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="D2">
-        <v>543</v>
+        <v>530</v>
       </c>
       <c r="E2">
-        <v>8589</v>
+        <v>8596</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -972,13 +972,13 @@
         <v>2381</v>
       </c>
       <c r="C3">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D3">
         <v>326</v>
       </c>
       <c r="E3">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="F3">
         <v>48</v>
@@ -992,13 +992,13 @@
         <v>1735</v>
       </c>
       <c r="C4">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D4">
         <v>233</v>
       </c>
       <c r="E4">
-        <v>1389</v>
+        <v>1391</v>
       </c>
       <c r="F4">
         <v>19</v>
@@ -1012,10 +1012,10 @@
         <v>1649</v>
       </c>
       <c r="C5">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D5">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E5">
         <v>1283</v>
@@ -1032,13 +1032,13 @@
         <v>1500</v>
       </c>
       <c r="C6">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D6">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E6">
-        <v>1101</v>
+        <v>1105</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1052,13 +1052,13 @@
         <v>1280</v>
       </c>
       <c r="C7">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D7">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="E7">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -1072,13 +1072,13 @@
         <v>1203</v>
       </c>
       <c r="C8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D8">
         <v>71</v>
       </c>
       <c r="E8">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -1092,13 +1092,13 @@
         <v>1135</v>
       </c>
       <c r="C9">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D9">
         <v>400</v>
       </c>
       <c r="E9">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -1112,13 +1112,13 @@
         <v>977</v>
       </c>
       <c r="C10">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D10">
         <v>68</v>
       </c>
       <c r="E10">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1132,13 +1132,13 @@
         <v>920</v>
       </c>
       <c r="C11">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D11">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E11">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1172,13 +1172,13 @@
         <v>843</v>
       </c>
       <c r="C13">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="D13">
         <v>156</v>
       </c>
       <c r="E13">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="F13">
         <v>140</v>
@@ -1332,10 +1332,10 @@
         <v>616</v>
       </c>
       <c r="C21">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D21">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E21">
         <v>303</v>
@@ -1392,13 +1392,13 @@
         <v>503</v>
       </c>
       <c r="C24">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D24">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="E24">
-        <v>433</v>
+        <v>478</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1432,13 +1432,13 @@
         <v>449</v>
       </c>
       <c r="C26">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="D26">
         <v>188</v>
       </c>
       <c r="E26">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -1452,13 +1452,13 @@
         <v>448</v>
       </c>
       <c r="C27">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D27">
         <v>0</v>
       </c>
       <c r="E27">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -1512,13 +1512,13 @@
         <v>402</v>
       </c>
       <c r="C30">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D30">
         <v>48</v>
       </c>
       <c r="E30">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -1592,13 +1592,13 @@
         <v>295</v>
       </c>
       <c r="C34">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D34">
         <v>74</v>
       </c>
       <c r="E34">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F34">
         <v>0</v>
@@ -1652,13 +1652,13 @@
         <v>238</v>
       </c>
       <c r="C37">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D37">
         <v>36</v>
       </c>
       <c r="E37">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -1712,13 +1712,13 @@
         <v>224</v>
       </c>
       <c r="C40">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D40">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E40">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -1812,13 +1812,13 @@
         <v>187</v>
       </c>
       <c r="C45">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D45">
         <v>0</v>
       </c>
       <c r="E45">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F45">
         <v>0</v>
@@ -1858,10 +1858,10 @@
         <v>0</v>
       </c>
       <c r="E47">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F47">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -1932,13 +1932,13 @@
         <v>151</v>
       </c>
       <c r="C51">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D51">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="E51">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -2475,10 +2475,10 @@
         <v>4</v>
       </c>
       <c r="D78">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E78">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F78">
         <v>0</v>

--- a/resumo_busca_ativa_consolidado.xlsx
+++ b/resumo_busca_ativa_consolidado.xlsx
@@ -862,13 +862,13 @@
         <v>19133</v>
       </c>
       <c r="C2">
-        <v>1158</v>
+        <v>1184</v>
       </c>
       <c r="D2">
-        <v>1688</v>
+        <v>1669</v>
       </c>
       <c r="E2">
-        <v>16286</v>
+        <v>16279</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -882,16 +882,16 @@
         <v>16817</v>
       </c>
       <c r="C3">
-        <v>874</v>
+        <v>901</v>
       </c>
       <c r="D3">
-        <v>1589</v>
+        <v>1560</v>
       </c>
       <c r="E3">
-        <v>14275</v>
+        <v>14278</v>
       </c>
       <c r="F3">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -902,16 +902,16 @@
         <v>9446</v>
       </c>
       <c r="C4">
-        <v>552</v>
+        <v>596</v>
       </c>
       <c r="D4">
-        <v>1349</v>
+        <v>1325</v>
       </c>
       <c r="E4">
-        <v>7378</v>
+        <v>7331</v>
       </c>
       <c r="F4">
-        <v>167</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -952,13 +952,13 @@
         <v>9670</v>
       </c>
       <c r="C2">
-        <v>544</v>
+        <v>554</v>
       </c>
       <c r="D2">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="E2">
-        <v>8596</v>
+        <v>8593</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -972,13 +972,13 @@
         <v>2381</v>
       </c>
       <c r="C3">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D3">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E3">
-        <v>1866</v>
+        <v>1864</v>
       </c>
       <c r="F3">
         <v>48</v>
@@ -992,13 +992,13 @@
         <v>1735</v>
       </c>
       <c r="C4">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D4">
         <v>233</v>
       </c>
       <c r="E4">
-        <v>1391</v>
+        <v>1389</v>
       </c>
       <c r="F4">
         <v>19</v>
@@ -1012,10 +1012,10 @@
         <v>1649</v>
       </c>
       <c r="C5">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="D5">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="E5">
         <v>1283</v>
@@ -1032,10 +1032,10 @@
         <v>1500</v>
       </c>
       <c r="C6">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D6">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="E6">
         <v>1105</v>
@@ -1052,13 +1052,13 @@
         <v>1280</v>
       </c>
       <c r="C7">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="D7">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E7">
-        <v>1038</v>
+        <v>1034</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -1092,13 +1092,13 @@
         <v>1135</v>
       </c>
       <c r="C9">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D9">
-        <v>400</v>
+        <v>388</v>
       </c>
       <c r="E9">
-        <v>649</v>
+        <v>656</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -1112,13 +1112,13 @@
         <v>977</v>
       </c>
       <c r="C10">
+        <v>69</v>
+      </c>
+      <c r="D10">
         <v>67</v>
       </c>
-      <c r="D10">
-        <v>68</v>
-      </c>
       <c r="E10">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1132,13 +1132,13 @@
         <v>920</v>
       </c>
       <c r="C11">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D11">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E11">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1152,7 +1152,7 @@
         <v>911</v>
       </c>
       <c r="C12">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -1161,7 +1161,7 @@
         <v>860</v>
       </c>
       <c r="F12">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1175,10 +1175,10 @@
         <v>58</v>
       </c>
       <c r="D13">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E13">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="F13">
         <v>140</v>
@@ -1215,10 +1215,10 @@
         <v>41</v>
       </c>
       <c r="D15">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E15">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -1232,16 +1232,16 @@
         <v>790</v>
       </c>
       <c r="C16">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="D16">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E16">
-        <v>543</v>
+        <v>518</v>
       </c>
       <c r="F16">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1292,13 +1292,13 @@
         <v>667</v>
       </c>
       <c r="C19">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D19">
         <v>132</v>
       </c>
       <c r="E19">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1412,13 +1412,13 @@
         <v>495</v>
       </c>
       <c r="C25">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D25">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E25">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1432,13 +1432,13 @@
         <v>449</v>
       </c>
       <c r="C26">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="D26">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="E26">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -1472,10 +1472,10 @@
         <v>441</v>
       </c>
       <c r="C28">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D28">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="E28">
         <v>346</v>
@@ -1592,10 +1592,10 @@
         <v>295</v>
       </c>
       <c r="C34">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D34">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="E34">
         <v>208</v>
@@ -1712,13 +1712,13 @@
         <v>224</v>
       </c>
       <c r="C40">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D40">
         <v>72</v>
       </c>
       <c r="E40">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -1818,10 +1818,10 @@
         <v>0</v>
       </c>
       <c r="E45">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="F45">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -1932,10 +1932,10 @@
         <v>151</v>
       </c>
       <c r="C51">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D51">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E51">
         <v>51</v>
@@ -1952,13 +1952,13 @@
         <v>150</v>
       </c>
       <c r="C52">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D52">
         <v>0</v>
       </c>
       <c r="E52">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F52">
         <v>0</v>
@@ -2112,10 +2112,10 @@
         <v>124</v>
       </c>
       <c r="C60">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D60">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E60">
         <v>44</v>
@@ -2152,13 +2152,13 @@
         <v>118</v>
       </c>
       <c r="C62">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D62">
         <v>0</v>
       </c>
       <c r="E62">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F62">
         <v>0</v>
@@ -2258,10 +2258,10 @@
         <v>0</v>
       </c>
       <c r="E67">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="F67">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -2312,13 +2312,13 @@
         <v>99</v>
       </c>
       <c r="C70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D70">
         <v>0</v>
       </c>
       <c r="E70">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F70">
         <v>3</v>

--- a/resumo_busca_ativa_consolidado.xlsx
+++ b/resumo_busca_ativa_consolidado.xlsx
@@ -862,16 +862,16 @@
         <v>19133</v>
       </c>
       <c r="C2">
-        <v>1184</v>
+        <v>1198</v>
       </c>
       <c r="D2">
-        <v>1669</v>
+        <v>1660</v>
       </c>
       <c r="E2">
-        <v>16279</v>
+        <v>16275</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -882,13 +882,13 @@
         <v>16817</v>
       </c>
       <c r="C3">
-        <v>901</v>
+        <v>936</v>
       </c>
       <c r="D3">
-        <v>1560</v>
+        <v>1527</v>
       </c>
       <c r="E3">
-        <v>14278</v>
+        <v>14276</v>
       </c>
       <c r="F3">
         <v>78</v>
@@ -902,13 +902,13 @@
         <v>9446</v>
       </c>
       <c r="C4">
-        <v>596</v>
+        <v>622</v>
       </c>
       <c r="D4">
-        <v>1325</v>
+        <v>1305</v>
       </c>
       <c r="E4">
-        <v>7331</v>
+        <v>7325</v>
       </c>
       <c r="F4">
         <v>194</v>
@@ -952,13 +952,13 @@
         <v>9670</v>
       </c>
       <c r="C2">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="D2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E2">
-        <v>8593</v>
+        <v>8591</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -972,10 +972,10 @@
         <v>2381</v>
       </c>
       <c r="C3">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="D3">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="E3">
         <v>1864</v>
@@ -992,13 +992,13 @@
         <v>1735</v>
       </c>
       <c r="C4">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D4">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E4">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="F4">
         <v>19</v>
@@ -1012,10 +1012,10 @@
         <v>1649</v>
       </c>
       <c r="C5">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D5">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E5">
         <v>1283</v>
@@ -1032,13 +1032,13 @@
         <v>1500</v>
       </c>
       <c r="C6">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D6">
         <v>279</v>
       </c>
       <c r="E6">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1052,10 +1052,10 @@
         <v>1280</v>
       </c>
       <c r="C7">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D7">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E7">
         <v>1034</v>
@@ -1072,10 +1072,10 @@
         <v>1203</v>
       </c>
       <c r="C8">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D8">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E8">
         <v>1076</v>
@@ -1092,10 +1092,10 @@
         <v>1135</v>
       </c>
       <c r="C9">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D9">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="E9">
         <v>656</v>
@@ -1112,10 +1112,10 @@
         <v>977</v>
       </c>
       <c r="C10">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="D10">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="E10">
         <v>841</v>
@@ -1132,13 +1132,13 @@
         <v>920</v>
       </c>
       <c r="C11">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D11">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E11">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1172,13 +1172,13 @@
         <v>843</v>
       </c>
       <c r="C13">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D13">
         <v>155</v>
       </c>
       <c r="E13">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="F13">
         <v>140</v>
@@ -1192,13 +1192,13 @@
         <v>813</v>
       </c>
       <c r="C14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1232,13 +1232,13 @@
         <v>790</v>
       </c>
       <c r="C16">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D16">
         <v>174</v>
       </c>
       <c r="E16">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="F16">
         <v>33</v>
@@ -1332,10 +1332,10 @@
         <v>616</v>
       </c>
       <c r="C21">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D21">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E21">
         <v>303</v>
@@ -1372,10 +1372,10 @@
         <v>601</v>
       </c>
       <c r="C23">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D23">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="E23">
         <v>435</v>
@@ -1412,10 +1412,10 @@
         <v>495</v>
       </c>
       <c r="C25">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D25">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E25">
         <v>430</v>
@@ -1432,13 +1432,13 @@
         <v>449</v>
       </c>
       <c r="C26">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D26">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="E26">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -1532,13 +1532,13 @@
         <v>394</v>
       </c>
       <c r="C31">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D31">
         <v>71</v>
       </c>
       <c r="E31">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F31">
         <v>0</v>
@@ -1592,10 +1592,10 @@
         <v>295</v>
       </c>
       <c r="C34">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D34">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E34">
         <v>208</v>
@@ -1692,10 +1692,10 @@
         <v>232</v>
       </c>
       <c r="C39">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D39">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E39">
         <v>194</v>
@@ -1712,13 +1712,13 @@
         <v>224</v>
       </c>
       <c r="C40">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D40">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="E40">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -1855,13 +1855,13 @@
         <v>2</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E47">
         <v>164</v>
       </c>
       <c r="F47">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:6">

--- a/resumo_busca_ativa_consolidado.xlsx
+++ b/resumo_busca_ativa_consolidado.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="200">
   <si>
     <t>REGIONAL</t>
   </si>
@@ -50,6 +50,9 @@
     <t>ANAPOLIS</t>
   </si>
   <si>
+    <t>SAO LUIS</t>
+  </si>
+  <si>
     <t>RIO VERDE</t>
   </si>
   <si>
@@ -140,9 +143,15 @@
     <t>PONTALINA</t>
   </si>
   <si>
+    <t>IMPERATRIZ</t>
+  </si>
+  <si>
     <t>PADRE BERNARDO</t>
   </si>
   <si>
+    <t>SAO JOSE DE RIBAMAR</t>
+  </si>
+  <si>
     <t>POSSE</t>
   </si>
   <si>
@@ -152,6 +161,9 @@
     <t>ACREUNA</t>
   </si>
   <si>
+    <t>ACAILANDIA</t>
+  </si>
+  <si>
     <t>ITAPACI</t>
   </si>
   <si>
@@ -179,6 +191,9 @@
     <t>CAMPOS BELOS</t>
   </si>
   <si>
+    <t>BALSAS</t>
+  </si>
+  <si>
     <t>MAURILANDIA</t>
   </si>
   <si>
@@ -188,12 +203,12 @@
     <t>SAO SIMAO</t>
   </si>
   <si>
+    <t>CRIXAS</t>
+  </si>
+  <si>
     <t>SANTA TEREZINHA DE GOIAS</t>
   </si>
   <si>
-    <t>CRIXAS</t>
-  </si>
-  <si>
     <t>PETROLINA DE GOIAS</t>
   </si>
   <si>
@@ -203,6 +218,9 @@
     <t>CORUMBA DE GOIAS</t>
   </si>
   <si>
+    <t>PACO DO LUMIAR</t>
+  </si>
+  <si>
     <t>GOIANDIRA</t>
   </si>
   <si>
@@ -215,21 +233,27 @@
     <t>CAMPO ALEGRE DE GOIAS</t>
   </si>
   <si>
+    <t>FORMOSO</t>
+  </si>
+  <si>
     <t>BARRO ALTO</t>
   </si>
   <si>
-    <t>FORMOSO</t>
-  </si>
-  <si>
     <t>CAMPINORTE</t>
   </si>
   <si>
     <t>TEREZOPOLIS DE GOIAS</t>
   </si>
   <si>
+    <t>SAO BERNARDO</t>
+  </si>
+  <si>
     <t>INACIOLANDIA</t>
   </si>
   <si>
+    <t>GRAJAU</t>
+  </si>
+  <si>
     <t>CORUMBAIBA</t>
   </si>
   <si>
@@ -254,9 +278,15 @@
     <t>CACHOEIRA ALTA</t>
   </si>
   <si>
+    <t>BARREIRINHAS</t>
+  </si>
+  <si>
     <t>JOVIANIA</t>
   </si>
   <si>
+    <t>ARAIOSES</t>
+  </si>
+  <si>
     <t>PARANAIGUARA</t>
   </si>
   <si>
@@ -281,6 +311,12 @@
     <t>CACHOEIRA DOURADA</t>
   </si>
   <si>
+    <t>ITINGA DO MARANHAO</t>
+  </si>
+  <si>
+    <t>ROSARIO</t>
+  </si>
+  <si>
     <t>MONTE ALEGRE DE GOIAS</t>
   </si>
   <si>
@@ -293,12 +329,15 @@
     <t>URUTAI</t>
   </si>
   <si>
+    <t>TUTOIA</t>
+  </si>
+  <si>
+    <t>CABECEIRAS</t>
+  </si>
+  <si>
     <t>PALMELO</t>
   </si>
   <si>
-    <t>CABECEIRAS</t>
-  </si>
-  <si>
     <t>OUVIDOR</t>
   </si>
   <si>
@@ -311,19 +350,28 @@
     <t>PORTEIRAO</t>
   </si>
   <si>
+    <t>MONTIVIDIU</t>
+  </si>
+  <si>
     <t>HIDROLINA</t>
   </si>
   <si>
-    <t>MONTIVIDIU</t>
-  </si>
-  <si>
     <t>TURVELANDIA</t>
   </si>
   <si>
+    <t>MAGALHAES DE ALMEIDA</t>
+  </si>
+  <si>
+    <t>TROMBAS</t>
+  </si>
+  <si>
     <t>CAVALCANTE</t>
   </si>
   <si>
-    <t>TROMBAS</t>
+    <t>SANTO ANTONIO DA BARRA</t>
+  </si>
+  <si>
+    <t>UIRAPURU</t>
   </si>
   <si>
     <t>SAO JOAO D ALIANCA</t>
@@ -332,10 +380,7 @@
     <t>CROMINIA</t>
   </si>
   <si>
-    <t>SANTO ANTONIO DA BARRA</t>
-  </si>
-  <si>
-    <t>UIRAPURU</t>
+    <t>CAROLINA</t>
   </si>
   <si>
     <t>SIMOLANDIA</t>
@@ -350,30 +395,42 @@
     <t>FLORES DE GOIAS</t>
   </si>
   <si>
+    <t>RIACHAO</t>
+  </si>
+  <si>
+    <t>SAO RAIMUNDO DAS MANGABEIRAS</t>
+  </si>
+  <si>
+    <t>AGUA DOCE DO MARANHAO</t>
+  </si>
+  <si>
+    <t>TRES RANCHOS</t>
+  </si>
+  <si>
+    <t>MAIRIPOTABA</t>
+  </si>
+  <si>
     <t>CAMPOS VERDES</t>
   </si>
   <si>
     <t>ALTO PARAISO DE GOIAS</t>
   </si>
   <si>
-    <t>TRES RANCHOS</t>
-  </si>
-  <si>
-    <t>MAIRIPOTABA</t>
+    <t>ARAME</t>
   </si>
   <si>
     <t>NOVO PLANALTO</t>
   </si>
   <si>
+    <t>ITARUMA</t>
+  </si>
+  <si>
+    <t>PROFESSOR JAMIL</t>
+  </si>
+  <si>
     <t>ESTRELA DO NORTE</t>
   </si>
   <si>
-    <t>ITARUMA</t>
-  </si>
-  <si>
-    <t>PROFESSOR JAMIL</t>
-  </si>
-  <si>
     <t>CAMPINACU</t>
   </si>
   <si>
@@ -386,91 +443,175 @@
     <t>NOVA AURORA</t>
   </si>
   <si>
+    <t>HUMBERTO DE CAMPOS</t>
+  </si>
+  <si>
     <t>AGUA FRIA DE GOIAS</t>
   </si>
   <si>
+    <t>SANTA RITA</t>
+  </si>
+  <si>
+    <t>LORETO</t>
+  </si>
+  <si>
     <t>JESUPOLIS</t>
   </si>
   <si>
+    <t>ALOANDIA</t>
+  </si>
+  <si>
+    <t>MONTIVIDIU DO NORTE</t>
+  </si>
+  <si>
     <t>VILA BOA</t>
   </si>
   <si>
-    <t>ALOANDIA</t>
-  </si>
-  <si>
-    <t>MONTIVIDIU DO NORTE</t>
-  </si>
-  <si>
     <t>NOVA ROMA</t>
   </si>
   <si>
+    <t>ICATU</t>
+  </si>
+  <si>
     <t>BURITINOPOLIS</t>
   </si>
   <si>
+    <t>VILA PROPICIO</t>
+  </si>
+  <si>
     <t>APARECIDA DO RIO DOCE</t>
   </si>
   <si>
-    <t>VILA PROPICIO</t>
+    <t>NOVA AMERICA</t>
   </si>
   <si>
     <t>MAMBAI</t>
   </si>
   <si>
-    <t>NOVA AMERICA</t>
-  </si>
-  <si>
     <t>SANTA RITA DO NOVO DESTINO</t>
   </si>
   <si>
     <t>BONOPOLIS</t>
   </si>
   <si>
+    <t>MORROS</t>
+  </si>
+  <si>
+    <t>COLINAS DO SUL</t>
+  </si>
+  <si>
     <t>AGUA LIMPA</t>
   </si>
   <si>
-    <t>COLINAS DO SUL</t>
+    <t>PILAR DE GOIAS</t>
+  </si>
+  <si>
+    <t>AMARALINA</t>
   </si>
   <si>
     <t>NOVA IGUACU DE GOIAS</t>
   </si>
   <si>
-    <t>AMARALINA</t>
-  </si>
-  <si>
-    <t>PILAR DE GOIAS</t>
-  </si>
-  <si>
     <t>ALTO HORIZONTE</t>
   </si>
   <si>
     <t>GUARINOS</t>
   </si>
   <si>
+    <t>EDEALINA</t>
+  </si>
+  <si>
     <t>MIMOSO DE GOIAS</t>
   </si>
   <si>
-    <t>EDEALINA</t>
-  </si>
-  <si>
     <t>GUARANI DE GOIAS</t>
   </si>
   <si>
     <t>DAVINOPOLIS</t>
   </si>
   <si>
+    <t>FORTALEZA DOS NOGUEIRAS</t>
+  </si>
+  <si>
+    <t>AXIXA</t>
+  </si>
+  <si>
+    <t>CIDELANDIA</t>
+  </si>
+  <si>
     <t>ANHANGUERA</t>
   </si>
   <si>
+    <t>BURITICUPU</t>
+  </si>
+  <si>
+    <t>PAULINO NEVES</t>
+  </si>
+  <si>
+    <t>SAO PEDRO DA AGUA BRANCA</t>
+  </si>
+  <si>
+    <t>SANTANA DO MARANHAO</t>
+  </si>
+  <si>
+    <t>SAO FELIX DE BALSAS</t>
+  </si>
+  <si>
     <t>MARZAGAO</t>
   </si>
   <si>
+    <t>SITIO D ABADIA</t>
+  </si>
+  <si>
     <t>PANAMA</t>
   </si>
   <si>
-    <t>SITIO D ABADIA</t>
+    <t>PRIMEIRA CRUZ</t>
+  </si>
+  <si>
+    <t>TASSO FRAGOSO</t>
   </si>
   <si>
     <t>TERESINA DE GOIAS</t>
+  </si>
+  <si>
+    <t>SANTO AMARO DO MARANHAO</t>
+  </si>
+  <si>
+    <t>BACABEIRA</t>
+  </si>
+  <si>
+    <t>BOM JESUS DA SELVA</t>
+  </si>
+  <si>
+    <t>RAPOSA</t>
+  </si>
+  <si>
+    <t>VILA NOVA DOS MARTIRIOS</t>
+  </si>
+  <si>
+    <t>PRESIDENTE JUSCELINO</t>
+  </si>
+  <si>
+    <t>ALTO PARNAIBA</t>
+  </si>
+  <si>
+    <t>SAMBAIBA</t>
+  </si>
+  <si>
+    <t>FORMOSA DA SERRA NEGRA</t>
+  </si>
+  <si>
+    <t>CACHOEIRA GRANDE</t>
+  </si>
+  <si>
+    <t>SAO FRANCISCO DO BREJAO</t>
+  </si>
+  <si>
+    <t>NOVA COLINAS</t>
+  </si>
+  <si>
+    <t>ITAIPAVA DO GRAJAU</t>
   </si>
   <si>
     <t>SAO JOAO DA ALIANCA</t>
@@ -859,19 +1000,19 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>19133</v>
+        <v>24745</v>
       </c>
       <c r="C2">
-        <v>1198</v>
+        <v>1518</v>
       </c>
       <c r="D2">
-        <v>1660</v>
+        <v>1667</v>
       </c>
       <c r="E2">
-        <v>16275</v>
+        <v>21542</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -879,16 +1020,16 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>16817</v>
+        <v>18293</v>
       </c>
       <c r="C3">
-        <v>936</v>
+        <v>1090</v>
       </c>
       <c r="D3">
-        <v>1527</v>
+        <v>1481</v>
       </c>
       <c r="E3">
-        <v>14276</v>
+        <v>15639</v>
       </c>
       <c r="F3">
         <v>78</v>
@@ -899,19 +1040,19 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>9446</v>
+        <v>9443</v>
       </c>
       <c r="C4">
-        <v>622</v>
+        <v>644</v>
       </c>
       <c r="D4">
-        <v>1305</v>
+        <v>1288</v>
       </c>
       <c r="E4">
-        <v>7325</v>
+        <v>7324</v>
       </c>
       <c r="F4">
-        <v>194</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -921,7 +1062,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F144"/>
+  <dimension ref="A1:F191"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -949,16 +1090,16 @@
         <v>10</v>
       </c>
       <c r="B2">
-        <v>9670</v>
+        <v>9667</v>
       </c>
       <c r="C2">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="D2">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="E2">
-        <v>8591</v>
+        <v>8592</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -969,19 +1110,19 @@
         <v>11</v>
       </c>
       <c r="B3">
-        <v>2381</v>
+        <v>4220</v>
       </c>
       <c r="C3">
-        <v>154</v>
+        <v>231</v>
       </c>
       <c r="D3">
-        <v>315</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>1864</v>
+        <v>3975</v>
       </c>
       <c r="F3">
-        <v>48</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -989,19 +1130,19 @@
         <v>12</v>
       </c>
       <c r="B4">
-        <v>1735</v>
+        <v>2381</v>
       </c>
       <c r="C4">
-        <v>96</v>
+        <v>160</v>
       </c>
       <c r="D4">
-        <v>232</v>
+        <v>309</v>
       </c>
       <c r="E4">
-        <v>1388</v>
+        <v>1864</v>
       </c>
       <c r="F4">
-        <v>19</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1009,19 +1150,19 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>1649</v>
+        <v>1735</v>
       </c>
       <c r="C5">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="D5">
-        <v>252</v>
+        <v>226</v>
       </c>
       <c r="E5">
-        <v>1283</v>
+        <v>1388</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1029,19 +1170,19 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>1500</v>
+        <v>1649</v>
       </c>
       <c r="C6">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D6">
-        <v>279</v>
+        <v>252</v>
       </c>
       <c r="E6">
-        <v>1104</v>
+        <v>1283</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1049,19 +1190,19 @@
         <v>15</v>
       </c>
       <c r="B7">
-        <v>1280</v>
+        <v>1500</v>
       </c>
       <c r="C7">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="D7">
-        <v>137</v>
+        <v>275</v>
       </c>
       <c r="E7">
-        <v>1034</v>
+        <v>1102</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1069,16 +1210,16 @@
         <v>16</v>
       </c>
       <c r="B8">
-        <v>1203</v>
+        <v>1279</v>
       </c>
       <c r="C8">
-        <v>57</v>
+        <v>115</v>
       </c>
       <c r="D8">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="E8">
-        <v>1076</v>
+        <v>1034</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -1089,16 +1230,16 @@
         <v>17</v>
       </c>
       <c r="B9">
-        <v>1135</v>
+        <v>1203</v>
       </c>
       <c r="C9">
-        <v>96</v>
+        <v>57</v>
       </c>
       <c r="D9">
-        <v>383</v>
+        <v>70</v>
       </c>
       <c r="E9">
-        <v>656</v>
+        <v>1076</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -1109,16 +1250,16 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>977</v>
+        <v>1135</v>
       </c>
       <c r="C10">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="D10">
-        <v>56</v>
+        <v>331</v>
       </c>
       <c r="E10">
-        <v>841</v>
+        <v>694</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1129,16 +1270,16 @@
         <v>19</v>
       </c>
       <c r="B11">
-        <v>920</v>
+        <v>977</v>
       </c>
       <c r="C11">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="D11">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="E11">
-        <v>836</v>
+        <v>828</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1149,19 +1290,19 @@
         <v>20</v>
       </c>
       <c r="B12">
-        <v>911</v>
+        <v>920</v>
       </c>
       <c r="C12">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="E12">
-        <v>860</v>
+        <v>836</v>
       </c>
       <c r="F12">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1169,19 +1310,19 @@
         <v>21</v>
       </c>
       <c r="B13">
-        <v>843</v>
+        <v>911</v>
       </c>
       <c r="C13">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="D13">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>489</v>
+        <v>860</v>
       </c>
       <c r="F13">
-        <v>140</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1189,19 +1330,19 @@
         <v>22</v>
       </c>
       <c r="B14">
-        <v>813</v>
+        <v>842</v>
       </c>
       <c r="C14">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="E14">
-        <v>791</v>
+        <v>490</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>140</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1209,16 +1350,16 @@
         <v>23</v>
       </c>
       <c r="B15">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="C15">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="D15">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="E15">
-        <v>710</v>
+        <v>791</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -1229,19 +1370,19 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>790</v>
+        <v>811</v>
       </c>
       <c r="C16">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="D16">
-        <v>174</v>
+        <v>60</v>
       </c>
       <c r="E16">
-        <v>516</v>
+        <v>710</v>
       </c>
       <c r="F16">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1249,19 +1390,19 @@
         <v>25</v>
       </c>
       <c r="B17">
-        <v>729</v>
+        <v>790</v>
       </c>
       <c r="C17">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="E17">
-        <v>707</v>
+        <v>516</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -1269,16 +1410,16 @@
         <v>26</v>
       </c>
       <c r="B18">
-        <v>695</v>
+        <v>729</v>
       </c>
       <c r="C18">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D18">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="E18">
-        <v>616</v>
+        <v>707</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1289,16 +1430,16 @@
         <v>27</v>
       </c>
       <c r="B19">
-        <v>667</v>
+        <v>695</v>
       </c>
       <c r="C19">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="D19">
-        <v>132</v>
+        <v>49</v>
       </c>
       <c r="E19">
-        <v>474</v>
+        <v>616</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1309,16 +1450,16 @@
         <v>28</v>
       </c>
       <c r="B20">
-        <v>646</v>
+        <v>666</v>
       </c>
       <c r="C20">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="D20">
-        <v>38</v>
+        <v>132</v>
       </c>
       <c r="E20">
-        <v>581</v>
+        <v>474</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1329,16 +1470,16 @@
         <v>29</v>
       </c>
       <c r="B21">
-        <v>616</v>
+        <v>646</v>
       </c>
       <c r="C21">
-        <v>87</v>
+        <v>27</v>
       </c>
       <c r="D21">
-        <v>226</v>
+        <v>38</v>
       </c>
       <c r="E21">
-        <v>303</v>
+        <v>581</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1349,16 +1490,16 @@
         <v>30</v>
       </c>
       <c r="B22">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="C22">
-        <v>36</v>
+        <v>87</v>
       </c>
       <c r="D22">
-        <v>94</v>
+        <v>226</v>
       </c>
       <c r="E22">
-        <v>481</v>
+        <v>303</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1369,16 +1510,16 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>601</v>
+        <v>611</v>
       </c>
       <c r="C23">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D23">
-        <v>126</v>
+        <v>94</v>
       </c>
       <c r="E23">
-        <v>435</v>
+        <v>481</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -1389,16 +1530,16 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>503</v>
+        <v>601</v>
       </c>
       <c r="C24">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="E24">
-        <v>478</v>
+        <v>435</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1409,16 +1550,16 @@
         <v>33</v>
       </c>
       <c r="B25">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="C25">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="D25">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="E25">
-        <v>430</v>
+        <v>478</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1429,16 +1570,16 @@
         <v>34</v>
       </c>
       <c r="B26">
-        <v>449</v>
+        <v>495</v>
       </c>
       <c r="C26">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="D26">
-        <v>168</v>
+        <v>29</v>
       </c>
       <c r="E26">
-        <v>226</v>
+        <v>430</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -1449,16 +1590,16 @@
         <v>35</v>
       </c>
       <c r="B27">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C27">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="E27">
-        <v>420</v>
+        <v>226</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -1469,16 +1610,16 @@
         <v>36</v>
       </c>
       <c r="B28">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="C28">
         <v>28</v>
       </c>
       <c r="D28">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="E28">
-        <v>346</v>
+        <v>420</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -1489,16 +1630,16 @@
         <v>37</v>
       </c>
       <c r="B29">
-        <v>406</v>
+        <v>441</v>
       </c>
       <c r="C29">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D29">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E29">
-        <v>309</v>
+        <v>346</v>
       </c>
       <c r="F29">
         <v>0</v>
@@ -1509,16 +1650,16 @@
         <v>38</v>
       </c>
       <c r="B30">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="C30">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D30">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="E30">
-        <v>329</v>
+        <v>309</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -1529,16 +1670,16 @@
         <v>39</v>
       </c>
       <c r="B31">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="C31">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D31">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="E31">
-        <v>292</v>
+        <v>329</v>
       </c>
       <c r="F31">
         <v>0</v>
@@ -1549,16 +1690,16 @@
         <v>40</v>
       </c>
       <c r="B32">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="C32">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="E32">
-        <v>376</v>
+        <v>292</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -1569,16 +1710,16 @@
         <v>41</v>
       </c>
       <c r="B33">
-        <v>316</v>
+        <v>389</v>
       </c>
       <c r="C33">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D33">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="E33">
-        <v>252</v>
+        <v>376</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -1589,16 +1730,16 @@
         <v>42</v>
       </c>
       <c r="B34">
-        <v>295</v>
+        <v>346</v>
       </c>
       <c r="C34">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="D34">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="E34">
-        <v>208</v>
+        <v>261</v>
       </c>
       <c r="F34">
         <v>0</v>
@@ -1609,16 +1750,16 @@
         <v>43</v>
       </c>
       <c r="B35">
-        <v>269</v>
+        <v>316</v>
       </c>
       <c r="C35">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D35">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="E35">
-        <v>175</v>
+        <v>252</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -1629,16 +1770,16 @@
         <v>44</v>
       </c>
       <c r="B36">
-        <v>246</v>
+        <v>312</v>
       </c>
       <c r="C36">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E36">
-        <v>209</v>
+        <v>261</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -1649,16 +1790,16 @@
         <v>45</v>
       </c>
       <c r="B37">
-        <v>238</v>
+        <v>295</v>
       </c>
       <c r="C37">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D37">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="E37">
-        <v>180</v>
+        <v>208</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -1669,16 +1810,16 @@
         <v>46</v>
       </c>
       <c r="B38">
-        <v>237</v>
+        <v>269</v>
       </c>
       <c r="C38">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D38">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E38">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="F38">
         <v>0</v>
@@ -1689,16 +1830,16 @@
         <v>47</v>
       </c>
       <c r="B39">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="C39">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D39">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E39">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -1709,16 +1850,16 @@
         <v>48</v>
       </c>
       <c r="B40">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="C40">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D40">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="E40">
-        <v>131</v>
+        <v>221</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -1729,16 +1870,16 @@
         <v>49</v>
       </c>
       <c r="B41">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="C41">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="E41">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -1749,16 +1890,16 @@
         <v>50</v>
       </c>
       <c r="B42">
-        <v>207</v>
+        <v>237</v>
       </c>
       <c r="C42">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="E42">
-        <v>199</v>
+        <v>145</v>
       </c>
       <c r="F42">
         <v>0</v>
@@ -1769,16 +1910,16 @@
         <v>51</v>
       </c>
       <c r="B43">
-        <v>200</v>
+        <v>232</v>
       </c>
       <c r="C43">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D43">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="E43">
-        <v>138</v>
+        <v>194</v>
       </c>
       <c r="F43">
         <v>0</v>
@@ -1789,16 +1930,16 @@
         <v>52</v>
       </c>
       <c r="B44">
-        <v>194</v>
+        <v>223</v>
       </c>
       <c r="C44">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="D44">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="E44">
-        <v>183</v>
+        <v>131</v>
       </c>
       <c r="F44">
         <v>0</v>
@@ -1809,19 +1950,19 @@
         <v>53</v>
       </c>
       <c r="B45">
-        <v>187</v>
+        <v>223</v>
       </c>
       <c r="C45">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D45">
         <v>0</v>
       </c>
       <c r="E45">
-        <v>172</v>
+        <v>220</v>
       </c>
       <c r="F45">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -1829,19 +1970,19 @@
         <v>54</v>
       </c>
       <c r="B46">
-        <v>182</v>
+        <v>207</v>
       </c>
       <c r="C46">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D46">
         <v>0</v>
       </c>
       <c r="E46">
-        <v>177</v>
+        <v>199</v>
       </c>
       <c r="F46">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -1849,16 +1990,16 @@
         <v>55</v>
       </c>
       <c r="B47">
-        <v>167</v>
+        <v>199</v>
       </c>
       <c r="C47">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D47">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="E47">
-        <v>164</v>
+        <v>138</v>
       </c>
       <c r="F47">
         <v>0</v>
@@ -1869,16 +2010,16 @@
         <v>56</v>
       </c>
       <c r="B48">
-        <v>163</v>
+        <v>194</v>
       </c>
       <c r="C48">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D48">
         <v>0</v>
       </c>
       <c r="E48">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="F48">
         <v>0</v>
@@ -1889,19 +2030,19 @@
         <v>57</v>
       </c>
       <c r="B49">
-        <v>154</v>
+        <v>187</v>
       </c>
       <c r="C49">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D49">
         <v>0</v>
       </c>
       <c r="E49">
-        <v>148</v>
+        <v>172</v>
       </c>
       <c r="F49">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -1909,16 +2050,16 @@
         <v>58</v>
       </c>
       <c r="B50">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="C50">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D50">
         <v>0</v>
       </c>
       <c r="E50">
-        <v>144</v>
+        <v>177</v>
       </c>
       <c r="F50">
         <v>0</v>
@@ -1929,19 +2070,19 @@
         <v>59</v>
       </c>
       <c r="B51">
-        <v>151</v>
+        <v>182</v>
       </c>
       <c r="C51">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="D51">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="E51">
-        <v>51</v>
+        <v>177</v>
       </c>
       <c r="F51">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -1949,16 +2090,16 @@
         <v>60</v>
       </c>
       <c r="B52">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="C52">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E52">
-        <v>142</v>
+        <v>164</v>
       </c>
       <c r="F52">
         <v>0</v>
@@ -1969,7 +2110,7 @@
         <v>61</v>
       </c>
       <c r="B53">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="C53">
         <v>7</v>
@@ -1978,7 +2119,7 @@
         <v>0</v>
       </c>
       <c r="E53">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="F53">
         <v>0</v>
@@ -1989,16 +2130,16 @@
         <v>62</v>
       </c>
       <c r="B54">
+        <v>154</v>
+      </c>
+      <c r="C54">
+        <v>10</v>
+      </c>
+      <c r="D54">
+        <v>0</v>
+      </c>
+      <c r="E54">
         <v>144</v>
-      </c>
-      <c r="C54">
-        <v>4</v>
-      </c>
-      <c r="D54">
-        <v>0</v>
-      </c>
-      <c r="E54">
-        <v>140</v>
       </c>
       <c r="F54">
         <v>0</v>
@@ -2009,16 +2150,16 @@
         <v>63</v>
       </c>
       <c r="B55">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="C55">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D55">
         <v>0</v>
       </c>
       <c r="E55">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="F55">
         <v>0</v>
@@ -2029,16 +2170,16 @@
         <v>64</v>
       </c>
       <c r="B56">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="C56">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="E56">
-        <v>129</v>
+        <v>51</v>
       </c>
       <c r="F56">
         <v>0</v>
@@ -2049,16 +2190,16 @@
         <v>65</v>
       </c>
       <c r="B57">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="C57">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D57">
         <v>0</v>
       </c>
       <c r="E57">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="F57">
         <v>0</v>
@@ -2069,16 +2210,16 @@
         <v>66</v>
       </c>
       <c r="B58">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="C58">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D58">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E58">
-        <v>109</v>
+        <v>143</v>
       </c>
       <c r="F58">
         <v>0</v>
@@ -2089,16 +2230,16 @@
         <v>67</v>
       </c>
       <c r="B59">
-        <v>127</v>
+        <v>149</v>
       </c>
       <c r="C59">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D59">
         <v>0</v>
       </c>
       <c r="E59">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="F59">
         <v>0</v>
@@ -2109,16 +2250,16 @@
         <v>68</v>
       </c>
       <c r="B60">
-        <v>124</v>
+        <v>144</v>
       </c>
       <c r="C60">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D60">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="E60">
-        <v>44</v>
+        <v>140</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -2129,16 +2270,16 @@
         <v>69</v>
       </c>
       <c r="B61">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="C61">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D61">
         <v>0</v>
       </c>
       <c r="E61">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="F61">
         <v>0</v>
@@ -2149,16 +2290,16 @@
         <v>70</v>
       </c>
       <c r="B62">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="C62">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D62">
         <v>0</v>
       </c>
       <c r="E62">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="F62">
         <v>0</v>
@@ -2169,16 +2310,16 @@
         <v>71</v>
       </c>
       <c r="B63">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="C63">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D63">
         <v>0</v>
       </c>
       <c r="E63">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="F63">
         <v>0</v>
@@ -2189,16 +2330,16 @@
         <v>72</v>
       </c>
       <c r="B64">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="C64">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D64">
         <v>0</v>
       </c>
       <c r="E64">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -2209,16 +2350,16 @@
         <v>73</v>
       </c>
       <c r="B65">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="C65">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D65">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E65">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F65">
         <v>0</v>
@@ -2229,16 +2370,16 @@
         <v>74</v>
       </c>
       <c r="B66">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="C66">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D66">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="E66">
-        <v>104</v>
+        <v>44</v>
       </c>
       <c r="F66">
         <v>0</v>
@@ -2249,19 +2390,19 @@
         <v>75</v>
       </c>
       <c r="B67">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="C67">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D67">
         <v>0</v>
       </c>
       <c r="E67">
-        <v>92</v>
+        <v>119</v>
       </c>
       <c r="F67">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -2269,16 +2410,16 @@
         <v>76</v>
       </c>
       <c r="B68">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="C68">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D68">
         <v>0</v>
       </c>
       <c r="E68">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="F68">
         <v>0</v>
@@ -2289,16 +2430,16 @@
         <v>77</v>
       </c>
       <c r="B69">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="C69">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D69">
         <v>0</v>
       </c>
       <c r="E69">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="F69">
         <v>0</v>
@@ -2309,19 +2450,19 @@
         <v>78</v>
       </c>
       <c r="B70">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="C70">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D70">
         <v>0</v>
       </c>
       <c r="E70">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="F70">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:6">
@@ -2329,7 +2470,7 @@
         <v>79</v>
       </c>
       <c r="B71">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="C71">
         <v>4</v>
@@ -2338,7 +2479,7 @@
         <v>0</v>
       </c>
       <c r="E71">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="F71">
         <v>0</v>
@@ -2349,16 +2490,16 @@
         <v>80</v>
       </c>
       <c r="B72">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="C72">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D72">
         <v>0</v>
       </c>
       <c r="E72">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="F72">
         <v>0</v>
@@ -2369,16 +2510,16 @@
         <v>81</v>
       </c>
       <c r="B73">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="C73">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D73">
         <v>0</v>
       </c>
       <c r="E73">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="F73">
         <v>0</v>
@@ -2389,7 +2530,7 @@
         <v>82</v>
       </c>
       <c r="B74">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="C74">
         <v>3</v>
@@ -2398,7 +2539,7 @@
         <v>0</v>
       </c>
       <c r="E74">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="F74">
         <v>0</v>
@@ -2409,19 +2550,19 @@
         <v>83</v>
       </c>
       <c r="B75">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="C75">
+        <v>2</v>
+      </c>
+      <c r="D75">
+        <v>0</v>
+      </c>
+      <c r="E75">
+        <v>92</v>
+      </c>
+      <c r="F75">
         <v>10</v>
-      </c>
-      <c r="D75">
-        <v>0</v>
-      </c>
-      <c r="E75">
-        <v>74</v>
-      </c>
-      <c r="F75">
-        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -2429,16 +2570,16 @@
         <v>84</v>
       </c>
       <c r="B76">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="C76">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D76">
         <v>0</v>
       </c>
       <c r="E76">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="F76">
         <v>0</v>
@@ -2449,16 +2590,16 @@
         <v>85</v>
       </c>
       <c r="B77">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="C77">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D77">
         <v>0</v>
       </c>
       <c r="E77">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="F77">
         <v>0</v>
@@ -2469,19 +2610,19 @@
         <v>86</v>
       </c>
       <c r="B78">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="C78">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D78">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="E78">
-        <v>7</v>
+        <v>94</v>
       </c>
       <c r="F78">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -2489,16 +2630,16 @@
         <v>87</v>
       </c>
       <c r="B79">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="C79">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D79">
         <v>0</v>
       </c>
       <c r="E79">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="F79">
         <v>0</v>
@@ -2509,16 +2650,16 @@
         <v>88</v>
       </c>
       <c r="B80">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="C80">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D80">
         <v>0</v>
       </c>
       <c r="E80">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="F80">
         <v>0</v>
@@ -2529,16 +2670,16 @@
         <v>89</v>
       </c>
       <c r="B81">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="C81">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D81">
         <v>0</v>
       </c>
       <c r="E81">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="F81">
         <v>0</v>
@@ -2549,7 +2690,7 @@
         <v>90</v>
       </c>
       <c r="B82">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="C82">
         <v>3</v>
@@ -2558,7 +2699,7 @@
         <v>0</v>
       </c>
       <c r="E82">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="F82">
         <v>0</v>
@@ -2569,16 +2710,16 @@
         <v>91</v>
       </c>
       <c r="B83">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="C83">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D83">
         <v>0</v>
       </c>
       <c r="E83">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="F83">
         <v>0</v>
@@ -2589,7 +2730,7 @@
         <v>92</v>
       </c>
       <c r="B84">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="C84">
         <v>3</v>
@@ -2598,10 +2739,10 @@
         <v>0</v>
       </c>
       <c r="E84">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="F84">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -2609,16 +2750,16 @@
         <v>93</v>
       </c>
       <c r="B85">
+        <v>84</v>
+      </c>
+      <c r="C85">
+        <v>10</v>
+      </c>
+      <c r="D85">
+        <v>0</v>
+      </c>
+      <c r="E85">
         <v>74</v>
-      </c>
-      <c r="C85">
-        <v>1</v>
-      </c>
-      <c r="D85">
-        <v>0</v>
-      </c>
-      <c r="E85">
-        <v>73</v>
       </c>
       <c r="F85">
         <v>0</v>
@@ -2629,16 +2770,16 @@
         <v>94</v>
       </c>
       <c r="B86">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="C86">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D86">
         <v>0</v>
       </c>
       <c r="E86">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="F86">
         <v>0</v>
@@ -2649,16 +2790,16 @@
         <v>95</v>
       </c>
       <c r="B87">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="C87">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D87">
         <v>0</v>
       </c>
       <c r="E87">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F87">
         <v>0</v>
@@ -2669,16 +2810,16 @@
         <v>96</v>
       </c>
       <c r="B88">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="C88">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D88">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="E88">
-        <v>63</v>
+        <v>7</v>
       </c>
       <c r="F88">
         <v>0</v>
@@ -2689,16 +2830,16 @@
         <v>97</v>
       </c>
       <c r="B89">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C89">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D89">
         <v>0</v>
       </c>
       <c r="E89">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="F89">
         <v>0</v>
@@ -2709,16 +2850,16 @@
         <v>98</v>
       </c>
       <c r="B90">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="C90">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D90">
         <v>0</v>
       </c>
       <c r="E90">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="F90">
         <v>0</v>
@@ -2729,16 +2870,16 @@
         <v>99</v>
       </c>
       <c r="B91">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="C91">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D91">
         <v>0</v>
       </c>
       <c r="E91">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="F91">
         <v>0</v>
@@ -2749,7 +2890,7 @@
         <v>100</v>
       </c>
       <c r="B92">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="C92">
         <v>1</v>
@@ -2758,7 +2899,7 @@
         <v>0</v>
       </c>
       <c r="E92">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="F92">
         <v>0</v>
@@ -2769,16 +2910,16 @@
         <v>101</v>
       </c>
       <c r="B93">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="C93">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D93">
         <v>0</v>
       </c>
       <c r="E93">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="F93">
         <v>0</v>
@@ -2789,16 +2930,16 @@
         <v>102</v>
       </c>
       <c r="B94">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="C94">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D94">
         <v>0</v>
       </c>
       <c r="E94">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="F94">
         <v>0</v>
@@ -2809,7 +2950,7 @@
         <v>103</v>
       </c>
       <c r="B95">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="C95">
         <v>1</v>
@@ -2818,7 +2959,7 @@
         <v>0</v>
       </c>
       <c r="E95">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="F95">
         <v>0</v>
@@ -2829,19 +2970,19 @@
         <v>104</v>
       </c>
       <c r="B96">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="C96">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D96">
         <v>0</v>
       </c>
       <c r="E96">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="F96">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97" spans="1:6">
@@ -2849,16 +2990,16 @@
         <v>105</v>
       </c>
       <c r="B97">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="C97">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D97">
         <v>0</v>
       </c>
       <c r="E97">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="F97">
         <v>0</v>
@@ -2869,7 +3010,7 @@
         <v>106</v>
       </c>
       <c r="B98">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="C98">
         <v>3</v>
@@ -2878,10 +3019,10 @@
         <v>0</v>
       </c>
       <c r="E98">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="F98">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99" spans="1:6">
@@ -2889,16 +3030,16 @@
         <v>107</v>
       </c>
       <c r="B99">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="C99">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D99">
         <v>0</v>
       </c>
       <c r="E99">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="F99">
         <v>0</v>
@@ -2909,16 +3050,16 @@
         <v>108</v>
       </c>
       <c r="B100">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="C100">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D100">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E100">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="F100">
         <v>0</v>
@@ -2929,16 +3070,16 @@
         <v>109</v>
       </c>
       <c r="B101">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="C101">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D101">
         <v>0</v>
       </c>
       <c r="E101">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="F101">
         <v>0</v>
@@ -2949,16 +3090,16 @@
         <v>110</v>
       </c>
       <c r="B102">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="C102">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D102">
         <v>0</v>
       </c>
       <c r="E102">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="F102">
         <v>0</v>
@@ -2969,16 +3110,16 @@
         <v>111</v>
       </c>
       <c r="B103">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="C103">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D103">
         <v>0</v>
       </c>
       <c r="E103">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="F103">
         <v>0</v>
@@ -2989,16 +3130,16 @@
         <v>112</v>
       </c>
       <c r="B104">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="C104">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D104">
         <v>0</v>
       </c>
       <c r="E104">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="F104">
         <v>0</v>
@@ -3009,16 +3150,16 @@
         <v>113</v>
       </c>
       <c r="B105">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="C105">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D105">
         <v>0</v>
       </c>
       <c r="E105">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="F105">
         <v>0</v>
@@ -3029,16 +3170,16 @@
         <v>114</v>
       </c>
       <c r="B106">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="C106">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D106">
         <v>0</v>
       </c>
       <c r="E106">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="F106">
         <v>0</v>
@@ -3049,16 +3190,16 @@
         <v>115</v>
       </c>
       <c r="B107">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="C107">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D107">
         <v>0</v>
       </c>
       <c r="E107">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="F107">
         <v>0</v>
@@ -3069,16 +3210,16 @@
         <v>116</v>
       </c>
       <c r="B108">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="C108">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D108">
         <v>0</v>
       </c>
       <c r="E108">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="F108">
         <v>0</v>
@@ -3089,16 +3230,16 @@
         <v>117</v>
       </c>
       <c r="B109">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="C109">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D109">
         <v>0</v>
       </c>
       <c r="E109">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F109">
         <v>0</v>
@@ -3109,16 +3250,16 @@
         <v>118</v>
       </c>
       <c r="B110">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="C110">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D110">
         <v>0</v>
       </c>
       <c r="E110">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="F110">
         <v>0</v>
@@ -3129,7 +3270,7 @@
         <v>119</v>
       </c>
       <c r="B111">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="C111">
         <v>1</v>
@@ -3138,7 +3279,7 @@
         <v>0</v>
       </c>
       <c r="E111">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="F111">
         <v>0</v>
@@ -3149,16 +3290,16 @@
         <v>120</v>
       </c>
       <c r="B112">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="C112">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D112">
         <v>0</v>
       </c>
       <c r="E112">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="F112">
         <v>0</v>
@@ -3169,16 +3310,16 @@
         <v>121</v>
       </c>
       <c r="B113">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="C113">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D113">
         <v>0</v>
       </c>
       <c r="E113">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="F113">
         <v>0</v>
@@ -3189,16 +3330,16 @@
         <v>122</v>
       </c>
       <c r="B114">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="C114">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D114">
         <v>0</v>
       </c>
       <c r="E114">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="F114">
         <v>0</v>
@@ -3209,16 +3350,16 @@
         <v>123</v>
       </c>
       <c r="B115">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="C115">
         <v>2</v>
       </c>
       <c r="D115">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E115">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F115">
         <v>0</v>
@@ -3229,16 +3370,16 @@
         <v>124</v>
       </c>
       <c r="B116">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="C116">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D116">
         <v>0</v>
       </c>
       <c r="E116">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="F116">
         <v>0</v>
@@ -3249,16 +3390,16 @@
         <v>125</v>
       </c>
       <c r="B117">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="C117">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D117">
         <v>0</v>
       </c>
       <c r="E117">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="F117">
         <v>0</v>
@@ -3269,16 +3410,16 @@
         <v>126</v>
       </c>
       <c r="B118">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="C118">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D118">
         <v>0</v>
       </c>
       <c r="E118">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="F118">
         <v>0</v>
@@ -3289,16 +3430,16 @@
         <v>127</v>
       </c>
       <c r="B119">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="C119">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D119">
         <v>0</v>
       </c>
       <c r="E119">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="F119">
         <v>0</v>
@@ -3309,7 +3450,7 @@
         <v>128</v>
       </c>
       <c r="B120">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="C120">
         <v>2</v>
@@ -3318,7 +3459,7 @@
         <v>0</v>
       </c>
       <c r="E120">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="F120">
         <v>0</v>
@@ -3329,16 +3470,16 @@
         <v>129</v>
       </c>
       <c r="B121">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="C121">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D121">
         <v>0</v>
       </c>
       <c r="E121">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F121">
         <v>0</v>
@@ -3349,16 +3490,16 @@
         <v>130</v>
       </c>
       <c r="B122">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="C122">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D122">
         <v>0</v>
       </c>
       <c r="E122">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="F122">
         <v>0</v>
@@ -3369,16 +3510,16 @@
         <v>131</v>
       </c>
       <c r="B123">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="C123">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D123">
         <v>0</v>
       </c>
       <c r="E123">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="F123">
         <v>0</v>
@@ -3389,16 +3530,16 @@
         <v>132</v>
       </c>
       <c r="B124">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="C124">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D124">
         <v>0</v>
       </c>
       <c r="E124">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="F124">
         <v>0</v>
@@ -3409,16 +3550,16 @@
         <v>133</v>
       </c>
       <c r="B125">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="C125">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D125">
         <v>0</v>
       </c>
       <c r="E125">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="F125">
         <v>0</v>
@@ -3429,16 +3570,16 @@
         <v>134</v>
       </c>
       <c r="B126">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="C126">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D126">
         <v>0</v>
       </c>
       <c r="E126">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="F126">
         <v>0</v>
@@ -3449,16 +3590,16 @@
         <v>135</v>
       </c>
       <c r="B127">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="C127">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D127">
         <v>0</v>
       </c>
       <c r="E127">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="F127">
         <v>0</v>
@@ -3469,16 +3610,16 @@
         <v>136</v>
       </c>
       <c r="B128">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="C128">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D128">
         <v>0</v>
       </c>
       <c r="E128">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="F128">
         <v>0</v>
@@ -3489,7 +3630,7 @@
         <v>137</v>
       </c>
       <c r="B129">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="C129">
         <v>4</v>
@@ -3498,7 +3639,7 @@
         <v>0</v>
       </c>
       <c r="E129">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="F129">
         <v>0</v>
@@ -3509,7 +3650,7 @@
         <v>138</v>
       </c>
       <c r="B130">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="C130">
         <v>1</v>
@@ -3518,7 +3659,7 @@
         <v>0</v>
       </c>
       <c r="E130">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="F130">
         <v>0</v>
@@ -3529,7 +3670,7 @@
         <v>139</v>
       </c>
       <c r="B131">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="C131">
         <v>1</v>
@@ -3538,7 +3679,7 @@
         <v>0</v>
       </c>
       <c r="E131">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="F131">
         <v>0</v>
@@ -3549,7 +3690,7 @@
         <v>140</v>
       </c>
       <c r="B132">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="C132">
         <v>1</v>
@@ -3558,7 +3699,7 @@
         <v>0</v>
       </c>
       <c r="E132">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="F132">
         <v>0</v>
@@ -3569,16 +3710,16 @@
         <v>141</v>
       </c>
       <c r="B133">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="C133">
         <v>2</v>
       </c>
       <c r="D133">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E133">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="F133">
         <v>0</v>
@@ -3589,16 +3730,16 @@
         <v>142</v>
       </c>
       <c r="B134">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="C134">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D134">
         <v>0</v>
       </c>
       <c r="E134">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="F134">
         <v>0</v>
@@ -3609,16 +3750,16 @@
         <v>143</v>
       </c>
       <c r="B135">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="C135">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D135">
         <v>0</v>
       </c>
       <c r="E135">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="F135">
         <v>0</v>
@@ -3629,7 +3770,7 @@
         <v>144</v>
       </c>
       <c r="B136">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="C136">
         <v>1</v>
@@ -3638,7 +3779,7 @@
         <v>0</v>
       </c>
       <c r="E136">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="F136">
         <v>0</v>
@@ -3649,16 +3790,16 @@
         <v>145</v>
       </c>
       <c r="B137">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="C137">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D137">
         <v>0</v>
       </c>
       <c r="E137">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="F137">
         <v>0</v>
@@ -3669,16 +3810,16 @@
         <v>146</v>
       </c>
       <c r="B138">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="C138">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D138">
         <v>0</v>
       </c>
       <c r="E138">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="F138">
         <v>0</v>
@@ -3689,16 +3830,16 @@
         <v>147</v>
       </c>
       <c r="B139">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="C139">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D139">
         <v>0</v>
       </c>
       <c r="E139">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="F139">
         <v>0</v>
@@ -3709,16 +3850,16 @@
         <v>148</v>
       </c>
       <c r="B140">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="C140">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D140">
         <v>0</v>
       </c>
       <c r="E140">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="F140">
         <v>0</v>
@@ -3729,7 +3870,7 @@
         <v>149</v>
       </c>
       <c r="B141">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="C141">
         <v>0</v>
@@ -3738,7 +3879,7 @@
         <v>0</v>
       </c>
       <c r="E141">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="F141">
         <v>0</v>
@@ -3749,16 +3890,16 @@
         <v>150</v>
       </c>
       <c r="B142">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="C142">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D142">
         <v>0</v>
       </c>
       <c r="E142">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="F142">
         <v>0</v>
@@ -3769,16 +3910,16 @@
         <v>151</v>
       </c>
       <c r="B143">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="C143">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D143">
         <v>0</v>
       </c>
       <c r="E143">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F143">
         <v>0</v>
@@ -3789,18 +3930,958 @@
         <v>152</v>
       </c>
       <c r="B144">
+        <v>41</v>
+      </c>
+      <c r="C144">
+        <v>1</v>
+      </c>
+      <c r="D144">
+        <v>0</v>
+      </c>
+      <c r="E144">
+        <v>40</v>
+      </c>
+      <c r="F144">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6">
+      <c r="A145" t="s">
+        <v>153</v>
+      </c>
+      <c r="B145">
+        <v>39</v>
+      </c>
+      <c r="C145">
+        <v>3</v>
+      </c>
+      <c r="D145">
+        <v>0</v>
+      </c>
+      <c r="E145">
+        <v>36</v>
+      </c>
+      <c r="F145">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6">
+      <c r="A146" t="s">
+        <v>154</v>
+      </c>
+      <c r="B146">
+        <v>39</v>
+      </c>
+      <c r="C146">
+        <v>1</v>
+      </c>
+      <c r="D146">
+        <v>0</v>
+      </c>
+      <c r="E146">
+        <v>38</v>
+      </c>
+      <c r="F146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6">
+      <c r="A147" t="s">
+        <v>155</v>
+      </c>
+      <c r="B147">
+        <v>38</v>
+      </c>
+      <c r="C147">
+        <v>4</v>
+      </c>
+      <c r="D147">
+        <v>0</v>
+      </c>
+      <c r="E147">
+        <v>34</v>
+      </c>
+      <c r="F147">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6">
+      <c r="A148" t="s">
+        <v>156</v>
+      </c>
+      <c r="B148">
+        <v>38</v>
+      </c>
+      <c r="C148">
+        <v>0</v>
+      </c>
+      <c r="D148">
+        <v>0</v>
+      </c>
+      <c r="E148">
+        <v>38</v>
+      </c>
+      <c r="F148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6">
+      <c r="A149" t="s">
+        <v>157</v>
+      </c>
+      <c r="B149">
+        <v>37</v>
+      </c>
+      <c r="C149">
+        <v>4</v>
+      </c>
+      <c r="D149">
+        <v>0</v>
+      </c>
+      <c r="E149">
+        <v>33</v>
+      </c>
+      <c r="F149">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6">
+      <c r="A150" t="s">
+        <v>158</v>
+      </c>
+      <c r="B150">
+        <v>37</v>
+      </c>
+      <c r="C150">
+        <v>4</v>
+      </c>
+      <c r="D150">
+        <v>0</v>
+      </c>
+      <c r="E150">
+        <v>33</v>
+      </c>
+      <c r="F150">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6">
+      <c r="A151" t="s">
+        <v>159</v>
+      </c>
+      <c r="B151">
+        <v>36</v>
+      </c>
+      <c r="C151">
         <v>2</v>
       </c>
-      <c r="C144">
-        <v>0</v>
-      </c>
-      <c r="D144">
-        <v>0</v>
-      </c>
-      <c r="E144">
+      <c r="D151">
+        <v>0</v>
+      </c>
+      <c r="E151">
+        <v>34</v>
+      </c>
+      <c r="F151">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6">
+      <c r="A152" t="s">
+        <v>160</v>
+      </c>
+      <c r="B152">
+        <v>36</v>
+      </c>
+      <c r="C152">
+        <v>4</v>
+      </c>
+      <c r="D152">
+        <v>0</v>
+      </c>
+      <c r="E152">
+        <v>32</v>
+      </c>
+      <c r="F152">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6">
+      <c r="A153" t="s">
+        <v>161</v>
+      </c>
+      <c r="B153">
+        <v>36</v>
+      </c>
+      <c r="C153">
+        <v>0</v>
+      </c>
+      <c r="D153">
+        <v>0</v>
+      </c>
+      <c r="E153">
+        <v>36</v>
+      </c>
+      <c r="F153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6">
+      <c r="A154" t="s">
+        <v>162</v>
+      </c>
+      <c r="B154">
+        <v>35</v>
+      </c>
+      <c r="C154">
+        <v>1</v>
+      </c>
+      <c r="D154">
+        <v>0</v>
+      </c>
+      <c r="E154">
+        <v>34</v>
+      </c>
+      <c r="F154">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6">
+      <c r="A155" t="s">
+        <v>163</v>
+      </c>
+      <c r="B155">
+        <v>35</v>
+      </c>
+      <c r="C155">
+        <v>1</v>
+      </c>
+      <c r="D155">
+        <v>0</v>
+      </c>
+      <c r="E155">
+        <v>34</v>
+      </c>
+      <c r="F155">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6">
+      <c r="A156" t="s">
+        <v>164</v>
+      </c>
+      <c r="B156">
+        <v>35</v>
+      </c>
+      <c r="C156">
+        <v>1</v>
+      </c>
+      <c r="D156">
+        <v>0</v>
+      </c>
+      <c r="E156">
+        <v>34</v>
+      </c>
+      <c r="F156">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6">
+      <c r="A157" t="s">
+        <v>165</v>
+      </c>
+      <c r="B157">
+        <v>34</v>
+      </c>
+      <c r="C157">
         <v>2</v>
       </c>
-      <c r="F144">
+      <c r="D157">
+        <v>2</v>
+      </c>
+      <c r="E157">
+        <v>30</v>
+      </c>
+      <c r="F157">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6">
+      <c r="A158" t="s">
+        <v>166</v>
+      </c>
+      <c r="B158">
+        <v>33</v>
+      </c>
+      <c r="C158">
+        <v>0</v>
+      </c>
+      <c r="D158">
+        <v>0</v>
+      </c>
+      <c r="E158">
+        <v>33</v>
+      </c>
+      <c r="F158">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6">
+      <c r="A159" t="s">
+        <v>167</v>
+      </c>
+      <c r="B159">
+        <v>32</v>
+      </c>
+      <c r="C159">
+        <v>1</v>
+      </c>
+      <c r="D159">
+        <v>0</v>
+      </c>
+      <c r="E159">
+        <v>31</v>
+      </c>
+      <c r="F159">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6">
+      <c r="A160" t="s">
+        <v>168</v>
+      </c>
+      <c r="B160">
+        <v>32</v>
+      </c>
+      <c r="C160">
+        <v>4</v>
+      </c>
+      <c r="D160">
+        <v>0</v>
+      </c>
+      <c r="E160">
+        <v>28</v>
+      </c>
+      <c r="F160">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6">
+      <c r="A161" t="s">
+        <v>169</v>
+      </c>
+      <c r="B161">
+        <v>31</v>
+      </c>
+      <c r="C161">
+        <v>0</v>
+      </c>
+      <c r="D161">
+        <v>0</v>
+      </c>
+      <c r="E161">
+        <v>31</v>
+      </c>
+      <c r="F161">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6">
+      <c r="A162" t="s">
+        <v>170</v>
+      </c>
+      <c r="B162">
+        <v>29</v>
+      </c>
+      <c r="C162">
+        <v>1</v>
+      </c>
+      <c r="D162">
+        <v>0</v>
+      </c>
+      <c r="E162">
+        <v>28</v>
+      </c>
+      <c r="F162">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6">
+      <c r="A163" t="s">
+        <v>171</v>
+      </c>
+      <c r="B163">
+        <v>27</v>
+      </c>
+      <c r="C163">
+        <v>1</v>
+      </c>
+      <c r="D163">
+        <v>0</v>
+      </c>
+      <c r="E163">
+        <v>26</v>
+      </c>
+      <c r="F163">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6">
+      <c r="A164" t="s">
+        <v>172</v>
+      </c>
+      <c r="B164">
+        <v>26</v>
+      </c>
+      <c r="C164">
+        <v>0</v>
+      </c>
+      <c r="D164">
+        <v>0</v>
+      </c>
+      <c r="E164">
+        <v>26</v>
+      </c>
+      <c r="F164">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6">
+      <c r="A165" t="s">
+        <v>173</v>
+      </c>
+      <c r="B165">
+        <v>26</v>
+      </c>
+      <c r="C165">
+        <v>2</v>
+      </c>
+      <c r="D165">
+        <v>0</v>
+      </c>
+      <c r="E165">
+        <v>24</v>
+      </c>
+      <c r="F165">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6">
+      <c r="A166" t="s">
+        <v>174</v>
+      </c>
+      <c r="B166">
+        <v>25</v>
+      </c>
+      <c r="C166">
+        <v>0</v>
+      </c>
+      <c r="D166">
+        <v>0</v>
+      </c>
+      <c r="E166">
+        <v>25</v>
+      </c>
+      <c r="F166">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6">
+      <c r="A167" t="s">
+        <v>175</v>
+      </c>
+      <c r="B167">
+        <v>25</v>
+      </c>
+      <c r="C167">
+        <v>2</v>
+      </c>
+      <c r="D167">
+        <v>0</v>
+      </c>
+      <c r="E167">
+        <v>23</v>
+      </c>
+      <c r="F167">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6">
+      <c r="A168" t="s">
+        <v>176</v>
+      </c>
+      <c r="B168">
+        <v>25</v>
+      </c>
+      <c r="C168">
+        <v>0</v>
+      </c>
+      <c r="D168">
+        <v>0</v>
+      </c>
+      <c r="E168">
+        <v>25</v>
+      </c>
+      <c r="F168">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6">
+      <c r="A169" t="s">
+        <v>177</v>
+      </c>
+      <c r="B169">
+        <v>25</v>
+      </c>
+      <c r="C169">
+        <v>1</v>
+      </c>
+      <c r="D169">
+        <v>0</v>
+      </c>
+      <c r="E169">
+        <v>24</v>
+      </c>
+      <c r="F169">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6">
+      <c r="A170" t="s">
+        <v>178</v>
+      </c>
+      <c r="B170">
+        <v>25</v>
+      </c>
+      <c r="C170">
+        <v>0</v>
+      </c>
+      <c r="D170">
+        <v>0</v>
+      </c>
+      <c r="E170">
+        <v>24</v>
+      </c>
+      <c r="F170">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6">
+      <c r="A171" t="s">
+        <v>179</v>
+      </c>
+      <c r="B171">
+        <v>25</v>
+      </c>
+      <c r="C171">
+        <v>0</v>
+      </c>
+      <c r="D171">
+        <v>0</v>
+      </c>
+      <c r="E171">
+        <v>25</v>
+      </c>
+      <c r="F171">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6">
+      <c r="A172" t="s">
+        <v>180</v>
+      </c>
+      <c r="B172">
+        <v>23</v>
+      </c>
+      <c r="C172">
+        <v>1</v>
+      </c>
+      <c r="D172">
+        <v>0</v>
+      </c>
+      <c r="E172">
+        <v>22</v>
+      </c>
+      <c r="F172">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6">
+      <c r="A173" t="s">
+        <v>181</v>
+      </c>
+      <c r="B173">
+        <v>23</v>
+      </c>
+      <c r="C173">
+        <v>1</v>
+      </c>
+      <c r="D173">
+        <v>0</v>
+      </c>
+      <c r="E173">
+        <v>22</v>
+      </c>
+      <c r="F173">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6">
+      <c r="A174" t="s">
+        <v>182</v>
+      </c>
+      <c r="B174">
+        <v>23</v>
+      </c>
+      <c r="C174">
+        <v>0</v>
+      </c>
+      <c r="D174">
+        <v>0</v>
+      </c>
+      <c r="E174">
+        <v>23</v>
+      </c>
+      <c r="F174">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6">
+      <c r="A175" t="s">
+        <v>183</v>
+      </c>
+      <c r="B175">
+        <v>22</v>
+      </c>
+      <c r="C175">
+        <v>2</v>
+      </c>
+      <c r="D175">
+        <v>0</v>
+      </c>
+      <c r="E175">
+        <v>20</v>
+      </c>
+      <c r="F175">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6">
+      <c r="A176" t="s">
+        <v>184</v>
+      </c>
+      <c r="B176">
+        <v>22</v>
+      </c>
+      <c r="C176">
+        <v>1</v>
+      </c>
+      <c r="D176">
+        <v>0</v>
+      </c>
+      <c r="E176">
+        <v>21</v>
+      </c>
+      <c r="F176">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6">
+      <c r="A177" t="s">
+        <v>185</v>
+      </c>
+      <c r="B177">
+        <v>22</v>
+      </c>
+      <c r="C177">
+        <v>2</v>
+      </c>
+      <c r="D177">
+        <v>0</v>
+      </c>
+      <c r="E177">
+        <v>20</v>
+      </c>
+      <c r="F177">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6">
+      <c r="A178" t="s">
+        <v>186</v>
+      </c>
+      <c r="B178">
+        <v>21</v>
+      </c>
+      <c r="C178">
+        <v>1</v>
+      </c>
+      <c r="D178">
+        <v>0</v>
+      </c>
+      <c r="E178">
+        <v>19</v>
+      </c>
+      <c r="F178">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6">
+      <c r="A179" t="s">
+        <v>187</v>
+      </c>
+      <c r="B179">
+        <v>20</v>
+      </c>
+      <c r="C179">
+        <v>4</v>
+      </c>
+      <c r="D179">
+        <v>0</v>
+      </c>
+      <c r="E179">
+        <v>16</v>
+      </c>
+      <c r="F179">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6">
+      <c r="A180" t="s">
+        <v>188</v>
+      </c>
+      <c r="B180">
+        <v>19</v>
+      </c>
+      <c r="C180">
+        <v>1</v>
+      </c>
+      <c r="D180">
+        <v>0</v>
+      </c>
+      <c r="E180">
+        <v>18</v>
+      </c>
+      <c r="F180">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6">
+      <c r="A181" t="s">
+        <v>189</v>
+      </c>
+      <c r="B181">
+        <v>18</v>
+      </c>
+      <c r="C181">
+        <v>1</v>
+      </c>
+      <c r="D181">
+        <v>0</v>
+      </c>
+      <c r="E181">
+        <v>17</v>
+      </c>
+      <c r="F181">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6">
+      <c r="A182" t="s">
+        <v>190</v>
+      </c>
+      <c r="B182">
+        <v>17</v>
+      </c>
+      <c r="C182">
+        <v>1</v>
+      </c>
+      <c r="D182">
+        <v>0</v>
+      </c>
+      <c r="E182">
+        <v>16</v>
+      </c>
+      <c r="F182">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6">
+      <c r="A183" t="s">
+        <v>191</v>
+      </c>
+      <c r="B183">
+        <v>16</v>
+      </c>
+      <c r="C183">
+        <v>0</v>
+      </c>
+      <c r="D183">
+        <v>0</v>
+      </c>
+      <c r="E183">
+        <v>16</v>
+      </c>
+      <c r="F183">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6">
+      <c r="A184" t="s">
+        <v>192</v>
+      </c>
+      <c r="B184">
+        <v>15</v>
+      </c>
+      <c r="C184">
+        <v>0</v>
+      </c>
+      <c r="D184">
+        <v>0</v>
+      </c>
+      <c r="E184">
+        <v>15</v>
+      </c>
+      <c r="F184">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6">
+      <c r="A185" t="s">
+        <v>193</v>
+      </c>
+      <c r="B185">
+        <v>14</v>
+      </c>
+      <c r="C185">
+        <v>0</v>
+      </c>
+      <c r="D185">
+        <v>0</v>
+      </c>
+      <c r="E185">
+        <v>14</v>
+      </c>
+      <c r="F185">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6">
+      <c r="A186" t="s">
+        <v>194</v>
+      </c>
+      <c r="B186">
+        <v>13</v>
+      </c>
+      <c r="C186">
+        <v>1</v>
+      </c>
+      <c r="D186">
+        <v>0</v>
+      </c>
+      <c r="E186">
+        <v>12</v>
+      </c>
+      <c r="F186">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6">
+      <c r="A187" t="s">
+        <v>195</v>
+      </c>
+      <c r="B187">
+        <v>9</v>
+      </c>
+      <c r="C187">
+        <v>1</v>
+      </c>
+      <c r="D187">
+        <v>0</v>
+      </c>
+      <c r="E187">
+        <v>8</v>
+      </c>
+      <c r="F187">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6">
+      <c r="A188" t="s">
+        <v>196</v>
+      </c>
+      <c r="B188">
+        <v>9</v>
+      </c>
+      <c r="C188">
+        <v>1</v>
+      </c>
+      <c r="D188">
+        <v>0</v>
+      </c>
+      <c r="E188">
+        <v>8</v>
+      </c>
+      <c r="F188">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6">
+      <c r="A189" t="s">
+        <v>197</v>
+      </c>
+      <c r="B189">
+        <v>5</v>
+      </c>
+      <c r="C189">
+        <v>0</v>
+      </c>
+      <c r="D189">
+        <v>0</v>
+      </c>
+      <c r="E189">
+        <v>5</v>
+      </c>
+      <c r="F189">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6">
+      <c r="A190" t="s">
+        <v>198</v>
+      </c>
+      <c r="B190">
+        <v>4</v>
+      </c>
+      <c r="C190">
+        <v>0</v>
+      </c>
+      <c r="D190">
+        <v>0</v>
+      </c>
+      <c r="E190">
+        <v>4</v>
+      </c>
+      <c r="F190">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6">
+      <c r="A191" t="s">
+        <v>199</v>
+      </c>
+      <c r="B191">
+        <v>2</v>
+      </c>
+      <c r="C191">
+        <v>0</v>
+      </c>
+      <c r="D191">
+        <v>0</v>
+      </c>
+      <c r="E191">
+        <v>2</v>
+      </c>
+      <c r="F191">
         <v>0</v>
       </c>
     </row>

--- a/resumo_busca_ativa_consolidado.xlsx
+++ b/resumo_busca_ativa_consolidado.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="153">
   <si>
     <t>REGIONAL</t>
   </si>
@@ -50,9 +50,6 @@
     <t>ANAPOLIS</t>
   </si>
   <si>
-    <t>SAO LUIS</t>
-  </si>
-  <si>
     <t>RIO VERDE</t>
   </si>
   <si>
@@ -143,15 +140,9 @@
     <t>PONTALINA</t>
   </si>
   <si>
-    <t>IMPERATRIZ</t>
-  </si>
-  <si>
     <t>PADRE BERNARDO</t>
   </si>
   <si>
-    <t>SAO JOSE DE RIBAMAR</t>
-  </si>
-  <si>
     <t>POSSE</t>
   </si>
   <si>
@@ -161,9 +152,6 @@
     <t>ACREUNA</t>
   </si>
   <si>
-    <t>ACAILANDIA</t>
-  </si>
-  <si>
     <t>ITAPACI</t>
   </si>
   <si>
@@ -173,12 +161,12 @@
     <t>MARA ROSA</t>
   </si>
   <si>
+    <t>GOIANAPOLIS</t>
+  </si>
+  <si>
     <t>COCALZINHO DE GOIAS</t>
   </si>
   <si>
-    <t>GOIANAPOLIS</t>
-  </si>
-  <si>
     <t>BURITI ALEGRE</t>
   </si>
   <si>
@@ -191,9 +179,6 @@
     <t>CAMPOS BELOS</t>
   </si>
   <si>
-    <t>BALSAS</t>
-  </si>
-  <si>
     <t>MAURILANDIA</t>
   </si>
   <si>
@@ -203,12 +188,12 @@
     <t>SAO SIMAO</t>
   </si>
   <si>
+    <t>SANTA TEREZINHA DE GOIAS</t>
+  </si>
+  <si>
     <t>CRIXAS</t>
   </si>
   <si>
-    <t>SANTA TEREZINHA DE GOIAS</t>
-  </si>
-  <si>
     <t>PETROLINA DE GOIAS</t>
   </si>
   <si>
@@ -218,9 +203,6 @@
     <t>CORUMBA DE GOIAS</t>
   </si>
   <si>
-    <t>PACO DO LUMIAR</t>
-  </si>
-  <si>
     <t>GOIANDIRA</t>
   </si>
   <si>
@@ -233,27 +215,21 @@
     <t>CAMPO ALEGRE DE GOIAS</t>
   </si>
   <si>
+    <t>BARRO ALTO</t>
+  </si>
+  <si>
     <t>FORMOSO</t>
   </si>
   <si>
-    <t>BARRO ALTO</t>
-  </si>
-  <si>
     <t>CAMPINORTE</t>
   </si>
   <si>
     <t>TEREZOPOLIS DE GOIAS</t>
   </si>
   <si>
-    <t>SAO BERNARDO</t>
-  </si>
-  <si>
     <t>INACIOLANDIA</t>
   </si>
   <si>
-    <t>GRAJAU</t>
-  </si>
-  <si>
     <t>CORUMBAIBA</t>
   </si>
   <si>
@@ -278,15 +254,9 @@
     <t>CACHOEIRA ALTA</t>
   </si>
   <si>
-    <t>BARREIRINHAS</t>
-  </si>
-  <si>
     <t>JOVIANIA</t>
   </si>
   <si>
-    <t>ARAIOSES</t>
-  </si>
-  <si>
     <t>PARANAIGUARA</t>
   </si>
   <si>
@@ -311,12 +281,6 @@
     <t>CACHOEIRA DOURADA</t>
   </si>
   <si>
-    <t>ITINGA DO MARANHAO</t>
-  </si>
-  <si>
-    <t>ROSARIO</t>
-  </si>
-  <si>
     <t>MONTE ALEGRE DE GOIAS</t>
   </si>
   <si>
@@ -329,15 +293,12 @@
     <t>URUTAI</t>
   </si>
   <si>
-    <t>TUTOIA</t>
+    <t>PALMELO</t>
   </si>
   <si>
     <t>CABECEIRAS</t>
   </si>
   <si>
-    <t>PALMELO</t>
-  </si>
-  <si>
     <t>OUVIDOR</t>
   </si>
   <si>
@@ -350,22 +311,25 @@
     <t>PORTEIRAO</t>
   </si>
   <si>
+    <t>HIDROLINA</t>
+  </si>
+  <si>
     <t>MONTIVIDIU</t>
   </si>
   <si>
-    <t>HIDROLINA</t>
-  </si>
-  <si>
     <t>TURVELANDIA</t>
   </si>
   <si>
-    <t>MAGALHAES DE ALMEIDA</t>
+    <t>CAVALCANTE</t>
   </si>
   <si>
     <t>TROMBAS</t>
   </si>
   <si>
-    <t>CAVALCANTE</t>
+    <t>SAO JOAO D ALIANCA</t>
+  </si>
+  <si>
+    <t>CROMINIA</t>
   </si>
   <si>
     <t>SANTO ANTONIO DA BARRA</t>
@@ -374,15 +338,6 @@
     <t>UIRAPURU</t>
   </si>
   <si>
-    <t>SAO JOAO D ALIANCA</t>
-  </si>
-  <si>
-    <t>CROMINIA</t>
-  </si>
-  <si>
-    <t>CAROLINA</t>
-  </si>
-  <si>
     <t>SIMOLANDIA</t>
   </si>
   <si>
@@ -395,13 +350,10 @@
     <t>FLORES DE GOIAS</t>
   </si>
   <si>
-    <t>RIACHAO</t>
-  </si>
-  <si>
-    <t>SAO RAIMUNDO DAS MANGABEIRAS</t>
-  </si>
-  <si>
-    <t>AGUA DOCE DO MARANHAO</t>
+    <t>CAMPOS VERDES</t>
+  </si>
+  <si>
+    <t>ALTO PARAISO DE GOIAS</t>
   </si>
   <si>
     <t>TRES RANCHOS</t>
@@ -410,27 +362,18 @@
     <t>MAIRIPOTABA</t>
   </si>
   <si>
-    <t>CAMPOS VERDES</t>
-  </si>
-  <si>
-    <t>ALTO PARAISO DE GOIAS</t>
-  </si>
-  <si>
-    <t>ARAME</t>
-  </si>
-  <si>
     <t>NOVO PLANALTO</t>
   </si>
   <si>
+    <t>ESTRELA DO NORTE</t>
+  </si>
+  <si>
     <t>ITARUMA</t>
   </si>
   <si>
     <t>PROFESSOR JAMIL</t>
   </si>
   <si>
-    <t>ESTRELA DO NORTE</t>
-  </si>
-  <si>
     <t>CAMPINACU</t>
   </si>
   <si>
@@ -443,175 +386,91 @@
     <t>NOVA AURORA</t>
   </si>
   <si>
-    <t>HUMBERTO DE CAMPOS</t>
-  </si>
-  <si>
     <t>AGUA FRIA DE GOIAS</t>
   </si>
   <si>
-    <t>SANTA RITA</t>
-  </si>
-  <si>
-    <t>LORETO</t>
-  </si>
-  <si>
     <t>JESUPOLIS</t>
   </si>
   <si>
+    <t>VILA BOA</t>
+  </si>
+  <si>
     <t>ALOANDIA</t>
   </si>
   <si>
     <t>MONTIVIDIU DO NORTE</t>
   </si>
   <si>
-    <t>VILA BOA</t>
-  </si>
-  <si>
     <t>NOVA ROMA</t>
   </si>
   <si>
-    <t>ICATU</t>
-  </si>
-  <si>
     <t>BURITINOPOLIS</t>
   </si>
   <si>
+    <t>APARECIDA DO RIO DOCE</t>
+  </si>
+  <si>
     <t>VILA PROPICIO</t>
   </si>
   <si>
-    <t>APARECIDA DO RIO DOCE</t>
+    <t>MAMBAI</t>
   </si>
   <si>
     <t>NOVA AMERICA</t>
   </si>
   <si>
-    <t>MAMBAI</t>
-  </si>
-  <si>
     <t>SANTA RITA DO NOVO DESTINO</t>
   </si>
   <si>
     <t>BONOPOLIS</t>
   </si>
   <si>
-    <t>MORROS</t>
+    <t>AGUA LIMPA</t>
   </si>
   <si>
     <t>COLINAS DO SUL</t>
   </si>
   <si>
-    <t>AGUA LIMPA</t>
+    <t>NOVA IGUACU DE GOIAS</t>
+  </si>
+  <si>
+    <t>AMARALINA</t>
   </si>
   <si>
     <t>PILAR DE GOIAS</t>
   </si>
   <si>
-    <t>AMARALINA</t>
-  </si>
-  <si>
-    <t>NOVA IGUACU DE GOIAS</t>
-  </si>
-  <si>
     <t>ALTO HORIZONTE</t>
   </si>
   <si>
     <t>GUARINOS</t>
   </si>
   <si>
+    <t>MIMOSO DE GOIAS</t>
+  </si>
+  <si>
     <t>EDEALINA</t>
   </si>
   <si>
-    <t>MIMOSO DE GOIAS</t>
-  </si>
-  <si>
     <t>GUARANI DE GOIAS</t>
   </si>
   <si>
     <t>DAVINOPOLIS</t>
   </si>
   <si>
-    <t>FORTALEZA DOS NOGUEIRAS</t>
-  </si>
-  <si>
-    <t>AXIXA</t>
-  </si>
-  <si>
-    <t>CIDELANDIA</t>
-  </si>
-  <si>
     <t>ANHANGUERA</t>
   </si>
   <si>
-    <t>BURITICUPU</t>
-  </si>
-  <si>
-    <t>PAULINO NEVES</t>
-  </si>
-  <si>
-    <t>SAO PEDRO DA AGUA BRANCA</t>
-  </si>
-  <si>
-    <t>SANTANA DO MARANHAO</t>
-  </si>
-  <si>
-    <t>SAO FELIX DE BALSAS</t>
-  </si>
-  <si>
     <t>MARZAGAO</t>
   </si>
   <si>
+    <t>PANAMA</t>
+  </si>
+  <si>
     <t>SITIO D ABADIA</t>
   </si>
   <si>
-    <t>PANAMA</t>
-  </si>
-  <si>
-    <t>PRIMEIRA CRUZ</t>
-  </si>
-  <si>
-    <t>TASSO FRAGOSO</t>
-  </si>
-  <si>
     <t>TERESINA DE GOIAS</t>
-  </si>
-  <si>
-    <t>SANTO AMARO DO MARANHAO</t>
-  </si>
-  <si>
-    <t>BACABEIRA</t>
-  </si>
-  <si>
-    <t>BOM JESUS DA SELVA</t>
-  </si>
-  <si>
-    <t>RAPOSA</t>
-  </si>
-  <si>
-    <t>VILA NOVA DOS MARTIRIOS</t>
-  </si>
-  <si>
-    <t>PRESIDENTE JUSCELINO</t>
-  </si>
-  <si>
-    <t>ALTO PARNAIBA</t>
-  </si>
-  <si>
-    <t>SAMBAIBA</t>
-  </si>
-  <si>
-    <t>FORMOSA DA SERRA NEGRA</t>
-  </si>
-  <si>
-    <t>CACHOEIRA GRANDE</t>
-  </si>
-  <si>
-    <t>SAO FRANCISCO DO BREJAO</t>
-  </si>
-  <si>
-    <t>NOVA COLINAS</t>
-  </si>
-  <si>
-    <t>ITAIPAVA DO GRAJAU</t>
   </si>
   <si>
     <t>SAO JOAO DA ALIANCA</t>
@@ -1000,19 +859,19 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>24745</v>
+        <v>19128</v>
       </c>
       <c r="C2">
-        <v>1518</v>
+        <v>1197</v>
       </c>
       <c r="D2">
-        <v>1667</v>
+        <v>1655</v>
       </c>
       <c r="E2">
-        <v>21542</v>
+        <v>16276</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1020,16 +879,16 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>18293</v>
+        <v>16814</v>
       </c>
       <c r="C3">
-        <v>1090</v>
+        <v>959</v>
       </c>
       <c r="D3">
-        <v>1481</v>
+        <v>1476</v>
       </c>
       <c r="E3">
-        <v>15639</v>
+        <v>14301</v>
       </c>
       <c r="F3">
         <v>78</v>
@@ -1062,7 +921,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F191"/>
+  <dimension ref="A1:F144"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1110,19 +969,19 @@
         <v>11</v>
       </c>
       <c r="B3">
-        <v>4220</v>
+        <v>2381</v>
       </c>
       <c r="C3">
-        <v>231</v>
+        <v>160</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>309</v>
       </c>
       <c r="E3">
-        <v>3975</v>
+        <v>1864</v>
       </c>
       <c r="F3">
-        <v>8</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1130,19 +989,19 @@
         <v>12</v>
       </c>
       <c r="B4">
-        <v>2381</v>
+        <v>1735</v>
       </c>
       <c r="C4">
-        <v>160</v>
+        <v>102</v>
       </c>
       <c r="D4">
-        <v>309</v>
+        <v>226</v>
       </c>
       <c r="E4">
-        <v>1864</v>
+        <v>1388</v>
       </c>
       <c r="F4">
-        <v>48</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1150,19 +1009,19 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>1735</v>
+        <v>1649</v>
       </c>
       <c r="C5">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="D5">
-        <v>226</v>
+        <v>252</v>
       </c>
       <c r="E5">
-        <v>1388</v>
+        <v>1283</v>
       </c>
       <c r="F5">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1170,19 +1029,19 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>1649</v>
+        <v>1500</v>
       </c>
       <c r="C6">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="D6">
-        <v>252</v>
+        <v>275</v>
       </c>
       <c r="E6">
-        <v>1283</v>
+        <v>1102</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1190,19 +1049,19 @@
         <v>15</v>
       </c>
       <c r="B7">
-        <v>1500</v>
+        <v>1279</v>
       </c>
       <c r="C7">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="D7">
-        <v>275</v>
+        <v>130</v>
       </c>
       <c r="E7">
-        <v>1102</v>
+        <v>1034</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1210,16 +1069,16 @@
         <v>16</v>
       </c>
       <c r="B8">
-        <v>1279</v>
+        <v>1203</v>
       </c>
       <c r="C8">
-        <v>115</v>
+        <v>57</v>
       </c>
       <c r="D8">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="E8">
-        <v>1034</v>
+        <v>1076</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -1230,16 +1089,16 @@
         <v>17</v>
       </c>
       <c r="B9">
-        <v>1203</v>
+        <v>1135</v>
       </c>
       <c r="C9">
-        <v>57</v>
+        <v>110</v>
       </c>
       <c r="D9">
-        <v>70</v>
+        <v>331</v>
       </c>
       <c r="E9">
-        <v>1076</v>
+        <v>694</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -1250,16 +1109,16 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>1135</v>
+        <v>977</v>
       </c>
       <c r="C10">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="D10">
-        <v>331</v>
+        <v>69</v>
       </c>
       <c r="E10">
-        <v>694</v>
+        <v>828</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1270,16 +1129,16 @@
         <v>19</v>
       </c>
       <c r="B11">
-        <v>977</v>
+        <v>920</v>
       </c>
       <c r="C11">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="D11">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="E11">
-        <v>828</v>
+        <v>836</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1290,19 +1149,19 @@
         <v>20</v>
       </c>
       <c r="B12">
-        <v>920</v>
+        <v>911</v>
       </c>
       <c r="C12">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D12">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="E12">
-        <v>836</v>
+        <v>860</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1310,19 +1169,19 @@
         <v>21</v>
       </c>
       <c r="B13">
-        <v>911</v>
+        <v>842</v>
       </c>
       <c r="C13">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="E13">
-        <v>860</v>
+        <v>490</v>
       </c>
       <c r="F13">
-        <v>3</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1330,19 +1189,19 @@
         <v>22</v>
       </c>
       <c r="B14">
-        <v>842</v>
+        <v>813</v>
       </c>
       <c r="C14">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="D14">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="E14">
-        <v>490</v>
+        <v>791</v>
       </c>
       <c r="F14">
-        <v>140</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1350,16 +1209,16 @@
         <v>23</v>
       </c>
       <c r="B15">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="C15">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E15">
-        <v>791</v>
+        <v>710</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -1370,19 +1229,19 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>811</v>
+        <v>790</v>
       </c>
       <c r="C16">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="D16">
-        <v>60</v>
+        <v>179</v>
       </c>
       <c r="E16">
-        <v>710</v>
+        <v>516</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1390,19 +1249,19 @@
         <v>25</v>
       </c>
       <c r="B17">
-        <v>790</v>
+        <v>729</v>
       </c>
       <c r="C17">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="D17">
-        <v>179</v>
+        <v>0</v>
       </c>
       <c r="E17">
-        <v>516</v>
+        <v>707</v>
       </c>
       <c r="F17">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -1410,16 +1269,16 @@
         <v>26</v>
       </c>
       <c r="B18">
-        <v>729</v>
+        <v>695</v>
       </c>
       <c r="C18">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="E18">
-        <v>707</v>
+        <v>616</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1430,16 +1289,16 @@
         <v>27</v>
       </c>
       <c r="B19">
-        <v>695</v>
+        <v>666</v>
       </c>
       <c r="C19">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D19">
-        <v>49</v>
+        <v>132</v>
       </c>
       <c r="E19">
-        <v>616</v>
+        <v>474</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1450,16 +1309,16 @@
         <v>28</v>
       </c>
       <c r="B20">
-        <v>666</v>
+        <v>646</v>
       </c>
       <c r="C20">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="D20">
-        <v>132</v>
+        <v>38</v>
       </c>
       <c r="E20">
-        <v>474</v>
+        <v>581</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1470,16 +1329,16 @@
         <v>29</v>
       </c>
       <c r="B21">
-        <v>646</v>
+        <v>616</v>
       </c>
       <c r="C21">
-        <v>27</v>
+        <v>87</v>
       </c>
       <c r="D21">
-        <v>38</v>
+        <v>226</v>
       </c>
       <c r="E21">
-        <v>581</v>
+        <v>303</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1490,16 +1349,16 @@
         <v>30</v>
       </c>
       <c r="B22">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="C22">
-        <v>87</v>
+        <v>36</v>
       </c>
       <c r="D22">
-        <v>226</v>
+        <v>94</v>
       </c>
       <c r="E22">
-        <v>303</v>
+        <v>481</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1510,16 +1369,16 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>611</v>
+        <v>601</v>
       </c>
       <c r="C23">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D23">
-        <v>94</v>
+        <v>125</v>
       </c>
       <c r="E23">
-        <v>481</v>
+        <v>435</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -1530,16 +1389,16 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>601</v>
+        <v>503</v>
       </c>
       <c r="C24">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="D24">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="E24">
-        <v>435</v>
+        <v>478</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1550,16 +1409,16 @@
         <v>33</v>
       </c>
       <c r="B25">
-        <v>503</v>
+        <v>495</v>
       </c>
       <c r="C25">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="E25">
-        <v>478</v>
+        <v>430</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1570,16 +1429,16 @@
         <v>34</v>
       </c>
       <c r="B26">
-        <v>495</v>
+        <v>449</v>
       </c>
       <c r="C26">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D26">
-        <v>29</v>
+        <v>164</v>
       </c>
       <c r="E26">
-        <v>430</v>
+        <v>226</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -1590,16 +1449,16 @@
         <v>35</v>
       </c>
       <c r="B27">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C27">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="D27">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="E27">
-        <v>226</v>
+        <v>420</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -1610,16 +1469,16 @@
         <v>36</v>
       </c>
       <c r="B28">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="C28">
         <v>28</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="E28">
-        <v>420</v>
+        <v>346</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -1630,16 +1489,16 @@
         <v>37</v>
       </c>
       <c r="B29">
-        <v>441</v>
+        <v>406</v>
       </c>
       <c r="C29">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D29">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E29">
-        <v>346</v>
+        <v>309</v>
       </c>
       <c r="F29">
         <v>0</v>
@@ -1650,16 +1509,16 @@
         <v>38</v>
       </c>
       <c r="B30">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C30">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D30">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="E30">
-        <v>309</v>
+        <v>329</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -1670,16 +1529,16 @@
         <v>39</v>
       </c>
       <c r="B31">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="C31">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D31">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="E31">
-        <v>329</v>
+        <v>292</v>
       </c>
       <c r="F31">
         <v>0</v>
@@ -1690,16 +1549,16 @@
         <v>40</v>
       </c>
       <c r="B32">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="C32">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="D32">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="E32">
-        <v>292</v>
+        <v>376</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -1710,16 +1569,16 @@
         <v>41</v>
       </c>
       <c r="B33">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="C33">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="E33">
-        <v>376</v>
+        <v>252</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -1730,16 +1589,16 @@
         <v>42</v>
       </c>
       <c r="B34">
-        <v>346</v>
+        <v>295</v>
       </c>
       <c r="C34">
-        <v>79</v>
+        <v>19</v>
       </c>
       <c r="D34">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="E34">
-        <v>261</v>
+        <v>208</v>
       </c>
       <c r="F34">
         <v>0</v>
@@ -1750,16 +1609,16 @@
         <v>43</v>
       </c>
       <c r="B35">
-        <v>316</v>
+        <v>269</v>
       </c>
       <c r="C35">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D35">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="E35">
-        <v>252</v>
+        <v>175</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -1770,16 +1629,16 @@
         <v>44</v>
       </c>
       <c r="B36">
-        <v>312</v>
+        <v>244</v>
       </c>
       <c r="C36">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D36">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E36">
-        <v>261</v>
+        <v>209</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -1790,16 +1649,16 @@
         <v>45</v>
       </c>
       <c r="B37">
-        <v>295</v>
+        <v>238</v>
       </c>
       <c r="C37">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D37">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="E37">
-        <v>208</v>
+        <v>180</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -1810,16 +1669,16 @@
         <v>46</v>
       </c>
       <c r="B38">
-        <v>269</v>
+        <v>237</v>
       </c>
       <c r="C38">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D38">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="E38">
-        <v>175</v>
+        <v>145</v>
       </c>
       <c r="F38">
         <v>0</v>
@@ -1830,16 +1689,16 @@
         <v>47</v>
       </c>
       <c r="B39">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="C39">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E39">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -1850,16 +1709,16 @@
         <v>48</v>
       </c>
       <c r="B40">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="C40">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D40">
         <v>0</v>
       </c>
       <c r="E40">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -1870,16 +1729,16 @@
         <v>49</v>
       </c>
       <c r="B41">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="C41">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D41">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="E41">
-        <v>180</v>
+        <v>131</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -1890,16 +1749,16 @@
         <v>50</v>
       </c>
       <c r="B42">
-        <v>237</v>
+        <v>207</v>
       </c>
       <c r="C42">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D42">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="E42">
-        <v>145</v>
+        <v>199</v>
       </c>
       <c r="F42">
         <v>0</v>
@@ -1910,16 +1769,16 @@
         <v>51</v>
       </c>
       <c r="B43">
-        <v>232</v>
+        <v>199</v>
       </c>
       <c r="C43">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D43">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="E43">
-        <v>194</v>
+        <v>138</v>
       </c>
       <c r="F43">
         <v>0</v>
@@ -1930,16 +1789,16 @@
         <v>52</v>
       </c>
       <c r="B44">
-        <v>223</v>
+        <v>194</v>
       </c>
       <c r="C44">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D44">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="E44">
-        <v>131</v>
+        <v>183</v>
       </c>
       <c r="F44">
         <v>0</v>
@@ -1950,19 +1809,19 @@
         <v>53</v>
       </c>
       <c r="B45">
-        <v>223</v>
+        <v>187</v>
       </c>
       <c r="C45">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D45">
         <v>0</v>
       </c>
       <c r="E45">
-        <v>220</v>
+        <v>172</v>
       </c>
       <c r="F45">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -1970,19 +1829,19 @@
         <v>54</v>
       </c>
       <c r="B46">
-        <v>207</v>
+        <v>182</v>
       </c>
       <c r="C46">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D46">
         <v>0</v>
       </c>
       <c r="E46">
-        <v>199</v>
+        <v>177</v>
       </c>
       <c r="F46">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -1990,16 +1849,16 @@
         <v>55</v>
       </c>
       <c r="B47">
-        <v>199</v>
+        <v>167</v>
       </c>
       <c r="C47">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D47">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="E47">
-        <v>138</v>
+        <v>164</v>
       </c>
       <c r="F47">
         <v>0</v>
@@ -2010,16 +1869,16 @@
         <v>56</v>
       </c>
       <c r="B48">
-        <v>194</v>
+        <v>163</v>
       </c>
       <c r="C48">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D48">
         <v>0</v>
       </c>
       <c r="E48">
-        <v>183</v>
+        <v>156</v>
       </c>
       <c r="F48">
         <v>0</v>
@@ -2030,19 +1889,19 @@
         <v>57</v>
       </c>
       <c r="B49">
-        <v>187</v>
+        <v>154</v>
       </c>
       <c r="C49">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D49">
         <v>0</v>
       </c>
       <c r="E49">
-        <v>172</v>
+        <v>148</v>
       </c>
       <c r="F49">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -2050,16 +1909,16 @@
         <v>58</v>
       </c>
       <c r="B50">
-        <v>185</v>
+        <v>154</v>
       </c>
       <c r="C50">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D50">
         <v>0</v>
       </c>
       <c r="E50">
-        <v>177</v>
+        <v>144</v>
       </c>
       <c r="F50">
         <v>0</v>
@@ -2070,19 +1929,19 @@
         <v>59</v>
       </c>
       <c r="B51">
-        <v>182</v>
+        <v>151</v>
       </c>
       <c r="C51">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="E51">
-        <v>177</v>
+        <v>51</v>
       </c>
       <c r="F51">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -2090,16 +1949,16 @@
         <v>60</v>
       </c>
       <c r="B52">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="C52">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E52">
-        <v>164</v>
+        <v>142</v>
       </c>
       <c r="F52">
         <v>0</v>
@@ -2110,7 +1969,7 @@
         <v>61</v>
       </c>
       <c r="B53">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="C53">
         <v>7</v>
@@ -2119,7 +1978,7 @@
         <v>0</v>
       </c>
       <c r="E53">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="F53">
         <v>0</v>
@@ -2130,16 +1989,16 @@
         <v>62</v>
       </c>
       <c r="B54">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="C54">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D54">
         <v>0</v>
       </c>
       <c r="E54">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F54">
         <v>0</v>
@@ -2150,16 +2009,16 @@
         <v>63</v>
       </c>
       <c r="B55">
-        <v>154</v>
+        <v>138</v>
       </c>
       <c r="C55">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D55">
         <v>0</v>
       </c>
       <c r="E55">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="F55">
         <v>0</v>
@@ -2170,16 +2029,16 @@
         <v>64</v>
       </c>
       <c r="B56">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="C56">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D56">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="E56">
-        <v>51</v>
+        <v>129</v>
       </c>
       <c r="F56">
         <v>0</v>
@@ -2190,16 +2049,16 @@
         <v>65</v>
       </c>
       <c r="B57">
-        <v>150</v>
+        <v>128</v>
       </c>
       <c r="C57">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D57">
         <v>0</v>
       </c>
       <c r="E57">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="F57">
         <v>0</v>
@@ -2210,16 +2069,16 @@
         <v>66</v>
       </c>
       <c r="B58">
-        <v>150</v>
+        <v>127</v>
       </c>
       <c r="C58">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D58">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E58">
-        <v>143</v>
+        <v>109</v>
       </c>
       <c r="F58">
         <v>0</v>
@@ -2230,16 +2089,16 @@
         <v>67</v>
       </c>
       <c r="B59">
-        <v>149</v>
+        <v>127</v>
       </c>
       <c r="C59">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D59">
         <v>0</v>
       </c>
       <c r="E59">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="F59">
         <v>0</v>
@@ -2250,16 +2109,16 @@
         <v>68</v>
       </c>
       <c r="B60">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="C60">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D60">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="E60">
-        <v>140</v>
+        <v>44</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -2270,16 +2129,16 @@
         <v>69</v>
       </c>
       <c r="B61">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="C61">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D61">
         <v>0</v>
       </c>
       <c r="E61">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="F61">
         <v>0</v>
@@ -2290,16 +2149,16 @@
         <v>70</v>
       </c>
       <c r="B62">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="C62">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D62">
         <v>0</v>
       </c>
       <c r="E62">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="F62">
         <v>0</v>
@@ -2310,16 +2169,16 @@
         <v>71</v>
       </c>
       <c r="B63">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="C63">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D63">
         <v>0</v>
       </c>
       <c r="E63">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="F63">
         <v>0</v>
@@ -2330,16 +2189,16 @@
         <v>72</v>
       </c>
       <c r="B64">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="C64">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D64">
         <v>0</v>
       </c>
       <c r="E64">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -2350,16 +2209,16 @@
         <v>73</v>
       </c>
       <c r="B65">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="C65">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D65">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E65">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F65">
         <v>0</v>
@@ -2370,16 +2229,16 @@
         <v>74</v>
       </c>
       <c r="B66">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="C66">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D66">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="E66">
-        <v>44</v>
+        <v>104</v>
       </c>
       <c r="F66">
         <v>0</v>
@@ -2390,19 +2249,19 @@
         <v>75</v>
       </c>
       <c r="B67">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="C67">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D67">
         <v>0</v>
       </c>
       <c r="E67">
-        <v>119</v>
+        <v>92</v>
       </c>
       <c r="F67">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -2410,16 +2269,16 @@
         <v>76</v>
       </c>
       <c r="B68">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="C68">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D68">
         <v>0</v>
       </c>
       <c r="E68">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="F68">
         <v>0</v>
@@ -2430,16 +2289,16 @@
         <v>77</v>
       </c>
       <c r="B69">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="C69">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D69">
         <v>0</v>
       </c>
       <c r="E69">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="F69">
         <v>0</v>
@@ -2450,19 +2309,19 @@
         <v>78</v>
       </c>
       <c r="B70">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="C70">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D70">
         <v>0</v>
       </c>
       <c r="E70">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="F70">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71" spans="1:6">
@@ -2470,7 +2329,7 @@
         <v>79</v>
       </c>
       <c r="B71">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C71">
         <v>4</v>
@@ -2479,7 +2338,7 @@
         <v>0</v>
       </c>
       <c r="E71">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="F71">
         <v>0</v>
@@ -2490,16 +2349,16 @@
         <v>80</v>
       </c>
       <c r="B72">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="C72">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D72">
         <v>0</v>
       </c>
       <c r="E72">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="F72">
         <v>0</v>
@@ -2510,16 +2369,16 @@
         <v>81</v>
       </c>
       <c r="B73">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="C73">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D73">
         <v>0</v>
       </c>
       <c r="E73">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="F73">
         <v>0</v>
@@ -2530,7 +2389,7 @@
         <v>82</v>
       </c>
       <c r="B74">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="C74">
         <v>3</v>
@@ -2539,7 +2398,7 @@
         <v>0</v>
       </c>
       <c r="E74">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="F74">
         <v>0</v>
@@ -2550,19 +2409,19 @@
         <v>83</v>
       </c>
       <c r="B75">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="C75">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D75">
         <v>0</v>
       </c>
       <c r="E75">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="F75">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -2570,16 +2429,16 @@
         <v>84</v>
       </c>
       <c r="B76">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="C76">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D76">
         <v>0</v>
       </c>
       <c r="E76">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="F76">
         <v>0</v>
@@ -2590,16 +2449,16 @@
         <v>85</v>
       </c>
       <c r="B77">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="C77">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D77">
         <v>0</v>
       </c>
       <c r="E77">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="F77">
         <v>0</v>
@@ -2610,19 +2469,19 @@
         <v>86</v>
       </c>
       <c r="B78">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="C78">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D78">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="E78">
-        <v>94</v>
+        <v>7</v>
       </c>
       <c r="F78">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -2630,16 +2489,16 @@
         <v>87</v>
       </c>
       <c r="B79">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="C79">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D79">
         <v>0</v>
       </c>
       <c r="E79">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="F79">
         <v>0</v>
@@ -2650,16 +2509,16 @@
         <v>88</v>
       </c>
       <c r="B80">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="C80">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D80">
         <v>0</v>
       </c>
       <c r="E80">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="F80">
         <v>0</v>
@@ -2670,16 +2529,16 @@
         <v>89</v>
       </c>
       <c r="B81">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="C81">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D81">
         <v>0</v>
       </c>
       <c r="E81">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="F81">
         <v>0</v>
@@ -2690,7 +2549,7 @@
         <v>90</v>
       </c>
       <c r="B82">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="C82">
         <v>3</v>
@@ -2699,7 +2558,7 @@
         <v>0</v>
       </c>
       <c r="E82">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="F82">
         <v>0</v>
@@ -2710,16 +2569,16 @@
         <v>91</v>
       </c>
       <c r="B83">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="C83">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D83">
         <v>0</v>
       </c>
       <c r="E83">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="F83">
         <v>0</v>
@@ -2730,7 +2589,7 @@
         <v>92</v>
       </c>
       <c r="B84">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="C84">
         <v>3</v>
@@ -2739,10 +2598,10 @@
         <v>0</v>
       </c>
       <c r="E84">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="F84">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -2750,16 +2609,16 @@
         <v>93</v>
       </c>
       <c r="B85">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="C85">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D85">
         <v>0</v>
       </c>
       <c r="E85">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F85">
         <v>0</v>
@@ -2770,16 +2629,16 @@
         <v>94</v>
       </c>
       <c r="B86">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C86">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D86">
         <v>0</v>
       </c>
       <c r="E86">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="F86">
         <v>0</v>
@@ -2790,16 +2649,16 @@
         <v>95</v>
       </c>
       <c r="B87">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="C87">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D87">
         <v>0</v>
       </c>
       <c r="E87">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F87">
         <v>0</v>
@@ -2810,16 +2669,16 @@
         <v>96</v>
       </c>
       <c r="B88">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="C88">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D88">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="E88">
-        <v>7</v>
+        <v>63</v>
       </c>
       <c r="F88">
         <v>0</v>
@@ -2830,16 +2689,16 @@
         <v>97</v>
       </c>
       <c r="B89">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="C89">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D89">
         <v>0</v>
       </c>
       <c r="E89">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="F89">
         <v>0</v>
@@ -2850,16 +2709,16 @@
         <v>98</v>
       </c>
       <c r="B90">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="C90">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D90">
         <v>0</v>
       </c>
       <c r="E90">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="F90">
         <v>0</v>
@@ -2870,16 +2729,16 @@
         <v>99</v>
       </c>
       <c r="B91">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="C91">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D91">
         <v>0</v>
       </c>
       <c r="E91">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="F91">
         <v>0</v>
@@ -2890,7 +2749,7 @@
         <v>100</v>
       </c>
       <c r="B92">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="C92">
         <v>1</v>
@@ -2899,7 +2758,7 @@
         <v>0</v>
       </c>
       <c r="E92">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="F92">
         <v>0</v>
@@ -2910,16 +2769,16 @@
         <v>101</v>
       </c>
       <c r="B93">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="C93">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D93">
         <v>0</v>
       </c>
       <c r="E93">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="F93">
         <v>0</v>
@@ -2930,16 +2789,16 @@
         <v>102</v>
       </c>
       <c r="B94">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="C94">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D94">
         <v>0</v>
       </c>
       <c r="E94">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="F94">
         <v>0</v>
@@ -2950,7 +2809,7 @@
         <v>103</v>
       </c>
       <c r="B95">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="C95">
         <v>1</v>
@@ -2959,7 +2818,7 @@
         <v>0</v>
       </c>
       <c r="E95">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="F95">
         <v>0</v>
@@ -2970,19 +2829,19 @@
         <v>104</v>
       </c>
       <c r="B96">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="C96">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D96">
         <v>0</v>
       </c>
       <c r="E96">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="F96">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:6">
@@ -2990,16 +2849,16 @@
         <v>105</v>
       </c>
       <c r="B97">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="C97">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D97">
         <v>0</v>
       </c>
       <c r="E97">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="F97">
         <v>0</v>
@@ -3010,7 +2869,7 @@
         <v>106</v>
       </c>
       <c r="B98">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="C98">
         <v>3</v>
@@ -3019,10 +2878,10 @@
         <v>0</v>
       </c>
       <c r="E98">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="F98">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:6">
@@ -3030,16 +2889,16 @@
         <v>107</v>
       </c>
       <c r="B99">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C99">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D99">
         <v>0</v>
       </c>
       <c r="E99">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="F99">
         <v>0</v>
@@ -3050,16 +2909,16 @@
         <v>108</v>
       </c>
       <c r="B100">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="C100">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D100">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E100">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="F100">
         <v>0</v>
@@ -3070,16 +2929,16 @@
         <v>109</v>
       </c>
       <c r="B101">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="C101">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D101">
         <v>0</v>
       </c>
       <c r="E101">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="F101">
         <v>0</v>
@@ -3090,16 +2949,16 @@
         <v>110</v>
       </c>
       <c r="B102">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C102">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D102">
         <v>0</v>
       </c>
       <c r="E102">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="F102">
         <v>0</v>
@@ -3110,16 +2969,16 @@
         <v>111</v>
       </c>
       <c r="B103">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="C103">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D103">
         <v>0</v>
       </c>
       <c r="E103">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="F103">
         <v>0</v>
@@ -3130,16 +2989,16 @@
         <v>112</v>
       </c>
       <c r="B104">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="C104">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D104">
         <v>0</v>
       </c>
       <c r="E104">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="F104">
         <v>0</v>
@@ -3150,16 +3009,16 @@
         <v>113</v>
       </c>
       <c r="B105">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C105">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D105">
         <v>0</v>
       </c>
       <c r="E105">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="F105">
         <v>0</v>
@@ -3170,16 +3029,16 @@
         <v>114</v>
       </c>
       <c r="B106">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C106">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D106">
         <v>0</v>
       </c>
       <c r="E106">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="F106">
         <v>0</v>
@@ -3190,16 +3049,16 @@
         <v>115</v>
       </c>
       <c r="B107">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="C107">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D107">
         <v>0</v>
       </c>
       <c r="E107">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="F107">
         <v>0</v>
@@ -3210,16 +3069,16 @@
         <v>116</v>
       </c>
       <c r="B108">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="C108">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D108">
         <v>0</v>
       </c>
       <c r="E108">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="F108">
         <v>0</v>
@@ -3230,16 +3089,16 @@
         <v>117</v>
       </c>
       <c r="B109">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C109">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D109">
         <v>0</v>
       </c>
       <c r="E109">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F109">
         <v>0</v>
@@ -3250,16 +3109,16 @@
         <v>118</v>
       </c>
       <c r="B110">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C110">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D110">
         <v>0</v>
       </c>
       <c r="E110">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="F110">
         <v>0</v>
@@ -3270,7 +3129,7 @@
         <v>119</v>
       </c>
       <c r="B111">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="C111">
         <v>1</v>
@@ -3279,7 +3138,7 @@
         <v>0</v>
       </c>
       <c r="E111">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="F111">
         <v>0</v>
@@ -3290,16 +3149,16 @@
         <v>120</v>
       </c>
       <c r="B112">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="C112">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D112">
         <v>0</v>
       </c>
       <c r="E112">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="F112">
         <v>0</v>
@@ -3310,16 +3169,16 @@
         <v>121</v>
       </c>
       <c r="B113">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="C113">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D113">
         <v>0</v>
       </c>
       <c r="E113">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="F113">
         <v>0</v>
@@ -3330,16 +3189,16 @@
         <v>122</v>
       </c>
       <c r="B114">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="C114">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D114">
         <v>0</v>
       </c>
       <c r="E114">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="F114">
         <v>0</v>
@@ -3350,16 +3209,16 @@
         <v>123</v>
       </c>
       <c r="B115">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="C115">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D115">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E115">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F115">
         <v>0</v>
@@ -3370,16 +3229,16 @@
         <v>124</v>
       </c>
       <c r="B116">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="C116">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D116">
         <v>0</v>
       </c>
       <c r="E116">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="F116">
         <v>0</v>
@@ -3390,16 +3249,16 @@
         <v>125</v>
       </c>
       <c r="B117">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="C117">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D117">
         <v>0</v>
       </c>
       <c r="E117">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="F117">
         <v>0</v>
@@ -3410,16 +3269,16 @@
         <v>126</v>
       </c>
       <c r="B118">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="C118">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D118">
         <v>0</v>
       </c>
       <c r="E118">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="F118">
         <v>0</v>
@@ -3430,16 +3289,16 @@
         <v>127</v>
       </c>
       <c r="B119">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="C119">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D119">
         <v>0</v>
       </c>
       <c r="E119">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="F119">
         <v>0</v>
@@ -3450,7 +3309,7 @@
         <v>128</v>
       </c>
       <c r="B120">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="C120">
         <v>2</v>
@@ -3459,7 +3318,7 @@
         <v>0</v>
       </c>
       <c r="E120">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="F120">
         <v>0</v>
@@ -3470,16 +3329,16 @@
         <v>129</v>
       </c>
       <c r="B121">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="C121">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D121">
         <v>0</v>
       </c>
       <c r="E121">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="F121">
         <v>0</v>
@@ -3490,16 +3349,16 @@
         <v>130</v>
       </c>
       <c r="B122">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="C122">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D122">
         <v>0</v>
       </c>
       <c r="E122">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="F122">
         <v>0</v>
@@ -3510,16 +3369,16 @@
         <v>131</v>
       </c>
       <c r="B123">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="C123">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D123">
         <v>0</v>
       </c>
       <c r="E123">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="F123">
         <v>0</v>
@@ -3530,16 +3389,16 @@
         <v>132</v>
       </c>
       <c r="B124">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="C124">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D124">
         <v>0</v>
       </c>
       <c r="E124">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="F124">
         <v>0</v>
@@ -3550,16 +3409,16 @@
         <v>133</v>
       </c>
       <c r="B125">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="C125">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D125">
         <v>0</v>
       </c>
       <c r="E125">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="F125">
         <v>0</v>
@@ -3570,16 +3429,16 @@
         <v>134</v>
       </c>
       <c r="B126">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="C126">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D126">
         <v>0</v>
       </c>
       <c r="E126">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="F126">
         <v>0</v>
@@ -3590,16 +3449,16 @@
         <v>135</v>
       </c>
       <c r="B127">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="C127">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D127">
         <v>0</v>
       </c>
       <c r="E127">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="F127">
         <v>0</v>
@@ -3610,16 +3469,16 @@
         <v>136</v>
       </c>
       <c r="B128">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="C128">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D128">
         <v>0</v>
       </c>
       <c r="E128">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="F128">
         <v>0</v>
@@ -3630,7 +3489,7 @@
         <v>137</v>
       </c>
       <c r="B129">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="C129">
         <v>4</v>
@@ -3639,7 +3498,7 @@
         <v>0</v>
       </c>
       <c r="E129">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="F129">
         <v>0</v>
@@ -3650,7 +3509,7 @@
         <v>138</v>
       </c>
       <c r="B130">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="C130">
         <v>1</v>
@@ -3659,7 +3518,7 @@
         <v>0</v>
       </c>
       <c r="E130">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="F130">
         <v>0</v>
@@ -3670,7 +3529,7 @@
         <v>139</v>
       </c>
       <c r="B131">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="C131">
         <v>1</v>
@@ -3679,7 +3538,7 @@
         <v>0</v>
       </c>
       <c r="E131">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="F131">
         <v>0</v>
@@ -3690,7 +3549,7 @@
         <v>140</v>
       </c>
       <c r="B132">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="C132">
         <v>1</v>
@@ -3699,7 +3558,7 @@
         <v>0</v>
       </c>
       <c r="E132">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="F132">
         <v>0</v>
@@ -3710,16 +3569,16 @@
         <v>141</v>
       </c>
       <c r="B133">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="C133">
         <v>2</v>
       </c>
       <c r="D133">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E133">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="F133">
         <v>0</v>
@@ -3730,16 +3589,16 @@
         <v>142</v>
       </c>
       <c r="B134">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="C134">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D134">
         <v>0</v>
       </c>
       <c r="E134">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="F134">
         <v>0</v>
@@ -3750,16 +3609,16 @@
         <v>143</v>
       </c>
       <c r="B135">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="C135">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D135">
         <v>0</v>
       </c>
       <c r="E135">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="F135">
         <v>0</v>
@@ -3770,7 +3629,7 @@
         <v>144</v>
       </c>
       <c r="B136">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="C136">
         <v>1</v>
@@ -3779,7 +3638,7 @@
         <v>0</v>
       </c>
       <c r="E136">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="F136">
         <v>0</v>
@@ -3790,16 +3649,16 @@
         <v>145</v>
       </c>
       <c r="B137">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="C137">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D137">
         <v>0</v>
       </c>
       <c r="E137">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="F137">
         <v>0</v>
@@ -3810,16 +3669,16 @@
         <v>146</v>
       </c>
       <c r="B138">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="C138">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D138">
         <v>0</v>
       </c>
       <c r="E138">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="F138">
         <v>0</v>
@@ -3830,16 +3689,16 @@
         <v>147</v>
       </c>
       <c r="B139">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="C139">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D139">
         <v>0</v>
       </c>
       <c r="E139">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="F139">
         <v>0</v>
@@ -3850,16 +3709,16 @@
         <v>148</v>
       </c>
       <c r="B140">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="C140">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D140">
         <v>0</v>
       </c>
       <c r="E140">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="F140">
         <v>0</v>
@@ -3870,7 +3729,7 @@
         <v>149</v>
       </c>
       <c r="B141">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="C141">
         <v>0</v>
@@ -3879,7 +3738,7 @@
         <v>0</v>
       </c>
       <c r="E141">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="F141">
         <v>0</v>
@@ -3890,16 +3749,16 @@
         <v>150</v>
       </c>
       <c r="B142">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="C142">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D142">
         <v>0</v>
       </c>
       <c r="E142">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="F142">
         <v>0</v>
@@ -3910,16 +3769,16 @@
         <v>151</v>
       </c>
       <c r="B143">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="C143">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D143">
         <v>0</v>
       </c>
       <c r="E143">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F143">
         <v>0</v>
@@ -3930,958 +3789,18 @@
         <v>152</v>
       </c>
       <c r="B144">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="C144">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D144">
         <v>0</v>
       </c>
       <c r="E144">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="F144">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6">
-      <c r="A145" t="s">
-        <v>153</v>
-      </c>
-      <c r="B145">
-        <v>39</v>
-      </c>
-      <c r="C145">
-        <v>3</v>
-      </c>
-      <c r="D145">
-        <v>0</v>
-      </c>
-      <c r="E145">
-        <v>36</v>
-      </c>
-      <c r="F145">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6">
-      <c r="A146" t="s">
-        <v>154</v>
-      </c>
-      <c r="B146">
-        <v>39</v>
-      </c>
-      <c r="C146">
-        <v>1</v>
-      </c>
-      <c r="D146">
-        <v>0</v>
-      </c>
-      <c r="E146">
-        <v>38</v>
-      </c>
-      <c r="F146">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6">
-      <c r="A147" t="s">
-        <v>155</v>
-      </c>
-      <c r="B147">
-        <v>38</v>
-      </c>
-      <c r="C147">
-        <v>4</v>
-      </c>
-      <c r="D147">
-        <v>0</v>
-      </c>
-      <c r="E147">
-        <v>34</v>
-      </c>
-      <c r="F147">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6">
-      <c r="A148" t="s">
-        <v>156</v>
-      </c>
-      <c r="B148">
-        <v>38</v>
-      </c>
-      <c r="C148">
-        <v>0</v>
-      </c>
-      <c r="D148">
-        <v>0</v>
-      </c>
-      <c r="E148">
-        <v>38</v>
-      </c>
-      <c r="F148">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6">
-      <c r="A149" t="s">
-        <v>157</v>
-      </c>
-      <c r="B149">
-        <v>37</v>
-      </c>
-      <c r="C149">
-        <v>4</v>
-      </c>
-      <c r="D149">
-        <v>0</v>
-      </c>
-      <c r="E149">
-        <v>33</v>
-      </c>
-      <c r="F149">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6">
-      <c r="A150" t="s">
-        <v>158</v>
-      </c>
-      <c r="B150">
-        <v>37</v>
-      </c>
-      <c r="C150">
-        <v>4</v>
-      </c>
-      <c r="D150">
-        <v>0</v>
-      </c>
-      <c r="E150">
-        <v>33</v>
-      </c>
-      <c r="F150">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6">
-      <c r="A151" t="s">
-        <v>159</v>
-      </c>
-      <c r="B151">
-        <v>36</v>
-      </c>
-      <c r="C151">
-        <v>2</v>
-      </c>
-      <c r="D151">
-        <v>0</v>
-      </c>
-      <c r="E151">
-        <v>34</v>
-      </c>
-      <c r="F151">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6">
-      <c r="A152" t="s">
-        <v>160</v>
-      </c>
-      <c r="B152">
-        <v>36</v>
-      </c>
-      <c r="C152">
-        <v>4</v>
-      </c>
-      <c r="D152">
-        <v>0</v>
-      </c>
-      <c r="E152">
-        <v>32</v>
-      </c>
-      <c r="F152">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6">
-      <c r="A153" t="s">
-        <v>161</v>
-      </c>
-      <c r="B153">
-        <v>36</v>
-      </c>
-      <c r="C153">
-        <v>0</v>
-      </c>
-      <c r="D153">
-        <v>0</v>
-      </c>
-      <c r="E153">
-        <v>36</v>
-      </c>
-      <c r="F153">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6">
-      <c r="A154" t="s">
-        <v>162</v>
-      </c>
-      <c r="B154">
-        <v>35</v>
-      </c>
-      <c r="C154">
-        <v>1</v>
-      </c>
-      <c r="D154">
-        <v>0</v>
-      </c>
-      <c r="E154">
-        <v>34</v>
-      </c>
-      <c r="F154">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6">
-      <c r="A155" t="s">
-        <v>163</v>
-      </c>
-      <c r="B155">
-        <v>35</v>
-      </c>
-      <c r="C155">
-        <v>1</v>
-      </c>
-      <c r="D155">
-        <v>0</v>
-      </c>
-      <c r="E155">
-        <v>34</v>
-      </c>
-      <c r="F155">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6">
-      <c r="A156" t="s">
-        <v>164</v>
-      </c>
-      <c r="B156">
-        <v>35</v>
-      </c>
-      <c r="C156">
-        <v>1</v>
-      </c>
-      <c r="D156">
-        <v>0</v>
-      </c>
-      <c r="E156">
-        <v>34</v>
-      </c>
-      <c r="F156">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="157" spans="1:6">
-      <c r="A157" t="s">
-        <v>165</v>
-      </c>
-      <c r="B157">
-        <v>34</v>
-      </c>
-      <c r="C157">
-        <v>2</v>
-      </c>
-      <c r="D157">
-        <v>2</v>
-      </c>
-      <c r="E157">
-        <v>30</v>
-      </c>
-      <c r="F157">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6">
-      <c r="A158" t="s">
-        <v>166</v>
-      </c>
-      <c r="B158">
-        <v>33</v>
-      </c>
-      <c r="C158">
-        <v>0</v>
-      </c>
-      <c r="D158">
-        <v>0</v>
-      </c>
-      <c r="E158">
-        <v>33</v>
-      </c>
-      <c r="F158">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6">
-      <c r="A159" t="s">
-        <v>167</v>
-      </c>
-      <c r="B159">
-        <v>32</v>
-      </c>
-      <c r="C159">
-        <v>1</v>
-      </c>
-      <c r="D159">
-        <v>0</v>
-      </c>
-      <c r="E159">
-        <v>31</v>
-      </c>
-      <c r="F159">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6">
-      <c r="A160" t="s">
-        <v>168</v>
-      </c>
-      <c r="B160">
-        <v>32</v>
-      </c>
-      <c r="C160">
-        <v>4</v>
-      </c>
-      <c r="D160">
-        <v>0</v>
-      </c>
-      <c r="E160">
-        <v>28</v>
-      </c>
-      <c r="F160">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="161" spans="1:6">
-      <c r="A161" t="s">
-        <v>169</v>
-      </c>
-      <c r="B161">
-        <v>31</v>
-      </c>
-      <c r="C161">
-        <v>0</v>
-      </c>
-      <c r="D161">
-        <v>0</v>
-      </c>
-      <c r="E161">
-        <v>31</v>
-      </c>
-      <c r="F161">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="162" spans="1:6">
-      <c r="A162" t="s">
-        <v>170</v>
-      </c>
-      <c r="B162">
-        <v>29</v>
-      </c>
-      <c r="C162">
-        <v>1</v>
-      </c>
-      <c r="D162">
-        <v>0</v>
-      </c>
-      <c r="E162">
-        <v>28</v>
-      </c>
-      <c r="F162">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="163" spans="1:6">
-      <c r="A163" t="s">
-        <v>171</v>
-      </c>
-      <c r="B163">
-        <v>27</v>
-      </c>
-      <c r="C163">
-        <v>1</v>
-      </c>
-      <c r="D163">
-        <v>0</v>
-      </c>
-      <c r="E163">
-        <v>26</v>
-      </c>
-      <c r="F163">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6">
-      <c r="A164" t="s">
-        <v>172</v>
-      </c>
-      <c r="B164">
-        <v>26</v>
-      </c>
-      <c r="C164">
-        <v>0</v>
-      </c>
-      <c r="D164">
-        <v>0</v>
-      </c>
-      <c r="E164">
-        <v>26</v>
-      </c>
-      <c r="F164">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="165" spans="1:6">
-      <c r="A165" t="s">
-        <v>173</v>
-      </c>
-      <c r="B165">
-        <v>26</v>
-      </c>
-      <c r="C165">
-        <v>2</v>
-      </c>
-      <c r="D165">
-        <v>0</v>
-      </c>
-      <c r="E165">
-        <v>24</v>
-      </c>
-      <c r="F165">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="166" spans="1:6">
-      <c r="A166" t="s">
-        <v>174</v>
-      </c>
-      <c r="B166">
-        <v>25</v>
-      </c>
-      <c r="C166">
-        <v>0</v>
-      </c>
-      <c r="D166">
-        <v>0</v>
-      </c>
-      <c r="E166">
-        <v>25</v>
-      </c>
-      <c r="F166">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6">
-      <c r="A167" t="s">
-        <v>175</v>
-      </c>
-      <c r="B167">
-        <v>25</v>
-      </c>
-      <c r="C167">
-        <v>2</v>
-      </c>
-      <c r="D167">
-        <v>0</v>
-      </c>
-      <c r="E167">
-        <v>23</v>
-      </c>
-      <c r="F167">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6">
-      <c r="A168" t="s">
-        <v>176</v>
-      </c>
-      <c r="B168">
-        <v>25</v>
-      </c>
-      <c r="C168">
-        <v>0</v>
-      </c>
-      <c r="D168">
-        <v>0</v>
-      </c>
-      <c r="E168">
-        <v>25</v>
-      </c>
-      <c r="F168">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="169" spans="1:6">
-      <c r="A169" t="s">
-        <v>177</v>
-      </c>
-      <c r="B169">
-        <v>25</v>
-      </c>
-      <c r="C169">
-        <v>1</v>
-      </c>
-      <c r="D169">
-        <v>0</v>
-      </c>
-      <c r="E169">
-        <v>24</v>
-      </c>
-      <c r="F169">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="170" spans="1:6">
-      <c r="A170" t="s">
-        <v>178</v>
-      </c>
-      <c r="B170">
-        <v>25</v>
-      </c>
-      <c r="C170">
-        <v>0</v>
-      </c>
-      <c r="D170">
-        <v>0</v>
-      </c>
-      <c r="E170">
-        <v>24</v>
-      </c>
-      <c r="F170">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="171" spans="1:6">
-      <c r="A171" t="s">
-        <v>179</v>
-      </c>
-      <c r="B171">
-        <v>25</v>
-      </c>
-      <c r="C171">
-        <v>0</v>
-      </c>
-      <c r="D171">
-        <v>0</v>
-      </c>
-      <c r="E171">
-        <v>25</v>
-      </c>
-      <c r="F171">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6">
-      <c r="A172" t="s">
-        <v>180</v>
-      </c>
-      <c r="B172">
-        <v>23</v>
-      </c>
-      <c r="C172">
-        <v>1</v>
-      </c>
-      <c r="D172">
-        <v>0</v>
-      </c>
-      <c r="E172">
-        <v>22</v>
-      </c>
-      <c r="F172">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="173" spans="1:6">
-      <c r="A173" t="s">
-        <v>181</v>
-      </c>
-      <c r="B173">
-        <v>23</v>
-      </c>
-      <c r="C173">
-        <v>1</v>
-      </c>
-      <c r="D173">
-        <v>0</v>
-      </c>
-      <c r="E173">
-        <v>22</v>
-      </c>
-      <c r="F173">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="174" spans="1:6">
-      <c r="A174" t="s">
-        <v>182</v>
-      </c>
-      <c r="B174">
-        <v>23</v>
-      </c>
-      <c r="C174">
-        <v>0</v>
-      </c>
-      <c r="D174">
-        <v>0</v>
-      </c>
-      <c r="E174">
-        <v>23</v>
-      </c>
-      <c r="F174">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="175" spans="1:6">
-      <c r="A175" t="s">
-        <v>183</v>
-      </c>
-      <c r="B175">
-        <v>22</v>
-      </c>
-      <c r="C175">
-        <v>2</v>
-      </c>
-      <c r="D175">
-        <v>0</v>
-      </c>
-      <c r="E175">
-        <v>20</v>
-      </c>
-      <c r="F175">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="176" spans="1:6">
-      <c r="A176" t="s">
-        <v>184</v>
-      </c>
-      <c r="B176">
-        <v>22</v>
-      </c>
-      <c r="C176">
-        <v>1</v>
-      </c>
-      <c r="D176">
-        <v>0</v>
-      </c>
-      <c r="E176">
-        <v>21</v>
-      </c>
-      <c r="F176">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="177" spans="1:6">
-      <c r="A177" t="s">
-        <v>185</v>
-      </c>
-      <c r="B177">
-        <v>22</v>
-      </c>
-      <c r="C177">
-        <v>2</v>
-      </c>
-      <c r="D177">
-        <v>0</v>
-      </c>
-      <c r="E177">
-        <v>20</v>
-      </c>
-      <c r="F177">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="178" spans="1:6">
-      <c r="A178" t="s">
-        <v>186</v>
-      </c>
-      <c r="B178">
-        <v>21</v>
-      </c>
-      <c r="C178">
-        <v>1</v>
-      </c>
-      <c r="D178">
-        <v>0</v>
-      </c>
-      <c r="E178">
-        <v>19</v>
-      </c>
-      <c r="F178">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="179" spans="1:6">
-      <c r="A179" t="s">
-        <v>187</v>
-      </c>
-      <c r="B179">
-        <v>20</v>
-      </c>
-      <c r="C179">
-        <v>4</v>
-      </c>
-      <c r="D179">
-        <v>0</v>
-      </c>
-      <c r="E179">
-        <v>16</v>
-      </c>
-      <c r="F179">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="180" spans="1:6">
-      <c r="A180" t="s">
-        <v>188</v>
-      </c>
-      <c r="B180">
-        <v>19</v>
-      </c>
-      <c r="C180">
-        <v>1</v>
-      </c>
-      <c r="D180">
-        <v>0</v>
-      </c>
-      <c r="E180">
-        <v>18</v>
-      </c>
-      <c r="F180">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="181" spans="1:6">
-      <c r="A181" t="s">
-        <v>189</v>
-      </c>
-      <c r="B181">
-        <v>18</v>
-      </c>
-      <c r="C181">
-        <v>1</v>
-      </c>
-      <c r="D181">
-        <v>0</v>
-      </c>
-      <c r="E181">
-        <v>17</v>
-      </c>
-      <c r="F181">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="182" spans="1:6">
-      <c r="A182" t="s">
-        <v>190</v>
-      </c>
-      <c r="B182">
-        <v>17</v>
-      </c>
-      <c r="C182">
-        <v>1</v>
-      </c>
-      <c r="D182">
-        <v>0</v>
-      </c>
-      <c r="E182">
-        <v>16</v>
-      </c>
-      <c r="F182">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="183" spans="1:6">
-      <c r="A183" t="s">
-        <v>191</v>
-      </c>
-      <c r="B183">
-        <v>16</v>
-      </c>
-      <c r="C183">
-        <v>0</v>
-      </c>
-      <c r="D183">
-        <v>0</v>
-      </c>
-      <c r="E183">
-        <v>16</v>
-      </c>
-      <c r="F183">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="184" spans="1:6">
-      <c r="A184" t="s">
-        <v>192</v>
-      </c>
-      <c r="B184">
-        <v>15</v>
-      </c>
-      <c r="C184">
-        <v>0</v>
-      </c>
-      <c r="D184">
-        <v>0</v>
-      </c>
-      <c r="E184">
-        <v>15</v>
-      </c>
-      <c r="F184">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="185" spans="1:6">
-      <c r="A185" t="s">
-        <v>193</v>
-      </c>
-      <c r="B185">
-        <v>14</v>
-      </c>
-      <c r="C185">
-        <v>0</v>
-      </c>
-      <c r="D185">
-        <v>0</v>
-      </c>
-      <c r="E185">
-        <v>14</v>
-      </c>
-      <c r="F185">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="186" spans="1:6">
-      <c r="A186" t="s">
-        <v>194</v>
-      </c>
-      <c r="B186">
-        <v>13</v>
-      </c>
-      <c r="C186">
-        <v>1</v>
-      </c>
-      <c r="D186">
-        <v>0</v>
-      </c>
-      <c r="E186">
-        <v>12</v>
-      </c>
-      <c r="F186">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="187" spans="1:6">
-      <c r="A187" t="s">
-        <v>195</v>
-      </c>
-      <c r="B187">
-        <v>9</v>
-      </c>
-      <c r="C187">
-        <v>1</v>
-      </c>
-      <c r="D187">
-        <v>0</v>
-      </c>
-      <c r="E187">
-        <v>8</v>
-      </c>
-      <c r="F187">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="188" spans="1:6">
-      <c r="A188" t="s">
-        <v>196</v>
-      </c>
-      <c r="B188">
-        <v>9</v>
-      </c>
-      <c r="C188">
-        <v>1</v>
-      </c>
-      <c r="D188">
-        <v>0</v>
-      </c>
-      <c r="E188">
-        <v>8</v>
-      </c>
-      <c r="F188">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="189" spans="1:6">
-      <c r="A189" t="s">
-        <v>197</v>
-      </c>
-      <c r="B189">
-        <v>5</v>
-      </c>
-      <c r="C189">
-        <v>0</v>
-      </c>
-      <c r="D189">
-        <v>0</v>
-      </c>
-      <c r="E189">
-        <v>5</v>
-      </c>
-      <c r="F189">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="190" spans="1:6">
-      <c r="A190" t="s">
-        <v>198</v>
-      </c>
-      <c r="B190">
-        <v>4</v>
-      </c>
-      <c r="C190">
-        <v>0</v>
-      </c>
-      <c r="D190">
-        <v>0</v>
-      </c>
-      <c r="E190">
-        <v>4</v>
-      </c>
-      <c r="F190">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="191" spans="1:6">
-      <c r="A191" t="s">
-        <v>199</v>
-      </c>
-      <c r="B191">
-        <v>2</v>
-      </c>
-      <c r="C191">
-        <v>0</v>
-      </c>
-      <c r="D191">
-        <v>0</v>
-      </c>
-      <c r="E191">
-        <v>2</v>
-      </c>
-      <c r="F191">
         <v>0</v>
       </c>
     </row>

--- a/resumo_busca_ativa_consolidado.xlsx
+++ b/resumo_busca_ativa_consolidado.xlsx
@@ -161,10 +161,10 @@
     <t>MARA ROSA</t>
   </si>
   <si>
+    <t>COCALZINHO DE GOIAS</t>
+  </si>
+  <si>
     <t>GOIANAPOLIS</t>
-  </si>
-  <si>
-    <t>COCALZINHO DE GOIAS</t>
   </si>
   <si>
     <t>BURITI ALEGRE</t>
@@ -859,16 +859,16 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>19128</v>
+        <v>19133</v>
       </c>
       <c r="C2">
-        <v>1197</v>
+        <v>1241</v>
       </c>
       <c r="D2">
-        <v>1655</v>
+        <v>1633</v>
       </c>
       <c r="E2">
-        <v>16276</v>
+        <v>16259</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -879,16 +879,16 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>16814</v>
+        <v>16817</v>
       </c>
       <c r="C3">
-        <v>959</v>
+        <v>952</v>
       </c>
       <c r="D3">
-        <v>1476</v>
+        <v>1454</v>
       </c>
       <c r="E3">
-        <v>14301</v>
+        <v>14333</v>
       </c>
       <c r="F3">
         <v>78</v>
@@ -899,19 +899,19 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>9443</v>
+        <v>9446</v>
       </c>
       <c r="C4">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="D4">
-        <v>1288</v>
+        <v>1223</v>
       </c>
       <c r="E4">
-        <v>7324</v>
+        <v>7343</v>
       </c>
       <c r="F4">
-        <v>187</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -949,16 +949,16 @@
         <v>10</v>
       </c>
       <c r="B2">
-        <v>9667</v>
+        <v>9670</v>
       </c>
       <c r="C2">
-        <v>555</v>
+        <v>575</v>
       </c>
       <c r="D2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E2">
-        <v>8592</v>
+        <v>8574</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -975,10 +975,10 @@
         <v>160</v>
       </c>
       <c r="D3">
-        <v>309</v>
+        <v>287</v>
       </c>
       <c r="E3">
-        <v>1864</v>
+        <v>1886</v>
       </c>
       <c r="F3">
         <v>48</v>
@@ -992,13 +992,13 @@
         <v>1735</v>
       </c>
       <c r="C4">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D4">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E4">
-        <v>1388</v>
+        <v>1392</v>
       </c>
       <c r="F4">
         <v>19</v>
@@ -1012,13 +1012,13 @@
         <v>1649</v>
       </c>
       <c r="C5">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="D5">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="E5">
-        <v>1283</v>
+        <v>1299</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1032,13 +1032,13 @@
         <v>1500</v>
       </c>
       <c r="C6">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="D6">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="E6">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1049,19 +1049,19 @@
         <v>15</v>
       </c>
       <c r="B7">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="C7">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D7">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E7">
-        <v>1034</v>
+        <v>1025</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1092,13 +1092,13 @@
         <v>1135</v>
       </c>
       <c r="C9">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="D9">
-        <v>331</v>
+        <v>349</v>
       </c>
       <c r="E9">
-        <v>694</v>
+        <v>686</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -1115,10 +1115,10 @@
         <v>80</v>
       </c>
       <c r="D10">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E10">
-        <v>828</v>
+        <v>833</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1132,13 +1132,13 @@
         <v>920</v>
       </c>
       <c r="C11">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D11">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E11">
-        <v>836</v>
+        <v>843</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1169,10 +1169,10 @@
         <v>21</v>
       </c>
       <c r="B13">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="C13">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D13">
         <v>151</v>
@@ -1232,13 +1232,13 @@
         <v>790</v>
       </c>
       <c r="C16">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="D16">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="E16">
-        <v>516</v>
+        <v>537</v>
       </c>
       <c r="F16">
         <v>26</v>
@@ -1272,13 +1272,13 @@
         <v>695</v>
       </c>
       <c r="C18">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D18">
         <v>49</v>
       </c>
       <c r="E18">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1289,10 +1289,10 @@
         <v>27</v>
       </c>
       <c r="B19">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C19">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D19">
         <v>132</v>
@@ -1315,10 +1315,10 @@
         <v>27</v>
       </c>
       <c r="D20">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E20">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1332,13 +1332,13 @@
         <v>616</v>
       </c>
       <c r="C21">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="D21">
-        <v>226</v>
+        <v>207</v>
       </c>
       <c r="E21">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1352,13 +1352,13 @@
         <v>611</v>
       </c>
       <c r="C22">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D22">
         <v>94</v>
       </c>
       <c r="E22">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1372,16 +1372,16 @@
         <v>601</v>
       </c>
       <c r="C23">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D23">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="E23">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -1392,13 +1392,13 @@
         <v>503</v>
       </c>
       <c r="C24">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D24">
         <v>0</v>
       </c>
       <c r="E24">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1412,13 +1412,13 @@
         <v>495</v>
       </c>
       <c r="C25">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D25">
         <v>29</v>
       </c>
       <c r="E25">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1432,13 +1432,13 @@
         <v>449</v>
       </c>
       <c r="C26">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D26">
-        <v>164</v>
+        <v>138</v>
       </c>
       <c r="E26">
-        <v>226</v>
+        <v>253</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -1472,13 +1472,13 @@
         <v>441</v>
       </c>
       <c r="C28">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D28">
         <v>67</v>
       </c>
       <c r="E28">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -1492,13 +1492,13 @@
         <v>406</v>
       </c>
       <c r="C29">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D29">
         <v>73</v>
       </c>
       <c r="E29">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F29">
         <v>0</v>
@@ -1512,13 +1512,13 @@
         <v>402</v>
       </c>
       <c r="C30">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D30">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="E30">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -1572,13 +1572,13 @@
         <v>316</v>
       </c>
       <c r="C33">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D33">
         <v>44</v>
       </c>
       <c r="E33">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -1592,13 +1592,13 @@
         <v>295</v>
       </c>
       <c r="C34">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D34">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E34">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F34">
         <v>0</v>
@@ -1629,16 +1629,16 @@
         <v>44</v>
       </c>
       <c r="B36">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C36">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D36">
         <v>0</v>
       </c>
       <c r="E36">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -1652,13 +1652,13 @@
         <v>238</v>
       </c>
       <c r="C37">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D37">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E37">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -1675,10 +1675,10 @@
         <v>9</v>
       </c>
       <c r="D38">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E38">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F38">
         <v>0</v>
@@ -1692,13 +1692,13 @@
         <v>232</v>
       </c>
       <c r="C39">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D39">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="E39">
-        <v>194</v>
+        <v>177</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -1709,16 +1709,16 @@
         <v>48</v>
       </c>
       <c r="B40">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C40">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="E40">
-        <v>220</v>
+        <v>136</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -1732,13 +1732,13 @@
         <v>223</v>
       </c>
       <c r="C41">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="D41">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="E41">
-        <v>131</v>
+        <v>220</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -1769,10 +1769,10 @@
         <v>51</v>
       </c>
       <c r="B43">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C43">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D43">
         <v>52</v>
@@ -1792,13 +1792,13 @@
         <v>194</v>
       </c>
       <c r="C44">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D44">
         <v>0</v>
       </c>
       <c r="E44">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F44">
         <v>0</v>
@@ -1818,10 +1818,10 @@
         <v>0</v>
       </c>
       <c r="E45">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="F45">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -1872,13 +1872,13 @@
         <v>163</v>
       </c>
       <c r="C48">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D48">
         <v>0</v>
       </c>
       <c r="E48">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F48">
         <v>0</v>
@@ -1932,13 +1932,13 @@
         <v>151</v>
       </c>
       <c r="C51">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="D51">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="E51">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -1972,13 +1972,13 @@
         <v>150</v>
       </c>
       <c r="C53">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D53">
         <v>0</v>
       </c>
       <c r="E53">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F53">
         <v>0</v>
@@ -2112,13 +2112,13 @@
         <v>124</v>
       </c>
       <c r="C60">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D60">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E60">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -2152,13 +2152,13 @@
         <v>118</v>
       </c>
       <c r="C62">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D62">
         <v>0</v>
       </c>
       <c r="E62">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F62">
         <v>0</v>
@@ -2258,10 +2258,10 @@
         <v>0</v>
       </c>
       <c r="E67">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="F67">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -2618,10 +2618,10 @@
         <v>0</v>
       </c>
       <c r="E85">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F85">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="86" spans="1:6">
@@ -2975,10 +2975,10 @@
         <v>1</v>
       </c>
       <c r="D103">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E103">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="F103">
         <v>0</v>
@@ -3192,13 +3192,13 @@
         <v>47</v>
       </c>
       <c r="C114">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D114">
         <v>0</v>
       </c>
       <c r="E114">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F114">
         <v>0</v>
@@ -3209,10 +3209,10 @@
         <v>123</v>
       </c>
       <c r="B115">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C115">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D115">
         <v>0</v>
@@ -3532,13 +3532,13 @@
         <v>35</v>
       </c>
       <c r="C131">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D131">
         <v>0</v>
       </c>
       <c r="E131">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F131">
         <v>0</v>

--- a/resumo_busca_ativa_consolidado.xlsx
+++ b/resumo_busca_ativa_consolidado.xlsx
@@ -862,16 +862,16 @@
         <v>19133</v>
       </c>
       <c r="C2">
-        <v>1241</v>
+        <v>1404</v>
       </c>
       <c r="D2">
-        <v>1633</v>
+        <v>1712</v>
       </c>
       <c r="E2">
-        <v>16259</v>
+        <v>16002</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -882,13 +882,13 @@
         <v>16817</v>
       </c>
       <c r="C3">
-        <v>952</v>
+        <v>984</v>
       </c>
       <c r="D3">
-        <v>1454</v>
+        <v>1435</v>
       </c>
       <c r="E3">
-        <v>14333</v>
+        <v>14320</v>
       </c>
       <c r="F3">
         <v>78</v>
@@ -902,16 +902,16 @@
         <v>9446</v>
       </c>
       <c r="C4">
-        <v>648</v>
+        <v>761</v>
       </c>
       <c r="D4">
-        <v>1223</v>
+        <v>1109</v>
       </c>
       <c r="E4">
-        <v>7343</v>
+        <v>7345</v>
       </c>
       <c r="F4">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
   </sheetData>
@@ -952,16 +952,16 @@
         <v>9670</v>
       </c>
       <c r="C2">
-        <v>575</v>
+        <v>626</v>
       </c>
       <c r="D2">
-        <v>521</v>
+        <v>627</v>
       </c>
       <c r="E2">
-        <v>8574</v>
+        <v>8415</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -972,13 +972,13 @@
         <v>2381</v>
       </c>
       <c r="C3">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D3">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E3">
-        <v>1886</v>
+        <v>1892</v>
       </c>
       <c r="F3">
         <v>48</v>
@@ -992,13 +992,13 @@
         <v>1735</v>
       </c>
       <c r="C4">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D4">
         <v>224</v>
       </c>
       <c r="E4">
-        <v>1392</v>
+        <v>1388</v>
       </c>
       <c r="F4">
         <v>19</v>
@@ -1012,13 +1012,13 @@
         <v>1649</v>
       </c>
       <c r="C5">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D5">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E5">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1032,13 +1032,13 @@
         <v>1500</v>
       </c>
       <c r="C6">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="D6">
-        <v>266</v>
+        <v>246</v>
       </c>
       <c r="E6">
-        <v>1104</v>
+        <v>1112</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1052,13 +1052,13 @@
         <v>1280</v>
       </c>
       <c r="C7">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="D7">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="E7">
-        <v>1025</v>
+        <v>1022</v>
       </c>
       <c r="F7">
         <v>12</v>
@@ -1072,13 +1072,13 @@
         <v>1203</v>
       </c>
       <c r="C8">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D8">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E8">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -1092,13 +1092,13 @@
         <v>1135</v>
       </c>
       <c r="C9">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D9">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="E9">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -1112,13 +1112,13 @@
         <v>977</v>
       </c>
       <c r="C10">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D10">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E10">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1132,13 +1132,13 @@
         <v>920</v>
       </c>
       <c r="C11">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="D11">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E11">
-        <v>843</v>
+        <v>837</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1172,16 +1172,16 @@
         <v>843</v>
       </c>
       <c r="C13">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="D13">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="E13">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="F13">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1192,13 +1192,13 @@
         <v>813</v>
       </c>
       <c r="C14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1212,13 +1212,13 @@
         <v>811</v>
       </c>
       <c r="C15">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D15">
         <v>60</v>
       </c>
       <c r="E15">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -1232,13 +1232,13 @@
         <v>790</v>
       </c>
       <c r="C16">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="D16">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="E16">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F16">
         <v>26</v>
@@ -1252,13 +1252,13 @@
         <v>729</v>
       </c>
       <c r="C17">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1272,13 +1272,13 @@
         <v>695</v>
       </c>
       <c r="C18">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D18">
         <v>49</v>
       </c>
       <c r="E18">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1292,13 +1292,13 @@
         <v>667</v>
       </c>
       <c r="C19">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D19">
         <v>132</v>
       </c>
       <c r="E19">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1312,13 +1312,13 @@
         <v>646</v>
       </c>
       <c r="C20">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D20">
         <v>40</v>
       </c>
       <c r="E20">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1332,10 +1332,10 @@
         <v>616</v>
       </c>
       <c r="C21">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="D21">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="E21">
         <v>316</v>
@@ -1355,13 +1355,13 @@
         <v>37</v>
       </c>
       <c r="D22">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="E22">
-        <v>480</v>
+        <v>445</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -1372,13 +1372,13 @@
         <v>601</v>
       </c>
       <c r="C23">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D23">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E23">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="F23">
         <v>18</v>
@@ -1395,10 +1395,10 @@
         <v>26</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E24">
-        <v>477</v>
+        <v>453</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1412,13 +1412,13 @@
         <v>495</v>
       </c>
       <c r="C25">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D25">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E25">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1432,13 +1432,13 @@
         <v>449</v>
       </c>
       <c r="C26">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="D26">
-        <v>138</v>
+        <v>111</v>
       </c>
       <c r="E26">
-        <v>253</v>
+        <v>268</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -1452,13 +1452,13 @@
         <v>448</v>
       </c>
       <c r="C27">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D27">
         <v>0</v>
       </c>
       <c r="E27">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -1472,13 +1472,13 @@
         <v>441</v>
       </c>
       <c r="C28">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D28">
         <v>67</v>
       </c>
       <c r="E28">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -1512,13 +1512,13 @@
         <v>402</v>
       </c>
       <c r="C30">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D30">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E30">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -1532,13 +1532,13 @@
         <v>394</v>
       </c>
       <c r="C31">
-        <v>31</v>
+        <v>85</v>
       </c>
       <c r="D31">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="E31">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F31">
         <v>0</v>
@@ -1552,13 +1552,13 @@
         <v>389</v>
       </c>
       <c r="C32">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D32">
         <v>0</v>
       </c>
       <c r="E32">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -1572,13 +1572,13 @@
         <v>316</v>
       </c>
       <c r="C33">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D33">
         <v>44</v>
       </c>
       <c r="E33">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -1592,10 +1592,10 @@
         <v>295</v>
       </c>
       <c r="C34">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="D34">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="E34">
         <v>206</v>
@@ -1612,13 +1612,13 @@
         <v>269</v>
       </c>
       <c r="C35">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D35">
         <v>77</v>
       </c>
       <c r="E35">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -1632,13 +1632,13 @@
         <v>246</v>
       </c>
       <c r="C36">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D36">
         <v>0</v>
       </c>
       <c r="E36">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -1652,13 +1652,13 @@
         <v>238</v>
       </c>
       <c r="C37">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D37">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E37">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -1672,13 +1672,13 @@
         <v>237</v>
       </c>
       <c r="C38">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D38">
         <v>81</v>
       </c>
       <c r="E38">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F38">
         <v>0</v>
@@ -1692,10 +1692,10 @@
         <v>232</v>
       </c>
       <c r="C39">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D39">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E39">
         <v>177</v>
@@ -1712,13 +1712,13 @@
         <v>224</v>
       </c>
       <c r="C40">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D40">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E40">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -1752,13 +1752,13 @@
         <v>207</v>
       </c>
       <c r="C42">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D42">
         <v>0</v>
       </c>
       <c r="E42">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F42">
         <v>0</v>
@@ -1772,10 +1772,10 @@
         <v>200</v>
       </c>
       <c r="C43">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D43">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E43">
         <v>138</v>
@@ -1852,13 +1852,13 @@
         <v>167</v>
       </c>
       <c r="C47">
+        <v>11</v>
+      </c>
+      <c r="D47">
         <v>2</v>
       </c>
-      <c r="D47">
-        <v>1</v>
-      </c>
       <c r="E47">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="F47">
         <v>0</v>
@@ -1872,13 +1872,13 @@
         <v>163</v>
       </c>
       <c r="C48">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D48">
         <v>0</v>
       </c>
       <c r="E48">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F48">
         <v>0</v>
@@ -1932,13 +1932,13 @@
         <v>151</v>
       </c>
       <c r="C51">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="D51">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="E51">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -1952,13 +1952,13 @@
         <v>150</v>
       </c>
       <c r="C52">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D52">
         <v>0</v>
       </c>
       <c r="E52">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F52">
         <v>0</v>
@@ -1972,13 +1972,13 @@
         <v>150</v>
       </c>
       <c r="C53">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D53">
         <v>0</v>
       </c>
       <c r="E53">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F53">
         <v>0</v>
@@ -2012,13 +2012,13 @@
         <v>138</v>
       </c>
       <c r="C55">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D55">
         <v>0</v>
       </c>
       <c r="E55">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F55">
         <v>0</v>
@@ -2112,13 +2112,13 @@
         <v>124</v>
       </c>
       <c r="C60">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D60">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E60">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -2232,13 +2232,13 @@
         <v>107</v>
       </c>
       <c r="C66">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D66">
         <v>0</v>
       </c>
       <c r="E66">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F66">
         <v>0</v>
@@ -2352,13 +2352,13 @@
         <v>89</v>
       </c>
       <c r="C72">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D72">
         <v>0</v>
       </c>
       <c r="E72">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F72">
         <v>0</v>
@@ -2432,13 +2432,13 @@
         <v>81</v>
       </c>
       <c r="C76">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D76">
         <v>0</v>
       </c>
       <c r="E76">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F76">
         <v>0</v>
@@ -2472,10 +2472,10 @@
         <v>80</v>
       </c>
       <c r="C78">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D78">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="E78">
         <v>7</v>
@@ -2652,13 +2652,13 @@
         <v>72</v>
       </c>
       <c r="C87">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D87">
         <v>0</v>
       </c>
       <c r="E87">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F87">
         <v>0</v>
@@ -2752,13 +2752,13 @@
         <v>65</v>
       </c>
       <c r="C92">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D92">
         <v>0</v>
       </c>
       <c r="E92">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F92">
         <v>0</v>
@@ -3072,13 +3072,13 @@
         <v>52</v>
       </c>
       <c r="C108">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D108">
         <v>0</v>
       </c>
       <c r="E108">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F108">
         <v>0</v>
@@ -3555,10 +3555,10 @@
         <v>1</v>
       </c>
       <c r="D132">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="E132">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="F132">
         <v>0</v>

--- a/resumo_busca_ativa_consolidado.xlsx
+++ b/resumo_busca_ativa_consolidado.xlsx
@@ -862,13 +862,13 @@
         <v>19133</v>
       </c>
       <c r="C2">
-        <v>1404</v>
+        <v>1432</v>
       </c>
       <c r="D2">
-        <v>1712</v>
+        <v>1691</v>
       </c>
       <c r="E2">
-        <v>16002</v>
+        <v>15995</v>
       </c>
       <c r="F2">
         <v>15</v>
@@ -882,10 +882,10 @@
         <v>16817</v>
       </c>
       <c r="C3">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="D3">
-        <v>1435</v>
+        <v>1433</v>
       </c>
       <c r="E3">
         <v>14320</v>
@@ -902,16 +902,16 @@
         <v>9446</v>
       </c>
       <c r="C4">
-        <v>761</v>
+        <v>784</v>
       </c>
       <c r="D4">
-        <v>1109</v>
+        <v>1093</v>
       </c>
       <c r="E4">
-        <v>7345</v>
+        <v>7339</v>
       </c>
       <c r="F4">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -952,13 +952,13 @@
         <v>9670</v>
       </c>
       <c r="C2">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="D2">
-        <v>627</v>
+        <v>642</v>
       </c>
       <c r="E2">
-        <v>8415</v>
+        <v>8395</v>
       </c>
       <c r="F2">
         <v>2</v>
@@ -1032,13 +1032,13 @@
         <v>1500</v>
       </c>
       <c r="C6">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="D6">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="E6">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1052,13 +1052,13 @@
         <v>1280</v>
       </c>
       <c r="C7">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="D7">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="E7">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="F7">
         <v>12</v>
@@ -1092,10 +1092,10 @@
         <v>1135</v>
       </c>
       <c r="C9">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D9">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E9">
         <v>690</v>
@@ -1172,16 +1172,16 @@
         <v>843</v>
       </c>
       <c r="C13">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D13">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E13">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="F13">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1312,13 +1312,13 @@
         <v>646</v>
       </c>
       <c r="C20">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D20">
         <v>40</v>
       </c>
       <c r="E20">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1332,13 +1332,13 @@
         <v>616</v>
       </c>
       <c r="C21">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D21">
-        <v>196</v>
+        <v>166</v>
       </c>
       <c r="E21">
-        <v>316</v>
+        <v>340</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1352,13 +1352,13 @@
         <v>611</v>
       </c>
       <c r="C22">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D22">
         <v>116</v>
       </c>
       <c r="E22">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F22">
         <v>13</v>
@@ -1372,13 +1372,13 @@
         <v>601</v>
       </c>
       <c r="C23">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D23">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E23">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F23">
         <v>18</v>
@@ -1392,13 +1392,13 @@
         <v>503</v>
       </c>
       <c r="C24">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D24">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E24">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1432,13 +1432,13 @@
         <v>449</v>
       </c>
       <c r="C26">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D26">
         <v>111</v>
       </c>
       <c r="E26">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -1532,10 +1532,10 @@
         <v>394</v>
       </c>
       <c r="C31">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="D31">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E31">
         <v>291</v>
@@ -1652,13 +1652,13 @@
         <v>238</v>
       </c>
       <c r="C37">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D37">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E37">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -1712,13 +1712,13 @@
         <v>224</v>
       </c>
       <c r="C40">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D40">
         <v>57</v>
       </c>
       <c r="E40">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -1852,13 +1852,13 @@
         <v>167</v>
       </c>
       <c r="C47">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D47">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E47">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="F47">
         <v>0</v>

--- a/resumo_busca_ativa_consolidado.xlsx
+++ b/resumo_busca_ativa_consolidado.xlsx
@@ -862,13 +862,13 @@
         <v>19133</v>
       </c>
       <c r="C2">
-        <v>1432</v>
+        <v>1364</v>
       </c>
       <c r="D2">
-        <v>1691</v>
+        <v>1706</v>
       </c>
       <c r="E2">
-        <v>15995</v>
+        <v>16048</v>
       </c>
       <c r="F2">
         <v>15</v>
@@ -885,10 +885,10 @@
         <v>986</v>
       </c>
       <c r="D3">
-        <v>1433</v>
+        <v>1413</v>
       </c>
       <c r="E3">
-        <v>14320</v>
+        <v>14340</v>
       </c>
       <c r="F3">
         <v>78</v>
@@ -902,13 +902,13 @@
         <v>9446</v>
       </c>
       <c r="C4">
-        <v>784</v>
+        <v>733</v>
       </c>
       <c r="D4">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="E4">
-        <v>7339</v>
+        <v>7396</v>
       </c>
       <c r="F4">
         <v>230</v>
@@ -952,13 +952,13 @@
         <v>9670</v>
       </c>
       <c r="C2">
-        <v>631</v>
+        <v>600</v>
       </c>
       <c r="D2">
         <v>642</v>
       </c>
       <c r="E2">
-        <v>8395</v>
+        <v>8426</v>
       </c>
       <c r="F2">
         <v>2</v>
@@ -972,13 +972,13 @@
         <v>2381</v>
       </c>
       <c r="C3">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D3">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E3">
-        <v>1892</v>
+        <v>1894</v>
       </c>
       <c r="F3">
         <v>48</v>
@@ -992,13 +992,13 @@
         <v>1735</v>
       </c>
       <c r="C4">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D4">
         <v>224</v>
       </c>
       <c r="E4">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="F4">
         <v>19</v>
@@ -1032,13 +1032,13 @@
         <v>1500</v>
       </c>
       <c r="C6">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="D6">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E6">
-        <v>1111</v>
+        <v>1129</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1052,13 +1052,13 @@
         <v>1280</v>
       </c>
       <c r="C7">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D7">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E7">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="F7">
         <v>12</v>
@@ -1072,13 +1072,13 @@
         <v>1203</v>
       </c>
       <c r="C8">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D8">
         <v>69</v>
       </c>
       <c r="E8">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -1092,13 +1092,13 @@
         <v>1135</v>
       </c>
       <c r="C9">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D9">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E9">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -1112,13 +1112,13 @@
         <v>977</v>
       </c>
       <c r="C10">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D10">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E10">
-        <v>832</v>
+        <v>837</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1132,13 +1132,13 @@
         <v>920</v>
       </c>
       <c r="C11">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D11">
         <v>31</v>
       </c>
       <c r="E11">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1152,13 +1152,13 @@
         <v>911</v>
       </c>
       <c r="C12">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="F12">
         <v>3</v>
@@ -1172,13 +1172,13 @@
         <v>843</v>
       </c>
       <c r="C13">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="D13">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E13">
-        <v>480</v>
+        <v>490</v>
       </c>
       <c r="F13">
         <v>138</v>
@@ -1192,13 +1192,13 @@
         <v>813</v>
       </c>
       <c r="C14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1212,13 +1212,13 @@
         <v>811</v>
       </c>
       <c r="C15">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D15">
         <v>60</v>
       </c>
       <c r="E15">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -1232,13 +1232,13 @@
         <v>790</v>
       </c>
       <c r="C16">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="D16">
         <v>154</v>
       </c>
       <c r="E16">
-        <v>536</v>
+        <v>551</v>
       </c>
       <c r="F16">
         <v>26</v>
@@ -1252,13 +1252,13 @@
         <v>729</v>
       </c>
       <c r="C17">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1312,13 +1312,13 @@
         <v>646</v>
       </c>
       <c r="C20">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D20">
         <v>40</v>
       </c>
       <c r="E20">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1332,13 +1332,13 @@
         <v>616</v>
       </c>
       <c r="C21">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="D21">
         <v>166</v>
       </c>
       <c r="E21">
-        <v>340</v>
+        <v>353</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1352,13 +1352,13 @@
         <v>611</v>
       </c>
       <c r="C22">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D22">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="E22">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="F22">
         <v>13</v>
@@ -1392,13 +1392,13 @@
         <v>503</v>
       </c>
       <c r="C24">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D24">
         <v>23</v>
       </c>
       <c r="E24">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1412,13 +1412,13 @@
         <v>495</v>
       </c>
       <c r="C25">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D25">
         <v>24</v>
       </c>
       <c r="E25">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1432,13 +1432,13 @@
         <v>449</v>
       </c>
       <c r="C26">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D26">
         <v>111</v>
       </c>
       <c r="E26">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -1512,13 +1512,13 @@
         <v>402</v>
       </c>
       <c r="C30">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D30">
         <v>33</v>
       </c>
       <c r="E30">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -1532,13 +1532,13 @@
         <v>394</v>
       </c>
       <c r="C31">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="D31">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="E31">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="F31">
         <v>0</v>
@@ -1592,13 +1592,13 @@
         <v>295</v>
       </c>
       <c r="C34">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="D34">
         <v>50</v>
       </c>
       <c r="E34">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="F34">
         <v>0</v>
@@ -1675,10 +1675,10 @@
         <v>10</v>
       </c>
       <c r="D38">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E38">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="F38">
         <v>0</v>
@@ -1712,13 +1712,13 @@
         <v>224</v>
       </c>
       <c r="C40">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D40">
         <v>57</v>
       </c>
       <c r="E40">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -1732,13 +1732,13 @@
         <v>223</v>
       </c>
       <c r="C41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D41">
         <v>0</v>
       </c>
       <c r="E41">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -1772,13 +1772,13 @@
         <v>200</v>
       </c>
       <c r="C43">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D43">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E43">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="F43">
         <v>0</v>
@@ -1852,13 +1852,13 @@
         <v>167</v>
       </c>
       <c r="C47">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D47">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E47">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F47">
         <v>0</v>
@@ -1872,13 +1872,13 @@
         <v>163</v>
       </c>
       <c r="C48">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D48">
         <v>0</v>
       </c>
       <c r="E48">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F48">
         <v>0</v>
@@ -2112,13 +2112,13 @@
         <v>124</v>
       </c>
       <c r="C60">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D60">
         <v>58</v>
       </c>
       <c r="E60">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -2352,13 +2352,13 @@
         <v>89</v>
       </c>
       <c r="C72">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D72">
         <v>0</v>
       </c>
       <c r="E72">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F72">
         <v>0</v>
@@ -2472,13 +2472,13 @@
         <v>80</v>
       </c>
       <c r="C78">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D78">
         <v>58</v>
       </c>
       <c r="E78">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F78">
         <v>0</v>
@@ -2492,13 +2492,13 @@
         <v>79</v>
       </c>
       <c r="C79">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D79">
         <v>0</v>
       </c>
       <c r="E79">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F79">
         <v>0</v>
@@ -3575,10 +3575,10 @@
         <v>2</v>
       </c>
       <c r="D133">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E133">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F133">
         <v>0</v>
@@ -3592,13 +3592,13 @@
         <v>33</v>
       </c>
       <c r="C134">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D134">
         <v>0</v>
       </c>
       <c r="E134">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F134">
         <v>0</v>

--- a/resumo_busca_ativa_consolidado.xlsx
+++ b/resumo_busca_ativa_consolidado.xlsx
@@ -862,16 +862,16 @@
         <v>19133</v>
       </c>
       <c r="C2">
-        <v>1364</v>
+        <v>1389</v>
       </c>
       <c r="D2">
-        <v>1706</v>
+        <v>1629</v>
       </c>
       <c r="E2">
-        <v>16048</v>
+        <v>16113</v>
       </c>
       <c r="F2">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -882,13 +882,13 @@
         <v>16817</v>
       </c>
       <c r="C3">
-        <v>986</v>
+        <v>994</v>
       </c>
       <c r="D3">
-        <v>1413</v>
+        <v>1406</v>
       </c>
       <c r="E3">
-        <v>14340</v>
+        <v>14339</v>
       </c>
       <c r="F3">
         <v>78</v>
@@ -902,16 +902,16 @@
         <v>9446</v>
       </c>
       <c r="C4">
-        <v>733</v>
+        <v>771</v>
       </c>
       <c r="D4">
-        <v>1087</v>
+        <v>1052</v>
       </c>
       <c r="E4">
-        <v>7396</v>
+        <v>7377</v>
       </c>
       <c r="F4">
-        <v>230</v>
+        <v>246</v>
       </c>
     </row>
   </sheetData>
@@ -952,13 +952,13 @@
         <v>9670</v>
       </c>
       <c r="C2">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="D2">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="E2">
-        <v>8426</v>
+        <v>8427</v>
       </c>
       <c r="F2">
         <v>2</v>
@@ -972,13 +972,13 @@
         <v>2381</v>
       </c>
       <c r="C3">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D3">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E3">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F3">
         <v>48</v>
@@ -992,13 +992,13 @@
         <v>1735</v>
       </c>
       <c r="C4">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D4">
         <v>224</v>
       </c>
       <c r="E4">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="F4">
         <v>19</v>
@@ -1032,13 +1032,13 @@
         <v>1500</v>
       </c>
       <c r="C6">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D6">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E6">
-        <v>1129</v>
+        <v>1126</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1052,13 +1052,13 @@
         <v>1280</v>
       </c>
       <c r="C7">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="D7">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="E7">
-        <v>1020</v>
+        <v>1025</v>
       </c>
       <c r="F7">
         <v>12</v>
@@ -1072,13 +1072,13 @@
         <v>1203</v>
       </c>
       <c r="C8">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D8">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>1075</v>
+        <v>1142</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>100</v>
       </c>
       <c r="D9">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E9">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -1132,10 +1132,10 @@
         <v>920</v>
       </c>
       <c r="C11">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D11">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E11">
         <v>840</v>
@@ -1172,13 +1172,13 @@
         <v>843</v>
       </c>
       <c r="C13">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D13">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="E13">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="F13">
         <v>138</v>
@@ -1292,13 +1292,13 @@
         <v>667</v>
       </c>
       <c r="C19">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D19">
         <v>132</v>
       </c>
       <c r="E19">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1312,13 +1312,13 @@
         <v>646</v>
       </c>
       <c r="C20">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D20">
         <v>40</v>
       </c>
       <c r="E20">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1332,13 +1332,13 @@
         <v>616</v>
       </c>
       <c r="C21">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D21">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E21">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1352,16 +1352,16 @@
         <v>611</v>
       </c>
       <c r="C22">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D22">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="E22">
-        <v>448</v>
+        <v>425</v>
       </c>
       <c r="F22">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -1372,13 +1372,13 @@
         <v>601</v>
       </c>
       <c r="C23">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="D23">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="E23">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="F23">
         <v>18</v>
@@ -1392,13 +1392,13 @@
         <v>503</v>
       </c>
       <c r="C24">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D24">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E24">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1432,13 +1432,13 @@
         <v>449</v>
       </c>
       <c r="C26">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D26">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E26">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -1532,13 +1532,13 @@
         <v>394</v>
       </c>
       <c r="C31">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D31">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="E31">
-        <v>295</v>
+        <v>318</v>
       </c>
       <c r="F31">
         <v>0</v>
@@ -1592,10 +1592,10 @@
         <v>295</v>
       </c>
       <c r="C34">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D34">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E34">
         <v>218</v>
@@ -1692,10 +1692,10 @@
         <v>232</v>
       </c>
       <c r="C39">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D39">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E39">
         <v>177</v>
@@ -1772,10 +1772,10 @@
         <v>200</v>
       </c>
       <c r="C43">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D43">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E43">
         <v>149</v>
@@ -1815,13 +1815,13 @@
         <v>5</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E45">
         <v>166</v>
       </c>
       <c r="F45">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -1915,10 +1915,10 @@
         <v>10</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="E50">
-        <v>144</v>
+        <v>117</v>
       </c>
       <c r="F50">
         <v>0</v>
@@ -1932,10 +1932,10 @@
         <v>151</v>
       </c>
       <c r="C51">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D51">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E51">
         <v>57</v>
@@ -2075,10 +2075,10 @@
         <v>4</v>
       </c>
       <c r="D58">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E58">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="F58">
         <v>0</v>
@@ -2112,10 +2112,10 @@
         <v>124</v>
       </c>
       <c r="C60">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D60">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E60">
         <v>50</v>
@@ -2258,10 +2258,10 @@
         <v>0</v>
       </c>
       <c r="E67">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="F67">
-        <v>15</v>
+        <v>41</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -2475,10 +2475,10 @@
         <v>4</v>
       </c>
       <c r="D78">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="E78">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F78">
         <v>0</v>
@@ -2992,13 +2992,13 @@
         <v>54</v>
       </c>
       <c r="C104">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D104">
         <v>0</v>
       </c>
       <c r="E104">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F104">
         <v>0</v>

--- a/resumo_busca_ativa_consolidado.xlsx
+++ b/resumo_busca_ativa_consolidado.xlsx
@@ -862,16 +862,16 @@
         <v>19133</v>
       </c>
       <c r="C2">
-        <v>1389</v>
+        <v>1423</v>
       </c>
       <c r="D2">
-        <v>1629</v>
+        <v>1601</v>
       </c>
       <c r="E2">
-        <v>16113</v>
+        <v>16108</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -882,13 +882,13 @@
         <v>16817</v>
       </c>
       <c r="C3">
-        <v>994</v>
+        <v>1016</v>
       </c>
       <c r="D3">
-        <v>1406</v>
+        <v>1391</v>
       </c>
       <c r="E3">
-        <v>14339</v>
+        <v>14332</v>
       </c>
       <c r="F3">
         <v>78</v>
@@ -902,13 +902,13 @@
         <v>9446</v>
       </c>
       <c r="C4">
-        <v>771</v>
+        <v>791</v>
       </c>
       <c r="D4">
-        <v>1052</v>
+        <v>1045</v>
       </c>
       <c r="E4">
-        <v>7377</v>
+        <v>7364</v>
       </c>
       <c r="F4">
         <v>246</v>
@@ -952,16 +952,16 @@
         <v>9670</v>
       </c>
       <c r="C2">
-        <v>603</v>
+        <v>615</v>
       </c>
       <c r="D2">
         <v>638</v>
       </c>
       <c r="E2">
-        <v>8427</v>
+        <v>8417</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -972,13 +972,13 @@
         <v>2381</v>
       </c>
       <c r="C3">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D3">
         <v>281</v>
       </c>
       <c r="E3">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="F3">
         <v>48</v>
@@ -992,13 +992,13 @@
         <v>1735</v>
       </c>
       <c r="C4">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D4">
         <v>224</v>
       </c>
       <c r="E4">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="F4">
         <v>19</v>
@@ -1032,13 +1032,13 @@
         <v>1500</v>
       </c>
       <c r="C6">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D6">
         <v>239</v>
       </c>
       <c r="E6">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1072,13 +1072,13 @@
         <v>1203</v>
       </c>
       <c r="C8">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -1132,13 +1132,13 @@
         <v>920</v>
       </c>
       <c r="C11">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D11">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E11">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1172,13 +1172,13 @@
         <v>843</v>
       </c>
       <c r="C13">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D13">
         <v>127</v>
       </c>
       <c r="E13">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F13">
         <v>138</v>
@@ -1232,13 +1232,13 @@
         <v>790</v>
       </c>
       <c r="C16">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D16">
         <v>154</v>
       </c>
       <c r="E16">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="F16">
         <v>26</v>
@@ -1272,13 +1272,13 @@
         <v>695</v>
       </c>
       <c r="C18">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D18">
         <v>49</v>
       </c>
       <c r="E18">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1332,10 +1332,10 @@
         <v>616</v>
       </c>
       <c r="C21">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D21">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E21">
         <v>356</v>
@@ -1352,13 +1352,13 @@
         <v>611</v>
       </c>
       <c r="C22">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="D22">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="E22">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1375,10 +1375,10 @@
         <v>57</v>
       </c>
       <c r="D23">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E23">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F23">
         <v>18</v>
@@ -1395,10 +1395,10 @@
         <v>34</v>
       </c>
       <c r="D24">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E24">
-        <v>452</v>
+        <v>469</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1412,10 +1412,10 @@
         <v>495</v>
       </c>
       <c r="C25">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="D25">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="E25">
         <v>435</v>
@@ -1432,13 +1432,13 @@
         <v>449</v>
       </c>
       <c r="C26">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D26">
         <v>107</v>
       </c>
       <c r="E26">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -1452,13 +1452,13 @@
         <v>448</v>
       </c>
       <c r="C27">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D27">
         <v>0</v>
       </c>
       <c r="E27">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -1512,13 +1512,13 @@
         <v>402</v>
       </c>
       <c r="C30">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D30">
         <v>33</v>
       </c>
       <c r="E30">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -1532,13 +1532,13 @@
         <v>394</v>
       </c>
       <c r="C31">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D31">
         <v>1</v>
       </c>
       <c r="E31">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F31">
         <v>0</v>
@@ -1572,13 +1572,13 @@
         <v>316</v>
       </c>
       <c r="C33">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D33">
         <v>44</v>
       </c>
       <c r="E33">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -1592,13 +1592,13 @@
         <v>295</v>
       </c>
       <c r="C34">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D34">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="E34">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F34">
         <v>0</v>
@@ -1652,10 +1652,10 @@
         <v>238</v>
       </c>
       <c r="C37">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D37">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E37">
         <v>173</v>
@@ -1692,16 +1692,16 @@
         <v>232</v>
       </c>
       <c r="C39">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D39">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E39">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F39">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -1772,13 +1772,13 @@
         <v>200</v>
       </c>
       <c r="C43">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D43">
         <v>36</v>
       </c>
       <c r="E43">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F43">
         <v>0</v>
@@ -1812,13 +1812,13 @@
         <v>187</v>
       </c>
       <c r="C45">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D45">
         <v>10</v>
       </c>
       <c r="E45">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F45">
         <v>6</v>
@@ -1932,13 +1932,13 @@
         <v>151</v>
       </c>
       <c r="C51">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D51">
         <v>55</v>
       </c>
       <c r="E51">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -2392,13 +2392,13 @@
         <v>86</v>
       </c>
       <c r="C74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D74">
         <v>0</v>
       </c>
       <c r="E74">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F74">
         <v>0</v>
@@ -2532,13 +2532,13 @@
         <v>76</v>
       </c>
       <c r="C81">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D81">
         <v>0</v>
       </c>
       <c r="E81">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F81">
         <v>0</v>
@@ -2672,13 +2672,13 @@
         <v>68</v>
       </c>
       <c r="C88">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D88">
         <v>0</v>
       </c>
       <c r="E88">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F88">
         <v>0</v>

--- a/resumo_busca_ativa_consolidado.xlsx
+++ b/resumo_busca_ativa_consolidado.xlsx
@@ -862,16 +862,16 @@
         <v>19133</v>
       </c>
       <c r="C2">
-        <v>1423</v>
+        <v>1425</v>
       </c>
       <c r="D2">
-        <v>1601</v>
+        <v>1596</v>
       </c>
       <c r="E2">
-        <v>16108</v>
+        <v>16112</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -882,13 +882,13 @@
         <v>16817</v>
       </c>
       <c r="C3">
-        <v>1016</v>
+        <v>1005</v>
       </c>
       <c r="D3">
-        <v>1391</v>
+        <v>1389</v>
       </c>
       <c r="E3">
-        <v>14332</v>
+        <v>14345</v>
       </c>
       <c r="F3">
         <v>78</v>
@@ -902,13 +902,13 @@
         <v>9446</v>
       </c>
       <c r="C4">
-        <v>791</v>
+        <v>777</v>
       </c>
       <c r="D4">
-        <v>1045</v>
+        <v>1041</v>
       </c>
       <c r="E4">
-        <v>7364</v>
+        <v>7382</v>
       </c>
       <c r="F4">
         <v>246</v>
@@ -952,13 +952,13 @@
         <v>9670</v>
       </c>
       <c r="C2">
-        <v>615</v>
+        <v>622</v>
       </c>
       <c r="D2">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="E2">
-        <v>8417</v>
+        <v>8413</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -972,13 +972,13 @@
         <v>2381</v>
       </c>
       <c r="C3">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D3">
         <v>281</v>
       </c>
       <c r="E3">
-        <v>1892</v>
+        <v>1894</v>
       </c>
       <c r="F3">
         <v>48</v>
@@ -1012,13 +1012,13 @@
         <v>1649</v>
       </c>
       <c r="C5">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D5">
         <v>241</v>
       </c>
       <c r="E5">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1032,10 +1032,10 @@
         <v>1500</v>
       </c>
       <c r="C6">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D6">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E6">
         <v>1124</v>
@@ -1052,13 +1052,13 @@
         <v>1280</v>
       </c>
       <c r="C7">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D7">
         <v>85</v>
       </c>
       <c r="E7">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="F7">
         <v>12</v>
@@ -1072,13 +1072,13 @@
         <v>1203</v>
       </c>
       <c r="C8">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -1112,13 +1112,13 @@
         <v>977</v>
       </c>
       <c r="C10">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D10">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E10">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1132,13 +1132,13 @@
         <v>920</v>
       </c>
       <c r="C11">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D11">
         <v>29</v>
       </c>
       <c r="E11">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1152,13 +1152,13 @@
         <v>911</v>
       </c>
       <c r="C12">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="F12">
         <v>3</v>
@@ -1172,13 +1172,13 @@
         <v>843</v>
       </c>
       <c r="C13">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D13">
         <v>127</v>
       </c>
       <c r="E13">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="F13">
         <v>138</v>
@@ -1252,13 +1252,13 @@
         <v>729</v>
       </c>
       <c r="C17">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1332,13 +1332,13 @@
         <v>616</v>
       </c>
       <c r="C21">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D21">
         <v>161</v>
       </c>
       <c r="E21">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1352,13 +1352,13 @@
         <v>611</v>
       </c>
       <c r="C22">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D22">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E22">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1372,13 +1372,13 @@
         <v>601</v>
       </c>
       <c r="C23">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D23">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E23">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="F23">
         <v>18</v>
@@ -1392,13 +1392,13 @@
         <v>503</v>
       </c>
       <c r="C24">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D24">
         <v>0</v>
       </c>
       <c r="E24">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1412,13 +1412,13 @@
         <v>495</v>
       </c>
       <c r="C25">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="D25">
         <v>9</v>
       </c>
       <c r="E25">
-        <v>435</v>
+        <v>449</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1532,13 +1532,13 @@
         <v>394</v>
       </c>
       <c r="C31">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D31">
         <v>1</v>
       </c>
       <c r="E31">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F31">
         <v>0</v>
@@ -1592,13 +1592,13 @@
         <v>295</v>
       </c>
       <c r="C34">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="D34">
         <v>41</v>
       </c>
       <c r="E34">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="F34">
         <v>0</v>
@@ -1692,16 +1692,16 @@
         <v>232</v>
       </c>
       <c r="C39">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D39">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E39">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F39">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -1712,13 +1712,13 @@
         <v>224</v>
       </c>
       <c r="C40">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D40">
         <v>57</v>
       </c>
       <c r="E40">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -1772,13 +1772,13 @@
         <v>200</v>
       </c>
       <c r="C43">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D43">
         <v>36</v>
       </c>
       <c r="E43">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="F43">
         <v>0</v>
@@ -1852,13 +1852,13 @@
         <v>167</v>
       </c>
       <c r="C47">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D47">
         <v>1</v>
       </c>
       <c r="E47">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F47">
         <v>0</v>
@@ -1872,13 +1872,13 @@
         <v>163</v>
       </c>
       <c r="C48">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D48">
         <v>0</v>
       </c>
       <c r="E48">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F48">
         <v>0</v>
@@ -2112,10 +2112,10 @@
         <v>124</v>
       </c>
       <c r="C60">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D60">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E60">
         <v>50</v>
@@ -2272,13 +2272,13 @@
         <v>103</v>
       </c>
       <c r="C68">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D68">
         <v>0</v>
       </c>
       <c r="E68">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F68">
         <v>0</v>
@@ -2392,13 +2392,13 @@
         <v>86</v>
       </c>
       <c r="C74">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D74">
         <v>0</v>
       </c>
       <c r="E74">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F74">
         <v>0</v>
@@ -2752,13 +2752,13 @@
         <v>65</v>
       </c>
       <c r="C92">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D92">
         <v>0</v>
       </c>
       <c r="E92">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F92">
         <v>0</v>
@@ -3075,10 +3075,10 @@
         <v>5</v>
       </c>
       <c r="D108">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E108">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F108">
         <v>0</v>
@@ -3392,13 +3392,13 @@
         <v>38</v>
       </c>
       <c r="C124">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D124">
         <v>0</v>
       </c>
       <c r="E124">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F124">
         <v>0</v>

--- a/resumo_busca_ativa_consolidado.xlsx
+++ b/resumo_busca_ativa_consolidado.xlsx
@@ -862,16 +862,16 @@
         <v>19133</v>
       </c>
       <c r="C2">
-        <v>1425</v>
+        <v>1446</v>
       </c>
       <c r="D2">
-        <v>1596</v>
+        <v>1470</v>
       </c>
       <c r="E2">
-        <v>16112</v>
+        <v>16212</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -882,13 +882,13 @@
         <v>16817</v>
       </c>
       <c r="C3">
-        <v>1005</v>
+        <v>1015</v>
       </c>
       <c r="D3">
-        <v>1389</v>
+        <v>1419</v>
       </c>
       <c r="E3">
-        <v>14345</v>
+        <v>14305</v>
       </c>
       <c r="F3">
         <v>78</v>
@@ -902,13 +902,13 @@
         <v>9446</v>
       </c>
       <c r="C4">
-        <v>777</v>
+        <v>791</v>
       </c>
       <c r="D4">
-        <v>1041</v>
+        <v>1055</v>
       </c>
       <c r="E4">
-        <v>7382</v>
+        <v>7354</v>
       </c>
       <c r="F4">
         <v>246</v>
@@ -952,16 +952,16 @@
         <v>9670</v>
       </c>
       <c r="C2">
-        <v>622</v>
+        <v>629</v>
       </c>
       <c r="D2">
-        <v>635</v>
+        <v>538</v>
       </c>
       <c r="E2">
-        <v>8413</v>
+        <v>8498</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1012,13 +1012,13 @@
         <v>1649</v>
       </c>
       <c r="C5">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D5">
         <v>241</v>
       </c>
       <c r="E5">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1035,10 +1035,10 @@
         <v>138</v>
       </c>
       <c r="D6">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E6">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1052,13 +1052,13 @@
         <v>1280</v>
       </c>
       <c r="C7">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="D7">
-        <v>85</v>
+        <v>117</v>
       </c>
       <c r="E7">
-        <v>1027</v>
+        <v>986</v>
       </c>
       <c r="F7">
         <v>12</v>
@@ -1092,13 +1092,13 @@
         <v>1135</v>
       </c>
       <c r="C9">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D9">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="E9">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -1112,13 +1112,13 @@
         <v>977</v>
       </c>
       <c r="C10">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D10">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="E10">
-        <v>838</v>
+        <v>803</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1132,13 +1132,13 @@
         <v>920</v>
       </c>
       <c r="C11">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D11">
         <v>29</v>
       </c>
       <c r="E11">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1152,13 +1152,13 @@
         <v>911</v>
       </c>
       <c r="C12">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="F12">
         <v>3</v>
@@ -1175,10 +1175,10 @@
         <v>81</v>
       </c>
       <c r="D13">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="E13">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="F13">
         <v>138</v>
@@ -1232,13 +1232,13 @@
         <v>790</v>
       </c>
       <c r="C16">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D16">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E16">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="F16">
         <v>26</v>
@@ -1252,13 +1252,13 @@
         <v>729</v>
       </c>
       <c r="C17">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1295,10 +1295,10 @@
         <v>61</v>
       </c>
       <c r="D19">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E19">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1332,13 +1332,13 @@
         <v>616</v>
       </c>
       <c r="C21">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D21">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="E21">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1352,13 +1352,13 @@
         <v>611</v>
       </c>
       <c r="C22">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D22">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E22">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1372,13 +1372,13 @@
         <v>601</v>
       </c>
       <c r="C23">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D23">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="E23">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="F23">
         <v>18</v>
@@ -1412,13 +1412,13 @@
         <v>495</v>
       </c>
       <c r="C25">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D25">
         <v>9</v>
       </c>
       <c r="E25">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1432,13 +1432,13 @@
         <v>449</v>
       </c>
       <c r="C26">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D26">
         <v>107</v>
       </c>
       <c r="E26">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -1452,13 +1452,13 @@
         <v>448</v>
       </c>
       <c r="C27">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D27">
         <v>0</v>
       </c>
       <c r="E27">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -1472,13 +1472,13 @@
         <v>441</v>
       </c>
       <c r="C28">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D28">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E28">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -1512,13 +1512,13 @@
         <v>402</v>
       </c>
       <c r="C30">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D30">
         <v>33</v>
       </c>
       <c r="E30">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -1695,10 +1695,10 @@
         <v>24</v>
       </c>
       <c r="D39">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E39">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -1732,13 +1732,13 @@
         <v>223</v>
       </c>
       <c r="C41">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D41">
         <v>0</v>
       </c>
       <c r="E41">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -1932,13 +1932,13 @@
         <v>151</v>
       </c>
       <c r="C51">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D51">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E51">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -2072,13 +2072,13 @@
         <v>127</v>
       </c>
       <c r="C58">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D58">
         <v>0</v>
       </c>
       <c r="E58">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F58">
         <v>0</v>
@@ -2115,10 +2115,10 @@
         <v>18</v>
       </c>
       <c r="D60">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E60">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -2372,13 +2372,13 @@
         <v>88</v>
       </c>
       <c r="C73">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D73">
         <v>0</v>
       </c>
       <c r="E73">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F73">
         <v>0</v>
@@ -2475,10 +2475,10 @@
         <v>4</v>
       </c>
       <c r="D78">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E78">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F78">
         <v>0</v>
@@ -3075,10 +3075,10 @@
         <v>5</v>
       </c>
       <c r="D108">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E108">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F108">
         <v>0</v>

--- a/resumo_busca_ativa_consolidado.xlsx
+++ b/resumo_busca_ativa_consolidado.xlsx
@@ -862,16 +862,16 @@
         <v>19133</v>
       </c>
       <c r="C2">
-        <v>1446</v>
+        <v>1486</v>
       </c>
       <c r="D2">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="E2">
-        <v>16212</v>
+        <v>16176</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -882,13 +882,13 @@
         <v>16817</v>
       </c>
       <c r="C3">
-        <v>1015</v>
+        <v>1046</v>
       </c>
       <c r="D3">
-        <v>1419</v>
+        <v>1406</v>
       </c>
       <c r="E3">
-        <v>14305</v>
+        <v>14287</v>
       </c>
       <c r="F3">
         <v>78</v>
@@ -902,16 +902,16 @@
         <v>9446</v>
       </c>
       <c r="C4">
-        <v>791</v>
+        <v>815</v>
       </c>
       <c r="D4">
-        <v>1055</v>
+        <v>1044</v>
       </c>
       <c r="E4">
-        <v>7354</v>
+        <v>7340</v>
       </c>
       <c r="F4">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
   </sheetData>
@@ -952,16 +952,16 @@
         <v>9670</v>
       </c>
       <c r="C2">
-        <v>629</v>
+        <v>644</v>
       </c>
       <c r="D2">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="E2">
-        <v>8498</v>
+        <v>8491</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -972,13 +972,13 @@
         <v>2381</v>
       </c>
       <c r="C3">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="D3">
         <v>281</v>
       </c>
       <c r="E3">
-        <v>1894</v>
+        <v>1888</v>
       </c>
       <c r="F3">
         <v>48</v>
@@ -992,13 +992,13 @@
         <v>1735</v>
       </c>
       <c r="C4">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D4">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E4">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="F4">
         <v>19</v>
@@ -1012,13 +1012,13 @@
         <v>1649</v>
       </c>
       <c r="C5">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D5">
         <v>241</v>
       </c>
       <c r="E5">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1032,13 +1032,13 @@
         <v>1500</v>
       </c>
       <c r="C6">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="D6">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E6">
-        <v>1125</v>
+        <v>1121</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1052,16 +1052,16 @@
         <v>1280</v>
       </c>
       <c r="C7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D7">
         <v>117</v>
       </c>
       <c r="E7">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="F7">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1072,13 +1072,13 @@
         <v>1203</v>
       </c>
       <c r="C8">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -1092,13 +1092,13 @@
         <v>1135</v>
       </c>
       <c r="C9">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D9">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E9">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -1112,13 +1112,13 @@
         <v>977</v>
       </c>
       <c r="C10">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="D10">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E10">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1132,13 +1132,13 @@
         <v>920</v>
       </c>
       <c r="C11">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D11">
         <v>29</v>
       </c>
       <c r="E11">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1172,13 +1172,13 @@
         <v>843</v>
       </c>
       <c r="C13">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="D13">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="E13">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="F13">
         <v>138</v>
@@ -1192,13 +1192,13 @@
         <v>813</v>
       </c>
       <c r="C14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1292,13 +1292,13 @@
         <v>667</v>
       </c>
       <c r="C19">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19">
         <v>129</v>
       </c>
       <c r="E19">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1332,13 +1332,13 @@
         <v>616</v>
       </c>
       <c r="C21">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D21">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E21">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1352,13 +1352,13 @@
         <v>611</v>
       </c>
       <c r="C22">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D22">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E22">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1372,13 +1372,13 @@
         <v>601</v>
       </c>
       <c r="C23">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D23">
         <v>85</v>
       </c>
       <c r="E23">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F23">
         <v>18</v>
@@ -1432,13 +1432,13 @@
         <v>449</v>
       </c>
       <c r="C26">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D26">
         <v>107</v>
       </c>
       <c r="E26">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -1452,13 +1452,13 @@
         <v>448</v>
       </c>
       <c r="C27">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D27">
         <v>0</v>
       </c>
       <c r="E27">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -1472,10 +1472,10 @@
         <v>441</v>
       </c>
       <c r="C28">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D28">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E28">
         <v>346</v>
@@ -1512,13 +1512,13 @@
         <v>402</v>
       </c>
       <c r="C30">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D30">
         <v>33</v>
       </c>
       <c r="E30">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -1532,13 +1532,13 @@
         <v>394</v>
       </c>
       <c r="C31">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D31">
         <v>1</v>
       </c>
       <c r="E31">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F31">
         <v>0</v>
@@ -1592,13 +1592,13 @@
         <v>295</v>
       </c>
       <c r="C34">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D34">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E34">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F34">
         <v>0</v>
@@ -1632,13 +1632,13 @@
         <v>246</v>
       </c>
       <c r="C36">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D36">
         <v>0</v>
       </c>
       <c r="E36">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -1675,10 +1675,10 @@
         <v>10</v>
       </c>
       <c r="D38">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="E38">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="F38">
         <v>0</v>
@@ -1695,10 +1695,10 @@
         <v>24</v>
       </c>
       <c r="D39">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="E39">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -1712,13 +1712,13 @@
         <v>224</v>
       </c>
       <c r="C40">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D40">
         <v>57</v>
       </c>
       <c r="E40">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -1772,13 +1772,13 @@
         <v>200</v>
       </c>
       <c r="C43">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D43">
         <v>36</v>
       </c>
       <c r="E43">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F43">
         <v>0</v>
@@ -1792,13 +1792,13 @@
         <v>194</v>
       </c>
       <c r="C44">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D44">
         <v>0</v>
       </c>
       <c r="E44">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F44">
         <v>0</v>
@@ -1812,13 +1812,13 @@
         <v>187</v>
       </c>
       <c r="C45">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D45">
         <v>10</v>
       </c>
       <c r="E45">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F45">
         <v>6</v>
@@ -1872,13 +1872,13 @@
         <v>163</v>
       </c>
       <c r="C48">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D48">
         <v>0</v>
       </c>
       <c r="E48">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="F48">
         <v>0</v>
@@ -1912,13 +1912,13 @@
         <v>154</v>
       </c>
       <c r="C50">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D50">
         <v>27</v>
       </c>
       <c r="E50">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F50">
         <v>0</v>
@@ -2072,13 +2072,13 @@
         <v>127</v>
       </c>
       <c r="C58">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D58">
         <v>0</v>
       </c>
       <c r="E58">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F58">
         <v>0</v>
@@ -2472,10 +2472,10 @@
         <v>80</v>
       </c>
       <c r="C78">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D78">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E78">
         <v>30</v>
@@ -2532,13 +2532,13 @@
         <v>76</v>
       </c>
       <c r="C81">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D81">
         <v>0</v>
       </c>
       <c r="E81">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F81">
         <v>0</v>
@@ -2552,13 +2552,13 @@
         <v>76</v>
       </c>
       <c r="C82">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D82">
         <v>0</v>
       </c>
       <c r="E82">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F82">
         <v>0</v>

--- a/resumo_busca_ativa_consolidado.xlsx
+++ b/resumo_busca_ativa_consolidado.xlsx
@@ -862,13 +862,13 @@
         <v>19133</v>
       </c>
       <c r="C2">
-        <v>1486</v>
+        <v>1474</v>
       </c>
       <c r="D2">
-        <v>1471</v>
+        <v>1515</v>
       </c>
       <c r="E2">
-        <v>16176</v>
+        <v>16144</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -882,13 +882,13 @@
         <v>16817</v>
       </c>
       <c r="C3">
-        <v>1046</v>
+        <v>1043</v>
       </c>
       <c r="D3">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="E3">
-        <v>14287</v>
+        <v>14292</v>
       </c>
       <c r="F3">
         <v>78</v>
@@ -902,16 +902,16 @@
         <v>9446</v>
       </c>
       <c r="C4">
-        <v>815</v>
+        <v>810</v>
       </c>
       <c r="D4">
-        <v>1044</v>
+        <v>1041</v>
       </c>
       <c r="E4">
-        <v>7340</v>
+        <v>7349</v>
       </c>
       <c r="F4">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
   </sheetData>
@@ -952,13 +952,13 @@
         <v>9670</v>
       </c>
       <c r="C2">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="D2">
-        <v>535</v>
+        <v>575</v>
       </c>
       <c r="E2">
-        <v>8491</v>
+        <v>8457</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -1035,10 +1035,10 @@
         <v>143</v>
       </c>
       <c r="D6">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E6">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1055,13 +1055,13 @@
         <v>166</v>
       </c>
       <c r="D7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E7">
         <v>984</v>
       </c>
       <c r="F7">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1092,13 +1092,13 @@
         <v>1135</v>
       </c>
       <c r="C9">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D9">
         <v>338</v>
       </c>
       <c r="E9">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -1112,13 +1112,13 @@
         <v>977</v>
       </c>
       <c r="C10">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D10">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E10">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1172,13 +1172,13 @@
         <v>843</v>
       </c>
       <c r="C13">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D13">
         <v>111</v>
       </c>
       <c r="E13">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="F13">
         <v>138</v>
@@ -1235,10 +1235,10 @@
         <v>62</v>
       </c>
       <c r="D16">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E16">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="F16">
         <v>26</v>
@@ -1332,13 +1332,13 @@
         <v>616</v>
       </c>
       <c r="C21">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D21">
         <v>152</v>
       </c>
       <c r="E21">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1352,13 +1352,13 @@
         <v>611</v>
       </c>
       <c r="C22">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D22">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="E22">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1592,10 +1592,10 @@
         <v>295</v>
       </c>
       <c r="C34">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D34">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E34">
         <v>224</v>
@@ -1695,10 +1695,10 @@
         <v>24</v>
       </c>
       <c r="D39">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E39">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -2472,13 +2472,13 @@
         <v>80</v>
       </c>
       <c r="C78">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D78">
         <v>36</v>
       </c>
       <c r="E78">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F78">
         <v>0</v>
@@ -3452,13 +3452,13 @@
         <v>37</v>
       </c>
       <c r="C127">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D127">
         <v>0</v>
       </c>
       <c r="E127">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F127">
         <v>0</v>
@@ -3532,13 +3532,13 @@
         <v>35</v>
       </c>
       <c r="C131">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D131">
         <v>0</v>
       </c>
       <c r="E131">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F131">
         <v>0</v>
@@ -3575,10 +3575,10 @@
         <v>2</v>
       </c>
       <c r="D133">
+        <v>21</v>
+      </c>
+      <c r="E133">
         <v>11</v>
-      </c>
-      <c r="E133">
-        <v>21</v>
       </c>
       <c r="F133">
         <v>0</v>

--- a/resumo_busca_ativa_consolidado.xlsx
+++ b/resumo_busca_ativa_consolidado.xlsx
@@ -862,16 +862,16 @@
         <v>19133</v>
       </c>
       <c r="C2">
-        <v>1474</v>
+        <v>1492</v>
       </c>
       <c r="D2">
-        <v>1515</v>
+        <v>1439</v>
       </c>
       <c r="E2">
-        <v>16144</v>
+        <v>16197</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -882,10 +882,10 @@
         <v>16817</v>
       </c>
       <c r="C3">
-        <v>1043</v>
+        <v>1056</v>
       </c>
       <c r="D3">
-        <v>1404</v>
+        <v>1391</v>
       </c>
       <c r="E3">
         <v>14292</v>
@@ -902,13 +902,13 @@
         <v>9446</v>
       </c>
       <c r="C4">
-        <v>810</v>
+        <v>828</v>
       </c>
       <c r="D4">
-        <v>1041</v>
+        <v>1013</v>
       </c>
       <c r="E4">
-        <v>7349</v>
+        <v>7359</v>
       </c>
       <c r="F4">
         <v>246</v>
@@ -952,13 +952,13 @@
         <v>9670</v>
       </c>
       <c r="C2">
-        <v>638</v>
+        <v>647</v>
       </c>
       <c r="D2">
-        <v>575</v>
+        <v>560</v>
       </c>
       <c r="E2">
-        <v>8457</v>
+        <v>8463</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -972,13 +972,13 @@
         <v>2381</v>
       </c>
       <c r="C3">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D3">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="E3">
-        <v>1888</v>
+        <v>1895</v>
       </c>
       <c r="F3">
         <v>48</v>
@@ -1032,13 +1032,13 @@
         <v>1500</v>
       </c>
       <c r="C6">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D6">
         <v>234</v>
       </c>
       <c r="E6">
-        <v>1122</v>
+        <v>1120</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1052,13 +1052,13 @@
         <v>1280</v>
       </c>
       <c r="C7">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="D7">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="E7">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="F7">
         <v>12</v>
@@ -1078,10 +1078,10 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>1141</v>
+        <v>1136</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1095,10 +1095,10 @@
         <v>105</v>
       </c>
       <c r="D9">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E9">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -1112,13 +1112,13 @@
         <v>977</v>
       </c>
       <c r="C10">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D10">
         <v>80</v>
       </c>
       <c r="E10">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1132,13 +1132,13 @@
         <v>920</v>
       </c>
       <c r="C11">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D11">
         <v>29</v>
       </c>
       <c r="E11">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1175,10 +1175,10 @@
         <v>85</v>
       </c>
       <c r="D13">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E13">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="F13">
         <v>138</v>
@@ -1252,13 +1252,13 @@
         <v>729</v>
       </c>
       <c r="C17">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1292,13 +1292,13 @@
         <v>667</v>
       </c>
       <c r="C19">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D19">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="E19">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1335,10 +1335,10 @@
         <v>103</v>
       </c>
       <c r="D21">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="E21">
-        <v>361</v>
+        <v>379</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1355,10 +1355,10 @@
         <v>53</v>
       </c>
       <c r="D22">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E22">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1372,13 +1372,13 @@
         <v>601</v>
       </c>
       <c r="C23">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D23">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="E23">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="F23">
         <v>18</v>
@@ -1412,13 +1412,13 @@
         <v>495</v>
       </c>
       <c r="C25">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D25">
         <v>9</v>
       </c>
       <c r="E25">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1432,13 +1432,13 @@
         <v>449</v>
       </c>
       <c r="C26">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D26">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E26">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -1632,13 +1632,13 @@
         <v>246</v>
       </c>
       <c r="C36">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D36">
         <v>0</v>
       </c>
       <c r="E36">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -1695,10 +1695,10 @@
         <v>24</v>
       </c>
       <c r="D39">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E39">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -1715,10 +1715,10 @@
         <v>33</v>
       </c>
       <c r="D40">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E40">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>13</v>
       </c>
       <c r="D43">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E43">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F43">
         <v>0</v>
@@ -1932,10 +1932,10 @@
         <v>151</v>
       </c>
       <c r="C51">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D51">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E51">
         <v>54</v>
@@ -2112,13 +2112,13 @@
         <v>124</v>
       </c>
       <c r="C60">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D60">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E60">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -2132,13 +2132,13 @@
         <v>123</v>
       </c>
       <c r="C61">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D61">
         <v>0</v>
       </c>
       <c r="E61">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F61">
         <v>0</v>
@@ -2452,13 +2452,13 @@
         <v>81</v>
       </c>
       <c r="C77">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D77">
         <v>0</v>
       </c>
       <c r="E77">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F77">
         <v>0</v>
@@ -2472,13 +2472,13 @@
         <v>80</v>
       </c>
       <c r="C78">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D78">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="E78">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="F78">
         <v>0</v>
@@ -2752,13 +2752,13 @@
         <v>65</v>
       </c>
       <c r="C92">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D92">
         <v>0</v>
       </c>
       <c r="E92">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F92">
         <v>0</v>
@@ -2872,13 +2872,13 @@
         <v>63</v>
       </c>
       <c r="C98">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D98">
         <v>0</v>
       </c>
       <c r="E98">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F98">
         <v>0</v>
@@ -3392,13 +3392,13 @@
         <v>38</v>
       </c>
       <c r="C124">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D124">
         <v>0</v>
       </c>
       <c r="E124">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F124">
         <v>0</v>

--- a/resumo_busca_ativa_consolidado.xlsx
+++ b/resumo_busca_ativa_consolidado.xlsx
@@ -862,16 +862,16 @@
         <v>19133</v>
       </c>
       <c r="C2">
-        <v>1492</v>
+        <v>1529</v>
       </c>
       <c r="D2">
-        <v>1439</v>
+        <v>1400</v>
       </c>
       <c r="E2">
-        <v>16197</v>
+        <v>16196</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -882,13 +882,13 @@
         <v>16817</v>
       </c>
       <c r="C3">
-        <v>1056</v>
+        <v>1080</v>
       </c>
       <c r="D3">
-        <v>1391</v>
+        <v>1374</v>
       </c>
       <c r="E3">
-        <v>14292</v>
+        <v>14285</v>
       </c>
       <c r="F3">
         <v>78</v>
@@ -902,16 +902,16 @@
         <v>9446</v>
       </c>
       <c r="C4">
-        <v>828</v>
+        <v>850</v>
       </c>
       <c r="D4">
-        <v>1013</v>
+        <v>1029</v>
       </c>
       <c r="E4">
-        <v>7359</v>
+        <v>7392</v>
       </c>
       <c r="F4">
-        <v>246</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -952,13 +952,13 @@
         <v>9670</v>
       </c>
       <c r="C2">
-        <v>647</v>
+        <v>664</v>
       </c>
       <c r="D2">
-        <v>560</v>
+        <v>553</v>
       </c>
       <c r="E2">
-        <v>8463</v>
+        <v>8453</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -972,13 +972,13 @@
         <v>2381</v>
       </c>
       <c r="C3">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="D3">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="E3">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="F3">
         <v>48</v>
@@ -992,13 +992,13 @@
         <v>1735</v>
       </c>
       <c r="C4">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D4">
         <v>223</v>
       </c>
       <c r="E4">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="F4">
         <v>19</v>
@@ -1012,13 +1012,13 @@
         <v>1649</v>
       </c>
       <c r="C5">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D5">
         <v>241</v>
       </c>
       <c r="E5">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1035,10 +1035,10 @@
         <v>145</v>
       </c>
       <c r="D6">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E6">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1052,13 +1052,13 @@
         <v>1280</v>
       </c>
       <c r="C7">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="D7">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E7">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="F7">
         <v>12</v>
@@ -1072,13 +1072,13 @@
         <v>1203</v>
       </c>
       <c r="C8">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -1092,13 +1092,13 @@
         <v>1135</v>
       </c>
       <c r="C9">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D9">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="E9">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -1112,13 +1112,13 @@
         <v>977</v>
       </c>
       <c r="C10">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D10">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E10">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1132,13 +1132,13 @@
         <v>920</v>
       </c>
       <c r="C11">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D11">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="E11">
-        <v>835</v>
+        <v>842</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1152,13 +1152,13 @@
         <v>911</v>
       </c>
       <c r="C12">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="F12">
         <v>3</v>
@@ -1172,16 +1172,16 @@
         <v>843</v>
       </c>
       <c r="C13">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D13">
-        <v>109</v>
+        <v>138</v>
       </c>
       <c r="E13">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="F13">
-        <v>138</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1235,10 +1235,10 @@
         <v>62</v>
       </c>
       <c r="D16">
-        <v>151</v>
+        <v>125</v>
       </c>
       <c r="E16">
-        <v>551</v>
+        <v>577</v>
       </c>
       <c r="F16">
         <v>26</v>
@@ -1252,13 +1252,13 @@
         <v>729</v>
       </c>
       <c r="C17">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1272,13 +1272,13 @@
         <v>695</v>
       </c>
       <c r="C18">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D18">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E18">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1295,10 +1295,10 @@
         <v>65</v>
       </c>
       <c r="D19">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="E19">
-        <v>480</v>
+        <v>500</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1312,13 +1312,13 @@
         <v>646</v>
       </c>
       <c r="C20">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D20">
         <v>40</v>
       </c>
       <c r="E20">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1332,16 +1332,16 @@
         <v>616</v>
       </c>
       <c r="C21">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D21">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E21">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -1352,13 +1352,13 @@
         <v>611</v>
       </c>
       <c r="C22">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D22">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E22">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1372,13 +1372,13 @@
         <v>601</v>
       </c>
       <c r="C23">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D23">
         <v>75</v>
       </c>
       <c r="E23">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="F23">
         <v>18</v>
@@ -1392,13 +1392,13 @@
         <v>503</v>
       </c>
       <c r="C24">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D24">
         <v>0</v>
       </c>
       <c r="E24">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1412,13 +1412,13 @@
         <v>495</v>
       </c>
       <c r="C25">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D25">
         <v>9</v>
       </c>
       <c r="E25">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1432,13 +1432,13 @@
         <v>449</v>
       </c>
       <c r="C26">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D26">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E26">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -1512,13 +1512,13 @@
         <v>402</v>
       </c>
       <c r="C30">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D30">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E30">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -1532,13 +1532,13 @@
         <v>394</v>
       </c>
       <c r="C31">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D31">
         <v>1</v>
       </c>
       <c r="E31">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F31">
         <v>0</v>
@@ -1592,13 +1592,13 @@
         <v>295</v>
       </c>
       <c r="C34">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D34">
         <v>39</v>
       </c>
       <c r="E34">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F34">
         <v>0</v>
@@ -1712,10 +1712,10 @@
         <v>224</v>
       </c>
       <c r="C40">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D40">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E40">
         <v>137</v>
@@ -1775,10 +1775,10 @@
         <v>13</v>
       </c>
       <c r="D43">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E43">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="F43">
         <v>0</v>
@@ -1912,13 +1912,13 @@
         <v>154</v>
       </c>
       <c r="C50">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D50">
         <v>27</v>
       </c>
       <c r="E50">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F50">
         <v>0</v>
@@ -1932,13 +1932,13 @@
         <v>151</v>
       </c>
       <c r="C51">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D51">
         <v>53</v>
       </c>
       <c r="E51">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -1952,13 +1952,13 @@
         <v>150</v>
       </c>
       <c r="C52">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D52">
         <v>0</v>
       </c>
       <c r="E52">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F52">
         <v>0</v>
@@ -2052,13 +2052,13 @@
         <v>128</v>
       </c>
       <c r="C57">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D57">
         <v>0</v>
       </c>
       <c r="E57">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F57">
         <v>0</v>
@@ -2132,13 +2132,13 @@
         <v>123</v>
       </c>
       <c r="C61">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D61">
         <v>0</v>
       </c>
       <c r="E61">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F61">
         <v>0</v>
@@ -2172,13 +2172,13 @@
         <v>111</v>
       </c>
       <c r="C63">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D63">
         <v>0</v>
       </c>
       <c r="E63">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F63">
         <v>0</v>
@@ -2192,13 +2192,13 @@
         <v>108</v>
       </c>
       <c r="C64">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D64">
         <v>0</v>
       </c>
       <c r="E64">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -2252,16 +2252,16 @@
         <v>104</v>
       </c>
       <c r="C67">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D67">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="E67">
         <v>61</v>
       </c>
       <c r="F67">
-        <v>41</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -2432,13 +2432,13 @@
         <v>81</v>
       </c>
       <c r="C76">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D76">
         <v>0</v>
       </c>
       <c r="E76">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F76">
         <v>0</v>
@@ -2472,13 +2472,13 @@
         <v>80</v>
       </c>
       <c r="C78">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D78">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E78">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="F78">
         <v>0</v>
@@ -2732,13 +2732,13 @@
         <v>66</v>
       </c>
       <c r="C91">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D91">
         <v>0</v>
       </c>
       <c r="E91">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F91">
         <v>0</v>
@@ -3052,13 +3052,13 @@
         <v>53</v>
       </c>
       <c r="C107">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D107">
         <v>0</v>
       </c>
       <c r="E107">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F107">
         <v>0</v>
@@ -3372,13 +3372,13 @@
         <v>39</v>
       </c>
       <c r="C123">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D123">
         <v>0</v>
       </c>
       <c r="E123">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F123">
         <v>0</v>

--- a/resumo_busca_ativa_consolidado.xlsx
+++ b/resumo_busca_ativa_consolidado.xlsx
@@ -862,16 +862,16 @@
         <v>19133</v>
       </c>
       <c r="C2">
-        <v>1529</v>
+        <v>1538</v>
       </c>
       <c r="D2">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="E2">
-        <v>16196</v>
+        <v>16191</v>
       </c>
       <c r="F2">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -882,13 +882,13 @@
         <v>16817</v>
       </c>
       <c r="C3">
-        <v>1080</v>
+        <v>1099</v>
       </c>
       <c r="D3">
-        <v>1374</v>
+        <v>1116</v>
       </c>
       <c r="E3">
-        <v>14285</v>
+        <v>14524</v>
       </c>
       <c r="F3">
         <v>78</v>
@@ -902,13 +902,13 @@
         <v>9446</v>
       </c>
       <c r="C4">
-        <v>850</v>
+        <v>865</v>
       </c>
       <c r="D4">
-        <v>1029</v>
+        <v>1016</v>
       </c>
       <c r="E4">
-        <v>7392</v>
+        <v>7390</v>
       </c>
       <c r="F4">
         <v>175</v>
@@ -952,13 +952,13 @@
         <v>9670</v>
       </c>
       <c r="C2">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="D2">
         <v>553</v>
       </c>
       <c r="E2">
-        <v>8453</v>
+        <v>8448</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -972,13 +972,13 @@
         <v>2381</v>
       </c>
       <c r="C3">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D3">
-        <v>268</v>
+        <v>243</v>
       </c>
       <c r="E3">
-        <v>1894</v>
+        <v>1918</v>
       </c>
       <c r="F3">
         <v>48</v>
@@ -992,13 +992,13 @@
         <v>1735</v>
       </c>
       <c r="C4">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D4">
-        <v>223</v>
+        <v>204</v>
       </c>
       <c r="E4">
-        <v>1383</v>
+        <v>1401</v>
       </c>
       <c r="F4">
         <v>19</v>
@@ -1012,13 +1012,13 @@
         <v>1649</v>
       </c>
       <c r="C5">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D5">
-        <v>241</v>
+        <v>187</v>
       </c>
       <c r="E5">
-        <v>1292</v>
+        <v>1344</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1032,13 +1032,13 @@
         <v>1500</v>
       </c>
       <c r="C6">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D6">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E6">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1052,13 +1052,13 @@
         <v>1280</v>
       </c>
       <c r="C7">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D7">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="E7">
-        <v>986</v>
+        <v>990</v>
       </c>
       <c r="F7">
         <v>12</v>
@@ -1072,13 +1072,13 @@
         <v>1203</v>
       </c>
       <c r="C8">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -1092,13 +1092,13 @@
         <v>1135</v>
       </c>
       <c r="C9">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D9">
-        <v>330</v>
+        <v>240</v>
       </c>
       <c r="E9">
-        <v>699</v>
+        <v>786</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -1112,13 +1112,13 @@
         <v>977</v>
       </c>
       <c r="C10">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D10">
-        <v>76</v>
+        <v>27</v>
       </c>
       <c r="E10">
-        <v>805</v>
+        <v>852</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1132,13 +1132,13 @@
         <v>920</v>
       </c>
       <c r="C11">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D11">
         <v>21</v>
       </c>
       <c r="E11">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1232,10 +1232,10 @@
         <v>790</v>
       </c>
       <c r="C16">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D16">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E16">
         <v>577</v>
@@ -1335,13 +1335,13 @@
         <v>104</v>
       </c>
       <c r="D21">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E21">
         <v>371</v>
       </c>
       <c r="F21">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -1372,16 +1372,16 @@
         <v>601</v>
       </c>
       <c r="C23">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D23">
         <v>75</v>
       </c>
       <c r="E23">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F23">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -1412,13 +1412,13 @@
         <v>495</v>
       </c>
       <c r="C25">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D25">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E25">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1432,13 +1432,13 @@
         <v>449</v>
       </c>
       <c r="C26">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D26">
         <v>96</v>
       </c>
       <c r="E26">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -1632,13 +1632,13 @@
         <v>246</v>
       </c>
       <c r="C36">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D36">
         <v>0</v>
       </c>
       <c r="E36">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -1772,13 +1772,13 @@
         <v>200</v>
       </c>
       <c r="C43">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D43">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="E43">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="F43">
         <v>0</v>
@@ -1932,10 +1932,10 @@
         <v>151</v>
       </c>
       <c r="C51">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D51">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E51">
         <v>53</v>
@@ -2112,13 +2112,13 @@
         <v>124</v>
       </c>
       <c r="C60">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D60">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E60">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -2152,13 +2152,13 @@
         <v>118</v>
       </c>
       <c r="C62">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D62">
         <v>0</v>
       </c>
       <c r="E62">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F62">
         <v>0</v>
@@ -2272,13 +2272,13 @@
         <v>103</v>
       </c>
       <c r="C68">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D68">
         <v>0</v>
       </c>
       <c r="E68">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F68">
         <v>0</v>
@@ -2992,16 +2992,16 @@
         <v>54</v>
       </c>
       <c r="C104">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D104">
         <v>0</v>
       </c>
       <c r="E104">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F104">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105" spans="1:6">

--- a/resumo_busca_ativa_consolidado.xlsx
+++ b/resumo_busca_ativa_consolidado.xlsx
@@ -862,13 +862,13 @@
         <v>19133</v>
       </c>
       <c r="C2">
-        <v>1538</v>
+        <v>1568</v>
       </c>
       <c r="D2">
-        <v>1399</v>
+        <v>1188</v>
       </c>
       <c r="E2">
-        <v>16191</v>
+        <v>16372</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -882,13 +882,13 @@
         <v>16817</v>
       </c>
       <c r="C3">
-        <v>1099</v>
+        <v>1110</v>
       </c>
       <c r="D3">
-        <v>1116</v>
+        <v>1106</v>
       </c>
       <c r="E3">
-        <v>14524</v>
+        <v>14523</v>
       </c>
       <c r="F3">
         <v>78</v>
@@ -902,16 +902,16 @@
         <v>9446</v>
       </c>
       <c r="C4">
-        <v>865</v>
+        <v>877</v>
       </c>
       <c r="D4">
-        <v>1016</v>
+        <v>1008</v>
       </c>
       <c r="E4">
-        <v>7390</v>
+        <v>7387</v>
       </c>
       <c r="F4">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -952,13 +952,13 @@
         <v>9670</v>
       </c>
       <c r="C2">
-        <v>669</v>
+        <v>682</v>
       </c>
       <c r="D2">
-        <v>553</v>
+        <v>543</v>
       </c>
       <c r="E2">
-        <v>8448</v>
+        <v>8445</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -992,13 +992,13 @@
         <v>1735</v>
       </c>
       <c r="C4">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D4">
         <v>204</v>
       </c>
       <c r="E4">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="F4">
         <v>19</v>
@@ -1012,13 +1012,13 @@
         <v>1649</v>
       </c>
       <c r="C5">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D5">
         <v>187</v>
       </c>
       <c r="E5">
-        <v>1344</v>
+        <v>1342</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1032,13 +1032,13 @@
         <v>1500</v>
       </c>
       <c r="C6">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D6">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E6">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1052,10 +1052,10 @@
         <v>1280</v>
       </c>
       <c r="C7">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="D7">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E7">
         <v>990</v>
@@ -1072,16 +1072,16 @@
         <v>1203</v>
       </c>
       <c r="C8">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E8">
-        <v>1134</v>
+        <v>1131</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1092,13 +1092,13 @@
         <v>1135</v>
       </c>
       <c r="C9">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D9">
         <v>240</v>
       </c>
       <c r="E9">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -1112,13 +1112,13 @@
         <v>977</v>
       </c>
       <c r="C10">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D10">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E10">
-        <v>852</v>
+        <v>846</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1172,13 +1172,13 @@
         <v>843</v>
       </c>
       <c r="C13">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D13">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E13">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F13">
         <v>103</v>
@@ -1212,13 +1212,13 @@
         <v>811</v>
       </c>
       <c r="C15">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D15">
         <v>60</v>
       </c>
       <c r="E15">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -1232,13 +1232,13 @@
         <v>790</v>
       </c>
       <c r="C16">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D16">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E16">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="F16">
         <v>26</v>
@@ -1275,10 +1275,10 @@
         <v>39</v>
       </c>
       <c r="D18">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="E18">
-        <v>608</v>
+        <v>620</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1292,13 +1292,13 @@
         <v>667</v>
       </c>
       <c r="C19">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D19">
-        <v>102</v>
+        <v>17</v>
       </c>
       <c r="E19">
-        <v>500</v>
+        <v>584</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1332,16 +1332,16 @@
         <v>616</v>
       </c>
       <c r="C21">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D21">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="E21">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -1355,10 +1355,10 @@
         <v>56</v>
       </c>
       <c r="D22">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="E22">
-        <v>448</v>
+        <v>555</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1552,13 +1552,13 @@
         <v>389</v>
       </c>
       <c r="C32">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D32">
         <v>0</v>
       </c>
       <c r="E32">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -1612,10 +1612,10 @@
         <v>269</v>
       </c>
       <c r="C35">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D35">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="E35">
         <v>174</v>
@@ -1932,10 +1932,10 @@
         <v>151</v>
       </c>
       <c r="C51">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D51">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E51">
         <v>53</v>
@@ -2112,10 +2112,10 @@
         <v>124</v>
       </c>
       <c r="C60">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D60">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E60">
         <v>55</v>
@@ -2392,13 +2392,13 @@
         <v>86</v>
       </c>
       <c r="C74">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D74">
         <v>0</v>
       </c>
       <c r="E74">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F74">
         <v>0</v>
@@ -2475,10 +2475,10 @@
         <v>7</v>
       </c>
       <c r="D78">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E78">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F78">
         <v>0</v>
@@ -2998,10 +2998,10 @@
         <v>0</v>
       </c>
       <c r="E104">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F104">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:6">

--- a/resumo_busca_ativa_consolidado.xlsx
+++ b/resumo_busca_ativa_consolidado.xlsx
@@ -862,16 +862,16 @@
         <v>19133</v>
       </c>
       <c r="C2">
-        <v>1568</v>
+        <v>1623</v>
       </c>
       <c r="D2">
-        <v>1188</v>
+        <v>1140</v>
       </c>
       <c r="E2">
-        <v>16372</v>
+        <v>16370</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -882,13 +882,13 @@
         <v>16817</v>
       </c>
       <c r="C3">
-        <v>1110</v>
+        <v>1120</v>
       </c>
       <c r="D3">
         <v>1106</v>
       </c>
       <c r="E3">
-        <v>14523</v>
+        <v>14513</v>
       </c>
       <c r="F3">
         <v>78</v>
@@ -902,13 +902,13 @@
         <v>9446</v>
       </c>
       <c r="C4">
-        <v>877</v>
+        <v>888</v>
       </c>
       <c r="D4">
-        <v>1008</v>
+        <v>980</v>
       </c>
       <c r="E4">
-        <v>7387</v>
+        <v>7404</v>
       </c>
       <c r="F4">
         <v>174</v>
@@ -952,13 +952,13 @@
         <v>9670</v>
       </c>
       <c r="C2">
-        <v>682</v>
+        <v>693</v>
       </c>
       <c r="D2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="E2">
-        <v>8445</v>
+        <v>8432</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -1012,13 +1012,13 @@
         <v>1649</v>
       </c>
       <c r="C5">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D5">
         <v>187</v>
       </c>
       <c r="E5">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1035,10 +1035,10 @@
         <v>152</v>
       </c>
       <c r="D6">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E6">
-        <v>1121</v>
+        <v>1124</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1052,13 +1052,13 @@
         <v>1280</v>
       </c>
       <c r="C7">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D7">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E7">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="F7">
         <v>12</v>
@@ -1072,13 +1072,13 @@
         <v>1203</v>
       </c>
       <c r="C8">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -1092,13 +1092,13 @@
         <v>1135</v>
       </c>
       <c r="C9">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D9">
         <v>240</v>
       </c>
       <c r="E9">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -1132,13 +1132,13 @@
         <v>920</v>
       </c>
       <c r="C11">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D11">
         <v>21</v>
       </c>
       <c r="E11">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1232,10 +1232,10 @@
         <v>790</v>
       </c>
       <c r="C16">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D16">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E16">
         <v>576</v>
@@ -1272,13 +1272,13 @@
         <v>695</v>
       </c>
       <c r="C18">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D18">
         <v>36</v>
       </c>
       <c r="E18">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1292,13 +1292,13 @@
         <v>667</v>
       </c>
       <c r="C19">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D19">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="E19">
-        <v>584</v>
+        <v>557</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1332,16 +1332,16 @@
         <v>616</v>
       </c>
       <c r="C21">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D21">
-        <v>136</v>
+        <v>112</v>
       </c>
       <c r="E21">
-        <v>366</v>
+        <v>398</v>
       </c>
       <c r="F21">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -1352,13 +1352,13 @@
         <v>611</v>
       </c>
       <c r="C22">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="E22">
-        <v>555</v>
+        <v>488</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1412,13 +1412,13 @@
         <v>495</v>
       </c>
       <c r="C25">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D25">
         <v>1</v>
       </c>
       <c r="E25">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1435,10 +1435,10 @@
         <v>80</v>
       </c>
       <c r="D26">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="E26">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -1452,13 +1452,13 @@
         <v>448</v>
       </c>
       <c r="C27">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D27">
         <v>0</v>
       </c>
       <c r="E27">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -1512,13 +1512,13 @@
         <v>402</v>
       </c>
       <c r="C30">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D30">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E30">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -1532,13 +1532,13 @@
         <v>394</v>
       </c>
       <c r="C31">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D31">
         <v>1</v>
       </c>
       <c r="E31">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F31">
         <v>0</v>
@@ -1552,13 +1552,13 @@
         <v>389</v>
       </c>
       <c r="C32">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D32">
         <v>0</v>
       </c>
       <c r="E32">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -1592,13 +1592,13 @@
         <v>295</v>
       </c>
       <c r="C34">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D34">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E34">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F34">
         <v>0</v>
@@ -1612,13 +1612,13 @@
         <v>269</v>
       </c>
       <c r="C35">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D35">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="E35">
-        <v>174</v>
+        <v>199</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -1655,10 +1655,10 @@
         <v>34</v>
       </c>
       <c r="D37">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="E37">
-        <v>173</v>
+        <v>132</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -1695,10 +1695,10 @@
         <v>24</v>
       </c>
       <c r="D39">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="E39">
-        <v>161</v>
+        <v>208</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -1772,13 +1772,13 @@
         <v>200</v>
       </c>
       <c r="C43">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D43">
         <v>19</v>
       </c>
       <c r="E43">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F43">
         <v>0</v>
@@ -1792,13 +1792,13 @@
         <v>194</v>
       </c>
       <c r="C44">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D44">
         <v>0</v>
       </c>
       <c r="E44">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F44">
         <v>0</v>
@@ -1932,13 +1932,13 @@
         <v>151</v>
       </c>
       <c r="C51">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D51">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E51">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -2112,13 +2112,13 @@
         <v>124</v>
       </c>
       <c r="C60">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D60">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="E60">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -2412,13 +2412,13 @@
         <v>84</v>
       </c>
       <c r="C75">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D75">
         <v>0</v>
       </c>
       <c r="E75">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F75">
         <v>0</v>
@@ -2472,13 +2472,13 @@
         <v>80</v>
       </c>
       <c r="C78">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D78">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E78">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="F78">
         <v>0</v>
@@ -2975,10 +2975,10 @@
         <v>1</v>
       </c>
       <c r="D103">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E103">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="F103">
         <v>0</v>
@@ -3012,13 +3012,13 @@
         <v>54</v>
       </c>
       <c r="C105">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D105">
         <v>0</v>
       </c>
       <c r="E105">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F105">
         <v>0</v>
@@ -3552,13 +3552,13 @@
         <v>35</v>
       </c>
       <c r="C132">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D132">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="E132">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F132">
         <v>0</v>
@@ -3575,10 +3575,10 @@
         <v>2</v>
       </c>
       <c r="D133">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E133">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F133">
         <v>0</v>

--- a/resumo_busca_ativa_consolidado.xlsx
+++ b/resumo_busca_ativa_consolidado.xlsx
@@ -862,13 +862,13 @@
         <v>19133</v>
       </c>
       <c r="C2">
-        <v>1623</v>
+        <v>1664</v>
       </c>
       <c r="D2">
-        <v>1140</v>
+        <v>1112</v>
       </c>
       <c r="E2">
-        <v>16370</v>
+        <v>16357</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -882,13 +882,13 @@
         <v>16817</v>
       </c>
       <c r="C3">
-        <v>1120</v>
+        <v>1136</v>
       </c>
       <c r="D3">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="E3">
-        <v>14513</v>
+        <v>14495</v>
       </c>
       <c r="F3">
         <v>78</v>
@@ -902,13 +902,13 @@
         <v>9446</v>
       </c>
       <c r="C4">
-        <v>888</v>
+        <v>896</v>
       </c>
       <c r="D4">
-        <v>980</v>
+        <v>976</v>
       </c>
       <c r="E4">
-        <v>7404</v>
+        <v>7400</v>
       </c>
       <c r="F4">
         <v>174</v>
@@ -952,13 +952,13 @@
         <v>9670</v>
       </c>
       <c r="C2">
-        <v>693</v>
+        <v>698</v>
       </c>
       <c r="D2">
         <v>545</v>
       </c>
       <c r="E2">
-        <v>8432</v>
+        <v>8427</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -992,13 +992,13 @@
         <v>1735</v>
       </c>
       <c r="C4">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D4">
         <v>204</v>
       </c>
       <c r="E4">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="F4">
         <v>19</v>
@@ -1012,13 +1012,13 @@
         <v>1649</v>
       </c>
       <c r="C5">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D5">
         <v>187</v>
       </c>
       <c r="E5">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1032,10 +1032,10 @@
         <v>1500</v>
       </c>
       <c r="C6">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D6">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="E6">
         <v>1124</v>
@@ -1055,10 +1055,10 @@
         <v>191</v>
       </c>
       <c r="D7">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E7">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="F7">
         <v>12</v>
@@ -1092,13 +1092,13 @@
         <v>1135</v>
       </c>
       <c r="C9">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D9">
         <v>240</v>
       </c>
       <c r="E9">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -1112,13 +1112,13 @@
         <v>977</v>
       </c>
       <c r="C10">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D10">
         <v>29</v>
       </c>
       <c r="E10">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1132,13 +1132,13 @@
         <v>920</v>
       </c>
       <c r="C11">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D11">
         <v>21</v>
       </c>
       <c r="E11">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1152,13 +1152,13 @@
         <v>911</v>
       </c>
       <c r="C12">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="F12">
         <v>3</v>
@@ -1172,13 +1172,13 @@
         <v>843</v>
       </c>
       <c r="C13">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D13">
         <v>137</v>
       </c>
       <c r="E13">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="F13">
         <v>103</v>
@@ -1192,13 +1192,13 @@
         <v>813</v>
       </c>
       <c r="C14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1272,13 +1272,13 @@
         <v>695</v>
       </c>
       <c r="C18">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D18">
         <v>36</v>
       </c>
       <c r="E18">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1292,13 +1292,13 @@
         <v>667</v>
       </c>
       <c r="C19">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="D19">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E19">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1332,10 +1332,10 @@
         <v>616</v>
       </c>
       <c r="C21">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D21">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E21">
         <v>398</v>
@@ -1352,13 +1352,13 @@
         <v>611</v>
       </c>
       <c r="C22">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="D22">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="E22">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1392,13 +1392,13 @@
         <v>503</v>
       </c>
       <c r="C24">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D24">
         <v>0</v>
       </c>
       <c r="E24">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1412,13 +1412,13 @@
         <v>495</v>
       </c>
       <c r="C25">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D25">
         <v>1</v>
       </c>
       <c r="E25">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1512,13 +1512,13 @@
         <v>402</v>
       </c>
       <c r="C30">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D30">
         <v>30</v>
       </c>
       <c r="E30">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -1592,10 +1592,10 @@
         <v>295</v>
       </c>
       <c r="C34">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D34">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E34">
         <v>223</v>
@@ -1612,13 +1612,13 @@
         <v>269</v>
       </c>
       <c r="C35">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D35">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E35">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -1752,13 +1752,13 @@
         <v>207</v>
       </c>
       <c r="C42">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D42">
         <v>0</v>
       </c>
       <c r="E42">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F42">
         <v>0</v>
@@ -2112,10 +2112,10 @@
         <v>124</v>
       </c>
       <c r="C60">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D60">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E60">
         <v>71</v>
@@ -2232,13 +2232,13 @@
         <v>107</v>
       </c>
       <c r="C66">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D66">
         <v>0</v>
       </c>
       <c r="E66">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F66">
         <v>0</v>
@@ -2472,13 +2472,13 @@
         <v>80</v>
       </c>
       <c r="C78">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D78">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E78">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F78">
         <v>0</v>
@@ -2532,13 +2532,13 @@
         <v>76</v>
       </c>
       <c r="C81">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D81">
         <v>0</v>
       </c>
       <c r="E81">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F81">
         <v>0</v>
@@ -3275,10 +3275,10 @@
         <v>4</v>
       </c>
       <c r="D118">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E118">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F118">
         <v>0</v>

--- a/resumo_busca_ativa_consolidado.xlsx
+++ b/resumo_busca_ativa_consolidado.xlsx
@@ -862,13 +862,13 @@
         <v>19133</v>
       </c>
       <c r="C2">
-        <v>1664</v>
+        <v>1695</v>
       </c>
       <c r="D2">
-        <v>1112</v>
+        <v>1108</v>
       </c>
       <c r="E2">
-        <v>16357</v>
+        <v>16330</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -882,16 +882,16 @@
         <v>16817</v>
       </c>
       <c r="C3">
-        <v>1136</v>
+        <v>1171</v>
       </c>
       <c r="D3">
-        <v>1108</v>
+        <v>1100</v>
       </c>
       <c r="E3">
-        <v>14495</v>
+        <v>14467</v>
       </c>
       <c r="F3">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -902,13 +902,13 @@
         <v>9446</v>
       </c>
       <c r="C4">
-        <v>896</v>
+        <v>950</v>
       </c>
       <c r="D4">
-        <v>976</v>
+        <v>1001</v>
       </c>
       <c r="E4">
-        <v>7400</v>
+        <v>7321</v>
       </c>
       <c r="F4">
         <v>174</v>
@@ -952,13 +952,13 @@
         <v>9670</v>
       </c>
       <c r="C2">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="D2">
-        <v>545</v>
+        <v>557</v>
       </c>
       <c r="E2">
-        <v>8427</v>
+        <v>8410</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -972,13 +972,13 @@
         <v>2381</v>
       </c>
       <c r="C3">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D3">
         <v>243</v>
       </c>
       <c r="E3">
-        <v>1918</v>
+        <v>1916</v>
       </c>
       <c r="F3">
         <v>48</v>
@@ -992,16 +992,16 @@
         <v>1735</v>
       </c>
       <c r="C4">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D4">
         <v>204</v>
       </c>
       <c r="E4">
-        <v>1399</v>
+        <v>1394</v>
       </c>
       <c r="F4">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1012,13 +1012,13 @@
         <v>1649</v>
       </c>
       <c r="C5">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D5">
         <v>187</v>
       </c>
       <c r="E5">
-        <v>1339</v>
+        <v>1337</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1032,13 +1032,13 @@
         <v>1500</v>
       </c>
       <c r="C6">
-        <v>156</v>
+        <v>177</v>
       </c>
       <c r="D6">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="E6">
-        <v>1124</v>
+        <v>1090</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1052,13 +1052,13 @@
         <v>1280</v>
       </c>
       <c r="C7">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="D7">
-        <v>85</v>
+        <v>122</v>
       </c>
       <c r="E7">
-        <v>992</v>
+        <v>947</v>
       </c>
       <c r="F7">
         <v>12</v>
@@ -1072,13 +1072,13 @@
         <v>1203</v>
       </c>
       <c r="C8">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -1092,13 +1092,13 @@
         <v>1135</v>
       </c>
       <c r="C9">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="D9">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E9">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -1112,13 +1112,13 @@
         <v>977</v>
       </c>
       <c r="C10">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D10">
         <v>29</v>
       </c>
       <c r="E10">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1132,13 +1132,13 @@
         <v>920</v>
       </c>
       <c r="C11">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D11">
         <v>21</v>
       </c>
       <c r="E11">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1152,13 +1152,13 @@
         <v>911</v>
       </c>
       <c r="C12">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="F12">
         <v>3</v>
@@ -1172,13 +1172,13 @@
         <v>843</v>
       </c>
       <c r="C13">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="D13">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="E13">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="F13">
         <v>103</v>
@@ -1192,13 +1192,13 @@
         <v>813</v>
       </c>
       <c r="C14">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1212,13 +1212,13 @@
         <v>811</v>
       </c>
       <c r="C15">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D15">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E15">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -1232,13 +1232,13 @@
         <v>790</v>
       </c>
       <c r="C16">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D16">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="E16">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="F16">
         <v>26</v>
@@ -1272,13 +1272,13 @@
         <v>695</v>
       </c>
       <c r="C18">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D18">
         <v>36</v>
       </c>
       <c r="E18">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1332,13 +1332,13 @@
         <v>616</v>
       </c>
       <c r="C21">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D21">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E21">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1352,13 +1352,13 @@
         <v>611</v>
       </c>
       <c r="C22">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D22">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="E22">
-        <v>487</v>
+        <v>501</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1432,13 +1432,13 @@
         <v>449</v>
       </c>
       <c r="C26">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D26">
         <v>85</v>
       </c>
       <c r="E26">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -1472,13 +1472,13 @@
         <v>441</v>
       </c>
       <c r="C28">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D28">
         <v>66</v>
       </c>
       <c r="E28">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -1512,13 +1512,13 @@
         <v>402</v>
       </c>
       <c r="C30">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D30">
         <v>30</v>
       </c>
       <c r="E30">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -1532,13 +1532,13 @@
         <v>394</v>
       </c>
       <c r="C31">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D31">
         <v>1</v>
       </c>
       <c r="E31">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F31">
         <v>0</v>
@@ -1575,10 +1575,10 @@
         <v>23</v>
       </c>
       <c r="D33">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E33">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -1612,13 +1612,13 @@
         <v>269</v>
       </c>
       <c r="C35">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D35">
         <v>36</v>
       </c>
       <c r="E35">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -1632,13 +1632,13 @@
         <v>246</v>
       </c>
       <c r="C36">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D36">
         <v>0</v>
       </c>
       <c r="E36">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -1652,13 +1652,13 @@
         <v>238</v>
       </c>
       <c r="C37">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D37">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="E37">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -1692,13 +1692,13 @@
         <v>232</v>
       </c>
       <c r="C39">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D39">
         <v>0</v>
       </c>
       <c r="E39">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -1712,10 +1712,10 @@
         <v>224</v>
       </c>
       <c r="C40">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D40">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E40">
         <v>137</v>
@@ -1895,10 +1895,10 @@
         <v>6</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E49">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="F49">
         <v>0</v>
@@ -1932,13 +1932,13 @@
         <v>151</v>
       </c>
       <c r="C51">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D51">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E51">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -1952,13 +1952,13 @@
         <v>150</v>
       </c>
       <c r="C52">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D52">
         <v>0</v>
       </c>
       <c r="E52">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F52">
         <v>0</v>
@@ -2115,10 +2115,10 @@
         <v>31</v>
       </c>
       <c r="D60">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E60">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -2392,13 +2392,13 @@
         <v>86</v>
       </c>
       <c r="C74">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D74">
         <v>0</v>
       </c>
       <c r="E74">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F74">
         <v>0</v>
@@ -2472,13 +2472,13 @@
         <v>80</v>
       </c>
       <c r="C78">
+        <v>25</v>
+      </c>
+      <c r="D78">
         <v>16</v>
       </c>
-      <c r="D78">
-        <v>7</v>
-      </c>
       <c r="E78">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="F78">
         <v>0</v>
@@ -2732,13 +2732,13 @@
         <v>66</v>
       </c>
       <c r="C91">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D91">
         <v>0</v>
       </c>
       <c r="E91">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F91">
         <v>0</v>
@@ -3112,13 +3112,13 @@
         <v>52</v>
       </c>
       <c r="C110">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D110">
         <v>0</v>
       </c>
       <c r="E110">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F110">
         <v>0</v>
@@ -3275,10 +3275,10 @@
         <v>4</v>
       </c>
       <c r="D118">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E118">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F118">
         <v>0</v>
@@ -3512,13 +3512,13 @@
         <v>35</v>
       </c>
       <c r="C130">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D130">
         <v>0</v>
       </c>
       <c r="E130">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F130">
         <v>0</v>
@@ -3552,10 +3552,10 @@
         <v>35</v>
       </c>
       <c r="C132">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D132">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E132">
         <v>11</v>
@@ -3712,13 +3712,13 @@
         <v>23</v>
       </c>
       <c r="C140">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D140">
         <v>0</v>
       </c>
       <c r="E140">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F140">
         <v>0</v>

--- a/resumo_busca_ativa_consolidado.xlsx
+++ b/resumo_busca_ativa_consolidado.xlsx
@@ -862,13 +862,13 @@
         <v>19133</v>
       </c>
       <c r="C2">
-        <v>1695</v>
+        <v>1737</v>
       </c>
       <c r="D2">
-        <v>1108</v>
+        <v>1068</v>
       </c>
       <c r="E2">
-        <v>16330</v>
+        <v>16328</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -882,16 +882,16 @@
         <v>16817</v>
       </c>
       <c r="C3">
-        <v>1171</v>
+        <v>1204</v>
       </c>
       <c r="D3">
-        <v>1100</v>
+        <v>1056</v>
       </c>
       <c r="E3">
-        <v>14467</v>
+        <v>14479</v>
       </c>
       <c r="F3">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -902,13 +902,13 @@
         <v>9446</v>
       </c>
       <c r="C4">
-        <v>950</v>
+        <v>1015</v>
       </c>
       <c r="D4">
-        <v>1001</v>
+        <v>996</v>
       </c>
       <c r="E4">
-        <v>7321</v>
+        <v>7261</v>
       </c>
       <c r="F4">
         <v>174</v>
@@ -952,13 +952,13 @@
         <v>9670</v>
       </c>
       <c r="C2">
-        <v>703</v>
+        <v>714</v>
       </c>
       <c r="D2">
-        <v>557</v>
+        <v>545</v>
       </c>
       <c r="E2">
-        <v>8410</v>
+        <v>8411</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -972,10 +972,10 @@
         <v>2381</v>
       </c>
       <c r="C3">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="D3">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E3">
         <v>1916</v>
@@ -992,16 +992,16 @@
         <v>1735</v>
       </c>
       <c r="C4">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D4">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E4">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="F4">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1032,13 +1032,13 @@
         <v>1500</v>
       </c>
       <c r="C6">
-        <v>177</v>
+        <v>212</v>
       </c>
       <c r="D6">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="E6">
-        <v>1090</v>
+        <v>1048</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1052,10 +1052,10 @@
         <v>1280</v>
       </c>
       <c r="C7">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="D7">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="E7">
         <v>947</v>
@@ -1092,10 +1092,10 @@
         <v>1135</v>
       </c>
       <c r="C9">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="D9">
-        <v>234</v>
+        <v>209</v>
       </c>
       <c r="E9">
         <v>778</v>
@@ -1152,13 +1152,13 @@
         <v>911</v>
       </c>
       <c r="C12">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="F12">
         <v>3</v>
@@ -1172,13 +1172,13 @@
         <v>843</v>
       </c>
       <c r="C13">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D13">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="E13">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="F13">
         <v>103</v>
@@ -1232,10 +1232,10 @@
         <v>790</v>
       </c>
       <c r="C16">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D16">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E16">
         <v>580</v>
@@ -1292,10 +1292,10 @@
         <v>667</v>
       </c>
       <c r="C19">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D19">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E19">
         <v>554</v>
@@ -1332,10 +1332,10 @@
         <v>616</v>
       </c>
       <c r="C21">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D21">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E21">
         <v>401</v>
@@ -1352,10 +1352,10 @@
         <v>611</v>
       </c>
       <c r="C22">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="D22">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E22">
         <v>501</v>
@@ -1372,13 +1372,13 @@
         <v>601</v>
       </c>
       <c r="C23">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D23">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="E23">
-        <v>444</v>
+        <v>421</v>
       </c>
       <c r="F23">
         <v>17</v>
@@ -1512,10 +1512,10 @@
         <v>402</v>
       </c>
       <c r="C30">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D30">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E30">
         <v>336</v>
@@ -1592,10 +1592,10 @@
         <v>295</v>
       </c>
       <c r="C34">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D34">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="E34">
         <v>223</v>
@@ -1652,10 +1652,10 @@
         <v>238</v>
       </c>
       <c r="C37">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D37">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E37">
         <v>137</v>
@@ -1712,10 +1712,10 @@
         <v>224</v>
       </c>
       <c r="C40">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D40">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E40">
         <v>137</v>
@@ -1932,13 +1932,13 @@
         <v>151</v>
       </c>
       <c r="C51">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D51">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="E51">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -2112,13 +2112,13 @@
         <v>124</v>
       </c>
       <c r="C60">
+        <v>32</v>
+      </c>
+      <c r="D60">
         <v>31</v>
       </c>
-      <c r="D60">
-        <v>24</v>
-      </c>
       <c r="E60">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -2475,10 +2475,10 @@
         <v>25</v>
       </c>
       <c r="D78">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E78">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F78">
         <v>0</v>
@@ -2915,10 +2915,10 @@
         <v>2</v>
       </c>
       <c r="D100">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E100">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="F100">
         <v>0</v>

--- a/resumo_busca_ativa_consolidado.xlsx
+++ b/resumo_busca_ativa_consolidado.xlsx
@@ -862,13 +862,13 @@
         <v>19133</v>
       </c>
       <c r="C2">
-        <v>1737</v>
+        <v>1797</v>
       </c>
       <c r="D2">
-        <v>1068</v>
+        <v>1013</v>
       </c>
       <c r="E2">
-        <v>16328</v>
+        <v>16323</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -882,13 +882,13 @@
         <v>16817</v>
       </c>
       <c r="C3">
-        <v>1204</v>
+        <v>1227</v>
       </c>
       <c r="D3">
         <v>1056</v>
       </c>
       <c r="E3">
-        <v>14479</v>
+        <v>14456</v>
       </c>
       <c r="F3">
         <v>78</v>
@@ -902,10 +902,10 @@
         <v>9446</v>
       </c>
       <c r="C4">
-        <v>1015</v>
+        <v>1066</v>
       </c>
       <c r="D4">
-        <v>996</v>
+        <v>945</v>
       </c>
       <c r="E4">
         <v>7261</v>
@@ -952,13 +952,13 @@
         <v>9670</v>
       </c>
       <c r="C2">
-        <v>714</v>
+        <v>737</v>
       </c>
       <c r="D2">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="E2">
-        <v>8411</v>
+        <v>8380</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -972,13 +972,13 @@
         <v>2381</v>
       </c>
       <c r="C3">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D3">
         <v>239</v>
       </c>
       <c r="E3">
-        <v>1916</v>
+        <v>1913</v>
       </c>
       <c r="F3">
         <v>48</v>
@@ -992,13 +992,13 @@
         <v>1735</v>
       </c>
       <c r="C4">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D4">
         <v>205</v>
       </c>
       <c r="E4">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="F4">
         <v>19</v>
@@ -1012,13 +1012,13 @@
         <v>1649</v>
       </c>
       <c r="C5">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D5">
         <v>187</v>
       </c>
       <c r="E5">
-        <v>1337</v>
+        <v>1335</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1032,13 +1032,13 @@
         <v>1500</v>
       </c>
       <c r="C6">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="D6">
-        <v>239</v>
+        <v>217</v>
       </c>
       <c r="E6">
-        <v>1048</v>
+        <v>1058</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1052,13 +1052,13 @@
         <v>1280</v>
       </c>
       <c r="C7">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="D7">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="E7">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="F7">
         <v>12</v>
@@ -1072,13 +1072,13 @@
         <v>1203</v>
       </c>
       <c r="C8">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -1112,13 +1112,13 @@
         <v>977</v>
       </c>
       <c r="C10">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D10">
         <v>29</v>
       </c>
       <c r="E10">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1172,13 +1172,13 @@
         <v>843</v>
       </c>
       <c r="C13">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="D13">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="E13">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="F13">
         <v>103</v>
@@ -1212,13 +1212,13 @@
         <v>811</v>
       </c>
       <c r="C15">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D15">
         <v>59</v>
       </c>
       <c r="E15">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -1232,13 +1232,13 @@
         <v>790</v>
       </c>
       <c r="C16">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D16">
         <v>112</v>
       </c>
       <c r="E16">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="F16">
         <v>26</v>
@@ -1272,13 +1272,13 @@
         <v>695</v>
       </c>
       <c r="C18">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D18">
         <v>36</v>
       </c>
       <c r="E18">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1292,13 +1292,13 @@
         <v>667</v>
       </c>
       <c r="C19">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D19">
         <v>34</v>
       </c>
       <c r="E19">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1332,13 +1332,13 @@
         <v>616</v>
       </c>
       <c r="C21">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="D21">
-        <v>100</v>
+        <v>51</v>
       </c>
       <c r="E21">
-        <v>401</v>
+        <v>437</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1352,13 +1352,13 @@
         <v>611</v>
       </c>
       <c r="C22">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="D22">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E22">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1372,13 +1372,13 @@
         <v>601</v>
       </c>
       <c r="C23">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D23">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E23">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F23">
         <v>17</v>
@@ -1412,13 +1412,13 @@
         <v>495</v>
       </c>
       <c r="C25">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D25">
         <v>1</v>
       </c>
       <c r="E25">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1432,13 +1432,13 @@
         <v>449</v>
       </c>
       <c r="C26">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D26">
         <v>85</v>
       </c>
       <c r="E26">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -1552,13 +1552,13 @@
         <v>389</v>
       </c>
       <c r="C32">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D32">
         <v>0</v>
       </c>
       <c r="E32">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -1592,13 +1592,13 @@
         <v>295</v>
       </c>
       <c r="C34">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D34">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E34">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F34">
         <v>0</v>
@@ -1612,13 +1612,13 @@
         <v>269</v>
       </c>
       <c r="C35">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D35">
         <v>36</v>
       </c>
       <c r="E35">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -1652,13 +1652,13 @@
         <v>238</v>
       </c>
       <c r="C37">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D37">
         <v>64</v>
       </c>
       <c r="E37">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -1812,13 +1812,13 @@
         <v>187</v>
       </c>
       <c r="C45">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D45">
         <v>10</v>
       </c>
       <c r="E45">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F45">
         <v>6</v>
@@ -1932,13 +1932,13 @@
         <v>151</v>
       </c>
       <c r="C51">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D51">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E51">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -1992,13 +1992,13 @@
         <v>144</v>
       </c>
       <c r="C54">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D54">
         <v>0</v>
       </c>
       <c r="E54">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F54">
         <v>0</v>
@@ -2112,13 +2112,13 @@
         <v>124</v>
       </c>
       <c r="C60">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D60">
         <v>31</v>
       </c>
       <c r="E60">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -2232,13 +2232,13 @@
         <v>107</v>
       </c>
       <c r="C66">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D66">
         <v>0</v>
       </c>
       <c r="E66">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F66">
         <v>0</v>
@@ -2312,13 +2312,13 @@
         <v>99</v>
       </c>
       <c r="C70">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D70">
         <v>0</v>
       </c>
       <c r="E70">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F70">
         <v>3</v>
@@ -2372,13 +2372,13 @@
         <v>88</v>
       </c>
       <c r="C73">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D73">
         <v>0</v>
       </c>
       <c r="E73">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F73">
         <v>0</v>
@@ -2452,13 +2452,13 @@
         <v>81</v>
       </c>
       <c r="C77">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D77">
         <v>0</v>
       </c>
       <c r="E77">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F77">
         <v>0</v>
@@ -2472,10 +2472,10 @@
         <v>80</v>
       </c>
       <c r="C78">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D78">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E78">
         <v>42</v>
@@ -2732,13 +2732,13 @@
         <v>66</v>
       </c>
       <c r="C91">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D91">
         <v>0</v>
       </c>
       <c r="E91">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F91">
         <v>0</v>
@@ -2792,13 +2792,13 @@
         <v>64</v>
       </c>
       <c r="C94">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D94">
         <v>0</v>
       </c>
       <c r="E94">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F94">
         <v>0</v>
@@ -2852,13 +2852,13 @@
         <v>63</v>
       </c>
       <c r="C97">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D97">
         <v>0</v>
       </c>
       <c r="E97">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F97">
         <v>0</v>
@@ -3152,13 +3152,13 @@
         <v>49</v>
       </c>
       <c r="C112">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D112">
         <v>0</v>
       </c>
       <c r="E112">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F112">
         <v>0</v>

--- a/resumo_busca_ativa_consolidado.xlsx
+++ b/resumo_busca_ativa_consolidado.xlsx
@@ -862,13 +862,13 @@
         <v>19133</v>
       </c>
       <c r="C2">
-        <v>1797</v>
+        <v>1827</v>
       </c>
       <c r="D2">
-        <v>1013</v>
+        <v>1048</v>
       </c>
       <c r="E2">
-        <v>16323</v>
+        <v>16258</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -882,13 +882,13 @@
         <v>16817</v>
       </c>
       <c r="C3">
-        <v>1227</v>
+        <v>1262</v>
       </c>
       <c r="D3">
-        <v>1056</v>
+        <v>1046</v>
       </c>
       <c r="E3">
-        <v>14456</v>
+        <v>14431</v>
       </c>
       <c r="F3">
         <v>78</v>
@@ -902,13 +902,13 @@
         <v>9446</v>
       </c>
       <c r="C4">
-        <v>1066</v>
+        <v>1100</v>
       </c>
       <c r="D4">
-        <v>945</v>
+        <v>874</v>
       </c>
       <c r="E4">
-        <v>7261</v>
+        <v>7298</v>
       </c>
       <c r="F4">
         <v>174</v>
@@ -952,13 +952,13 @@
         <v>9670</v>
       </c>
       <c r="C2">
-        <v>737</v>
+        <v>754</v>
       </c>
       <c r="D2">
-        <v>553</v>
+        <v>571</v>
       </c>
       <c r="E2">
-        <v>8380</v>
+        <v>8345</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -972,10 +972,10 @@
         <v>2381</v>
       </c>
       <c r="C3">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D3">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E3">
         <v>1913</v>
@@ -995,10 +995,10 @@
         <v>121</v>
       </c>
       <c r="D4">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E4">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="F4">
         <v>19</v>
@@ -1012,13 +1012,13 @@
         <v>1649</v>
       </c>
       <c r="C5">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="D5">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="E5">
-        <v>1335</v>
+        <v>1315</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1032,10 +1032,10 @@
         <v>1500</v>
       </c>
       <c r="C6">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="D6">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="E6">
         <v>1058</v>
@@ -1072,13 +1072,13 @@
         <v>1203</v>
       </c>
       <c r="C8">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -1135,10 +1135,10 @@
         <v>61</v>
       </c>
       <c r="D11">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E11">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1172,10 +1172,10 @@
         <v>843</v>
       </c>
       <c r="C13">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="D13">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="E13">
         <v>511</v>
@@ -1252,13 +1252,13 @@
         <v>729</v>
       </c>
       <c r="C17">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1292,13 +1292,13 @@
         <v>667</v>
       </c>
       <c r="C19">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D19">
         <v>34</v>
       </c>
       <c r="E19">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1332,13 +1332,13 @@
         <v>616</v>
       </c>
       <c r="C21">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D21">
         <v>51</v>
       </c>
       <c r="E21">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1352,13 +1352,13 @@
         <v>611</v>
       </c>
       <c r="C22">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D22">
         <v>16</v>
       </c>
       <c r="E22">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1372,13 +1372,13 @@
         <v>601</v>
       </c>
       <c r="C23">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D23">
         <v>93</v>
       </c>
       <c r="E23">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="F23">
         <v>17</v>
@@ -1432,13 +1432,13 @@
         <v>449</v>
       </c>
       <c r="C26">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D26">
         <v>85</v>
       </c>
       <c r="E26">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -1515,10 +1515,10 @@
         <v>41</v>
       </c>
       <c r="D30">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="E30">
-        <v>336</v>
+        <v>314</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -1532,13 +1532,13 @@
         <v>394</v>
       </c>
       <c r="C31">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D31">
         <v>1</v>
       </c>
       <c r="E31">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F31">
         <v>0</v>
@@ -1575,10 +1575,10 @@
         <v>23</v>
       </c>
       <c r="D33">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="E33">
-        <v>252</v>
+        <v>293</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -1592,13 +1592,13 @@
         <v>295</v>
       </c>
       <c r="C34">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="D34">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E34">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F34">
         <v>0</v>
@@ -1772,10 +1772,10 @@
         <v>200</v>
       </c>
       <c r="C43">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D43">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E43">
         <v>164</v>
@@ -1852,13 +1852,13 @@
         <v>167</v>
       </c>
       <c r="C47">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D47">
         <v>1</v>
       </c>
       <c r="E47">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F47">
         <v>0</v>
@@ -1932,10 +1932,10 @@
         <v>151</v>
       </c>
       <c r="C51">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D51">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E51">
         <v>63</v>
@@ -2732,13 +2732,13 @@
         <v>66</v>
       </c>
       <c r="C91">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D91">
         <v>0</v>
       </c>
       <c r="E91">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F91">
         <v>0</v>

--- a/resumo_busca_ativa_consolidado.xlsx
+++ b/resumo_busca_ativa_consolidado.xlsx
@@ -862,13 +862,13 @@
         <v>19133</v>
       </c>
       <c r="C2">
-        <v>1827</v>
+        <v>1776</v>
       </c>
       <c r="D2">
-        <v>1048</v>
+        <v>1033</v>
       </c>
       <c r="E2">
-        <v>16258</v>
+        <v>16324</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -882,13 +882,13 @@
         <v>16817</v>
       </c>
       <c r="C3">
-        <v>1262</v>
+        <v>1223</v>
       </c>
       <c r="D3">
-        <v>1046</v>
+        <v>1043</v>
       </c>
       <c r="E3">
-        <v>14431</v>
+        <v>14473</v>
       </c>
       <c r="F3">
         <v>78</v>
@@ -902,16 +902,16 @@
         <v>9446</v>
       </c>
       <c r="C4">
-        <v>1100</v>
+        <v>971</v>
       </c>
       <c r="D4">
-        <v>874</v>
+        <v>856</v>
       </c>
       <c r="E4">
-        <v>7298</v>
+        <v>7446</v>
       </c>
       <c r="F4">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -952,13 +952,13 @@
         <v>9670</v>
       </c>
       <c r="C2">
-        <v>754</v>
+        <v>737</v>
       </c>
       <c r="D2">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="E2">
-        <v>8345</v>
+        <v>8364</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -972,13 +972,13 @@
         <v>2381</v>
       </c>
       <c r="C3">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D3">
         <v>237</v>
       </c>
       <c r="E3">
-        <v>1913</v>
+        <v>1915</v>
       </c>
       <c r="F3">
         <v>48</v>
@@ -992,13 +992,13 @@
         <v>1735</v>
       </c>
       <c r="C4">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D4">
         <v>204</v>
       </c>
       <c r="E4">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="F4">
         <v>19</v>
@@ -1012,13 +1012,13 @@
         <v>1649</v>
       </c>
       <c r="C5">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="D5">
         <v>181</v>
       </c>
       <c r="E5">
-        <v>1315</v>
+        <v>1336</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1032,13 +1032,13 @@
         <v>1500</v>
       </c>
       <c r="C6">
-        <v>235</v>
+        <v>165</v>
       </c>
       <c r="D6">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="E6">
-        <v>1058</v>
+        <v>1134</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1052,13 +1052,13 @@
         <v>1280</v>
       </c>
       <c r="C7">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="D7">
         <v>103</v>
       </c>
       <c r="E7">
-        <v>946</v>
+        <v>953</v>
       </c>
       <c r="F7">
         <v>12</v>
@@ -1072,13 +1072,13 @@
         <v>1203</v>
       </c>
       <c r="C8">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -1092,13 +1092,13 @@
         <v>1135</v>
       </c>
       <c r="C9">
-        <v>148</v>
+        <v>119</v>
       </c>
       <c r="D9">
         <v>209</v>
       </c>
       <c r="E9">
-        <v>778</v>
+        <v>807</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -1112,13 +1112,13 @@
         <v>977</v>
       </c>
       <c r="C10">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D10">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E10">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1152,13 +1152,13 @@
         <v>911</v>
       </c>
       <c r="C12">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="F12">
         <v>3</v>
@@ -1172,16 +1172,16 @@
         <v>843</v>
       </c>
       <c r="C13">
-        <v>136</v>
+        <v>100</v>
       </c>
       <c r="D13">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E13">
-        <v>511</v>
+        <v>552</v>
       </c>
       <c r="F13">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1212,13 +1212,13 @@
         <v>811</v>
       </c>
       <c r="C15">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D15">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E15">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -1232,13 +1232,13 @@
         <v>790</v>
       </c>
       <c r="C16">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D16">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E16">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="F16">
         <v>26</v>
@@ -1252,13 +1252,13 @@
         <v>729</v>
       </c>
       <c r="C17">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1292,13 +1292,13 @@
         <v>667</v>
       </c>
       <c r="C19">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D19">
         <v>34</v>
       </c>
       <c r="E19">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1312,13 +1312,13 @@
         <v>646</v>
       </c>
       <c r="C20">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D20">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E20">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1332,13 +1332,13 @@
         <v>616</v>
       </c>
       <c r="C21">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="D21">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E21">
-        <v>436</v>
+        <v>451</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1352,13 +1352,13 @@
         <v>611</v>
       </c>
       <c r="C22">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="D22">
         <v>16</v>
       </c>
       <c r="E22">
-        <v>498</v>
+        <v>517</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1372,13 +1372,13 @@
         <v>601</v>
       </c>
       <c r="C23">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D23">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E23">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F23">
         <v>17</v>
@@ -1412,13 +1412,13 @@
         <v>495</v>
       </c>
       <c r="C25">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D25">
         <v>1</v>
       </c>
       <c r="E25">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1472,10 +1472,10 @@
         <v>441</v>
       </c>
       <c r="C28">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D28">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E28">
         <v>345</v>
@@ -1512,13 +1512,13 @@
         <v>402</v>
       </c>
       <c r="C30">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D30">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E30">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -1532,13 +1532,13 @@
         <v>394</v>
       </c>
       <c r="C31">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D31">
         <v>1</v>
       </c>
       <c r="E31">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F31">
         <v>0</v>
@@ -1592,13 +1592,13 @@
         <v>295</v>
       </c>
       <c r="C34">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="D34">
         <v>2</v>
       </c>
       <c r="E34">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="F34">
         <v>0</v>
@@ -1652,13 +1652,13 @@
         <v>238</v>
       </c>
       <c r="C37">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D37">
         <v>64</v>
       </c>
       <c r="E37">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -1692,13 +1692,13 @@
         <v>232</v>
       </c>
       <c r="C39">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D39">
         <v>0</v>
       </c>
       <c r="E39">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -1712,13 +1712,13 @@
         <v>224</v>
       </c>
       <c r="C40">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D40">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E40">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -1732,13 +1732,13 @@
         <v>223</v>
       </c>
       <c r="C41">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D41">
         <v>0</v>
       </c>
       <c r="E41">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -1932,13 +1932,13 @@
         <v>151</v>
       </c>
       <c r="C51">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D51">
         <v>23</v>
       </c>
       <c r="E51">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -2032,13 +2032,13 @@
         <v>138</v>
       </c>
       <c r="C56">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D56">
         <v>0</v>
       </c>
       <c r="E56">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F56">
         <v>0</v>
@@ -2112,13 +2112,13 @@
         <v>124</v>
       </c>
       <c r="C60">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D60">
         <v>31</v>
       </c>
       <c r="E60">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -2372,13 +2372,13 @@
         <v>88</v>
       </c>
       <c r="C73">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D73">
         <v>0</v>
       </c>
       <c r="E73">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F73">
         <v>0</v>
@@ -2472,13 +2472,13 @@
         <v>80</v>
       </c>
       <c r="C78">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D78">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E78">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F78">
         <v>0</v>
@@ -2592,13 +2592,13 @@
         <v>74</v>
       </c>
       <c r="C84">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D84">
         <v>0</v>
       </c>
       <c r="E84">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F84">
         <v>2</v>
@@ -2672,13 +2672,13 @@
         <v>68</v>
       </c>
       <c r="C88">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D88">
         <v>0</v>
       </c>
       <c r="E88">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F88">
         <v>0</v>
@@ -3452,13 +3452,13 @@
         <v>37</v>
       </c>
       <c r="C127">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D127">
         <v>0</v>
       </c>
       <c r="E127">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F127">
         <v>0</v>
@@ -3492,13 +3492,13 @@
         <v>36</v>
       </c>
       <c r="C129">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D129">
         <v>0</v>
       </c>
       <c r="E129">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F129">
         <v>0</v>

--- a/resumo_busca_ativa_consolidado.xlsx
+++ b/resumo_busca_ativa_consolidado.xlsx
@@ -862,16 +862,16 @@
         <v>19133</v>
       </c>
       <c r="C2">
-        <v>1776</v>
+        <v>1805</v>
       </c>
       <c r="D2">
-        <v>1033</v>
+        <v>1018</v>
       </c>
       <c r="E2">
-        <v>16324</v>
+        <v>16252</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -882,13 +882,13 @@
         <v>16817</v>
       </c>
       <c r="C3">
-        <v>1223</v>
+        <v>1245</v>
       </c>
       <c r="D3">
-        <v>1043</v>
+        <v>1055</v>
       </c>
       <c r="E3">
-        <v>14473</v>
+        <v>14439</v>
       </c>
       <c r="F3">
         <v>78</v>
@@ -902,16 +902,16 @@
         <v>9446</v>
       </c>
       <c r="C4">
-        <v>971</v>
+        <v>981</v>
       </c>
       <c r="D4">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="E4">
-        <v>7446</v>
+        <v>7433</v>
       </c>
       <c r="F4">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -952,13 +952,13 @@
         <v>9670</v>
       </c>
       <c r="C2">
-        <v>737</v>
+        <v>746</v>
       </c>
       <c r="D2">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="E2">
-        <v>8364</v>
+        <v>8347</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -972,13 +972,13 @@
         <v>2381</v>
       </c>
       <c r="C3">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D3">
         <v>237</v>
       </c>
       <c r="E3">
-        <v>1915</v>
+        <v>1913</v>
       </c>
       <c r="F3">
         <v>48</v>
@@ -992,13 +992,13 @@
         <v>1735</v>
       </c>
       <c r="C4">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D4">
         <v>204</v>
       </c>
       <c r="E4">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="F4">
         <v>19</v>
@@ -1012,13 +1012,13 @@
         <v>1649</v>
       </c>
       <c r="C5">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="D5">
         <v>181</v>
       </c>
       <c r="E5">
-        <v>1336</v>
+        <v>1332</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1035,13 +1035,13 @@
         <v>165</v>
       </c>
       <c r="D6">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="E6">
-        <v>1134</v>
+        <v>1137</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1052,10 +1052,10 @@
         <v>1280</v>
       </c>
       <c r="C7">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D7">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E7">
         <v>953</v>
@@ -1072,13 +1072,13 @@
         <v>1203</v>
       </c>
       <c r="C8">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -1092,13 +1092,13 @@
         <v>1135</v>
       </c>
       <c r="C9">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D9">
         <v>209</v>
       </c>
       <c r="E9">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -1112,13 +1112,13 @@
         <v>977</v>
       </c>
       <c r="C10">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D10">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E10">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1172,13 +1172,13 @@
         <v>843</v>
       </c>
       <c r="C13">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D13">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="E13">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="F13">
         <v>102</v>
@@ -1192,13 +1192,13 @@
         <v>813</v>
       </c>
       <c r="C14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1235,10 +1235,10 @@
         <v>69</v>
       </c>
       <c r="D16">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="E16">
-        <v>586</v>
+        <v>568</v>
       </c>
       <c r="F16">
         <v>26</v>
@@ -1252,13 +1252,13 @@
         <v>729</v>
       </c>
       <c r="C17">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1272,13 +1272,13 @@
         <v>695</v>
       </c>
       <c r="C18">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D18">
         <v>36</v>
       </c>
       <c r="E18">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1332,13 +1332,13 @@
         <v>616</v>
       </c>
       <c r="C21">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D21">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E21">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1355,10 +1355,10 @@
         <v>78</v>
       </c>
       <c r="D22">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E22">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1372,13 +1372,13 @@
         <v>601</v>
       </c>
       <c r="C23">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D23">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="E23">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="F23">
         <v>17</v>
@@ -1392,13 +1392,13 @@
         <v>503</v>
       </c>
       <c r="C24">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D24">
         <v>0</v>
       </c>
       <c r="E24">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1412,13 +1412,13 @@
         <v>495</v>
       </c>
       <c r="C25">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D25">
         <v>1</v>
       </c>
       <c r="E25">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1432,13 +1432,13 @@
         <v>449</v>
       </c>
       <c r="C26">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D26">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="E26">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -1475,10 +1475,10 @@
         <v>31</v>
       </c>
       <c r="D28">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E28">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -1512,13 +1512,13 @@
         <v>402</v>
       </c>
       <c r="C30">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D30">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E30">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -1552,13 +1552,13 @@
         <v>389</v>
       </c>
       <c r="C32">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E32">
-        <v>372</v>
+        <v>355</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -1595,10 +1595,10 @@
         <v>58</v>
       </c>
       <c r="D34">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E34">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F34">
         <v>0</v>
@@ -1612,10 +1612,10 @@
         <v>269</v>
       </c>
       <c r="C35">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D35">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E35">
         <v>199</v>
@@ -1695,10 +1695,10 @@
         <v>26</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E39">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -1712,13 +1712,13 @@
         <v>224</v>
       </c>
       <c r="C40">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D40">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="E40">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -1732,13 +1732,13 @@
         <v>223</v>
       </c>
       <c r="C41">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D41">
         <v>0</v>
       </c>
       <c r="E41">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -1832,13 +1832,13 @@
         <v>182</v>
       </c>
       <c r="C46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D46">
         <v>0</v>
       </c>
       <c r="E46">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F46">
         <v>3</v>
@@ -1958,10 +1958,10 @@
         <v>0</v>
       </c>
       <c r="E52">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="F52">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -2052,13 +2052,13 @@
         <v>128</v>
       </c>
       <c r="C57">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D57">
         <v>0</v>
       </c>
       <c r="E57">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F57">
         <v>0</v>
@@ -2072,13 +2072,13 @@
         <v>127</v>
       </c>
       <c r="C58">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D58">
         <v>0</v>
       </c>
       <c r="E58">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F58">
         <v>0</v>
@@ -2115,10 +2115,10 @@
         <v>31</v>
       </c>
       <c r="D60">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E60">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -2475,13 +2475,13 @@
         <v>25</v>
       </c>
       <c r="D78">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E78">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="F78">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -3532,13 +3532,13 @@
         <v>35</v>
       </c>
       <c r="C131">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D131">
         <v>0</v>
       </c>
       <c r="E131">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F131">
         <v>0</v>
@@ -3572,13 +3572,13 @@
         <v>34</v>
       </c>
       <c r="C133">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D133">
         <v>0</v>
       </c>
       <c r="E133">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F133">
         <v>0</v>

--- a/resumo_busca_ativa_consolidado.xlsx
+++ b/resumo_busca_ativa_consolidado.xlsx
@@ -862,13 +862,13 @@
         <v>19133</v>
       </c>
       <c r="C2">
-        <v>1805</v>
+        <v>1818</v>
       </c>
       <c r="D2">
-        <v>1018</v>
+        <v>991</v>
       </c>
       <c r="E2">
-        <v>16252</v>
+        <v>16266</v>
       </c>
       <c r="F2">
         <v>58</v>
@@ -885,10 +885,10 @@
         <v>1245</v>
       </c>
       <c r="D3">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="E3">
-        <v>14439</v>
+        <v>14441</v>
       </c>
       <c r="F3">
         <v>78</v>
@@ -902,16 +902,16 @@
         <v>9446</v>
       </c>
       <c r="C4">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="D4">
-        <v>857</v>
+        <v>882</v>
       </c>
       <c r="E4">
-        <v>7433</v>
+        <v>7409</v>
       </c>
       <c r="F4">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -952,13 +952,13 @@
         <v>9670</v>
       </c>
       <c r="C2">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="D2">
-        <v>577</v>
+        <v>558</v>
       </c>
       <c r="E2">
-        <v>8347</v>
+        <v>8361</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -975,10 +975,10 @@
         <v>183</v>
       </c>
       <c r="D3">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E3">
-        <v>1913</v>
+        <v>1915</v>
       </c>
       <c r="F3">
         <v>48</v>
@@ -1032,16 +1032,16 @@
         <v>1500</v>
       </c>
       <c r="C6">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D6">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="E6">
-        <v>1137</v>
+        <v>1133</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1055,10 +1055,10 @@
         <v>216</v>
       </c>
       <c r="D7">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E7">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="F7">
         <v>12</v>
@@ -1235,10 +1235,10 @@
         <v>69</v>
       </c>
       <c r="D16">
-        <v>127</v>
+        <v>149</v>
       </c>
       <c r="E16">
-        <v>568</v>
+        <v>546</v>
       </c>
       <c r="F16">
         <v>26</v>
@@ -1712,13 +1712,13 @@
         <v>224</v>
       </c>
       <c r="C40">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D40">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="E40">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -1732,13 +1732,13 @@
         <v>223</v>
       </c>
       <c r="C41">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E41">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -1932,13 +1932,13 @@
         <v>151</v>
       </c>
       <c r="C51">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D51">
         <v>23</v>
       </c>
       <c r="E51">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F51">
         <v>0</v>

--- a/resumo_busca_ativa_consolidado.xlsx
+++ b/resumo_busca_ativa_consolidado.xlsx
@@ -862,13 +862,13 @@
         <v>19133</v>
       </c>
       <c r="C2">
-        <v>1818</v>
+        <v>1843</v>
       </c>
       <c r="D2">
-        <v>991</v>
+        <v>975</v>
       </c>
       <c r="E2">
-        <v>16266</v>
+        <v>16257</v>
       </c>
       <c r="F2">
         <v>58</v>
@@ -882,13 +882,13 @@
         <v>16817</v>
       </c>
       <c r="C3">
-        <v>1245</v>
+        <v>1253</v>
       </c>
       <c r="D3">
         <v>1053</v>
       </c>
       <c r="E3">
-        <v>14441</v>
+        <v>14433</v>
       </c>
       <c r="F3">
         <v>78</v>
@@ -902,13 +902,13 @@
         <v>9446</v>
       </c>
       <c r="C4">
-        <v>982</v>
+        <v>1003</v>
       </c>
       <c r="D4">
-        <v>882</v>
+        <v>858</v>
       </c>
       <c r="E4">
-        <v>7409</v>
+        <v>7412</v>
       </c>
       <c r="F4">
         <v>173</v>
@@ -952,13 +952,13 @@
         <v>9670</v>
       </c>
       <c r="C2">
-        <v>751</v>
+        <v>761</v>
       </c>
       <c r="D2">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="E2">
-        <v>8361</v>
+        <v>8356</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -972,13 +972,13 @@
         <v>2381</v>
       </c>
       <c r="C3">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D3">
         <v>235</v>
       </c>
       <c r="E3">
-        <v>1915</v>
+        <v>1913</v>
       </c>
       <c r="F3">
         <v>48</v>
@@ -1012,13 +1012,13 @@
         <v>1649</v>
       </c>
       <c r="C5">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D5">
         <v>181</v>
       </c>
       <c r="E5">
-        <v>1332</v>
+        <v>1330</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1032,13 +1032,13 @@
         <v>1500</v>
       </c>
       <c r="C6">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D6">
         <v>200</v>
       </c>
       <c r="E6">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1132,13 +1132,13 @@
         <v>920</v>
       </c>
       <c r="C11">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D11">
         <v>22</v>
       </c>
       <c r="E11">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1152,13 +1152,13 @@
         <v>911</v>
       </c>
       <c r="C12">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="F12">
         <v>3</v>
@@ -1232,13 +1232,13 @@
         <v>790</v>
       </c>
       <c r="C16">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="D16">
-        <v>149</v>
+        <v>125</v>
       </c>
       <c r="E16">
-        <v>546</v>
+        <v>555</v>
       </c>
       <c r="F16">
         <v>26</v>
@@ -1292,13 +1292,13 @@
         <v>667</v>
       </c>
       <c r="C19">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D19">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="E19">
-        <v>550</v>
+        <v>560</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1332,13 +1332,13 @@
         <v>616</v>
       </c>
       <c r="C21">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D21">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E21">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1352,13 +1352,13 @@
         <v>611</v>
       </c>
       <c r="C22">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D22">
         <v>11</v>
       </c>
       <c r="E22">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1452,13 +1452,13 @@
         <v>448</v>
       </c>
       <c r="C27">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D27">
         <v>0</v>
       </c>
       <c r="E27">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -1492,13 +1492,13 @@
         <v>406</v>
       </c>
       <c r="C29">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D29">
         <v>73</v>
       </c>
       <c r="E29">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F29">
         <v>0</v>
@@ -1532,13 +1532,13 @@
         <v>394</v>
       </c>
       <c r="C31">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D31">
         <v>1</v>
       </c>
       <c r="E31">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F31">
         <v>0</v>
@@ -1932,13 +1932,13 @@
         <v>151</v>
       </c>
       <c r="C51">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D51">
         <v>23</v>
       </c>
       <c r="E51">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -2072,13 +2072,13 @@
         <v>127</v>
       </c>
       <c r="C58">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E58">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="F58">
         <v>0</v>
@@ -2532,13 +2532,13 @@
         <v>76</v>
       </c>
       <c r="C81">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D81">
         <v>0</v>
       </c>
       <c r="E81">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F81">
         <v>0</v>
@@ -2752,13 +2752,13 @@
         <v>65</v>
       </c>
       <c r="C92">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D92">
         <v>0</v>
       </c>
       <c r="E92">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F92">
         <v>0</v>
@@ -2952,13 +2952,13 @@
         <v>57</v>
       </c>
       <c r="C102">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D102">
         <v>0</v>
       </c>
       <c r="E102">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F102">
         <v>0</v>

--- a/resumo_busca_ativa_consolidado.xlsx
+++ b/resumo_busca_ativa_consolidado.xlsx
@@ -862,16 +862,16 @@
         <v>19133</v>
       </c>
       <c r="C2">
-        <v>1843</v>
+        <v>1907</v>
       </c>
       <c r="D2">
-        <v>975</v>
+        <v>1084</v>
       </c>
       <c r="E2">
-        <v>16257</v>
+        <v>16142</v>
       </c>
       <c r="F2">
-        <v>58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -882,13 +882,13 @@
         <v>16817</v>
       </c>
       <c r="C3">
-        <v>1253</v>
+        <v>1329</v>
       </c>
       <c r="D3">
-        <v>1053</v>
+        <v>1069</v>
       </c>
       <c r="E3">
-        <v>14433</v>
+        <v>14341</v>
       </c>
       <c r="F3">
         <v>78</v>
@@ -902,16 +902,16 @@
         <v>9446</v>
       </c>
       <c r="C4">
-        <v>1003</v>
+        <v>1032</v>
       </c>
       <c r="D4">
-        <v>858</v>
+        <v>886</v>
       </c>
       <c r="E4">
-        <v>7412</v>
+        <v>7338</v>
       </c>
       <c r="F4">
-        <v>173</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -952,13 +952,13 @@
         <v>9670</v>
       </c>
       <c r="C2">
-        <v>761</v>
+        <v>779</v>
       </c>
       <c r="D2">
-        <v>553</v>
+        <v>543</v>
       </c>
       <c r="E2">
-        <v>8356</v>
+        <v>8348</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -972,13 +972,13 @@
         <v>2381</v>
       </c>
       <c r="C3">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="D3">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E3">
-        <v>1913</v>
+        <v>1910</v>
       </c>
       <c r="F3">
         <v>48</v>
@@ -992,13 +992,13 @@
         <v>1735</v>
       </c>
       <c r="C4">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D4">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E4">
-        <v>1389</v>
+        <v>1387</v>
       </c>
       <c r="F4">
         <v>19</v>
@@ -1012,13 +1012,13 @@
         <v>1649</v>
       </c>
       <c r="C5">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="D5">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="E5">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1032,13 +1032,13 @@
         <v>1500</v>
       </c>
       <c r="C6">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="D6">
-        <v>200</v>
+        <v>247</v>
       </c>
       <c r="E6">
-        <v>1131</v>
+        <v>1077</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1052,13 +1052,13 @@
         <v>1280</v>
       </c>
       <c r="C7">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="D7">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="E7">
-        <v>955</v>
+        <v>961</v>
       </c>
       <c r="F7">
         <v>12</v>
@@ -1072,13 +1072,13 @@
         <v>1203</v>
       </c>
       <c r="C8">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -1092,13 +1092,13 @@
         <v>1135</v>
       </c>
       <c r="C9">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="D9">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="E9">
-        <v>806</v>
+        <v>775</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -1112,13 +1112,13 @@
         <v>977</v>
       </c>
       <c r="C10">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="D10">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E10">
-        <v>838</v>
+        <v>832</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1132,13 +1132,13 @@
         <v>920</v>
       </c>
       <c r="C11">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D11">
         <v>22</v>
       </c>
       <c r="E11">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1152,13 +1152,13 @@
         <v>911</v>
       </c>
       <c r="C12">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12">
-        <v>848</v>
+        <v>827</v>
       </c>
       <c r="F12">
         <v>3</v>
@@ -1172,13 +1172,13 @@
         <v>843</v>
       </c>
       <c r="C13">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D13">
         <v>82</v>
       </c>
       <c r="E13">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="F13">
         <v>102</v>
@@ -1192,13 +1192,13 @@
         <v>813</v>
       </c>
       <c r="C14">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1212,13 +1212,13 @@
         <v>811</v>
       </c>
       <c r="C15">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15">
         <v>58</v>
       </c>
       <c r="E15">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -1232,16 +1232,16 @@
         <v>790</v>
       </c>
       <c r="C16">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D16">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E16">
-        <v>555</v>
+        <v>537</v>
       </c>
       <c r="F16">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1252,13 +1252,13 @@
         <v>729</v>
       </c>
       <c r="C17">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E17">
-        <v>693</v>
+        <v>682</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1272,13 +1272,13 @@
         <v>695</v>
       </c>
       <c r="C18">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D18">
         <v>36</v>
       </c>
       <c r="E18">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1292,13 +1292,13 @@
         <v>667</v>
       </c>
       <c r="C19">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D19">
         <v>23</v>
       </c>
       <c r="E19">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1312,13 +1312,13 @@
         <v>646</v>
       </c>
       <c r="C20">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D20">
         <v>38</v>
       </c>
       <c r="E20">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1332,13 +1332,13 @@
         <v>616</v>
       </c>
       <c r="C21">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D21">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E21">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1352,13 +1352,13 @@
         <v>611</v>
       </c>
       <c r="C22">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D22">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E22">
-        <v>519</v>
+        <v>529</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1372,13 +1372,13 @@
         <v>601</v>
       </c>
       <c r="C23">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D23">
         <v>84</v>
       </c>
       <c r="E23">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="F23">
         <v>17</v>
@@ -1392,13 +1392,13 @@
         <v>503</v>
       </c>
       <c r="C24">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E24">
-        <v>466</v>
+        <v>444</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1412,13 +1412,13 @@
         <v>495</v>
       </c>
       <c r="C25">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E25">
-        <v>438</v>
+        <v>419</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1432,13 +1432,13 @@
         <v>449</v>
       </c>
       <c r="C26">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D26">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E26">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -1452,13 +1452,13 @@
         <v>448</v>
       </c>
       <c r="C27">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D27">
         <v>0</v>
       </c>
       <c r="E27">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -1472,13 +1472,13 @@
         <v>441</v>
       </c>
       <c r="C28">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D28">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E28">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -1492,10 +1492,10 @@
         <v>406</v>
       </c>
       <c r="C29">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D29">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E29">
         <v>307</v>
@@ -1512,13 +1512,13 @@
         <v>402</v>
       </c>
       <c r="C30">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D30">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E30">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -1532,13 +1532,13 @@
         <v>394</v>
       </c>
       <c r="C31">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D31">
-        <v>1</v>
+        <v>96</v>
       </c>
       <c r="E31">
-        <v>306</v>
+        <v>210</v>
       </c>
       <c r="F31">
         <v>0</v>
@@ -1552,13 +1552,13 @@
         <v>389</v>
       </c>
       <c r="C32">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D32">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E32">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -1572,13 +1572,13 @@
         <v>316</v>
       </c>
       <c r="C33">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D33">
         <v>0</v>
       </c>
       <c r="E33">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -1612,13 +1612,13 @@
         <v>269</v>
       </c>
       <c r="C35">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D35">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E35">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -1632,13 +1632,13 @@
         <v>246</v>
       </c>
       <c r="C36">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D36">
         <v>0</v>
       </c>
       <c r="E36">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -1652,13 +1652,13 @@
         <v>238</v>
       </c>
       <c r="C37">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D37">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E37">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -1692,13 +1692,13 @@
         <v>232</v>
       </c>
       <c r="C39">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D39">
         <v>11</v>
       </c>
       <c r="E39">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -1712,13 +1712,13 @@
         <v>224</v>
       </c>
       <c r="C40">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="D40">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E40">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -1735,10 +1735,10 @@
         <v>18</v>
       </c>
       <c r="D41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E41">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -1752,13 +1752,13 @@
         <v>207</v>
       </c>
       <c r="C42">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D42">
         <v>0</v>
       </c>
       <c r="E42">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F42">
         <v>0</v>
@@ -1772,10 +1772,10 @@
         <v>200</v>
       </c>
       <c r="C43">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D43">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E43">
         <v>164</v>
@@ -1792,13 +1792,13 @@
         <v>194</v>
       </c>
       <c r="C44">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D44">
         <v>0</v>
       </c>
       <c r="E44">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F44">
         <v>0</v>
@@ -1932,13 +1932,13 @@
         <v>151</v>
       </c>
       <c r="C51">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D51">
         <v>23</v>
       </c>
       <c r="E51">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -1955,13 +1955,13 @@
         <v>12</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E52">
         <v>120</v>
       </c>
       <c r="F52">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -2072,13 +2072,13 @@
         <v>127</v>
       </c>
       <c r="C58">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D58">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E58">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F58">
         <v>0</v>
@@ -2192,13 +2192,13 @@
         <v>108</v>
       </c>
       <c r="C64">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D64">
         <v>0</v>
       </c>
       <c r="E64">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -2312,13 +2312,13 @@
         <v>99</v>
       </c>
       <c r="C70">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D70">
         <v>0</v>
       </c>
       <c r="E70">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F70">
         <v>3</v>
@@ -2352,13 +2352,13 @@
         <v>89</v>
       </c>
       <c r="C72">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D72">
         <v>0</v>
       </c>
       <c r="E72">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F72">
         <v>0</v>
@@ -2372,13 +2372,13 @@
         <v>88</v>
       </c>
       <c r="C73">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D73">
         <v>0</v>
       </c>
       <c r="E73">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F73">
         <v>0</v>
@@ -2472,16 +2472,16 @@
         <v>80</v>
       </c>
       <c r="C78">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D78">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="E78">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F78">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -3352,13 +3352,13 @@
         <v>39</v>
       </c>
       <c r="C122">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D122">
         <v>0</v>
       </c>
       <c r="E122">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F122">
         <v>0</v>

--- a/resumo_busca_ativa_consolidado.xlsx
+++ b/resumo_busca_ativa_consolidado.xlsx
@@ -862,13 +862,13 @@
         <v>19133</v>
       </c>
       <c r="C2">
-        <v>1907</v>
+        <v>1913</v>
       </c>
       <c r="D2">
-        <v>1084</v>
+        <v>1080</v>
       </c>
       <c r="E2">
-        <v>16142</v>
+        <v>16140</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -882,13 +882,13 @@
         <v>16817</v>
       </c>
       <c r="C3">
-        <v>1329</v>
+        <v>1334</v>
       </c>
       <c r="D3">
         <v>1069</v>
       </c>
       <c r="E3">
-        <v>14341</v>
+        <v>14336</v>
       </c>
       <c r="F3">
         <v>78</v>
@@ -902,13 +902,13 @@
         <v>9446</v>
       </c>
       <c r="C4">
-        <v>1032</v>
+        <v>1029</v>
       </c>
       <c r="D4">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="E4">
-        <v>7338</v>
+        <v>7343</v>
       </c>
       <c r="F4">
         <v>190</v>
@@ -952,13 +952,13 @@
         <v>9670</v>
       </c>
       <c r="C2">
-        <v>779</v>
+        <v>784</v>
       </c>
       <c r="D2">
-        <v>543</v>
+        <v>533</v>
       </c>
       <c r="E2">
-        <v>8348</v>
+        <v>8353</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -992,13 +992,13 @@
         <v>1735</v>
       </c>
       <c r="C4">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D4">
         <v>203</v>
       </c>
       <c r="E4">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="F4">
         <v>19</v>
@@ -1055,10 +1055,10 @@
         <v>230</v>
       </c>
       <c r="D7">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E7">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="F7">
         <v>12</v>
@@ -1135,10 +1135,10 @@
         <v>64</v>
       </c>
       <c r="D11">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E11">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1152,13 +1152,13 @@
         <v>911</v>
       </c>
       <c r="C12">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12">
-        <v>827</v>
+        <v>821</v>
       </c>
       <c r="F12">
         <v>3</v>
@@ -1232,13 +1232,13 @@
         <v>790</v>
       </c>
       <c r="C16">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D16">
         <v>129</v>
       </c>
       <c r="E16">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="F16">
         <v>43</v>
@@ -1332,13 +1332,13 @@
         <v>616</v>
       </c>
       <c r="C21">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D21">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="E21">
-        <v>453</v>
+        <v>439</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1612,13 +1612,13 @@
         <v>269</v>
       </c>
       <c r="C35">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D35">
         <v>27</v>
       </c>
       <c r="E35">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -1715,10 +1715,10 @@
         <v>49</v>
       </c>
       <c r="D40">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E40">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="F40">
         <v>0</v>

--- a/resumo_busca_ativa_consolidado.xlsx
+++ b/resumo_busca_ativa_consolidado.xlsx
@@ -862,16 +862,16 @@
         <v>19133</v>
       </c>
       <c r="C2">
-        <v>1913</v>
+        <v>1950</v>
       </c>
       <c r="D2">
-        <v>1080</v>
+        <v>1129</v>
       </c>
       <c r="E2">
-        <v>16140</v>
+        <v>16038</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -882,13 +882,13 @@
         <v>16817</v>
       </c>
       <c r="C3">
-        <v>1334</v>
+        <v>1396</v>
       </c>
       <c r="D3">
-        <v>1069</v>
+        <v>1084</v>
       </c>
       <c r="E3">
-        <v>14336</v>
+        <v>14259</v>
       </c>
       <c r="F3">
         <v>78</v>
@@ -902,16 +902,16 @@
         <v>9446</v>
       </c>
       <c r="C4">
-        <v>1029</v>
+        <v>1062</v>
       </c>
       <c r="D4">
-        <v>884</v>
+        <v>870</v>
       </c>
       <c r="E4">
-        <v>7343</v>
+        <v>7323</v>
       </c>
       <c r="F4">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>
@@ -952,13 +952,13 @@
         <v>9670</v>
       </c>
       <c r="C2">
-        <v>784</v>
+        <v>800</v>
       </c>
       <c r="D2">
-        <v>533</v>
+        <v>515</v>
       </c>
       <c r="E2">
-        <v>8353</v>
+        <v>8355</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -972,13 +972,13 @@
         <v>2381</v>
       </c>
       <c r="C3">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="D3">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="E3">
-        <v>1910</v>
+        <v>1897</v>
       </c>
       <c r="F3">
         <v>48</v>
@@ -992,13 +992,13 @@
         <v>1735</v>
       </c>
       <c r="C4">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D4">
         <v>203</v>
       </c>
       <c r="E4">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="F4">
         <v>19</v>
@@ -1012,13 +1012,13 @@
         <v>1649</v>
       </c>
       <c r="C5">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="D5">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E5">
-        <v>1331</v>
+        <v>1327</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1032,16 +1032,16 @@
         <v>1500</v>
       </c>
       <c r="C6">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="D6">
-        <v>247</v>
+        <v>266</v>
       </c>
       <c r="E6">
-        <v>1077</v>
+        <v>1051</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1052,13 +1052,13 @@
         <v>1280</v>
       </c>
       <c r="C7">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="D7">
         <v>76</v>
       </c>
       <c r="E7">
-        <v>962</v>
+        <v>954</v>
       </c>
       <c r="F7">
         <v>12</v>
@@ -1072,13 +1072,13 @@
         <v>1203</v>
       </c>
       <c r="C8">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -1092,13 +1092,13 @@
         <v>1135</v>
       </c>
       <c r="C9">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D9">
-        <v>232</v>
+        <v>214</v>
       </c>
       <c r="E9">
-        <v>775</v>
+        <v>791</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -1112,13 +1112,13 @@
         <v>977</v>
       </c>
       <c r="C10">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="D10">
         <v>23</v>
       </c>
       <c r="E10">
-        <v>832</v>
+        <v>825</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1132,13 +1132,13 @@
         <v>920</v>
       </c>
       <c r="C11">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D11">
         <v>21</v>
       </c>
       <c r="E11">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1152,13 +1152,13 @@
         <v>911</v>
       </c>
       <c r="C12">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12">
-        <v>821</v>
+        <v>806</v>
       </c>
       <c r="F12">
         <v>3</v>
@@ -1172,13 +1172,13 @@
         <v>843</v>
       </c>
       <c r="C13">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D13">
         <v>82</v>
       </c>
       <c r="E13">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="F13">
         <v>102</v>
@@ -1192,13 +1192,13 @@
         <v>813</v>
       </c>
       <c r="C14">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1212,13 +1212,13 @@
         <v>811</v>
       </c>
       <c r="C15">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D15">
         <v>58</v>
       </c>
       <c r="E15">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -1232,13 +1232,13 @@
         <v>790</v>
       </c>
       <c r="C16">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D16">
-        <v>129</v>
+        <v>108</v>
       </c>
       <c r="E16">
-        <v>540</v>
+        <v>557</v>
       </c>
       <c r="F16">
         <v>43</v>
@@ -1252,13 +1252,13 @@
         <v>729</v>
       </c>
       <c r="C17">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D17">
         <v>9</v>
       </c>
       <c r="E17">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1272,13 +1272,13 @@
         <v>695</v>
       </c>
       <c r="C18">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D18">
         <v>36</v>
       </c>
       <c r="E18">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1292,13 +1292,13 @@
         <v>667</v>
       </c>
       <c r="C19">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D19">
         <v>23</v>
       </c>
       <c r="E19">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1332,13 +1332,13 @@
         <v>616</v>
       </c>
       <c r="C21">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D21">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="E21">
-        <v>439</v>
+        <v>456</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1352,13 +1352,13 @@
         <v>611</v>
       </c>
       <c r="C22">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="E22">
-        <v>529</v>
+        <v>484</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1372,13 +1372,13 @@
         <v>601</v>
       </c>
       <c r="C23">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="D23">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="E23">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="F23">
         <v>17</v>
@@ -1392,10 +1392,10 @@
         <v>503</v>
       </c>
       <c r="C24">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D24">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E24">
         <v>444</v>
@@ -1412,13 +1412,13 @@
         <v>495</v>
       </c>
       <c r="C25">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D25">
         <v>15</v>
       </c>
       <c r="E25">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1432,10 +1432,10 @@
         <v>449</v>
       </c>
       <c r="C26">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D26">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E26">
         <v>268</v>
@@ -1452,13 +1452,13 @@
         <v>448</v>
       </c>
       <c r="C27">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D27">
         <v>0</v>
       </c>
       <c r="E27">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -1478,10 +1478,10 @@
         <v>59</v>
       </c>
       <c r="E28">
-        <v>346</v>
+        <v>330</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -1512,13 +1512,13 @@
         <v>402</v>
       </c>
       <c r="C30">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D30">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="E30">
-        <v>323</v>
+        <v>308</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -1532,10 +1532,10 @@
         <v>394</v>
       </c>
       <c r="C31">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D31">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E31">
         <v>210</v>
@@ -1552,13 +1552,13 @@
         <v>389</v>
       </c>
       <c r="C32">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D32">
         <v>0</v>
       </c>
       <c r="E32">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -1572,13 +1572,13 @@
         <v>316</v>
       </c>
       <c r="C33">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D33">
         <v>0</v>
       </c>
       <c r="E33">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -1612,13 +1612,13 @@
         <v>269</v>
       </c>
       <c r="C35">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D35">
         <v>27</v>
       </c>
       <c r="E35">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -1632,13 +1632,13 @@
         <v>246</v>
       </c>
       <c r="C36">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D36">
         <v>0</v>
       </c>
       <c r="E36">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -1672,13 +1672,13 @@
         <v>237</v>
       </c>
       <c r="C38">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D38">
         <v>71</v>
       </c>
       <c r="E38">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F38">
         <v>0</v>
@@ -1695,10 +1695,10 @@
         <v>27</v>
       </c>
       <c r="D39">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="E39">
-        <v>194</v>
+        <v>158</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -1712,13 +1712,13 @@
         <v>224</v>
       </c>
       <c r="C40">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E40">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -1835,10 +1835,10 @@
         <v>3</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E46">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="F46">
         <v>3</v>
@@ -1932,13 +1932,13 @@
         <v>151</v>
       </c>
       <c r="C51">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D51">
         <v>23</v>
       </c>
       <c r="E51">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -2052,13 +2052,13 @@
         <v>128</v>
       </c>
       <c r="C57">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D57">
         <v>0</v>
       </c>
       <c r="E57">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F57">
         <v>0</v>
@@ -2112,10 +2112,10 @@
         <v>124</v>
       </c>
       <c r="C60">
+        <v>32</v>
+      </c>
+      <c r="D60">
         <v>31</v>
-      </c>
-      <c r="D60">
-        <v>32</v>
       </c>
       <c r="E60">
         <v>61</v>
@@ -2292,13 +2292,13 @@
         <v>100</v>
       </c>
       <c r="C69">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D69">
         <v>0</v>
       </c>
       <c r="E69">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F69">
         <v>0</v>
@@ -2452,13 +2452,13 @@
         <v>81</v>
       </c>
       <c r="C77">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D77">
         <v>0</v>
       </c>
       <c r="E77">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F77">
         <v>0</v>
@@ -2472,10 +2472,10 @@
         <v>80</v>
       </c>
       <c r="C78">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D78">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E78">
         <v>13</v>
@@ -2752,13 +2752,13 @@
         <v>65</v>
       </c>
       <c r="C92">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D92">
         <v>0</v>
       </c>
       <c r="E92">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="F92">
         <v>0</v>
@@ -3292,13 +3292,13 @@
         <v>43</v>
       </c>
       <c r="C119">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D119">
         <v>0</v>
       </c>
       <c r="E119">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F119">
         <v>0</v>
@@ -3472,13 +3472,13 @@
         <v>36</v>
       </c>
       <c r="C128">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D128">
         <v>0</v>
       </c>
       <c r="E128">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F128">
         <v>0</v>
@@ -3592,13 +3592,13 @@
         <v>33</v>
       </c>
       <c r="C134">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D134">
         <v>0</v>
       </c>
       <c r="E134">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F134">
         <v>0</v>

--- a/resumo_busca_ativa_consolidado.xlsx
+++ b/resumo_busca_ativa_consolidado.xlsx
@@ -862,13 +862,13 @@
         <v>19133</v>
       </c>
       <c r="C2">
-        <v>1950</v>
+        <v>1974</v>
       </c>
       <c r="D2">
-        <v>1129</v>
+        <v>1119</v>
       </c>
       <c r="E2">
-        <v>16038</v>
+        <v>16024</v>
       </c>
       <c r="F2">
         <v>16</v>
@@ -882,13 +882,13 @@
         <v>16817</v>
       </c>
       <c r="C3">
-        <v>1396</v>
+        <v>1426</v>
       </c>
       <c r="D3">
-        <v>1084</v>
+        <v>1094</v>
       </c>
       <c r="E3">
-        <v>14259</v>
+        <v>14219</v>
       </c>
       <c r="F3">
         <v>78</v>
@@ -902,13 +902,13 @@
         <v>9446</v>
       </c>
       <c r="C4">
-        <v>1062</v>
+        <v>1077</v>
       </c>
       <c r="D4">
-        <v>870</v>
+        <v>861</v>
       </c>
       <c r="E4">
-        <v>7323</v>
+        <v>7317</v>
       </c>
       <c r="F4">
         <v>191</v>
@@ -952,13 +952,13 @@
         <v>9670</v>
       </c>
       <c r="C2">
-        <v>800</v>
+        <v>811</v>
       </c>
       <c r="D2">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="E2">
-        <v>8355</v>
+        <v>8349</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -972,13 +972,13 @@
         <v>2381</v>
       </c>
       <c r="C3">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="D3">
         <v>244</v>
       </c>
       <c r="E3">
-        <v>1897</v>
+        <v>1893</v>
       </c>
       <c r="F3">
         <v>48</v>
@@ -992,13 +992,13 @@
         <v>1735</v>
       </c>
       <c r="C4">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D4">
         <v>203</v>
       </c>
       <c r="E4">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="F4">
         <v>19</v>
@@ -1032,13 +1032,13 @@
         <v>1500</v>
       </c>
       <c r="C6">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="D6">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="E6">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="F6">
         <v>2</v>
@@ -1052,13 +1052,13 @@
         <v>1280</v>
       </c>
       <c r="C7">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D7">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E7">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="F7">
         <v>12</v>
@@ -1092,13 +1092,13 @@
         <v>1135</v>
       </c>
       <c r="C9">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D9">
         <v>214</v>
       </c>
       <c r="E9">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -1112,13 +1112,13 @@
         <v>977</v>
       </c>
       <c r="C10">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="D10">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="E10">
-        <v>825</v>
+        <v>807</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1152,13 +1152,13 @@
         <v>911</v>
       </c>
       <c r="C12">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="F12">
         <v>3</v>
@@ -1172,10 +1172,10 @@
         <v>843</v>
       </c>
       <c r="C13">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D13">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E13">
         <v>551</v>
@@ -1232,13 +1232,13 @@
         <v>790</v>
       </c>
       <c r="C16">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D16">
         <v>108</v>
       </c>
       <c r="E16">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="F16">
         <v>43</v>
@@ -1332,13 +1332,13 @@
         <v>616</v>
       </c>
       <c r="C21">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D21">
         <v>27</v>
       </c>
       <c r="E21">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1352,13 +1352,13 @@
         <v>611</v>
       </c>
       <c r="C22">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D22">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E22">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1452,13 +1452,13 @@
         <v>448</v>
       </c>
       <c r="C27">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D27">
         <v>0</v>
       </c>
       <c r="E27">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -1552,13 +1552,13 @@
         <v>389</v>
       </c>
       <c r="C32">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D32">
         <v>0</v>
       </c>
       <c r="E32">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -1672,13 +1672,13 @@
         <v>237</v>
       </c>
       <c r="C38">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D38">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E38">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="F38">
         <v>0</v>
@@ -1692,13 +1692,13 @@
         <v>232</v>
       </c>
       <c r="C39">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D39">
         <v>47</v>
       </c>
       <c r="E39">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -1932,13 +1932,13 @@
         <v>151</v>
       </c>
       <c r="C51">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D51">
         <v>23</v>
       </c>
       <c r="E51">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -2032,13 +2032,13 @@
         <v>138</v>
       </c>
       <c r="C56">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D56">
         <v>0</v>
       </c>
       <c r="E56">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F56">
         <v>0</v>
@@ -2472,10 +2472,10 @@
         <v>80</v>
       </c>
       <c r="C78">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D78">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E78">
         <v>13</v>
@@ -3092,13 +3092,13 @@
         <v>52</v>
       </c>
       <c r="C109">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D109">
         <v>0</v>
       </c>
       <c r="E109">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F109">
         <v>0</v>
@@ -3272,13 +3272,13 @@
         <v>43</v>
       </c>
       <c r="C118">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D118">
         <v>1</v>
       </c>
       <c r="E118">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F118">
         <v>0</v>
@@ -3452,13 +3452,13 @@
         <v>37</v>
       </c>
       <c r="C127">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D127">
         <v>0</v>
       </c>
       <c r="E127">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F127">
         <v>0</v>

--- a/resumo_busca_ativa_consolidado.xlsx
+++ b/resumo_busca_ativa_consolidado.xlsx
@@ -862,16 +862,16 @@
         <v>19133</v>
       </c>
       <c r="C2">
-        <v>1974</v>
+        <v>2087</v>
       </c>
       <c r="D2">
-        <v>1119</v>
+        <v>1127</v>
       </c>
       <c r="E2">
-        <v>16024</v>
+        <v>15889</v>
       </c>
       <c r="F2">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -882,16 +882,16 @@
         <v>16817</v>
       </c>
       <c r="C3">
-        <v>1426</v>
+        <v>1525</v>
       </c>
       <c r="D3">
-        <v>1094</v>
+        <v>1073</v>
       </c>
       <c r="E3">
-        <v>14219</v>
+        <v>14123</v>
       </c>
       <c r="F3">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -902,16 +902,16 @@
         <v>9446</v>
       </c>
       <c r="C4">
-        <v>1077</v>
+        <v>1149</v>
       </c>
       <c r="D4">
-        <v>861</v>
+        <v>854</v>
       </c>
       <c r="E4">
-        <v>7317</v>
+        <v>7253</v>
       </c>
       <c r="F4">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -952,16 +952,16 @@
         <v>9670</v>
       </c>
       <c r="C2">
-        <v>811</v>
+        <v>853</v>
       </c>
       <c r="D2">
-        <v>510</v>
+        <v>495</v>
       </c>
       <c r="E2">
-        <v>8349</v>
+        <v>8308</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -972,16 +972,16 @@
         <v>2381</v>
       </c>
       <c r="C3">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="D3">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="E3">
-        <v>1893</v>
+        <v>1879</v>
       </c>
       <c r="F3">
-        <v>48</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -992,13 +992,13 @@
         <v>1735</v>
       </c>
       <c r="C4">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D4">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="E4">
-        <v>1386</v>
+        <v>1395</v>
       </c>
       <c r="F4">
         <v>19</v>
@@ -1012,13 +1012,13 @@
         <v>1649</v>
       </c>
       <c r="C5">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="D5">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="E5">
-        <v>1327</v>
+        <v>1310</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1032,16 +1032,16 @@
         <v>1500</v>
       </c>
       <c r="C6">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="D6">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="E6">
-        <v>1048</v>
+        <v>1032</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1052,13 +1052,13 @@
         <v>1280</v>
       </c>
       <c r="C7">
-        <v>241</v>
+        <v>263</v>
       </c>
       <c r="D7">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="E7">
-        <v>953</v>
+        <v>916</v>
       </c>
       <c r="F7">
         <v>12</v>
@@ -1072,13 +1072,13 @@
         <v>1203</v>
       </c>
       <c r="C8">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D8">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="E8">
-        <v>1121</v>
+        <v>1098</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -1092,13 +1092,13 @@
         <v>1135</v>
       </c>
       <c r="C9">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D9">
-        <v>214</v>
+        <v>240</v>
       </c>
       <c r="E9">
-        <v>790</v>
+        <v>760</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -1112,13 +1112,13 @@
         <v>977</v>
       </c>
       <c r="C10">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="D10">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E10">
-        <v>807</v>
+        <v>816</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1132,13 +1132,13 @@
         <v>920</v>
       </c>
       <c r="C11">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D11">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="E11">
-        <v>834</v>
+        <v>822</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1152,13 +1152,13 @@
         <v>911</v>
       </c>
       <c r="C12">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="F12">
         <v>3</v>
@@ -1172,13 +1172,13 @@
         <v>843</v>
       </c>
       <c r="C13">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D13">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E13">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="F13">
         <v>102</v>
@@ -1192,13 +1192,13 @@
         <v>813</v>
       </c>
       <c r="C14">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1212,10 +1212,10 @@
         <v>811</v>
       </c>
       <c r="C15">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D15">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E15">
         <v>702</v>
@@ -1232,13 +1232,13 @@
         <v>790</v>
       </c>
       <c r="C16">
-        <v>84</v>
+        <v>120</v>
       </c>
       <c r="D16">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="E16">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="F16">
         <v>43</v>
@@ -1272,13 +1272,13 @@
         <v>695</v>
       </c>
       <c r="C18">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D18">
         <v>36</v>
       </c>
       <c r="E18">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1292,13 +1292,13 @@
         <v>667</v>
       </c>
       <c r="C19">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D19">
         <v>23</v>
       </c>
       <c r="E19">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1312,13 +1312,13 @@
         <v>646</v>
       </c>
       <c r="C20">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D20">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E20">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1332,13 +1332,13 @@
         <v>616</v>
       </c>
       <c r="C21">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="D21">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="E21">
-        <v>454</v>
+        <v>402</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1352,13 +1352,13 @@
         <v>611</v>
       </c>
       <c r="C22">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D22">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="E22">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1372,10 +1372,10 @@
         <v>601</v>
       </c>
       <c r="C23">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D23">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E23">
         <v>426</v>
@@ -1392,13 +1392,13 @@
         <v>503</v>
       </c>
       <c r="C24">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="D24">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E24">
-        <v>444</v>
+        <v>455</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1412,13 +1412,13 @@
         <v>495</v>
       </c>
       <c r="C25">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="D25">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E25">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1432,13 +1432,13 @@
         <v>449</v>
       </c>
       <c r="C26">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D26">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E26">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -1452,13 +1452,13 @@
         <v>448</v>
       </c>
       <c r="C27">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D27">
         <v>0</v>
       </c>
       <c r="E27">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -1512,13 +1512,13 @@
         <v>402</v>
       </c>
       <c r="C30">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D30">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="E30">
-        <v>308</v>
+        <v>288</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -1532,10 +1532,10 @@
         <v>394</v>
       </c>
       <c r="C31">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D31">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E31">
         <v>210</v>
@@ -1552,13 +1552,13 @@
         <v>389</v>
       </c>
       <c r="C32">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D32">
         <v>0</v>
       </c>
       <c r="E32">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -1612,13 +1612,13 @@
         <v>269</v>
       </c>
       <c r="C35">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D35">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E35">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -1655,10 +1655,10 @@
         <v>39</v>
       </c>
       <c r="D37">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="E37">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -1672,13 +1672,13 @@
         <v>237</v>
       </c>
       <c r="C38">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="D38">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E38">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="F38">
         <v>0</v>
@@ -1692,10 +1692,10 @@
         <v>232</v>
       </c>
       <c r="C39">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D39">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E39">
         <v>157</v>
@@ -1712,13 +1712,13 @@
         <v>224</v>
       </c>
       <c r="C40">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D40">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E40">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -1732,13 +1732,13 @@
         <v>223</v>
       </c>
       <c r="C41">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D41">
         <v>0</v>
       </c>
       <c r="E41">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -1752,13 +1752,13 @@
         <v>207</v>
       </c>
       <c r="C42">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D42">
         <v>0</v>
       </c>
       <c r="E42">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F42">
         <v>0</v>
@@ -1772,13 +1772,13 @@
         <v>200</v>
       </c>
       <c r="C43">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D43">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E43">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F43">
         <v>0</v>
@@ -1812,13 +1812,13 @@
         <v>187</v>
       </c>
       <c r="C45">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D45">
         <v>10</v>
       </c>
       <c r="E45">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F45">
         <v>6</v>
@@ -1952,10 +1952,10 @@
         <v>150</v>
       </c>
       <c r="C52">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D52">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E52">
         <v>120</v>
@@ -1972,13 +1972,13 @@
         <v>150</v>
       </c>
       <c r="C53">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D53">
         <v>0</v>
       </c>
       <c r="E53">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F53">
         <v>0</v>
@@ -1992,13 +1992,13 @@
         <v>144</v>
       </c>
       <c r="C54">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D54">
         <v>0</v>
       </c>
       <c r="E54">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F54">
         <v>0</v>
@@ -2032,13 +2032,13 @@
         <v>138</v>
       </c>
       <c r="C56">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D56">
         <v>0</v>
       </c>
       <c r="E56">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F56">
         <v>0</v>
@@ -2252,10 +2252,10 @@
         <v>104</v>
       </c>
       <c r="C67">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D67">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E67">
         <v>61</v>
@@ -2292,13 +2292,13 @@
         <v>100</v>
       </c>
       <c r="C69">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E69">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="F69">
         <v>0</v>
@@ -2432,13 +2432,13 @@
         <v>81</v>
       </c>
       <c r="C76">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D76">
         <v>0</v>
       </c>
       <c r="E76">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F76">
         <v>0</v>
@@ -2472,10 +2472,10 @@
         <v>80</v>
       </c>
       <c r="C78">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D78">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E78">
         <v>13</v>
@@ -2492,13 +2492,13 @@
         <v>79</v>
       </c>
       <c r="C79">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D79">
         <v>0</v>
       </c>
       <c r="E79">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="F79">
         <v>0</v>
@@ -2632,13 +2632,13 @@
         <v>74</v>
       </c>
       <c r="C86">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D86">
         <v>0</v>
       </c>
       <c r="E86">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F86">
         <v>0</v>
@@ -3555,10 +3555,10 @@
         <v>16</v>
       </c>
       <c r="D132">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E132">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F132">
         <v>0</v>
@@ -3575,10 +3575,10 @@
         <v>3</v>
       </c>
       <c r="D133">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E133">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F133">
         <v>0</v>

--- a/resumo_busca_ativa_consolidado.xlsx
+++ b/resumo_busca_ativa_consolidado.xlsx
@@ -862,16 +862,16 @@
         <v>19133</v>
       </c>
       <c r="C2">
-        <v>2087</v>
+        <v>2106</v>
       </c>
       <c r="D2">
-        <v>1127</v>
+        <v>1080</v>
       </c>
       <c r="E2">
-        <v>15889</v>
+        <v>15933</v>
       </c>
       <c r="F2">
-        <v>30</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -882,16 +882,16 @@
         <v>16817</v>
       </c>
       <c r="C3">
-        <v>1525</v>
+        <v>1586</v>
       </c>
       <c r="D3">
-        <v>1073</v>
+        <v>1029</v>
       </c>
       <c r="E3">
-        <v>14123</v>
+        <v>14088</v>
       </c>
       <c r="F3">
-        <v>96</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -902,16 +902,16 @@
         <v>9446</v>
       </c>
       <c r="C4">
-        <v>1149</v>
+        <v>1141</v>
       </c>
       <c r="D4">
-        <v>854</v>
+        <v>822</v>
       </c>
       <c r="E4">
-        <v>7253</v>
+        <v>7292</v>
       </c>
       <c r="F4">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>
@@ -952,13 +952,13 @@
         <v>9670</v>
       </c>
       <c r="C2">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="D2">
-        <v>495</v>
+        <v>454</v>
       </c>
       <c r="E2">
-        <v>8308</v>
+        <v>8350</v>
       </c>
       <c r="F2">
         <v>14</v>
@@ -972,16 +972,16 @@
         <v>2381</v>
       </c>
       <c r="C3">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="D3">
-        <v>235</v>
+        <v>254</v>
       </c>
       <c r="E3">
-        <v>1879</v>
+        <v>1828</v>
       </c>
       <c r="F3">
-        <v>66</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -992,13 +992,13 @@
         <v>1735</v>
       </c>
       <c r="C4">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D4">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="E4">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="F4">
         <v>19</v>
@@ -1012,13 +1012,13 @@
         <v>1649</v>
       </c>
       <c r="C5">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D5">
-        <v>178</v>
+        <v>139</v>
       </c>
       <c r="E5">
-        <v>1310</v>
+        <v>1350</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1032,13 +1032,13 @@
         <v>1500</v>
       </c>
       <c r="C6">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D6">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="E6">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1055,10 +1055,10 @@
         <v>263</v>
       </c>
       <c r="D7">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="E7">
-        <v>916</v>
+        <v>928</v>
       </c>
       <c r="F7">
         <v>12</v>
@@ -1072,13 +1072,13 @@
         <v>1203</v>
       </c>
       <c r="C8">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D8">
         <v>24</v>
       </c>
       <c r="E8">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -1092,13 +1092,13 @@
         <v>1135</v>
       </c>
       <c r="C9">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="D9">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="E9">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -1112,13 +1112,13 @@
         <v>977</v>
       </c>
       <c r="C10">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D10">
         <v>12</v>
       </c>
       <c r="E10">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1172,13 +1172,13 @@
         <v>843</v>
       </c>
       <c r="C13">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D13">
         <v>73</v>
       </c>
       <c r="E13">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="F13">
         <v>102</v>
@@ -1192,13 +1192,13 @@
         <v>813</v>
       </c>
       <c r="C14">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1212,13 +1212,13 @@
         <v>811</v>
       </c>
       <c r="C15">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D15">
         <v>56</v>
       </c>
       <c r="E15">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -1232,13 +1232,13 @@
         <v>790</v>
       </c>
       <c r="C16">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="D16">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="E16">
-        <v>550</v>
+        <v>586</v>
       </c>
       <c r="F16">
         <v>43</v>
@@ -1252,13 +1252,13 @@
         <v>729</v>
       </c>
       <c r="C17">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D17">
         <v>9</v>
       </c>
       <c r="E17">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1272,13 +1272,13 @@
         <v>695</v>
       </c>
       <c r="C18">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D18">
         <v>36</v>
       </c>
       <c r="E18">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1292,13 +1292,13 @@
         <v>667</v>
       </c>
       <c r="C19">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="D19">
         <v>23</v>
       </c>
       <c r="E19">
-        <v>554</v>
+        <v>545</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1312,13 +1312,13 @@
         <v>646</v>
       </c>
       <c r="C20">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D20">
         <v>35</v>
       </c>
       <c r="E20">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1332,13 +1332,13 @@
         <v>616</v>
       </c>
       <c r="C21">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="D21">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="E21">
-        <v>402</v>
+        <v>420</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1352,13 +1352,13 @@
         <v>611</v>
       </c>
       <c r="C22">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D22">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E22">
-        <v>489</v>
+        <v>499</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1372,13 +1372,13 @@
         <v>601</v>
       </c>
       <c r="C23">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D23">
         <v>73</v>
       </c>
       <c r="E23">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="F23">
         <v>17</v>
@@ -1392,13 +1392,13 @@
         <v>503</v>
       </c>
       <c r="C24">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E24">
-        <v>455</v>
+        <v>442</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1412,13 +1412,13 @@
         <v>495</v>
       </c>
       <c r="C25">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D25">
         <v>8</v>
       </c>
       <c r="E25">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1432,13 +1432,13 @@
         <v>449</v>
       </c>
       <c r="C26">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D26">
         <v>87</v>
       </c>
       <c r="E26">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -1452,13 +1452,13 @@
         <v>448</v>
       </c>
       <c r="C27">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D27">
         <v>0</v>
       </c>
       <c r="E27">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -1472,16 +1472,16 @@
         <v>441</v>
       </c>
       <c r="C28">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D28">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="E28">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="F28">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -1492,10 +1492,10 @@
         <v>406</v>
       </c>
       <c r="C29">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D29">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E29">
         <v>307</v>
@@ -1515,10 +1515,10 @@
         <v>49</v>
       </c>
       <c r="D30">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E30">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -1532,13 +1532,13 @@
         <v>394</v>
       </c>
       <c r="C31">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="D31">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="E31">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="F31">
         <v>0</v>
@@ -1592,13 +1592,13 @@
         <v>295</v>
       </c>
       <c r="C34">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D34">
         <v>0</v>
       </c>
       <c r="E34">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F34">
         <v>0</v>
@@ -1612,13 +1612,13 @@
         <v>269</v>
       </c>
       <c r="C35">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D35">
         <v>26</v>
       </c>
       <c r="E35">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -1652,13 +1652,13 @@
         <v>238</v>
       </c>
       <c r="C37">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D37">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E37">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -1672,13 +1672,13 @@
         <v>237</v>
       </c>
       <c r="C38">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D38">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E38">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F38">
         <v>0</v>
@@ -1692,13 +1692,13 @@
         <v>232</v>
       </c>
       <c r="C39">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D39">
         <v>44</v>
       </c>
       <c r="E39">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -1712,13 +1712,13 @@
         <v>224</v>
       </c>
       <c r="C40">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D40">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="E40">
-        <v>170</v>
+        <v>141</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -1872,13 +1872,13 @@
         <v>163</v>
       </c>
       <c r="C48">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D48">
         <v>0</v>
       </c>
       <c r="E48">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F48">
         <v>0</v>
@@ -1892,13 +1892,13 @@
         <v>154</v>
       </c>
       <c r="C49">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D49">
         <v>6</v>
       </c>
       <c r="E49">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F49">
         <v>0</v>
@@ -1952,13 +1952,13 @@
         <v>150</v>
       </c>
       <c r="C52">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D52">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E52">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="F52">
         <v>0</v>
@@ -1972,13 +1972,13 @@
         <v>150</v>
       </c>
       <c r="C53">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D53">
         <v>0</v>
       </c>
       <c r="E53">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F53">
         <v>0</v>
@@ -2032,13 +2032,13 @@
         <v>138</v>
       </c>
       <c r="C56">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D56">
         <v>0</v>
       </c>
       <c r="E56">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F56">
         <v>0</v>
@@ -2152,13 +2152,13 @@
         <v>118</v>
       </c>
       <c r="C62">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D62">
         <v>0</v>
       </c>
       <c r="E62">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F62">
         <v>0</v>
@@ -2252,7 +2252,7 @@
         <v>104</v>
       </c>
       <c r="C67">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D67">
         <v>34</v>
@@ -2261,7 +2261,7 @@
         <v>61</v>
       </c>
       <c r="F67">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -2295,10 +2295,10 @@
         <v>16</v>
       </c>
       <c r="D69">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E69">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F69">
         <v>0</v>
@@ -2312,13 +2312,13 @@
         <v>99</v>
       </c>
       <c r="C70">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D70">
         <v>0</v>
       </c>
       <c r="E70">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F70">
         <v>3</v>
@@ -2352,13 +2352,13 @@
         <v>89</v>
       </c>
       <c r="C72">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D72">
         <v>0</v>
       </c>
       <c r="E72">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F72">
         <v>0</v>
@@ -2392,13 +2392,13 @@
         <v>86</v>
       </c>
       <c r="C74">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D74">
         <v>0</v>
       </c>
       <c r="E74">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F74">
         <v>0</v>
@@ -2475,10 +2475,10 @@
         <v>33</v>
       </c>
       <c r="D78">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E78">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F78">
         <v>0</v>
@@ -2512,13 +2512,13 @@
         <v>77</v>
       </c>
       <c r="C80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D80">
         <v>0</v>
       </c>
       <c r="E80">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F80">
         <v>0</v>
@@ -2532,13 +2532,13 @@
         <v>76</v>
       </c>
       <c r="C81">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D81">
         <v>0</v>
       </c>
       <c r="E81">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F81">
         <v>0</v>
@@ -2692,13 +2692,13 @@
         <v>67</v>
       </c>
       <c r="C89">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D89">
         <v>0</v>
       </c>
       <c r="E89">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="F89">
         <v>0</v>
@@ -2832,13 +2832,13 @@
         <v>63</v>
       </c>
       <c r="C96">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D96">
         <v>0</v>
       </c>
       <c r="E96">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F96">
         <v>0</v>
@@ -2912,13 +2912,13 @@
         <v>58</v>
       </c>
       <c r="C100">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D100">
         <v>0</v>
       </c>
       <c r="E100">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F100">
         <v>0</v>
@@ -2932,13 +2932,13 @@
         <v>57</v>
       </c>
       <c r="C101">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D101">
         <v>0</v>
       </c>
       <c r="E101">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F101">
         <v>0</v>
@@ -2992,16 +2992,16 @@
         <v>54</v>
       </c>
       <c r="C104">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D104">
         <v>0</v>
       </c>
       <c r="E104">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F104">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105" spans="1:6">
@@ -3012,13 +3012,13 @@
         <v>54</v>
       </c>
       <c r="C105">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D105">
         <v>0</v>
       </c>
       <c r="E105">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F105">
         <v>0</v>
@@ -3052,13 +3052,13 @@
         <v>53</v>
       </c>
       <c r="C107">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D107">
         <v>0</v>
       </c>
       <c r="E107">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F107">
         <v>0</v>
@@ -3218,10 +3218,10 @@
         <v>0</v>
       </c>
       <c r="E115">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F115">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116" spans="1:6">
@@ -3372,13 +3372,13 @@
         <v>39</v>
       </c>
       <c r="C123">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D123">
         <v>0</v>
       </c>
       <c r="E123">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F123">
         <v>0</v>
@@ -3452,13 +3452,13 @@
         <v>37</v>
       </c>
       <c r="C127">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D127">
         <v>0</v>
       </c>
       <c r="E127">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F127">
         <v>0</v>
@@ -3512,13 +3512,13 @@
         <v>35</v>
       </c>
       <c r="C130">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D130">
         <v>0</v>
       </c>
       <c r="E130">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F130">
         <v>0</v>
@@ -3532,13 +3532,13 @@
         <v>35</v>
       </c>
       <c r="C131">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D131">
         <v>0</v>
       </c>
       <c r="E131">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F131">
         <v>0</v>
@@ -3555,10 +3555,10 @@
         <v>16</v>
       </c>
       <c r="D132">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E132">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F132">
         <v>0</v>
@@ -3612,13 +3612,13 @@
         <v>32</v>
       </c>
       <c r="C135">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D135">
         <v>0</v>
       </c>
       <c r="E135">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F135">
         <v>0</v>
@@ -3672,13 +3672,13 @@
         <v>29</v>
       </c>
       <c r="C138">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D138">
         <v>0</v>
       </c>
       <c r="E138">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F138">
         <v>0</v>

--- a/resumo_busca_ativa_consolidado.xlsx
+++ b/resumo_busca_ativa_consolidado.xlsx
@@ -862,13 +862,13 @@
         <v>19133</v>
       </c>
       <c r="C2">
-        <v>2106</v>
+        <v>2118</v>
       </c>
       <c r="D2">
-        <v>1080</v>
+        <v>1073</v>
       </c>
       <c r="E2">
-        <v>15933</v>
+        <v>15928</v>
       </c>
       <c r="F2">
         <v>14</v>
@@ -882,13 +882,13 @@
         <v>16817</v>
       </c>
       <c r="C3">
-        <v>1586</v>
+        <v>1605</v>
       </c>
       <c r="D3">
         <v>1029</v>
       </c>
       <c r="E3">
-        <v>14088</v>
+        <v>14069</v>
       </c>
       <c r="F3">
         <v>114</v>
@@ -902,16 +902,16 @@
         <v>9446</v>
       </c>
       <c r="C4">
-        <v>1141</v>
+        <v>1144</v>
       </c>
       <c r="D4">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="E4">
-        <v>7292</v>
+        <v>7289</v>
       </c>
       <c r="F4">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
   </sheetData>
@@ -952,13 +952,13 @@
         <v>9670</v>
       </c>
       <c r="C2">
-        <v>852</v>
+        <v>856</v>
       </c>
       <c r="D2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E2">
-        <v>8350</v>
+        <v>8348</v>
       </c>
       <c r="F2">
         <v>14</v>
@@ -1012,13 +1012,13 @@
         <v>1649</v>
       </c>
       <c r="C5">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D5">
         <v>139</v>
       </c>
       <c r="E5">
-        <v>1350</v>
+        <v>1348</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1092,13 +1092,13 @@
         <v>1135</v>
       </c>
       <c r="C9">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D9">
         <v>224</v>
       </c>
       <c r="E9">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -1112,13 +1112,13 @@
         <v>977</v>
       </c>
       <c r="C10">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D10">
         <v>12</v>
       </c>
       <c r="E10">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1172,10 +1172,10 @@
         <v>843</v>
       </c>
       <c r="C13">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D13">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E13">
         <v>556</v>
@@ -1232,13 +1232,13 @@
         <v>790</v>
       </c>
       <c r="C16">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D16">
         <v>62</v>
       </c>
       <c r="E16">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="F16">
         <v>43</v>
@@ -1252,13 +1252,13 @@
         <v>729</v>
       </c>
       <c r="C17">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D17">
         <v>9</v>
       </c>
       <c r="E17">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1272,13 +1272,13 @@
         <v>695</v>
       </c>
       <c r="C18">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D18">
         <v>36</v>
       </c>
       <c r="E18">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1312,13 +1312,13 @@
         <v>646</v>
       </c>
       <c r="C20">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D20">
         <v>35</v>
       </c>
       <c r="E20">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1472,13 +1472,13 @@
         <v>441</v>
       </c>
       <c r="C28">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D28">
         <v>66</v>
       </c>
       <c r="E28">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -1872,13 +1872,13 @@
         <v>163</v>
       </c>
       <c r="C48">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="D48">
         <v>0</v>
       </c>
       <c r="E48">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="F48">
         <v>0</v>
@@ -2112,10 +2112,10 @@
         <v>124</v>
       </c>
       <c r="C60">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D60">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E60">
         <v>61</v>
@@ -2472,13 +2472,13 @@
         <v>80</v>
       </c>
       <c r="C78">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D78">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E78">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F78">
         <v>0</v>
@@ -2998,10 +2998,10 @@
         <v>0</v>
       </c>
       <c r="E104">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F104">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105" spans="1:6">
@@ -3132,13 +3132,13 @@
         <v>49</v>
       </c>
       <c r="C111">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D111">
         <v>0</v>
       </c>
       <c r="E111">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F111">
         <v>0</v>
@@ -3172,13 +3172,13 @@
         <v>48</v>
       </c>
       <c r="C113">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D113">
         <v>0</v>
       </c>
       <c r="E113">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F113">
         <v>0</v>
@@ -3272,13 +3272,13 @@
         <v>43</v>
       </c>
       <c r="C118">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D118">
         <v>1</v>
       </c>
       <c r="E118">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F118">
         <v>0</v>
@@ -3472,13 +3472,13 @@
         <v>36</v>
       </c>
       <c r="C128">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D128">
         <v>0</v>
       </c>
       <c r="E128">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F128">
         <v>0</v>

--- a/resumo_busca_ativa_consolidado.xlsx
+++ b/resumo_busca_ativa_consolidado.xlsx
@@ -862,13 +862,13 @@
         <v>19133</v>
       </c>
       <c r="C2">
-        <v>2118</v>
+        <v>2154</v>
       </c>
       <c r="D2">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="E2">
-        <v>15928</v>
+        <v>15843</v>
       </c>
       <c r="F2">
         <v>14</v>
@@ -882,16 +882,16 @@
         <v>16817</v>
       </c>
       <c r="C3">
-        <v>1605</v>
+        <v>1648</v>
       </c>
       <c r="D3">
-        <v>1029</v>
+        <v>1022</v>
       </c>
       <c r="E3">
-        <v>14069</v>
+        <v>14000</v>
       </c>
       <c r="F3">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -902,16 +902,16 @@
         <v>9446</v>
       </c>
       <c r="C4">
-        <v>1144</v>
+        <v>1154</v>
       </c>
       <c r="D4">
-        <v>821</v>
+        <v>839</v>
       </c>
       <c r="E4">
-        <v>7289</v>
+        <v>7220</v>
       </c>
       <c r="F4">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>
@@ -952,13 +952,13 @@
         <v>9670</v>
       </c>
       <c r="C2">
-        <v>856</v>
+        <v>870</v>
       </c>
       <c r="D2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E2">
-        <v>8348</v>
+        <v>8319</v>
       </c>
       <c r="F2">
         <v>14</v>
@@ -972,13 +972,13 @@
         <v>2381</v>
       </c>
       <c r="C3">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D3">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E3">
-        <v>1828</v>
+        <v>1819</v>
       </c>
       <c r="F3">
         <v>84</v>
@@ -992,13 +992,13 @@
         <v>1735</v>
       </c>
       <c r="C4">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D4">
         <v>187</v>
       </c>
       <c r="E4">
-        <v>1396</v>
+        <v>1392</v>
       </c>
       <c r="F4">
         <v>19</v>
@@ -1012,16 +1012,16 @@
         <v>1649</v>
       </c>
       <c r="C5">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="D5">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E5">
-        <v>1348</v>
+        <v>1332</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1032,13 +1032,13 @@
         <v>1500</v>
       </c>
       <c r="C6">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D6">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="E6">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1052,13 +1052,13 @@
         <v>1280</v>
       </c>
       <c r="C7">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D7">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E7">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="F7">
         <v>12</v>
@@ -1072,13 +1072,13 @@
         <v>1203</v>
       </c>
       <c r="C8">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D8">
         <v>24</v>
       </c>
       <c r="E8">
-        <v>1096</v>
+        <v>1087</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -1092,13 +1092,13 @@
         <v>1135</v>
       </c>
       <c r="C9">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D9">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E9">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -1112,13 +1112,13 @@
         <v>977</v>
       </c>
       <c r="C10">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="D10">
         <v>12</v>
       </c>
       <c r="E10">
-        <v>817</v>
+        <v>802</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1132,13 +1132,13 @@
         <v>920</v>
       </c>
       <c r="C11">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D11">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E11">
-        <v>822</v>
+        <v>813</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1158,7 +1158,7 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="F12">
         <v>3</v>
@@ -1172,13 +1172,13 @@
         <v>843</v>
       </c>
       <c r="C13">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D13">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E13">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="F13">
         <v>102</v>
@@ -1192,13 +1192,13 @@
         <v>813</v>
       </c>
       <c r="C14">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1232,16 +1232,16 @@
         <v>790</v>
       </c>
       <c r="C16">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D16">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="E16">
-        <v>585</v>
+        <v>564</v>
       </c>
       <c r="F16">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1252,13 +1252,13 @@
         <v>729</v>
       </c>
       <c r="C17">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D17">
         <v>9</v>
       </c>
       <c r="E17">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1292,13 +1292,13 @@
         <v>667</v>
       </c>
       <c r="C19">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D19">
         <v>23</v>
       </c>
       <c r="E19">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1318,7 +1318,7 @@
         <v>35</v>
       </c>
       <c r="E20">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1332,13 +1332,13 @@
         <v>616</v>
       </c>
       <c r="C21">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D21">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="E21">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1352,13 +1352,13 @@
         <v>611</v>
       </c>
       <c r="C22">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D22">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="E22">
-        <v>499</v>
+        <v>471</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1372,13 +1372,13 @@
         <v>601</v>
       </c>
       <c r="C23">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D23">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E23">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="F23">
         <v>17</v>
@@ -1392,13 +1392,13 @@
         <v>503</v>
       </c>
       <c r="C24">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D24">
         <v>14</v>
       </c>
       <c r="E24">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1412,13 +1412,13 @@
         <v>495</v>
       </c>
       <c r="C25">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D25">
         <v>8</v>
       </c>
       <c r="E25">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1435,10 +1435,10 @@
         <v>98</v>
       </c>
       <c r="D26">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="E26">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -1452,13 +1452,13 @@
         <v>448</v>
       </c>
       <c r="C27">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D27">
         <v>0</v>
       </c>
       <c r="E27">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -1472,13 +1472,13 @@
         <v>441</v>
       </c>
       <c r="C28">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D28">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E28">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -1498,7 +1498,7 @@
         <v>70</v>
       </c>
       <c r="E29">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="F29">
         <v>0</v>
@@ -1512,13 +1512,13 @@
         <v>402</v>
       </c>
       <c r="C30">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D30">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E30">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -1535,7 +1535,7 @@
         <v>100</v>
       </c>
       <c r="D31">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E31">
         <v>221</v>
@@ -1578,7 +1578,7 @@
         <v>0</v>
       </c>
       <c r="E33">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -1592,13 +1592,13 @@
         <v>295</v>
       </c>
       <c r="C34">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D34">
         <v>0</v>
       </c>
       <c r="E34">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F34">
         <v>0</v>
@@ -1652,13 +1652,13 @@
         <v>238</v>
       </c>
       <c r="C37">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D37">
         <v>49</v>
       </c>
       <c r="E37">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -1675,7 +1675,7 @@
         <v>45</v>
       </c>
       <c r="D38">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E38">
         <v>129</v>
@@ -1718,7 +1718,7 @@
         <v>27</v>
       </c>
       <c r="E40">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -1758,7 +1758,7 @@
         <v>0</v>
       </c>
       <c r="E42">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F42">
         <v>0</v>
@@ -1858,7 +1858,7 @@
         <v>1</v>
       </c>
       <c r="E47">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F47">
         <v>0</v>
@@ -1872,13 +1872,13 @@
         <v>163</v>
       </c>
       <c r="C48">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="D48">
         <v>0</v>
       </c>
       <c r="E48">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="F48">
         <v>0</v>
@@ -1918,7 +1918,7 @@
         <v>27</v>
       </c>
       <c r="E50">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F50">
         <v>0</v>
@@ -1952,13 +1952,13 @@
         <v>150</v>
       </c>
       <c r="C52">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D52">
         <v>10</v>
       </c>
       <c r="E52">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F52">
         <v>0</v>
@@ -2032,13 +2032,13 @@
         <v>138</v>
       </c>
       <c r="C56">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D56">
         <v>0</v>
       </c>
       <c r="E56">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F56">
         <v>0</v>
@@ -2072,13 +2072,13 @@
         <v>127</v>
       </c>
       <c r="C58">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D58">
         <v>0</v>
       </c>
       <c r="E58">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F58">
         <v>0</v>
@@ -2178,7 +2178,7 @@
         <v>0</v>
       </c>
       <c r="E63">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F63">
         <v>0</v>
@@ -2418,7 +2418,7 @@
         <v>0</v>
       </c>
       <c r="E75">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F75">
         <v>0</v>
@@ -2438,7 +2438,7 @@
         <v>0</v>
       </c>
       <c r="E76">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F76">
         <v>0</v>
@@ -2472,13 +2472,13 @@
         <v>80</v>
       </c>
       <c r="C78">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D78">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E78">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F78">
         <v>0</v>
@@ -2638,7 +2638,7 @@
         <v>0</v>
       </c>
       <c r="E86">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F86">
         <v>0</v>
@@ -2752,13 +2752,13 @@
         <v>65</v>
       </c>
       <c r="C92">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D92">
         <v>0</v>
       </c>
       <c r="E92">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F92">
         <v>0</v>
@@ -2838,7 +2838,7 @@
         <v>0</v>
       </c>
       <c r="E96">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F96">
         <v>0</v>
@@ -2852,13 +2852,13 @@
         <v>63</v>
       </c>
       <c r="C97">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D97">
         <v>0</v>
       </c>
       <c r="E97">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F97">
         <v>0</v>
@@ -2972,13 +2972,13 @@
         <v>54</v>
       </c>
       <c r="C103">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D103">
         <v>0</v>
       </c>
       <c r="E103">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F103">
         <v>0</v>
@@ -3172,13 +3172,13 @@
         <v>48</v>
       </c>
       <c r="C113">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D113">
         <v>0</v>
       </c>
       <c r="E113">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F113">
         <v>0</v>
@@ -3458,7 +3458,7 @@
         <v>0</v>
       </c>
       <c r="E127">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F127">
         <v>0</v>
@@ -3575,7 +3575,7 @@
         <v>3</v>
       </c>
       <c r="D133">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E133">
         <v>14</v>

--- a/resumo_busca_ativa_consolidado.xlsx
+++ b/resumo_busca_ativa_consolidado.xlsx
@@ -119,12 +119,12 @@
     <t>PIRACANJUBA</t>
   </si>
   <si>
+    <t>RUBIATABA</t>
+  </si>
+  <si>
     <t>CIDADE OCIDENTAL</t>
   </si>
   <si>
-    <t>RUBIATABA</t>
-  </si>
-  <si>
     <t>PIRENOPOLIS</t>
   </si>
   <si>
@@ -161,12 +161,12 @@
     <t>MARA ROSA</t>
   </si>
   <si>
+    <t>GOIANAPOLIS</t>
+  </si>
+  <si>
     <t>COCALZINHO DE GOIAS</t>
   </si>
   <si>
-    <t>GOIANAPOLIS</t>
-  </si>
-  <si>
     <t>BURITI ALEGRE</t>
   </si>
   <si>
@@ -194,13 +194,13 @@
     <t>CRIXAS</t>
   </si>
   <si>
+    <t>CORUMBA DE GOIAS</t>
+  </si>
+  <si>
+    <t>NOVA CRIXAS</t>
+  </si>
+  <si>
     <t>PETROLINA DE GOIAS</t>
-  </si>
-  <si>
-    <t>NOVA CRIXAS</t>
-  </si>
-  <si>
-    <t>CORUMBA DE GOIAS</t>
   </si>
   <si>
     <t>GOIANDIRA</t>
@@ -859,16 +859,16 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>19133</v>
+        <v>19106</v>
       </c>
       <c r="C2">
-        <v>2154</v>
+        <v>2159</v>
       </c>
       <c r="D2">
-        <v>1075</v>
+        <v>1067</v>
       </c>
       <c r="E2">
-        <v>15843</v>
+        <v>15819</v>
       </c>
       <c r="F2">
         <v>14</v>
@@ -879,19 +879,19 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>16817</v>
+        <v>16805</v>
       </c>
       <c r="C3">
-        <v>1648</v>
+        <v>1656</v>
       </c>
       <c r="D3">
-        <v>1022</v>
+        <v>1082</v>
       </c>
       <c r="E3">
-        <v>14000</v>
+        <v>13924</v>
       </c>
       <c r="F3">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -899,19 +899,19 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>9446</v>
+        <v>9403</v>
       </c>
       <c r="C4">
-        <v>1154</v>
+        <v>1120</v>
       </c>
       <c r="D4">
-        <v>839</v>
+        <v>834</v>
       </c>
       <c r="E4">
-        <v>7220</v>
+        <v>7217</v>
       </c>
       <c r="F4">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -949,16 +949,16 @@
         <v>10</v>
       </c>
       <c r="B2">
-        <v>9670</v>
+        <v>9663</v>
       </c>
       <c r="C2">
-        <v>870</v>
+        <v>866</v>
       </c>
       <c r="D2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E2">
-        <v>8319</v>
+        <v>8317</v>
       </c>
       <c r="F2">
         <v>14</v>
@@ -969,19 +969,19 @@
         <v>11</v>
       </c>
       <c r="B3">
-        <v>2381</v>
+        <v>2379</v>
       </c>
       <c r="C3">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D3">
         <v>252</v>
       </c>
       <c r="E3">
-        <v>1819</v>
+        <v>1817</v>
       </c>
       <c r="F3">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -992,13 +992,13 @@
         <v>1735</v>
       </c>
       <c r="C4">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D4">
         <v>187</v>
       </c>
       <c r="E4">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="F4">
         <v>19</v>
@@ -1009,19 +1009,19 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="C5">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D5">
-        <v>141</v>
+        <v>203</v>
       </c>
       <c r="E5">
-        <v>1332</v>
+        <v>1269</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1029,16 +1029,16 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>1500</v>
+        <v>1495</v>
       </c>
       <c r="C6">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D6">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E6">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1049,16 +1049,16 @@
         <v>15</v>
       </c>
       <c r="B7">
-        <v>1280</v>
+        <v>1269</v>
       </c>
       <c r="C7">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="D7">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="E7">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="F7">
         <v>12</v>
@@ -1089,13 +1089,13 @@
         <v>17</v>
       </c>
       <c r="B9">
-        <v>1135</v>
+        <v>1132</v>
       </c>
       <c r="C9">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D9">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E9">
         <v>765</v>
@@ -1109,16 +1109,16 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="C10">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D10">
         <v>12</v>
       </c>
       <c r="E10">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1129,10 +1129,10 @@
         <v>19</v>
       </c>
       <c r="B11">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="C11">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D11">
         <v>33</v>
@@ -1169,10 +1169,10 @@
         <v>21</v>
       </c>
       <c r="B13">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="C13">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D13">
         <v>71</v>
@@ -1181,7 +1181,7 @@
         <v>550</v>
       </c>
       <c r="F13">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1192,13 +1192,13 @@
         <v>813</v>
       </c>
       <c r="C14">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1229,10 +1229,10 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>790</v>
+        <v>782</v>
       </c>
       <c r="C16">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="D16">
         <v>76</v>
@@ -1252,13 +1252,13 @@
         <v>729</v>
       </c>
       <c r="C17">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D17">
         <v>9</v>
       </c>
       <c r="E17">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1272,10 +1272,10 @@
         <v>695</v>
       </c>
       <c r="C18">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D18">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E18">
         <v>607</v>
@@ -1289,10 +1289,10 @@
         <v>27</v>
       </c>
       <c r="B19">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C19">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D19">
         <v>23</v>
@@ -1329,16 +1329,16 @@
         <v>29</v>
       </c>
       <c r="B21">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="C21">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D21">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="E21">
-        <v>426</v>
+        <v>407</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1349,16 +1349,16 @@
         <v>30</v>
       </c>
       <c r="B22">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C22">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D22">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E22">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1369,10 +1369,10 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C23">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D23">
         <v>72</v>
@@ -1389,7 +1389,7 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C24">
         <v>48</v>
@@ -1398,7 +1398,7 @@
         <v>14</v>
       </c>
       <c r="E24">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1429,16 +1429,16 @@
         <v>34</v>
       </c>
       <c r="B26">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C26">
-        <v>98</v>
+        <v>49</v>
       </c>
       <c r="D26">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E26">
-        <v>251</v>
+        <v>399</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -1449,16 +1449,16 @@
         <v>35</v>
       </c>
       <c r="B27">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="C27">
-        <v>49</v>
+        <v>92</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E27">
-        <v>399</v>
+        <v>251</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -1469,13 +1469,13 @@
         <v>36</v>
       </c>
       <c r="B28">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C28">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="D28">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="E28">
         <v>333</v>
@@ -1529,10 +1529,10 @@
         <v>39</v>
       </c>
       <c r="B31">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C31">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D31">
         <v>72</v>
@@ -1549,10 +1549,10 @@
         <v>40</v>
       </c>
       <c r="B32">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C32">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -1589,10 +1589,10 @@
         <v>42</v>
       </c>
       <c r="B34">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="C34">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -1609,10 +1609,10 @@
         <v>43</v>
       </c>
       <c r="B35">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C35">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D35">
         <v>26</v>
@@ -1629,10 +1629,10 @@
         <v>44</v>
       </c>
       <c r="B36">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C36">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -1689,10 +1689,10 @@
         <v>47</v>
       </c>
       <c r="B39">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C39">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D39">
         <v>44</v>
@@ -1709,16 +1709,16 @@
         <v>48</v>
       </c>
       <c r="B40">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C40">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="D40">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="E40">
-        <v>140</v>
+        <v>203</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -1729,16 +1729,16 @@
         <v>49</v>
       </c>
       <c r="B41">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C41">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="E41">
-        <v>203</v>
+        <v>140</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -1769,10 +1769,10 @@
         <v>51</v>
       </c>
       <c r="B43">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C43">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D43">
         <v>16</v>
@@ -1929,16 +1929,16 @@
         <v>59</v>
       </c>
       <c r="B51">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C51">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="D51">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E51">
-        <v>63</v>
+        <v>139</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -1969,16 +1969,16 @@
         <v>61</v>
       </c>
       <c r="B53">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C53">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="D53">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="E53">
-        <v>139</v>
+        <v>63</v>
       </c>
       <c r="F53">
         <v>0</v>
@@ -2192,13 +2192,13 @@
         <v>108</v>
       </c>
       <c r="C64">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D64">
         <v>0</v>
       </c>
       <c r="E64">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -2518,10 +2518,10 @@
         <v>0</v>
       </c>
       <c r="E80">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F80">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -2872,13 +2872,13 @@
         <v>63</v>
       </c>
       <c r="C98">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D98">
         <v>0</v>
       </c>
       <c r="E98">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F98">
         <v>0</v>
@@ -2995,13 +2995,13 @@
         <v>7</v>
       </c>
       <c r="D104">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E104">
         <v>45</v>
       </c>
       <c r="F104">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105" spans="1:6">
@@ -3209,10 +3209,10 @@
         <v>123</v>
       </c>
       <c r="B115">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C115">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D115">
         <v>0</v>

--- a/resumo_busca_ativa_consolidado.xlsx
+++ b/resumo_busca_ativa_consolidado.xlsx
@@ -119,12 +119,12 @@
     <t>PIRACANJUBA</t>
   </si>
   <si>
+    <t>CIDADE OCIDENTAL</t>
+  </si>
+  <si>
     <t>RUBIATABA</t>
   </si>
   <si>
-    <t>CIDADE OCIDENTAL</t>
-  </si>
-  <si>
     <t>PIRENOPOLIS</t>
   </si>
   <si>
@@ -161,12 +161,12 @@
     <t>MARA ROSA</t>
   </si>
   <si>
+    <t>COCALZINHO DE GOIAS</t>
+  </si>
+  <si>
     <t>GOIANAPOLIS</t>
   </si>
   <si>
-    <t>COCALZINHO DE GOIAS</t>
-  </si>
-  <si>
     <t>BURITI ALEGRE</t>
   </si>
   <si>
@@ -194,13 +194,13 @@
     <t>CRIXAS</t>
   </si>
   <si>
+    <t>PETROLINA DE GOIAS</t>
+  </si>
+  <si>
+    <t>NOVA CRIXAS</t>
+  </si>
+  <si>
     <t>CORUMBA DE GOIAS</t>
-  </si>
-  <si>
-    <t>NOVA CRIXAS</t>
-  </si>
-  <si>
-    <t>PETROLINA DE GOIAS</t>
   </si>
   <si>
     <t>GOIANDIRA</t>
@@ -859,16 +859,16 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>19106</v>
+        <v>19133</v>
       </c>
       <c r="C2">
-        <v>2159</v>
+        <v>2134</v>
       </c>
       <c r="D2">
-        <v>1067</v>
+        <v>1026</v>
       </c>
       <c r="E2">
-        <v>15819</v>
+        <v>15910</v>
       </c>
       <c r="F2">
         <v>14</v>
@@ -879,19 +879,19 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>16805</v>
+        <v>16817</v>
       </c>
       <c r="C3">
-        <v>1656</v>
+        <v>1708</v>
       </c>
       <c r="D3">
-        <v>1082</v>
+        <v>1101</v>
       </c>
       <c r="E3">
-        <v>13924</v>
+        <v>13865</v>
       </c>
       <c r="F3">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -899,19 +899,19 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>9403</v>
+        <v>9446</v>
       </c>
       <c r="C4">
-        <v>1120</v>
+        <v>1135</v>
       </c>
       <c r="D4">
-        <v>834</v>
+        <v>820</v>
       </c>
       <c r="E4">
-        <v>7217</v>
+        <v>7259</v>
       </c>
       <c r="F4">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>
@@ -949,16 +949,16 @@
         <v>10</v>
       </c>
       <c r="B2">
-        <v>9663</v>
+        <v>9670</v>
       </c>
       <c r="C2">
-        <v>866</v>
+        <v>875</v>
       </c>
       <c r="D2">
-        <v>450</v>
+        <v>428</v>
       </c>
       <c r="E2">
-        <v>8317</v>
+        <v>8336</v>
       </c>
       <c r="F2">
         <v>14</v>
@@ -969,16 +969,16 @@
         <v>11</v>
       </c>
       <c r="B3">
-        <v>2379</v>
+        <v>2381</v>
       </c>
       <c r="C3">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="D3">
         <v>252</v>
       </c>
       <c r="E3">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="F3">
         <v>83</v>
@@ -992,13 +992,13 @@
         <v>1735</v>
       </c>
       <c r="C4">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D4">
         <v>187</v>
       </c>
       <c r="E4">
-        <v>1391</v>
+        <v>1389</v>
       </c>
       <c r="F4">
         <v>19</v>
@@ -1009,16 +1009,16 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>1648</v>
+        <v>1649</v>
       </c>
       <c r="C5">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="D5">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="E5">
-        <v>1269</v>
+        <v>1245</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1029,16 +1029,16 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>1495</v>
+        <v>1500</v>
       </c>
       <c r="C6">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D6">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E6">
-        <v>1032</v>
+        <v>1037</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1049,16 +1049,16 @@
         <v>15</v>
       </c>
       <c r="B7">
-        <v>1269</v>
+        <v>1280</v>
       </c>
       <c r="C7">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="D7">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="E7">
-        <v>927</v>
+        <v>956</v>
       </c>
       <c r="F7">
         <v>12</v>
@@ -1089,16 +1089,16 @@
         <v>17</v>
       </c>
       <c r="B9">
-        <v>1132</v>
+        <v>1135</v>
       </c>
       <c r="C9">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="D9">
         <v>219</v>
       </c>
       <c r="E9">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -1109,16 +1109,16 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="C10">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D10">
         <v>12</v>
       </c>
       <c r="E10">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1129,16 +1129,16 @@
         <v>19</v>
       </c>
       <c r="B11">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="C11">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D11">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E11">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1152,13 +1152,13 @@
         <v>911</v>
       </c>
       <c r="C12">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="F12">
         <v>3</v>
@@ -1169,16 +1169,16 @@
         <v>21</v>
       </c>
       <c r="B13">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="C13">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D13">
         <v>71</v>
       </c>
       <c r="E13">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="F13">
         <v>101</v>
@@ -1192,13 +1192,13 @@
         <v>813</v>
       </c>
       <c r="C14">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1229,19 +1229,19 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="C16">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="D16">
         <v>76</v>
       </c>
       <c r="E16">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="F16">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1252,13 +1252,13 @@
         <v>729</v>
       </c>
       <c r="C17">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D17">
         <v>9</v>
       </c>
       <c r="E17">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1289,16 +1289,16 @@
         <v>27</v>
       </c>
       <c r="B19">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C19">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D19">
         <v>23</v>
       </c>
       <c r="E19">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1329,16 +1329,16 @@
         <v>29</v>
       </c>
       <c r="B21">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="C21">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D21">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E21">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1349,16 +1349,16 @@
         <v>30</v>
       </c>
       <c r="B22">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C22">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="D22">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E22">
-        <v>470</v>
+        <v>494</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1369,16 +1369,16 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C23">
         <v>87</v>
       </c>
       <c r="D23">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E23">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="F23">
         <v>17</v>
@@ -1389,7 +1389,7 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C24">
         <v>48</v>
@@ -1398,7 +1398,7 @@
         <v>14</v>
       </c>
       <c r="E24">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1429,16 +1429,16 @@
         <v>34</v>
       </c>
       <c r="B26">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C26">
-        <v>49</v>
+        <v>100</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="E26">
-        <v>399</v>
+        <v>251</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -1449,16 +1449,16 @@
         <v>35</v>
       </c>
       <c r="B27">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="C27">
-        <v>92</v>
+        <v>49</v>
       </c>
       <c r="D27">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E27">
-        <v>251</v>
+        <v>399</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -1469,16 +1469,16 @@
         <v>36</v>
       </c>
       <c r="B28">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C28">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="D28">
         <v>42</v>
       </c>
       <c r="E28">
-        <v>333</v>
+        <v>356</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -1512,13 +1512,13 @@
         <v>402</v>
       </c>
       <c r="C30">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D30">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E30">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -1529,16 +1529,16 @@
         <v>39</v>
       </c>
       <c r="B31">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C31">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D31">
         <v>72</v>
       </c>
       <c r="E31">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F31">
         <v>0</v>
@@ -1549,10 +1549,10 @@
         <v>40</v>
       </c>
       <c r="B32">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C32">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -1589,16 +1589,16 @@
         <v>42</v>
       </c>
       <c r="B34">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="C34">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D34">
         <v>0</v>
       </c>
       <c r="E34">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="F34">
         <v>0</v>
@@ -1609,16 +1609,16 @@
         <v>43</v>
       </c>
       <c r="B35">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C35">
         <v>43</v>
       </c>
       <c r="D35">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E35">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -1629,19 +1629,19 @@
         <v>44</v>
       </c>
       <c r="B36">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C36">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D36">
         <v>0</v>
       </c>
       <c r="E36">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F36">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -1672,13 +1672,13 @@
         <v>237</v>
       </c>
       <c r="C38">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D38">
         <v>60</v>
       </c>
       <c r="E38">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F38">
         <v>0</v>
@@ -1689,13 +1689,13 @@
         <v>47</v>
       </c>
       <c r="B39">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C39">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D39">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E39">
         <v>159</v>
@@ -1709,16 +1709,16 @@
         <v>48</v>
       </c>
       <c r="B40">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C40">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="E40">
-        <v>203</v>
+        <v>141</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -1729,16 +1729,16 @@
         <v>49</v>
       </c>
       <c r="B41">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C41">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="D41">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E41">
-        <v>140</v>
+        <v>203</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -1769,16 +1769,16 @@
         <v>51</v>
       </c>
       <c r="B43">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C43">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D43">
         <v>16</v>
       </c>
       <c r="E43">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F43">
         <v>0</v>
@@ -1929,16 +1929,16 @@
         <v>59</v>
       </c>
       <c r="B51">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C51">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="E51">
-        <v>139</v>
+        <v>66</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -1955,10 +1955,10 @@
         <v>15</v>
       </c>
       <c r="D52">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E52">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F52">
         <v>0</v>
@@ -1969,16 +1969,16 @@
         <v>61</v>
       </c>
       <c r="B53">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C53">
-        <v>61</v>
+        <v>12</v>
       </c>
       <c r="D53">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E53">
-        <v>63</v>
+        <v>138</v>
       </c>
       <c r="F53">
         <v>0</v>
@@ -2052,13 +2052,13 @@
         <v>128</v>
       </c>
       <c r="C57">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="D57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E57">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="F57">
         <v>0</v>
@@ -2112,13 +2112,13 @@
         <v>124</v>
       </c>
       <c r="C60">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D60">
         <v>30</v>
       </c>
       <c r="E60">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -2252,13 +2252,13 @@
         <v>104</v>
       </c>
       <c r="C67">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D67">
         <v>34</v>
       </c>
       <c r="E67">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F67">
         <v>4</v>
@@ -2472,13 +2472,13 @@
         <v>80</v>
       </c>
       <c r="C78">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D78">
         <v>22</v>
       </c>
       <c r="E78">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F78">
         <v>0</v>
@@ -2512,13 +2512,13 @@
         <v>77</v>
       </c>
       <c r="C80">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D80">
         <v>0</v>
       </c>
       <c r="E80">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F80">
         <v>1</v>
@@ -2652,13 +2652,13 @@
         <v>72</v>
       </c>
       <c r="C87">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D87">
         <v>0</v>
       </c>
       <c r="E87">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F87">
         <v>0</v>
@@ -2792,13 +2792,13 @@
         <v>64</v>
       </c>
       <c r="C94">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D94">
         <v>0</v>
       </c>
       <c r="E94">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F94">
         <v>0</v>
@@ -2832,7 +2832,7 @@
         <v>63</v>
       </c>
       <c r="C96">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D96">
         <v>0</v>
@@ -2978,7 +2978,7 @@
         <v>0</v>
       </c>
       <c r="E103">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F103">
         <v>0</v>
@@ -3209,10 +3209,10 @@
         <v>123</v>
       </c>
       <c r="B115">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C115">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D115">
         <v>0</v>
@@ -3352,13 +3352,13 @@
         <v>39</v>
       </c>
       <c r="C122">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D122">
         <v>0</v>
       </c>
       <c r="E122">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F122">
         <v>0</v>
@@ -3552,13 +3552,13 @@
         <v>35</v>
       </c>
       <c r="C132">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D132">
         <v>0</v>
       </c>
       <c r="E132">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F132">
         <v>0</v>

--- a/resumo_busca_ativa_consolidado.xlsx
+++ b/resumo_busca_ativa_consolidado.xlsx
@@ -119,12 +119,12 @@
     <t>PIRACANJUBA</t>
   </si>
   <si>
+    <t>RUBIATABA</t>
+  </si>
+  <si>
     <t>CIDADE OCIDENTAL</t>
   </si>
   <si>
-    <t>RUBIATABA</t>
-  </si>
-  <si>
     <t>PIRENOPOLIS</t>
   </si>
   <si>
@@ -161,12 +161,12 @@
     <t>MARA ROSA</t>
   </si>
   <si>
+    <t>GOIANAPOLIS</t>
+  </si>
+  <si>
     <t>COCALZINHO DE GOIAS</t>
   </si>
   <si>
-    <t>GOIANAPOLIS</t>
-  </si>
-  <si>
     <t>BURITI ALEGRE</t>
   </si>
   <si>
@@ -194,10 +194,10 @@
     <t>CRIXAS</t>
   </si>
   <si>
+    <t>NOVA CRIXAS</t>
+  </si>
+  <si>
     <t>PETROLINA DE GOIAS</t>
-  </si>
-  <si>
-    <t>NOVA CRIXAS</t>
   </si>
   <si>
     <t>CORUMBA DE GOIAS</t>
@@ -859,19 +859,19 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>19133</v>
+        <v>19106</v>
       </c>
       <c r="C2">
-        <v>2134</v>
+        <v>2341</v>
       </c>
       <c r="D2">
-        <v>1026</v>
+        <v>1015</v>
       </c>
       <c r="E2">
-        <v>15910</v>
+        <v>15676</v>
       </c>
       <c r="F2">
-        <v>14</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -879,19 +879,19 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>16817</v>
+        <v>16796</v>
       </c>
       <c r="C3">
-        <v>1708</v>
+        <v>1979</v>
       </c>
       <c r="D3">
-        <v>1101</v>
+        <v>1169</v>
       </c>
       <c r="E3">
-        <v>13865</v>
+        <v>13454</v>
       </c>
       <c r="F3">
-        <v>114</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -899,19 +899,19 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>9446</v>
+        <v>9407</v>
       </c>
       <c r="C4">
-        <v>1135</v>
+        <v>1153</v>
       </c>
       <c r="D4">
-        <v>820</v>
+        <v>828</v>
       </c>
       <c r="E4">
-        <v>7259</v>
+        <v>7169</v>
       </c>
       <c r="F4">
-        <v>189</v>
+        <v>213</v>
       </c>
     </row>
   </sheetData>
@@ -949,16 +949,16 @@
         <v>10</v>
       </c>
       <c r="B2">
-        <v>9670</v>
+        <v>9660</v>
       </c>
       <c r="C2">
-        <v>875</v>
+        <v>975</v>
       </c>
       <c r="D2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="E2">
-        <v>8336</v>
+        <v>8228</v>
       </c>
       <c r="F2">
         <v>14</v>
@@ -969,16 +969,16 @@
         <v>11</v>
       </c>
       <c r="B3">
-        <v>2381</v>
+        <v>2376</v>
       </c>
       <c r="C3">
-        <v>224</v>
+        <v>249</v>
       </c>
       <c r="D3">
-        <v>252</v>
+        <v>180</v>
       </c>
       <c r="E3">
-        <v>1815</v>
+        <v>1857</v>
       </c>
       <c r="F3">
         <v>83</v>
@@ -992,13 +992,13 @@
         <v>1735</v>
       </c>
       <c r="C4">
-        <v>139</v>
+        <v>202</v>
       </c>
       <c r="D4">
-        <v>187</v>
+        <v>155</v>
       </c>
       <c r="E4">
-        <v>1389</v>
+        <v>1358</v>
       </c>
       <c r="F4">
         <v>19</v>
@@ -1009,19 +1009,19 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>1649</v>
+        <v>1644</v>
       </c>
       <c r="C5">
-        <v>179</v>
+        <v>223</v>
       </c>
       <c r="D5">
-        <v>221</v>
+        <v>303</v>
       </c>
       <c r="E5">
-        <v>1245</v>
+        <v>1091</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1029,16 +1029,16 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="C6">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="D6">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="E6">
-        <v>1037</v>
+        <v>1022</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1049,16 +1049,16 @@
         <v>15</v>
       </c>
       <c r="B7">
-        <v>1280</v>
+        <v>1270</v>
       </c>
       <c r="C7">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D7">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E7">
-        <v>956</v>
+        <v>945</v>
       </c>
       <c r="F7">
         <v>12</v>
@@ -1072,13 +1072,13 @@
         <v>1203</v>
       </c>
       <c r="C8">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D8">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="E8">
-        <v>1087</v>
+        <v>1061</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -1089,19 +1089,19 @@
         <v>17</v>
       </c>
       <c r="B9">
-        <v>1135</v>
+        <v>1132</v>
       </c>
       <c r="C9">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D9">
-        <v>219</v>
+        <v>239</v>
       </c>
       <c r="E9">
-        <v>763</v>
+        <v>713</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1109,16 +1109,16 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="C10">
-        <v>163</v>
+        <v>202</v>
       </c>
       <c r="D10">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E10">
-        <v>800</v>
+        <v>762</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1129,7 +1129,7 @@
         <v>19</v>
       </c>
       <c r="B11">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="C11">
         <v>70</v>
@@ -1138,7 +1138,7 @@
         <v>32</v>
       </c>
       <c r="E11">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1152,16 +1152,16 @@
         <v>911</v>
       </c>
       <c r="C12">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E12">
-        <v>799</v>
+        <v>781</v>
       </c>
       <c r="F12">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1169,16 +1169,16 @@
         <v>21</v>
       </c>
       <c r="B13">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="C13">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D13">
         <v>71</v>
       </c>
       <c r="E13">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="F13">
         <v>101</v>
@@ -1192,13 +1192,13 @@
         <v>813</v>
       </c>
       <c r="C14">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E14">
-        <v>773</v>
+        <v>750</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1229,19 +1229,19 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>790</v>
+        <v>783</v>
       </c>
       <c r="C16">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D16">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="E16">
-        <v>561</v>
+        <v>525</v>
       </c>
       <c r="F16">
-        <v>41</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1252,13 +1252,13 @@
         <v>729</v>
       </c>
       <c r="C17">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E17">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1272,13 +1272,13 @@
         <v>695</v>
       </c>
       <c r="C18">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D18">
         <v>35</v>
       </c>
       <c r="E18">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1289,16 +1289,16 @@
         <v>27</v>
       </c>
       <c r="B19">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C19">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D19">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="E19">
-        <v>544</v>
+        <v>500</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1312,13 +1312,13 @@
         <v>646</v>
       </c>
       <c r="C20">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D20">
         <v>35</v>
       </c>
       <c r="E20">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1329,16 +1329,16 @@
         <v>29</v>
       </c>
       <c r="B21">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="C21">
-        <v>145</v>
+        <v>182</v>
       </c>
       <c r="D21">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="E21">
-        <v>404</v>
+        <v>380</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1349,16 +1349,16 @@
         <v>30</v>
       </c>
       <c r="B22">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C22">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D22">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E22">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1369,16 +1369,16 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C23">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D23">
         <v>71</v>
       </c>
       <c r="E23">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="F23">
         <v>17</v>
@@ -1389,16 +1389,16 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C24">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D24">
         <v>14</v>
       </c>
       <c r="E24">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1412,13 +1412,13 @@
         <v>495</v>
       </c>
       <c r="C25">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D25">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="E25">
-        <v>411</v>
+        <v>375</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1429,16 +1429,16 @@
         <v>34</v>
       </c>
       <c r="B26">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C26">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="D26">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="E26">
-        <v>251</v>
+        <v>395</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -1449,16 +1449,16 @@
         <v>35</v>
       </c>
       <c r="B27">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="C27">
-        <v>49</v>
+        <v>95</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="E27">
-        <v>399</v>
+        <v>252</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -1472,13 +1472,13 @@
         <v>441</v>
       </c>
       <c r="C28">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D28">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="E28">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -1492,13 +1492,13 @@
         <v>406</v>
       </c>
       <c r="C29">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D29">
         <v>70</v>
       </c>
       <c r="E29">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F29">
         <v>0</v>
@@ -1512,13 +1512,13 @@
         <v>402</v>
       </c>
       <c r="C30">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D30">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="E30">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -1529,16 +1529,16 @@
         <v>39</v>
       </c>
       <c r="B31">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="C31">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D31">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="E31">
-        <v>222</v>
+        <v>189</v>
       </c>
       <c r="F31">
         <v>0</v>
@@ -1549,16 +1549,16 @@
         <v>40</v>
       </c>
       <c r="B32">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C32">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="D32">
         <v>0</v>
       </c>
       <c r="E32">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -1572,13 +1572,13 @@
         <v>316</v>
       </c>
       <c r="C33">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D33">
         <v>0</v>
       </c>
       <c r="E33">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -1589,7 +1589,7 @@
         <v>42</v>
       </c>
       <c r="B34">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="C34">
         <v>50</v>
@@ -1598,7 +1598,7 @@
         <v>0</v>
       </c>
       <c r="E34">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="F34">
         <v>0</v>
@@ -1609,16 +1609,16 @@
         <v>43</v>
       </c>
       <c r="B35">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C35">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D35">
         <v>24</v>
       </c>
       <c r="E35">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -1629,16 +1629,16 @@
         <v>44</v>
       </c>
       <c r="B36">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C36">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E36">
-        <v>196</v>
+        <v>137</v>
       </c>
       <c r="F36">
         <v>1</v>
@@ -1652,13 +1652,13 @@
         <v>238</v>
       </c>
       <c r="C37">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D37">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="E37">
-        <v>146</v>
+        <v>194</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -1669,10 +1669,10 @@
         <v>46</v>
       </c>
       <c r="B38">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C38">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D38">
         <v>60</v>
@@ -1689,16 +1689,16 @@
         <v>47</v>
       </c>
       <c r="B39">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C39">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D39">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E39">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -1709,16 +1709,16 @@
         <v>48</v>
       </c>
       <c r="B40">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C40">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="D40">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E40">
-        <v>141</v>
+        <v>203</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -1729,16 +1729,16 @@
         <v>49</v>
       </c>
       <c r="B41">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C41">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="E41">
-        <v>203</v>
+        <v>127</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -1758,7 +1758,7 @@
         <v>0</v>
       </c>
       <c r="E42">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F42">
         <v>0</v>
@@ -1769,16 +1769,16 @@
         <v>51</v>
       </c>
       <c r="B43">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C43">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="D43">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E43">
-        <v>166</v>
+        <v>133</v>
       </c>
       <c r="F43">
         <v>0</v>
@@ -1832,13 +1832,13 @@
         <v>182</v>
       </c>
       <c r="C46">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D46">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E46">
-        <v>152</v>
+        <v>175</v>
       </c>
       <c r="F46">
         <v>3</v>
@@ -1872,13 +1872,13 @@
         <v>163</v>
       </c>
       <c r="C48">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D48">
         <v>0</v>
       </c>
       <c r="E48">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F48">
         <v>0</v>
@@ -1929,16 +1929,16 @@
         <v>59</v>
       </c>
       <c r="B51">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C51">
-        <v>62</v>
+        <v>17</v>
       </c>
       <c r="D51">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E51">
-        <v>66</v>
+        <v>111</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -1952,13 +1952,13 @@
         <v>150</v>
       </c>
       <c r="C52">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="D52">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E52">
-        <v>128</v>
+        <v>85</v>
       </c>
       <c r="F52">
         <v>0</v>
@@ -2052,13 +2052,13 @@
         <v>128</v>
       </c>
       <c r="C57">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E57">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F57">
         <v>0</v>
@@ -2112,13 +2112,13 @@
         <v>124</v>
       </c>
       <c r="C60">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D60">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E60">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -2152,13 +2152,13 @@
         <v>118</v>
       </c>
       <c r="C62">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D62">
         <v>0</v>
       </c>
       <c r="E62">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F62">
         <v>0</v>
@@ -2192,13 +2192,13 @@
         <v>108</v>
       </c>
       <c r="C64">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D64">
         <v>0</v>
       </c>
       <c r="E64">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -2232,13 +2232,13 @@
         <v>107</v>
       </c>
       <c r="C66">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D66">
         <v>0</v>
       </c>
       <c r="E66">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F66">
         <v>0</v>
@@ -2252,10 +2252,10 @@
         <v>104</v>
       </c>
       <c r="C67">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D67">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E67">
         <v>60</v>
@@ -2412,13 +2412,13 @@
         <v>84</v>
       </c>
       <c r="C75">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D75">
         <v>0</v>
       </c>
       <c r="E75">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F75">
         <v>0</v>
@@ -2432,13 +2432,13 @@
         <v>81</v>
       </c>
       <c r="C76">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="D76">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E76">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="F76">
         <v>0</v>
@@ -2452,13 +2452,13 @@
         <v>81</v>
       </c>
       <c r="C77">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D77">
         <v>0</v>
       </c>
       <c r="E77">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F77">
         <v>0</v>
@@ -2472,13 +2472,13 @@
         <v>80</v>
       </c>
       <c r="C78">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D78">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E78">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F78">
         <v>0</v>
@@ -2632,13 +2632,13 @@
         <v>74</v>
       </c>
       <c r="C86">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D86">
         <v>0</v>
       </c>
       <c r="E86">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F86">
         <v>0</v>
@@ -2652,13 +2652,13 @@
         <v>72</v>
       </c>
       <c r="C87">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D87">
         <v>0</v>
       </c>
       <c r="E87">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F87">
         <v>0</v>
@@ -2712,13 +2712,13 @@
         <v>66</v>
       </c>
       <c r="C90">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D90">
         <v>0</v>
       </c>
       <c r="E90">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F90">
         <v>0</v>
@@ -2912,13 +2912,13 @@
         <v>58</v>
       </c>
       <c r="C100">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D100">
         <v>0</v>
       </c>
       <c r="E100">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F100">
         <v>0</v>
@@ -2995,10 +2995,10 @@
         <v>7</v>
       </c>
       <c r="D104">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E104">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F104">
         <v>1</v>
@@ -3072,13 +3072,13 @@
         <v>52</v>
       </c>
       <c r="C108">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D108">
         <v>0</v>
       </c>
       <c r="E108">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F108">
         <v>0</v>
@@ -3112,13 +3112,13 @@
         <v>52</v>
       </c>
       <c r="C110">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D110">
         <v>0</v>
       </c>
       <c r="E110">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F110">
         <v>0</v>
@@ -3138,10 +3138,10 @@
         <v>0</v>
       </c>
       <c r="E111">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="F111">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="112" spans="1:6">
@@ -3172,13 +3172,13 @@
         <v>48</v>
       </c>
       <c r="C113">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D113">
         <v>0</v>
       </c>
       <c r="E113">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F113">
         <v>0</v>
@@ -3209,10 +3209,10 @@
         <v>123</v>
       </c>
       <c r="B115">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C115">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D115">
         <v>0</v>
@@ -3412,13 +3412,13 @@
         <v>38</v>
       </c>
       <c r="C125">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D125">
         <v>0</v>
       </c>
       <c r="E125">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F125">
         <v>0</v>
@@ -3492,13 +3492,13 @@
         <v>36</v>
       </c>
       <c r="C129">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D129">
         <v>0</v>
       </c>
       <c r="E129">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F129">
         <v>0</v>
@@ -3532,13 +3532,13 @@
         <v>35</v>
       </c>
       <c r="C131">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D131">
         <v>0</v>
       </c>
       <c r="E131">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F131">
         <v>0</v>

--- a/resumo_busca_ativa_consolidado.xlsx
+++ b/resumo_busca_ativa_consolidado.xlsx
@@ -859,16 +859,16 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>19106</v>
+        <v>19105</v>
       </c>
       <c r="C2">
-        <v>2341</v>
+        <v>2498</v>
       </c>
       <c r="D2">
-        <v>1015</v>
+        <v>962</v>
       </c>
       <c r="E2">
-        <v>15676</v>
+        <v>15568</v>
       </c>
       <c r="F2">
         <v>26</v>
@@ -882,16 +882,16 @@
         <v>16796</v>
       </c>
       <c r="C3">
-        <v>1979</v>
+        <v>2077</v>
       </c>
       <c r="D3">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="E3">
-        <v>13454</v>
+        <v>13365</v>
       </c>
       <c r="F3">
-        <v>164</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -902,13 +902,13 @@
         <v>9407</v>
       </c>
       <c r="C4">
-        <v>1153</v>
+        <v>1184</v>
       </c>
       <c r="D4">
-        <v>828</v>
+        <v>823</v>
       </c>
       <c r="E4">
-        <v>7169</v>
+        <v>7141</v>
       </c>
       <c r="F4">
         <v>213</v>
@@ -949,16 +949,16 @@
         <v>10</v>
       </c>
       <c r="B2">
-        <v>9660</v>
+        <v>9659</v>
       </c>
       <c r="C2">
-        <v>975</v>
+        <v>1071</v>
       </c>
       <c r="D2">
-        <v>426</v>
+        <v>351</v>
       </c>
       <c r="E2">
-        <v>8228</v>
+        <v>8204</v>
       </c>
       <c r="F2">
         <v>14</v>
@@ -972,16 +972,16 @@
         <v>2376</v>
       </c>
       <c r="C3">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="D3">
         <v>180</v>
       </c>
       <c r="E3">
-        <v>1857</v>
+        <v>1836</v>
       </c>
       <c r="F3">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -992,16 +992,16 @@
         <v>1735</v>
       </c>
       <c r="C4">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="D4">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E4">
-        <v>1358</v>
+        <v>1347</v>
       </c>
       <c r="F4">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1012,16 +1012,16 @@
         <v>1644</v>
       </c>
       <c r="C5">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="D5">
-        <v>303</v>
+        <v>279</v>
       </c>
       <c r="E5">
-        <v>1091</v>
+        <v>1104</v>
       </c>
       <c r="F5">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1032,13 +1032,13 @@
         <v>1499</v>
       </c>
       <c r="C6">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="D6">
         <v>264</v>
       </c>
       <c r="E6">
-        <v>1022</v>
+        <v>1014</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1052,13 +1052,13 @@
         <v>1270</v>
       </c>
       <c r="C7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D7">
         <v>59</v>
       </c>
       <c r="E7">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="F7">
         <v>12</v>
@@ -1072,13 +1072,13 @@
         <v>1203</v>
       </c>
       <c r="C8">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D8">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E8">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -1092,13 +1092,13 @@
         <v>1132</v>
       </c>
       <c r="C9">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="D9">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="E9">
-        <v>713</v>
+        <v>694</v>
       </c>
       <c r="F9">
         <v>28</v>
@@ -1112,13 +1112,13 @@
         <v>976</v>
       </c>
       <c r="C10">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="D10">
         <v>10</v>
       </c>
       <c r="E10">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1132,13 +1132,13 @@
         <v>919</v>
       </c>
       <c r="C11">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D11">
         <v>32</v>
       </c>
       <c r="E11">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1152,13 +1152,13 @@
         <v>911</v>
       </c>
       <c r="C12">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D12">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E12">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="F12">
         <v>2</v>
@@ -1172,13 +1172,13 @@
         <v>840</v>
       </c>
       <c r="C13">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D13">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E13">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="F13">
         <v>101</v>
@@ -1192,13 +1192,13 @@
         <v>813</v>
       </c>
       <c r="C14">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D14">
         <v>21</v>
       </c>
       <c r="E14">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1212,13 +1212,13 @@
         <v>811</v>
       </c>
       <c r="C15">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D15">
         <v>56</v>
       </c>
       <c r="E15">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -1232,13 +1232,13 @@
         <v>783</v>
       </c>
       <c r="C16">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="D16">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E16">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="F16">
         <v>65</v>
@@ -1252,13 +1252,13 @@
         <v>729</v>
       </c>
       <c r="C17">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D17">
         <v>8</v>
       </c>
       <c r="E17">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1272,13 +1272,13 @@
         <v>695</v>
       </c>
       <c r="C18">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D18">
         <v>35</v>
       </c>
       <c r="E18">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1292,13 +1292,13 @@
         <v>666</v>
       </c>
       <c r="C19">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D19">
         <v>64</v>
       </c>
       <c r="E19">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1312,13 +1312,13 @@
         <v>646</v>
       </c>
       <c r="C20">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D20">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E20">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1332,13 +1332,13 @@
         <v>614</v>
       </c>
       <c r="C21">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="D21">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="E21">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1352,13 +1352,13 @@
         <v>610</v>
       </c>
       <c r="C22">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D22">
         <v>18</v>
       </c>
       <c r="E22">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1372,13 +1372,13 @@
         <v>600</v>
       </c>
       <c r="C23">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D23">
         <v>71</v>
       </c>
       <c r="E23">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="F23">
         <v>17</v>
@@ -1412,13 +1412,13 @@
         <v>495</v>
       </c>
       <c r="C25">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D25">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E25">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1432,13 +1432,13 @@
         <v>448</v>
       </c>
       <c r="C26">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D26">
         <v>0</v>
       </c>
       <c r="E26">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -1492,13 +1492,13 @@
         <v>406</v>
       </c>
       <c r="C29">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D29">
         <v>70</v>
       </c>
       <c r="E29">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F29">
         <v>0</v>
@@ -1512,13 +1512,13 @@
         <v>402</v>
       </c>
       <c r="C30">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D30">
         <v>47</v>
       </c>
       <c r="E30">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -1552,13 +1552,13 @@
         <v>388</v>
       </c>
       <c r="C32">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D32">
         <v>0</v>
       </c>
       <c r="E32">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -1572,13 +1572,13 @@
         <v>316</v>
       </c>
       <c r="C33">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D33">
         <v>0</v>
       </c>
       <c r="E33">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -1612,13 +1612,13 @@
         <v>267</v>
       </c>
       <c r="C35">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D35">
         <v>24</v>
       </c>
       <c r="E35">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -1672,13 +1672,13 @@
         <v>236</v>
       </c>
       <c r="C38">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D38">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E38">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F38">
         <v>0</v>
@@ -1712,13 +1712,13 @@
         <v>223</v>
       </c>
       <c r="C40">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D40">
         <v>0</v>
       </c>
       <c r="E40">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -1732,13 +1732,13 @@
         <v>221</v>
       </c>
       <c r="C41">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D41">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E41">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -1772,13 +1772,13 @@
         <v>197</v>
       </c>
       <c r="C43">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D43">
         <v>21</v>
       </c>
       <c r="E43">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F43">
         <v>0</v>
@@ -1875,10 +1875,10 @@
         <v>38</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="E48">
-        <v>125</v>
+        <v>97</v>
       </c>
       <c r="F48">
         <v>0</v>
@@ -1892,13 +1892,13 @@
         <v>154</v>
       </c>
       <c r="C49">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D49">
         <v>6</v>
       </c>
       <c r="E49">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F49">
         <v>0</v>
@@ -1912,13 +1912,13 @@
         <v>154</v>
       </c>
       <c r="C50">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D50">
         <v>27</v>
       </c>
       <c r="E50">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F50">
         <v>0</v>
@@ -1932,13 +1932,13 @@
         <v>150</v>
       </c>
       <c r="C51">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D51">
         <v>22</v>
       </c>
       <c r="E51">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -1952,13 +1952,13 @@
         <v>150</v>
       </c>
       <c r="C52">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="E52">
-        <v>85</v>
+        <v>51</v>
       </c>
       <c r="F52">
         <v>0</v>
@@ -2032,13 +2032,13 @@
         <v>138</v>
       </c>
       <c r="C56">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E56">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="F56">
         <v>0</v>
@@ -2092,13 +2092,13 @@
         <v>127</v>
       </c>
       <c r="C59">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D59">
         <v>0</v>
       </c>
       <c r="E59">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F59">
         <v>0</v>
@@ -2112,13 +2112,13 @@
         <v>124</v>
       </c>
       <c r="C60">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D60">
         <v>27</v>
       </c>
       <c r="E60">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -2212,13 +2212,13 @@
         <v>108</v>
       </c>
       <c r="C65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D65">
         <v>0</v>
       </c>
       <c r="E65">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F65">
         <v>0</v>
@@ -2292,13 +2292,13 @@
         <v>100</v>
       </c>
       <c r="C69">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D69">
         <v>0</v>
       </c>
       <c r="E69">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F69">
         <v>0</v>
@@ -2312,13 +2312,13 @@
         <v>99</v>
       </c>
       <c r="C70">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D70">
         <v>0</v>
       </c>
       <c r="E70">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F70">
         <v>3</v>
@@ -2435,10 +2435,10 @@
         <v>30</v>
       </c>
       <c r="D76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E76">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F76">
         <v>0</v>
@@ -2618,7 +2618,7 @@
         <v>0</v>
       </c>
       <c r="E85">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F85">
         <v>4</v>
@@ -2652,13 +2652,13 @@
         <v>72</v>
       </c>
       <c r="C87">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D87">
         <v>0</v>
       </c>
       <c r="E87">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F87">
         <v>0</v>
@@ -3492,13 +3492,13 @@
         <v>36</v>
       </c>
       <c r="C129">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D129">
         <v>0</v>
       </c>
       <c r="E129">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F129">
         <v>0</v>
@@ -3632,13 +3632,13 @@
         <v>32</v>
       </c>
       <c r="C136">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D136">
         <v>0</v>
       </c>
       <c r="E136">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F136">
         <v>0</v>

--- a/resumo_busca_ativa_consolidado.xlsx
+++ b/resumo_busca_ativa_consolidado.xlsx
@@ -269,13 +269,13 @@
     <t>SANTA TEREZA DE GOIAS</t>
   </si>
   <si>
+    <t>RIO QUENTE</t>
+  </si>
+  <si>
+    <t>MUNDO NOVO</t>
+  </si>
+  <si>
     <t>OURO VERDE DE GOIAS</t>
-  </si>
-  <si>
-    <t>RIO QUENTE</t>
-  </si>
-  <si>
-    <t>MUNDO NOVO</t>
   </si>
   <si>
     <t>CACHOEIRA DOURADA</t>
@@ -859,16 +859,16 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>19105</v>
+        <v>19094</v>
       </c>
       <c r="C2">
-        <v>2498</v>
+        <v>2642</v>
       </c>
       <c r="D2">
-        <v>962</v>
+        <v>748</v>
       </c>
       <c r="E2">
-        <v>15568</v>
+        <v>15627</v>
       </c>
       <c r="F2">
         <v>26</v>
@@ -879,19 +879,19 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>16796</v>
+        <v>16790</v>
       </c>
       <c r="C3">
-        <v>2077</v>
+        <v>2164</v>
       </c>
       <c r="D3">
-        <v>1168</v>
+        <v>1281</v>
       </c>
       <c r="E3">
-        <v>13365</v>
+        <v>13153</v>
       </c>
       <c r="F3">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -902,13 +902,13 @@
         <v>9407</v>
       </c>
       <c r="C4">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="D4">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="E4">
-        <v>7141</v>
+        <v>7140</v>
       </c>
       <c r="F4">
         <v>213</v>
@@ -949,16 +949,16 @@
         <v>10</v>
       </c>
       <c r="B2">
-        <v>9659</v>
+        <v>9650</v>
       </c>
       <c r="C2">
-        <v>1071</v>
+        <v>1155</v>
       </c>
       <c r="D2">
-        <v>351</v>
+        <v>292</v>
       </c>
       <c r="E2">
-        <v>8204</v>
+        <v>8170</v>
       </c>
       <c r="F2">
         <v>14</v>
@@ -972,13 +972,13 @@
         <v>2376</v>
       </c>
       <c r="C3">
-        <v>270</v>
+        <v>288</v>
       </c>
       <c r="D3">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="E3">
-        <v>1836</v>
+        <v>1803</v>
       </c>
       <c r="F3">
         <v>82</v>
@@ -992,16 +992,16 @@
         <v>1735</v>
       </c>
       <c r="C4">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="D4">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="E4">
-        <v>1347</v>
+        <v>1327</v>
       </c>
       <c r="F4">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1009,16 +1009,16 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>1644</v>
+        <v>1641</v>
       </c>
       <c r="C5">
-        <v>246</v>
+        <v>274</v>
       </c>
       <c r="D5">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E5">
-        <v>1104</v>
+        <v>1072</v>
       </c>
       <c r="F5">
         <v>11</v>
@@ -1032,10 +1032,10 @@
         <v>1499</v>
       </c>
       <c r="C6">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D6">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E6">
         <v>1014</v>
@@ -1052,13 +1052,13 @@
         <v>1270</v>
       </c>
       <c r="C7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D7">
         <v>59</v>
       </c>
       <c r="E7">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="F7">
         <v>12</v>
@@ -1092,16 +1092,16 @@
         <v>1132</v>
       </c>
       <c r="C9">
-        <v>158</v>
+        <v>180</v>
       </c>
       <c r="D9">
-        <v>247</v>
+        <v>318</v>
       </c>
       <c r="E9">
-        <v>694</v>
+        <v>594</v>
       </c>
       <c r="F9">
-        <v>28</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1152,13 +1152,13 @@
         <v>911</v>
       </c>
       <c r="C12">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="D12">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E12">
-        <v>780</v>
+        <v>753</v>
       </c>
       <c r="F12">
         <v>2</v>
@@ -1292,13 +1292,13 @@
         <v>666</v>
       </c>
       <c r="C19">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="D19">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="E19">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1332,13 +1332,13 @@
         <v>614</v>
       </c>
       <c r="C21">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="D21">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="E21">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1352,13 +1352,13 @@
         <v>610</v>
       </c>
       <c r="C22">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D22">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E22">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1472,13 +1472,13 @@
         <v>441</v>
       </c>
       <c r="C28">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D28">
         <v>30</v>
       </c>
       <c r="E28">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -1512,13 +1512,13 @@
         <v>402</v>
       </c>
       <c r="C30">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D30">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E30">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -1535,10 +1535,10 @@
         <v>98</v>
       </c>
       <c r="D31">
-        <v>102</v>
+        <v>31</v>
       </c>
       <c r="E31">
-        <v>189</v>
+        <v>260</v>
       </c>
       <c r="F31">
         <v>0</v>
@@ -1629,10 +1629,10 @@
         <v>44</v>
       </c>
       <c r="B36">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C36">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D36">
         <v>21</v>
@@ -1732,13 +1732,13 @@
         <v>221</v>
       </c>
       <c r="C41">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="D41">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="E41">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -1952,13 +1952,13 @@
         <v>150</v>
       </c>
       <c r="C52">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="D52">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="E52">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="F52">
         <v>0</v>
@@ -2432,13 +2432,13 @@
         <v>81</v>
       </c>
       <c r="C76">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D76">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E76">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="F76">
         <v>0</v>
@@ -2449,16 +2449,16 @@
         <v>85</v>
       </c>
       <c r="B77">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C77">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D77">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E77">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="F77">
         <v>0</v>
@@ -2469,16 +2469,16 @@
         <v>86</v>
       </c>
       <c r="B78">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C78">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D78">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E78">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="F78">
         <v>0</v>
@@ -3072,13 +3072,13 @@
         <v>52</v>
       </c>
       <c r="C108">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D108">
         <v>0</v>
       </c>
       <c r="E108">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F108">
         <v>0</v>

--- a/resumo_busca_ativa_consolidado.xlsx
+++ b/resumo_busca_ativa_consolidado.xlsx
@@ -859,16 +859,16 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>19094</v>
+        <v>19079</v>
       </c>
       <c r="C2">
-        <v>2642</v>
+        <v>2730</v>
       </c>
       <c r="D2">
-        <v>748</v>
+        <v>817</v>
       </c>
       <c r="E2">
-        <v>15627</v>
+        <v>15455</v>
       </c>
       <c r="F2">
         <v>26</v>
@@ -879,16 +879,16 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>16790</v>
+        <v>16784</v>
       </c>
       <c r="C3">
-        <v>2164</v>
+        <v>2201</v>
       </c>
       <c r="D3">
-        <v>1281</v>
+        <v>1284</v>
       </c>
       <c r="E3">
-        <v>13153</v>
+        <v>13107</v>
       </c>
       <c r="F3">
         <v>158</v>
@@ -902,10 +902,10 @@
         <v>9407</v>
       </c>
       <c r="C4">
-        <v>1186</v>
+        <v>1200</v>
       </c>
       <c r="D4">
-        <v>822</v>
+        <v>808</v>
       </c>
       <c r="E4">
         <v>7140</v>
@@ -949,16 +949,16 @@
         <v>10</v>
       </c>
       <c r="B2">
-        <v>9650</v>
+        <v>9635</v>
       </c>
       <c r="C2">
-        <v>1155</v>
+        <v>1221</v>
       </c>
       <c r="D2">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="E2">
-        <v>8170</v>
+        <v>8081</v>
       </c>
       <c r="F2">
         <v>14</v>
@@ -969,16 +969,16 @@
         <v>11</v>
       </c>
       <c r="B3">
-        <v>2376</v>
+        <v>2373</v>
       </c>
       <c r="C3">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="D3">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="E3">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="F3">
         <v>82</v>
@@ -992,13 +992,13 @@
         <v>1735</v>
       </c>
       <c r="C4">
-        <v>228</v>
+        <v>247</v>
       </c>
       <c r="D4">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="E4">
-        <v>1327</v>
+        <v>1315</v>
       </c>
       <c r="F4">
         <v>19</v>
@@ -1009,16 +1009,16 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>1641</v>
+        <v>1639</v>
       </c>
       <c r="C5">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="D5">
-        <v>280</v>
+        <v>304</v>
       </c>
       <c r="E5">
-        <v>1072</v>
+        <v>1037</v>
       </c>
       <c r="F5">
         <v>11</v>
@@ -1149,10 +1149,10 @@
         <v>20</v>
       </c>
       <c r="B12">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="C12">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D12">
         <v>30</v>
@@ -1232,10 +1232,10 @@
         <v>783</v>
       </c>
       <c r="C16">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="D16">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E16">
         <v>519</v>
@@ -1292,13 +1292,13 @@
         <v>666</v>
       </c>
       <c r="C19">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="D19">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="E19">
-        <v>510</v>
+        <v>473</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1332,10 +1332,10 @@
         <v>614</v>
       </c>
       <c r="C21">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D21">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E21">
         <v>381</v>
@@ -1512,13 +1512,13 @@
         <v>402</v>
       </c>
       <c r="C30">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D30">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="E30">
-        <v>295</v>
+        <v>266</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -1612,10 +1612,10 @@
         <v>267</v>
       </c>
       <c r="C35">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D35">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E35">
         <v>200</v>
@@ -1952,10 +1952,10 @@
         <v>150</v>
       </c>
       <c r="C52">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D52">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E52">
         <v>59</v>
@@ -2035,10 +2035,10 @@
         <v>38</v>
       </c>
       <c r="D56">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="E56">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="F56">
         <v>0</v>

--- a/resumo_busca_ativa_consolidado.xlsx
+++ b/resumo_busca_ativa_consolidado.xlsx
@@ -194,13 +194,13 @@
     <t>CRIXAS</t>
   </si>
   <si>
+    <t>CORUMBA DE GOIAS</t>
+  </si>
+  <si>
     <t>NOVA CRIXAS</t>
   </si>
   <si>
     <t>PETROLINA DE GOIAS</t>
-  </si>
-  <si>
-    <t>CORUMBA DE GOIAS</t>
   </si>
   <si>
     <t>GOIANDIRA</t>
@@ -859,19 +859,19 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>19079</v>
+        <v>19061</v>
       </c>
       <c r="C2">
-        <v>2730</v>
+        <v>2501</v>
       </c>
       <c r="D2">
-        <v>817</v>
+        <v>715</v>
       </c>
       <c r="E2">
-        <v>15455</v>
+        <v>15740</v>
       </c>
       <c r="F2">
-        <v>26</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -879,19 +879,19 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>16784</v>
+        <v>16777</v>
       </c>
       <c r="C3">
-        <v>2201</v>
+        <v>2019</v>
       </c>
       <c r="D3">
-        <v>1284</v>
+        <v>1257</v>
       </c>
       <c r="E3">
-        <v>13107</v>
+        <v>13314</v>
       </c>
       <c r="F3">
-        <v>158</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -899,19 +899,19 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>9407</v>
+        <v>9406</v>
       </c>
       <c r="C4">
-        <v>1200</v>
+        <v>1184</v>
       </c>
       <c r="D4">
         <v>808</v>
       </c>
       <c r="E4">
-        <v>7140</v>
+        <v>7136</v>
       </c>
       <c r="F4">
-        <v>213</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -949,19 +949,19 @@
         <v>10</v>
       </c>
       <c r="B2">
-        <v>9635</v>
+        <v>9620</v>
       </c>
       <c r="C2">
-        <v>1221</v>
+        <v>1066</v>
       </c>
       <c r="D2">
-        <v>300</v>
+        <v>241</v>
       </c>
       <c r="E2">
-        <v>8081</v>
+        <v>8294</v>
       </c>
       <c r="F2">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -969,16 +969,16 @@
         <v>11</v>
       </c>
       <c r="B3">
-        <v>2373</v>
+        <v>2369</v>
       </c>
       <c r="C3">
-        <v>298</v>
+        <v>256</v>
       </c>
       <c r="D3">
-        <v>181</v>
+        <v>203</v>
       </c>
       <c r="E3">
-        <v>1804</v>
+        <v>1820</v>
       </c>
       <c r="F3">
         <v>82</v>
@@ -989,16 +989,16 @@
         <v>12</v>
       </c>
       <c r="B4">
-        <v>1735</v>
+        <v>1734</v>
       </c>
       <c r="C4">
-        <v>247</v>
+        <v>229</v>
       </c>
       <c r="D4">
         <v>152</v>
       </c>
       <c r="E4">
-        <v>1315</v>
+        <v>1332</v>
       </c>
       <c r="F4">
         <v>19</v>
@@ -1009,16 +1009,16 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="C5">
-        <v>283</v>
+        <v>223</v>
       </c>
       <c r="D5">
-        <v>304</v>
+        <v>279</v>
       </c>
       <c r="E5">
-        <v>1037</v>
+        <v>1121</v>
       </c>
       <c r="F5">
         <v>11</v>
@@ -1029,10 +1029,10 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="C6">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D6">
         <v>263</v>
@@ -1052,13 +1052,13 @@
         <v>1270</v>
       </c>
       <c r="C7">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D7">
         <v>59</v>
       </c>
       <c r="E7">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="F7">
         <v>12</v>
@@ -1089,19 +1089,19 @@
         <v>17</v>
       </c>
       <c r="B9">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="C9">
-        <v>180</v>
+        <v>161</v>
       </c>
       <c r="D9">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="E9">
-        <v>594</v>
+        <v>613</v>
       </c>
       <c r="F9">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1112,13 +1112,13 @@
         <v>976</v>
       </c>
       <c r="C10">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="D10">
         <v>10</v>
       </c>
       <c r="E10">
-        <v>758</v>
+        <v>780</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1152,13 +1152,13 @@
         <v>910</v>
       </c>
       <c r="C12">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="D12">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E12">
-        <v>753</v>
+        <v>792</v>
       </c>
       <c r="F12">
         <v>2</v>
@@ -1232,16 +1232,16 @@
         <v>783</v>
       </c>
       <c r="C16">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D16">
         <v>66</v>
       </c>
       <c r="E16">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="F16">
-        <v>65</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1292,16 +1292,16 @@
         <v>666</v>
       </c>
       <c r="C19">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="D19">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="E19">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1329,16 +1329,16 @@
         <v>29</v>
       </c>
       <c r="B21">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C21">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="D21">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="E21">
-        <v>381</v>
+        <v>403</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1352,13 +1352,13 @@
         <v>610</v>
       </c>
       <c r="C22">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="D22">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E22">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1478,10 +1478,10 @@
         <v>30</v>
       </c>
       <c r="E28">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -1509,16 +1509,16 @@
         <v>38</v>
       </c>
       <c r="B30">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C30">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D30">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="E30">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -1538,10 +1538,10 @@
         <v>31</v>
       </c>
       <c r="E31">
-        <v>260</v>
+        <v>236</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -1552,13 +1552,13 @@
         <v>388</v>
       </c>
       <c r="C32">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="D32">
         <v>0</v>
       </c>
       <c r="E32">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -1612,13 +1612,13 @@
         <v>267</v>
       </c>
       <c r="C35">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D35">
         <v>21</v>
       </c>
       <c r="E35">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -1632,13 +1632,13 @@
         <v>241</v>
       </c>
       <c r="C36">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="D36">
         <v>21</v>
       </c>
       <c r="E36">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="F36">
         <v>1</v>
@@ -1732,13 +1732,13 @@
         <v>221</v>
       </c>
       <c r="C41">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D41">
         <v>27</v>
       </c>
       <c r="E41">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -1932,13 +1932,13 @@
         <v>150</v>
       </c>
       <c r="C51">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D51">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="E51">
-        <v>109</v>
+        <v>138</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -1952,13 +1952,13 @@
         <v>150</v>
       </c>
       <c r="C52">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="D52">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="E52">
-        <v>59</v>
+        <v>109</v>
       </c>
       <c r="F52">
         <v>0</v>
@@ -1969,16 +1969,16 @@
         <v>61</v>
       </c>
       <c r="B53">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C53">
-        <v>12</v>
+        <v>79</v>
       </c>
       <c r="D53">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E53">
-        <v>138</v>
+        <v>67</v>
       </c>
       <c r="F53">
         <v>0</v>
@@ -2032,13 +2032,13 @@
         <v>138</v>
       </c>
       <c r="C56">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="D56">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="E56">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="F56">
         <v>0</v>
@@ -2112,13 +2112,13 @@
         <v>124</v>
       </c>
       <c r="C60">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D60">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E60">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -2172,13 +2172,13 @@
         <v>111</v>
       </c>
       <c r="C63">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D63">
         <v>0</v>
       </c>
       <c r="E63">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="F63">
         <v>0</v>
@@ -2472,13 +2472,13 @@
         <v>79</v>
       </c>
       <c r="C78">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D78">
         <v>0</v>
       </c>
       <c r="E78">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="F78">
         <v>0</v>
@@ -2832,13 +2832,13 @@
         <v>63</v>
       </c>
       <c r="C96">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D96">
         <v>0</v>
       </c>
       <c r="E96">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F96">
         <v>0</v>
@@ -3015,10 +3015,10 @@
         <v>2</v>
       </c>
       <c r="D105">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E105">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F105">
         <v>0</v>
@@ -3732,13 +3732,13 @@
         <v>23</v>
       </c>
       <c r="C141">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D141">
         <v>0</v>
       </c>
       <c r="E141">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F141">
         <v>0</v>

--- a/resumo_busca_ativa_consolidado.xlsx
+++ b/resumo_busca_ativa_consolidado.xlsx
@@ -149,10 +149,10 @@
     <t>SAO MIGUEL DO ARAGUAIA</t>
   </si>
   <si>
+    <t>ITAPACI</t>
+  </si>
+  <si>
     <t>ACREUNA</t>
-  </si>
-  <si>
-    <t>ITAPACI</t>
   </si>
   <si>
     <t>BOM JESUS DE GOIAS</t>
@@ -859,16 +859,16 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>19061</v>
+        <v>19050</v>
       </c>
       <c r="C2">
-        <v>2501</v>
+        <v>2698</v>
       </c>
       <c r="D2">
-        <v>715</v>
+        <v>749</v>
       </c>
       <c r="E2">
-        <v>15740</v>
+        <v>15498</v>
       </c>
       <c r="F2">
         <v>54</v>
@@ -879,19 +879,19 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>16777</v>
+        <v>16773</v>
       </c>
       <c r="C3">
-        <v>2019</v>
+        <v>2207</v>
       </c>
       <c r="D3">
-        <v>1257</v>
+        <v>1279</v>
       </c>
       <c r="E3">
-        <v>13314</v>
+        <v>13127</v>
       </c>
       <c r="F3">
-        <v>153</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -902,16 +902,16 @@
         <v>9406</v>
       </c>
       <c r="C4">
-        <v>1184</v>
+        <v>1203</v>
       </c>
       <c r="D4">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="E4">
-        <v>7136</v>
+        <v>7118</v>
       </c>
       <c r="F4">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
   </sheetData>
@@ -949,16 +949,16 @@
         <v>10</v>
       </c>
       <c r="B2">
-        <v>9620</v>
+        <v>9615</v>
       </c>
       <c r="C2">
-        <v>1066</v>
+        <v>1160</v>
       </c>
       <c r="D2">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="E2">
-        <v>8294</v>
+        <v>8203</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -972,16 +972,16 @@
         <v>2369</v>
       </c>
       <c r="C3">
-        <v>256</v>
+        <v>294</v>
       </c>
       <c r="D3">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="E3">
-        <v>1820</v>
+        <v>1801</v>
       </c>
       <c r="F3">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -989,16 +989,16 @@
         <v>12</v>
       </c>
       <c r="B4">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="C4">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="D4">
         <v>152</v>
       </c>
       <c r="E4">
-        <v>1332</v>
+        <v>1328</v>
       </c>
       <c r="F4">
         <v>19</v>
@@ -1009,16 +1009,16 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="C5">
-        <v>223</v>
+        <v>264</v>
       </c>
       <c r="D5">
-        <v>279</v>
+        <v>314</v>
       </c>
       <c r="E5">
-        <v>1121</v>
+        <v>1044</v>
       </c>
       <c r="F5">
         <v>11</v>
@@ -1032,13 +1032,13 @@
         <v>1498</v>
       </c>
       <c r="C6">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="D6">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E6">
-        <v>1014</v>
+        <v>1008</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1052,13 +1052,13 @@
         <v>1270</v>
       </c>
       <c r="C7">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D7">
         <v>59</v>
       </c>
       <c r="E7">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="F7">
         <v>12</v>
@@ -1092,16 +1092,16 @@
         <v>1131</v>
       </c>
       <c r="C9">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="D9">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="E9">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="F9">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1112,13 +1112,13 @@
         <v>976</v>
       </c>
       <c r="C10">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="D10">
         <v>10</v>
       </c>
       <c r="E10">
-        <v>780</v>
+        <v>775</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1132,13 +1132,13 @@
         <v>919</v>
       </c>
       <c r="C11">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D11">
         <v>32</v>
       </c>
       <c r="E11">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1152,13 +1152,13 @@
         <v>910</v>
       </c>
       <c r="C12">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="F12">
         <v>2</v>
@@ -1172,13 +1172,13 @@
         <v>840</v>
       </c>
       <c r="C13">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D13">
         <v>69</v>
       </c>
       <c r="E13">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F13">
         <v>101</v>
@@ -1192,13 +1192,13 @@
         <v>813</v>
       </c>
       <c r="C14">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D14">
         <v>21</v>
       </c>
       <c r="E14">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1212,13 +1212,13 @@
         <v>811</v>
       </c>
       <c r="C15">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D15">
         <v>56</v>
       </c>
       <c r="E15">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -1232,7 +1232,7 @@
         <v>783</v>
       </c>
       <c r="C16">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D16">
         <v>66</v>
@@ -1252,13 +1252,13 @@
         <v>729</v>
       </c>
       <c r="C17">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D17">
         <v>8</v>
       </c>
       <c r="E17">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1289,16 +1289,16 @@
         <v>27</v>
       </c>
       <c r="B19">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C19">
-        <v>115</v>
+        <v>148</v>
       </c>
       <c r="D19">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="E19">
-        <v>479</v>
+        <v>421</v>
       </c>
       <c r="F19">
         <v>12</v>
@@ -1329,16 +1329,16 @@
         <v>29</v>
       </c>
       <c r="B21">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="C21">
-        <v>189</v>
+        <v>218</v>
       </c>
       <c r="D21">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="E21">
-        <v>403</v>
+        <v>350</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1349,13 +1349,13 @@
         <v>30</v>
       </c>
       <c r="B22">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C22">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D22">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E22">
         <v>502</v>
@@ -1372,13 +1372,13 @@
         <v>600</v>
       </c>
       <c r="C23">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D23">
         <v>71</v>
       </c>
       <c r="E23">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="F23">
         <v>17</v>
@@ -1412,13 +1412,13 @@
         <v>495</v>
       </c>
       <c r="C25">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="D25">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E25">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1432,13 +1432,13 @@
         <v>448</v>
       </c>
       <c r="C26">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D26">
         <v>0</v>
       </c>
       <c r="E26">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -1452,13 +1452,13 @@
         <v>442</v>
       </c>
       <c r="C27">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D27">
         <v>95</v>
       </c>
       <c r="E27">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -1512,10 +1512,10 @@
         <v>401</v>
       </c>
       <c r="C30">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D30">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E30">
         <v>274</v>
@@ -1552,13 +1552,13 @@
         <v>388</v>
       </c>
       <c r="C32">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D32">
         <v>0</v>
       </c>
       <c r="E32">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -1592,13 +1592,13 @@
         <v>287</v>
       </c>
       <c r="C34">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D34">
         <v>0</v>
       </c>
       <c r="E34">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F34">
         <v>0</v>
@@ -1629,19 +1629,19 @@
         <v>44</v>
       </c>
       <c r="B36">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C36">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="D36">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E36">
-        <v>159</v>
+        <v>193</v>
       </c>
       <c r="F36">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -1649,19 +1649,19 @@
         <v>45</v>
       </c>
       <c r="B37">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C37">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E37">
-        <v>194</v>
+        <v>134</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -1692,13 +1692,13 @@
         <v>230</v>
       </c>
       <c r="C39">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D39">
         <v>42</v>
       </c>
       <c r="E39">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -1732,13 +1732,13 @@
         <v>221</v>
       </c>
       <c r="C41">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D41">
         <v>27</v>
       </c>
       <c r="E41">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -1752,13 +1752,13 @@
         <v>207</v>
       </c>
       <c r="C42">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D42">
         <v>0</v>
       </c>
       <c r="E42">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F42">
         <v>0</v>
@@ -1772,13 +1772,13 @@
         <v>197</v>
       </c>
       <c r="C43">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D43">
         <v>21</v>
       </c>
       <c r="E43">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F43">
         <v>0</v>
@@ -1792,13 +1792,13 @@
         <v>194</v>
       </c>
       <c r="C44">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D44">
         <v>0</v>
       </c>
       <c r="E44">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F44">
         <v>0</v>
@@ -1912,13 +1912,13 @@
         <v>154</v>
       </c>
       <c r="C50">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D50">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="E50">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="F50">
         <v>0</v>
@@ -1972,13 +1972,13 @@
         <v>149</v>
       </c>
       <c r="C53">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="D53">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E53">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="F53">
         <v>0</v>
@@ -2012,13 +2012,13 @@
         <v>138</v>
       </c>
       <c r="C55">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D55">
         <v>0</v>
       </c>
       <c r="E55">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F55">
         <v>0</v>
@@ -2035,10 +2035,10 @@
         <v>27</v>
       </c>
       <c r="D56">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="E56">
-        <v>107</v>
+        <v>74</v>
       </c>
       <c r="F56">
         <v>0</v>
@@ -2112,13 +2112,13 @@
         <v>124</v>
       </c>
       <c r="C60">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D60">
         <v>24</v>
       </c>
       <c r="E60">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -2152,13 +2152,13 @@
         <v>118</v>
       </c>
       <c r="C62">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D62">
         <v>0</v>
       </c>
       <c r="E62">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F62">
         <v>0</v>
@@ -2172,13 +2172,13 @@
         <v>111</v>
       </c>
       <c r="C63">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D63">
         <v>0</v>
       </c>
       <c r="E63">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F63">
         <v>0</v>
@@ -2212,13 +2212,13 @@
         <v>108</v>
       </c>
       <c r="C65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D65">
         <v>0</v>
       </c>
       <c r="E65">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F65">
         <v>0</v>
@@ -2272,13 +2272,13 @@
         <v>103</v>
       </c>
       <c r="C68">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D68">
         <v>0</v>
       </c>
       <c r="E68">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="F68">
         <v>0</v>
@@ -2292,13 +2292,13 @@
         <v>100</v>
       </c>
       <c r="C69">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D69">
         <v>0</v>
       </c>
       <c r="E69">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F69">
         <v>0</v>
@@ -2352,13 +2352,13 @@
         <v>89</v>
       </c>
       <c r="C72">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D72">
         <v>0</v>
       </c>
       <c r="E72">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F72">
         <v>0</v>
@@ -2452,10 +2452,10 @@
         <v>80</v>
       </c>
       <c r="C77">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D77">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E77">
         <v>28</v>
@@ -2472,13 +2472,13 @@
         <v>79</v>
       </c>
       <c r="C78">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="D78">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E78">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="F78">
         <v>0</v>
@@ -2612,7 +2612,7 @@
         <v>74</v>
       </c>
       <c r="C85">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D85">
         <v>0</v>
@@ -2621,7 +2621,7 @@
         <v>68</v>
       </c>
       <c r="F85">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86" spans="1:6">
@@ -2672,13 +2672,13 @@
         <v>68</v>
       </c>
       <c r="C88">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D88">
         <v>0</v>
       </c>
       <c r="E88">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F88">
         <v>0</v>
@@ -2812,13 +2812,13 @@
         <v>63</v>
       </c>
       <c r="C95">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D95">
         <v>0</v>
       </c>
       <c r="E95">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F95">
         <v>0</v>
@@ -2872,13 +2872,13 @@
         <v>63</v>
       </c>
       <c r="C98">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D98">
         <v>0</v>
       </c>
       <c r="E98">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F98">
         <v>0</v>
@@ -2952,13 +2952,13 @@
         <v>57</v>
       </c>
       <c r="C102">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D102">
         <v>0</v>
       </c>
       <c r="E102">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F102">
         <v>0</v>
@@ -3012,13 +3012,13 @@
         <v>54</v>
       </c>
       <c r="C105">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D105">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E105">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F105">
         <v>0</v>
@@ -3132,13 +3132,13 @@
         <v>49</v>
       </c>
       <c r="C111">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D111">
         <v>0</v>
       </c>
       <c r="E111">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F111">
         <v>12</v>
@@ -3172,13 +3172,13 @@
         <v>48</v>
       </c>
       <c r="C113">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D113">
         <v>0</v>
       </c>
       <c r="E113">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F113">
         <v>0</v>
@@ -3312,13 +3312,13 @@
         <v>41</v>
       </c>
       <c r="C120">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D120">
         <v>0</v>
       </c>
       <c r="E120">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F120">
         <v>0</v>
@@ -3352,13 +3352,13 @@
         <v>39</v>
       </c>
       <c r="C122">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D122">
         <v>0</v>
       </c>
       <c r="E122">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F122">
         <v>0</v>
@@ -3692,13 +3692,13 @@
         <v>25</v>
       </c>
       <c r="C139">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D139">
         <v>0</v>
       </c>
       <c r="E139">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F139">
         <v>0</v>

--- a/resumo_busca_ativa_consolidado.xlsx
+++ b/resumo_busca_ativa_consolidado.xlsx
@@ -104,10 +104,10 @@
     <t>CRISTALINA</t>
   </si>
   <si>
+    <t>PORANGATU</t>
+  </si>
+  <si>
     <t>JARAGUA</t>
-  </si>
-  <si>
-    <t>PORANGATU</t>
   </si>
   <si>
     <t>PLANALTINA</t>
@@ -859,19 +859,19 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>19050</v>
+        <v>19044</v>
       </c>
       <c r="C2">
-        <v>2698</v>
+        <v>2627</v>
       </c>
       <c r="D2">
-        <v>749</v>
+        <v>718</v>
       </c>
       <c r="E2">
-        <v>15498</v>
+        <v>15590</v>
       </c>
       <c r="F2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -879,19 +879,19 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>16773</v>
+        <v>16772</v>
       </c>
       <c r="C3">
-        <v>2207</v>
+        <v>2239</v>
       </c>
       <c r="D3">
-        <v>1279</v>
+        <v>1560</v>
       </c>
       <c r="E3">
-        <v>13127</v>
+        <v>12808</v>
       </c>
       <c r="F3">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -902,13 +902,13 @@
         <v>9406</v>
       </c>
       <c r="C4">
-        <v>1203</v>
+        <v>1206</v>
       </c>
       <c r="D4">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="E4">
-        <v>7118</v>
+        <v>7116</v>
       </c>
       <c r="F4">
         <v>231</v>
@@ -949,16 +949,16 @@
         <v>10</v>
       </c>
       <c r="B2">
-        <v>9615</v>
+        <v>9614</v>
       </c>
       <c r="C2">
-        <v>1160</v>
+        <v>1132</v>
       </c>
       <c r="D2">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="E2">
-        <v>8203</v>
+        <v>8210</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -972,13 +972,13 @@
         <v>2369</v>
       </c>
       <c r="C3">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="D3">
         <v>184</v>
       </c>
       <c r="E3">
-        <v>1801</v>
+        <v>1796</v>
       </c>
       <c r="F3">
         <v>81</v>
@@ -1009,16 +1009,16 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="C5">
-        <v>264</v>
+        <v>239</v>
       </c>
       <c r="D5">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="E5">
-        <v>1044</v>
+        <v>1077</v>
       </c>
       <c r="F5">
         <v>11</v>
@@ -1035,10 +1035,10 @@
         <v>219</v>
       </c>
       <c r="D6">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E6">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1052,13 +1052,13 @@
         <v>1270</v>
       </c>
       <c r="C7">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D7">
         <v>59</v>
       </c>
       <c r="E7">
-        <v>942</v>
+        <v>939</v>
       </c>
       <c r="F7">
         <v>12</v>
@@ -1092,16 +1092,16 @@
         <v>1131</v>
       </c>
       <c r="C9">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="D9">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="E9">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1112,13 +1112,13 @@
         <v>976</v>
       </c>
       <c r="C10">
-        <v>188</v>
+        <v>221</v>
       </c>
       <c r="D10">
-        <v>10</v>
+        <v>299</v>
       </c>
       <c r="E10">
-        <v>775</v>
+        <v>453</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1212,16 +1212,16 @@
         <v>811</v>
       </c>
       <c r="C15">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D15">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E15">
-        <v>696</v>
+        <v>691</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1289,19 +1289,19 @@
         <v>27</v>
       </c>
       <c r="B19">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="C19">
-        <v>148</v>
+        <v>122</v>
       </c>
       <c r="D19">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="E19">
-        <v>421</v>
+        <v>469</v>
       </c>
       <c r="F19">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1329,16 +1329,16 @@
         <v>29</v>
       </c>
       <c r="B21">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C21">
-        <v>218</v>
+        <v>97</v>
       </c>
       <c r="D21">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="E21">
-        <v>350</v>
+        <v>494</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1349,16 +1349,16 @@
         <v>30</v>
       </c>
       <c r="B22">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C22">
-        <v>99</v>
+        <v>209</v>
       </c>
       <c r="D22">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E22">
-        <v>502</v>
+        <v>382</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1395,10 +1395,10 @@
         <v>51</v>
       </c>
       <c r="D24">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="E24">
-        <v>437</v>
+        <v>418</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1412,16 +1412,16 @@
         <v>495</v>
       </c>
       <c r="C25">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="D25">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E25">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -1512,13 +1512,13 @@
         <v>401</v>
       </c>
       <c r="C30">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D30">
         <v>60</v>
       </c>
       <c r="E30">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -1655,13 +1655,13 @@
         <v>81</v>
       </c>
       <c r="D37">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E37">
         <v>134</v>
       </c>
       <c r="F37">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -1972,13 +1972,13 @@
         <v>149</v>
       </c>
       <c r="C53">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="D53">
         <v>0</v>
       </c>
       <c r="E53">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F53">
         <v>0</v>
@@ -2032,13 +2032,13 @@
         <v>138</v>
       </c>
       <c r="C56">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D56">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E56">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="F56">
         <v>0</v>
@@ -2472,13 +2472,13 @@
         <v>79</v>
       </c>
       <c r="C78">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D78">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E78">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="F78">
         <v>0</v>
@@ -2592,16 +2592,16 @@
         <v>74</v>
       </c>
       <c r="C84">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D84">
         <v>0</v>
       </c>
       <c r="E84">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="F84">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -2632,13 +2632,13 @@
         <v>74</v>
       </c>
       <c r="C86">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D86">
         <v>0</v>
       </c>
       <c r="E86">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F86">
         <v>0</v>
@@ -2672,13 +2672,13 @@
         <v>68</v>
       </c>
       <c r="C88">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D88">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E88">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="F88">
         <v>0</v>
@@ -2912,13 +2912,13 @@
         <v>58</v>
       </c>
       <c r="C100">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D100">
         <v>0</v>
       </c>
       <c r="E100">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F100">
         <v>0</v>
@@ -3112,13 +3112,13 @@
         <v>52</v>
       </c>
       <c r="C110">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D110">
         <v>0</v>
       </c>
       <c r="E110">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="F110">
         <v>0</v>
@@ -3172,13 +3172,13 @@
         <v>48</v>
       </c>
       <c r="C113">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D113">
         <v>0</v>
       </c>
       <c r="E113">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F113">
         <v>0</v>
@@ -3552,13 +3552,13 @@
         <v>35</v>
       </c>
       <c r="C132">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D132">
         <v>0</v>
       </c>
       <c r="E132">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F132">
         <v>0</v>

--- a/resumo_busca_ativa_consolidado.xlsx
+++ b/resumo_busca_ativa_consolidado.xlsx
@@ -862,13 +862,13 @@
         <v>19044</v>
       </c>
       <c r="C2">
-        <v>2627</v>
+        <v>2659</v>
       </c>
       <c r="D2">
-        <v>718</v>
+        <v>691</v>
       </c>
       <c r="E2">
-        <v>15590</v>
+        <v>15585</v>
       </c>
       <c r="F2">
         <v>58</v>
@@ -882,16 +882,16 @@
         <v>16772</v>
       </c>
       <c r="C3">
-        <v>2239</v>
+        <v>2360</v>
       </c>
       <c r="D3">
-        <v>1560</v>
+        <v>1562</v>
       </c>
       <c r="E3">
-        <v>12808</v>
+        <v>12691</v>
       </c>
       <c r="F3">
-        <v>129</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -952,13 +952,13 @@
         <v>9614</v>
       </c>
       <c r="C2">
-        <v>1132</v>
+        <v>1145</v>
       </c>
       <c r="D2">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="E2">
-        <v>8210</v>
+        <v>8205</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -972,13 +972,13 @@
         <v>2369</v>
       </c>
       <c r="C3">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="D3">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="E3">
-        <v>1796</v>
+        <v>1775</v>
       </c>
       <c r="F3">
         <v>81</v>
@@ -1012,10 +1012,10 @@
         <v>1636</v>
       </c>
       <c r="C5">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="D5">
-        <v>305</v>
+        <v>292</v>
       </c>
       <c r="E5">
         <v>1077</v>
@@ -1092,16 +1092,16 @@
         <v>1131</v>
       </c>
       <c r="C9">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="D9">
-        <v>337</v>
+        <v>371</v>
       </c>
       <c r="E9">
-        <v>612</v>
+        <v>566</v>
       </c>
       <c r="F9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1112,13 +1112,13 @@
         <v>976</v>
       </c>
       <c r="C10">
-        <v>221</v>
+        <v>279</v>
       </c>
       <c r="D10">
-        <v>299</v>
+        <v>281</v>
       </c>
       <c r="E10">
-        <v>453</v>
+        <v>413</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1212,16 +1212,16 @@
         <v>811</v>
       </c>
       <c r="C15">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D15">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E15">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="F15">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1392,10 +1392,10 @@
         <v>502</v>
       </c>
       <c r="C24">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D24">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E24">
         <v>418</v>
@@ -1412,16 +1412,16 @@
         <v>495</v>
       </c>
       <c r="C25">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="D25">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="E25">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -1512,10 +1512,10 @@
         <v>401</v>
       </c>
       <c r="C30">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D30">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E30">
         <v>280</v>
@@ -1772,13 +1772,13 @@
         <v>197</v>
       </c>
       <c r="C43">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D43">
         <v>21</v>
       </c>
       <c r="E43">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F43">
         <v>0</v>
@@ -2592,16 +2592,16 @@
         <v>74</v>
       </c>
       <c r="C84">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D84">
         <v>0</v>
       </c>
       <c r="E84">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F84">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -2672,10 +2672,10 @@
         <v>68</v>
       </c>
       <c r="C88">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="D88">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E88">
         <v>40</v>

--- a/resumo_busca_ativa_consolidado.xlsx
+++ b/resumo_busca_ativa_consolidado.xlsx
@@ -104,12 +104,12 @@
     <t>CRISTALINA</t>
   </si>
   <si>
+    <t>JARAGUA</t>
+  </si>
+  <si>
     <t>PORANGATU</t>
   </si>
   <si>
-    <t>JARAGUA</t>
-  </si>
-  <si>
     <t>PLANALTINA</t>
   </si>
   <si>
@@ -119,12 +119,12 @@
     <t>PIRACANJUBA</t>
   </si>
   <si>
+    <t>CIDADE OCIDENTAL</t>
+  </si>
+  <si>
     <t>RUBIATABA</t>
   </si>
   <si>
-    <t>CIDADE OCIDENTAL</t>
-  </si>
-  <si>
     <t>PIRENOPOLIS</t>
   </si>
   <si>
@@ -149,24 +149,24 @@
     <t>SAO MIGUEL DO ARAGUAIA</t>
   </si>
   <si>
+    <t>ACREUNA</t>
+  </si>
+  <si>
     <t>ITAPACI</t>
   </si>
   <si>
-    <t>ACREUNA</t>
-  </si>
-  <si>
     <t>BOM JESUS DE GOIAS</t>
   </si>
   <si>
     <t>MARA ROSA</t>
   </si>
   <si>
+    <t>COCALZINHO DE GOIAS</t>
+  </si>
+  <si>
     <t>GOIANAPOLIS</t>
   </si>
   <si>
-    <t>COCALZINHO DE GOIAS</t>
-  </si>
-  <si>
     <t>BURITI ALEGRE</t>
   </si>
   <si>
@@ -194,15 +194,15 @@
     <t>CRIXAS</t>
   </si>
   <si>
+    <t>PETROLINA DE GOIAS</t>
+  </si>
+  <si>
+    <t>NOVA CRIXAS</t>
+  </si>
+  <si>
     <t>CORUMBA DE GOIAS</t>
   </si>
   <si>
-    <t>NOVA CRIXAS</t>
-  </si>
-  <si>
-    <t>PETROLINA DE GOIAS</t>
-  </si>
-  <si>
     <t>GOIANDIRA</t>
   </si>
   <si>
@@ -269,13 +269,13 @@
     <t>SANTA TEREZA DE GOIAS</t>
   </si>
   <si>
+    <t>OURO VERDE DE GOIAS</t>
+  </si>
+  <si>
     <t>RIO QUENTE</t>
   </si>
   <si>
     <t>MUNDO NOVO</t>
-  </si>
-  <si>
-    <t>OURO VERDE DE GOIAS</t>
   </si>
   <si>
     <t>CACHOEIRA DOURADA</t>
@@ -859,19 +859,19 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>19044</v>
+        <v>19133</v>
       </c>
       <c r="C2">
-        <v>2659</v>
+        <v>2748</v>
       </c>
       <c r="D2">
-        <v>691</v>
+        <v>679</v>
       </c>
       <c r="E2">
-        <v>15585</v>
+        <v>15596</v>
       </c>
       <c r="F2">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -879,16 +879,16 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>16772</v>
+        <v>16817</v>
       </c>
       <c r="C3">
-        <v>2360</v>
+        <v>2457</v>
       </c>
       <c r="D3">
-        <v>1562</v>
+        <v>1536</v>
       </c>
       <c r="E3">
-        <v>12691</v>
+        <v>12665</v>
       </c>
       <c r="F3">
         <v>123</v>
@@ -899,10 +899,10 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>9406</v>
+        <v>9446</v>
       </c>
       <c r="C4">
-        <v>1206</v>
+        <v>1246</v>
       </c>
       <c r="D4">
         <v>806</v>
@@ -949,16 +949,16 @@
         <v>10</v>
       </c>
       <c r="B2">
-        <v>9614</v>
+        <v>9670</v>
       </c>
       <c r="C2">
-        <v>1145</v>
+        <v>1193</v>
       </c>
       <c r="D2">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="E2">
-        <v>8205</v>
+        <v>8221</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -969,16 +969,16 @@
         <v>11</v>
       </c>
       <c r="B3">
-        <v>2369</v>
+        <v>2381</v>
       </c>
       <c r="C3">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="D3">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="E3">
-        <v>1775</v>
+        <v>1760</v>
       </c>
       <c r="F3">
         <v>81</v>
@@ -1009,16 +1009,16 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>1636</v>
+        <v>1649</v>
       </c>
       <c r="C5">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="D5">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="E5">
-        <v>1077</v>
+        <v>1088</v>
       </c>
       <c r="F5">
         <v>11</v>
@@ -1029,10 +1029,10 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>1498</v>
+        <v>1500</v>
       </c>
       <c r="C6">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D6">
         <v>261</v>
@@ -1049,10 +1049,10 @@
         <v>15</v>
       </c>
       <c r="B7">
-        <v>1270</v>
+        <v>1280</v>
       </c>
       <c r="C7">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="D7">
         <v>59</v>
@@ -1089,16 +1089,16 @@
         <v>17</v>
       </c>
       <c r="B9">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="C9">
-        <v>185</v>
+        <v>218</v>
       </c>
       <c r="D9">
-        <v>371</v>
+        <v>356</v>
       </c>
       <c r="E9">
-        <v>566</v>
+        <v>552</v>
       </c>
       <c r="F9">
         <v>2</v>
@@ -1109,16 +1109,16 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="C10">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="D10">
-        <v>281</v>
+        <v>239</v>
       </c>
       <c r="E10">
-        <v>413</v>
+        <v>461</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1129,10 +1129,10 @@
         <v>19</v>
       </c>
       <c r="B11">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="C11">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D11">
         <v>32</v>
@@ -1149,10 +1149,10 @@
         <v>20</v>
       </c>
       <c r="B12">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="C12">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -1169,10 +1169,10 @@
         <v>21</v>
       </c>
       <c r="B13">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="C13">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D13">
         <v>69</v>
@@ -1212,13 +1212,13 @@
         <v>811</v>
       </c>
       <c r="C15">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="D15">
         <v>56</v>
       </c>
       <c r="E15">
-        <v>689</v>
+        <v>672</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -1229,10 +1229,10 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="C16">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="D16">
         <v>66</v>
@@ -1289,16 +1289,16 @@
         <v>27</v>
       </c>
       <c r="B19">
-        <v>661</v>
+        <v>667</v>
       </c>
       <c r="C19">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="D19">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E19">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="F19">
         <v>16</v>
@@ -1329,16 +1329,16 @@
         <v>29</v>
       </c>
       <c r="B21">
-        <v>609</v>
+        <v>616</v>
       </c>
       <c r="C21">
-        <v>97</v>
+        <v>226</v>
       </c>
       <c r="D21">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="E21">
-        <v>494</v>
+        <v>345</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1349,19 +1349,19 @@
         <v>30</v>
       </c>
       <c r="B22">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="C22">
-        <v>209</v>
+        <v>99</v>
       </c>
       <c r="D22">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E22">
-        <v>382</v>
+        <v>493</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -1369,10 +1369,10 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C23">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D23">
         <v>71</v>
@@ -1389,16 +1389,16 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C24">
         <v>53</v>
       </c>
       <c r="D24">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E24">
-        <v>418</v>
+        <v>450</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1412,13 +1412,13 @@
         <v>495</v>
       </c>
       <c r="C25">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D25">
         <v>22</v>
       </c>
       <c r="E25">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1429,16 +1429,16 @@
         <v>34</v>
       </c>
       <c r="B26">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C26">
-        <v>58</v>
+        <v>103</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="E26">
-        <v>390</v>
+        <v>251</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -1449,16 +1449,16 @@
         <v>35</v>
       </c>
       <c r="B27">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="C27">
-        <v>96</v>
+        <v>58</v>
       </c>
       <c r="D27">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="E27">
-        <v>251</v>
+        <v>390</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -1509,16 +1509,16 @@
         <v>38</v>
       </c>
       <c r="B30">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C30">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D30">
         <v>56</v>
       </c>
       <c r="E30">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -1529,10 +1529,10 @@
         <v>39</v>
       </c>
       <c r="B31">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C31">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D31">
         <v>31</v>
@@ -1549,10 +1549,10 @@
         <v>40</v>
       </c>
       <c r="B32">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C32">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -1589,10 +1589,10 @@
         <v>42</v>
       </c>
       <c r="B34">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="C34">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -1609,10 +1609,10 @@
         <v>43</v>
       </c>
       <c r="B35">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C35">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D35">
         <v>21</v>
@@ -1629,16 +1629,16 @@
         <v>44</v>
       </c>
       <c r="B36">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="C36">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="E36">
-        <v>193</v>
+        <v>134</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -1649,16 +1649,16 @@
         <v>45</v>
       </c>
       <c r="B37">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C37">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="D37">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="E37">
-        <v>134</v>
+        <v>193</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -1669,10 +1669,10 @@
         <v>46</v>
       </c>
       <c r="B38">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C38">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D38">
         <v>59</v>
@@ -1689,10 +1689,10 @@
         <v>47</v>
       </c>
       <c r="B39">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C39">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D39">
         <v>42</v>
@@ -1709,16 +1709,16 @@
         <v>48</v>
       </c>
       <c r="B40">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C40">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="E40">
-        <v>202</v>
+        <v>130</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -1729,16 +1729,16 @@
         <v>49</v>
       </c>
       <c r="B41">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C41">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="D41">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="E41">
-        <v>130</v>
+        <v>202</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -1769,10 +1769,10 @@
         <v>51</v>
       </c>
       <c r="B43">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C43">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D43">
         <v>21</v>
@@ -1929,16 +1929,16 @@
         <v>59</v>
       </c>
       <c r="B51">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C51">
-        <v>12</v>
+        <v>83</v>
       </c>
       <c r="D51">
         <v>0</v>
       </c>
       <c r="E51">
-        <v>138</v>
+        <v>68</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -1969,16 +1969,16 @@
         <v>61</v>
       </c>
       <c r="B53">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C53">
-        <v>81</v>
+        <v>12</v>
       </c>
       <c r="D53">
         <v>0</v>
       </c>
       <c r="E53">
-        <v>68</v>
+        <v>138</v>
       </c>
       <c r="F53">
         <v>0</v>
@@ -2012,13 +2012,13 @@
         <v>138</v>
       </c>
       <c r="C55">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D55">
         <v>0</v>
       </c>
       <c r="E55">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="F55">
         <v>0</v>
@@ -2115,10 +2115,10 @@
         <v>33</v>
       </c>
       <c r="D60">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E60">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -2232,13 +2232,13 @@
         <v>107</v>
       </c>
       <c r="C66">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D66">
         <v>0</v>
       </c>
       <c r="E66">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="F66">
         <v>0</v>
@@ -2272,13 +2272,13 @@
         <v>103</v>
       </c>
       <c r="C68">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D68">
         <v>0</v>
       </c>
       <c r="E68">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F68">
         <v>0</v>
@@ -2392,13 +2392,13 @@
         <v>86</v>
       </c>
       <c r="C74">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D74">
         <v>0</v>
       </c>
       <c r="E74">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F74">
         <v>0</v>
@@ -2432,13 +2432,13 @@
         <v>81</v>
       </c>
       <c r="C76">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D76">
         <v>0</v>
       </c>
       <c r="E76">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="F76">
         <v>0</v>
@@ -2449,16 +2449,16 @@
         <v>85</v>
       </c>
       <c r="B77">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C77">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="D77">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E77">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="F77">
         <v>0</v>
@@ -2469,16 +2469,16 @@
         <v>86</v>
       </c>
       <c r="B78">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C78">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="D78">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E78">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="F78">
         <v>0</v>
@@ -2572,13 +2572,13 @@
         <v>75</v>
       </c>
       <c r="C83">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D83">
         <v>0</v>
       </c>
       <c r="E83">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="F83">
         <v>0</v>
@@ -2672,13 +2672,13 @@
         <v>68</v>
       </c>
       <c r="C88">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="D88">
         <v>0</v>
       </c>
       <c r="E88">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="F88">
         <v>0</v>
@@ -3209,10 +3209,10 @@
         <v>123</v>
       </c>
       <c r="B115">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C115">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D115">
         <v>0</v>

--- a/resumo_busca_ativa_consolidado.xlsx
+++ b/resumo_busca_ativa_consolidado.xlsx
@@ -104,12 +104,12 @@
     <t>CRISTALINA</t>
   </si>
   <si>
+    <t>PORANGATU</t>
+  </si>
+  <si>
     <t>JARAGUA</t>
   </si>
   <si>
-    <t>PORANGATU</t>
-  </si>
-  <si>
     <t>PLANALTINA</t>
   </si>
   <si>
@@ -119,12 +119,12 @@
     <t>PIRACANJUBA</t>
   </si>
   <si>
+    <t>RUBIATABA</t>
+  </si>
+  <si>
     <t>CIDADE OCIDENTAL</t>
   </si>
   <si>
-    <t>RUBIATABA</t>
-  </si>
-  <si>
     <t>PIRENOPOLIS</t>
   </si>
   <si>
@@ -149,24 +149,24 @@
     <t>SAO MIGUEL DO ARAGUAIA</t>
   </si>
   <si>
+    <t>ITAPACI</t>
+  </si>
+  <si>
+    <t>BOM JESUS DE GOIAS</t>
+  </si>
+  <si>
     <t>ACREUNA</t>
   </si>
   <si>
-    <t>ITAPACI</t>
-  </si>
-  <si>
-    <t>BOM JESUS DE GOIAS</t>
-  </si>
-  <si>
     <t>MARA ROSA</t>
   </si>
   <si>
+    <t>GOIANAPOLIS</t>
+  </si>
+  <si>
     <t>COCALZINHO DE GOIAS</t>
   </si>
   <si>
-    <t>GOIANAPOLIS</t>
-  </si>
-  <si>
     <t>BURITI ALEGRE</t>
   </si>
   <si>
@@ -194,33 +194,33 @@
     <t>CRIXAS</t>
   </si>
   <si>
+    <t>CORUMBA DE GOIAS</t>
+  </si>
+  <si>
+    <t>NOVA CRIXAS</t>
+  </si>
+  <si>
     <t>PETROLINA DE GOIAS</t>
   </si>
   <si>
-    <t>NOVA CRIXAS</t>
-  </si>
-  <si>
-    <t>CORUMBA DE GOIAS</t>
-  </si>
-  <si>
     <t>GOIANDIRA</t>
   </si>
   <si>
+    <t>SAO FRANCISCO DE GOIAS</t>
+  </si>
+  <si>
+    <t>CAMPO ALEGRE DE GOIAS</t>
+  </si>
+  <si>
+    <t>FORMOSO</t>
+  </si>
+  <si>
+    <t>BARRO ALTO</t>
+  </si>
+  <si>
     <t>CAMPO LIMPO DE GOIAS</t>
   </si>
   <si>
-    <t>SAO FRANCISCO DE GOIAS</t>
-  </si>
-  <si>
-    <t>CAMPO ALEGRE DE GOIAS</t>
-  </si>
-  <si>
-    <t>BARRO ALTO</t>
-  </si>
-  <si>
-    <t>FORMOSO</t>
-  </si>
-  <si>
     <t>CAMPINORTE</t>
   </si>
   <si>
@@ -269,15 +269,15 @@
     <t>SANTA TEREZA DE GOIAS</t>
   </si>
   <si>
+    <t>RIO QUENTE</t>
+  </si>
+  <si>
+    <t>MUNDO NOVO</t>
+  </si>
+  <si>
     <t>OURO VERDE DE GOIAS</t>
   </si>
   <si>
-    <t>RIO QUENTE</t>
-  </si>
-  <si>
-    <t>MUNDO NOVO</t>
-  </si>
-  <si>
     <t>CACHOEIRA DOURADA</t>
   </si>
   <si>
@@ -437,10 +437,10 @@
     <t>AMARALINA</t>
   </si>
   <si>
+    <t>ALTO HORIZONTE</t>
+  </si>
+  <si>
     <t>PILAR DE GOIAS</t>
-  </si>
-  <si>
-    <t>ALTO HORIZONTE</t>
   </si>
   <si>
     <t>GUARINOS</t>
@@ -859,19 +859,19 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>19133</v>
+        <v>19014</v>
       </c>
       <c r="C2">
-        <v>2748</v>
+        <v>2881</v>
       </c>
       <c r="D2">
-        <v>679</v>
+        <v>696</v>
       </c>
       <c r="E2">
-        <v>15596</v>
+        <v>15294</v>
       </c>
       <c r="F2">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -879,19 +879,19 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>16817</v>
+        <v>16723</v>
       </c>
       <c r="C3">
-        <v>2457</v>
+        <v>2674</v>
       </c>
       <c r="D3">
-        <v>1536</v>
+        <v>1429</v>
       </c>
       <c r="E3">
-        <v>12665</v>
+        <v>12420</v>
       </c>
       <c r="F3">
-        <v>123</v>
+        <v>162</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -899,16 +899,16 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>9446</v>
+        <v>9404</v>
       </c>
       <c r="C4">
-        <v>1246</v>
+        <v>1262</v>
       </c>
       <c r="D4">
-        <v>806</v>
+        <v>788</v>
       </c>
       <c r="E4">
-        <v>7116</v>
+        <v>7074</v>
       </c>
       <c r="F4">
         <v>231</v>
@@ -949,16 +949,16 @@
         <v>10</v>
       </c>
       <c r="B2">
-        <v>9670</v>
+        <v>9608</v>
       </c>
       <c r="C2">
-        <v>1193</v>
+        <v>1247</v>
       </c>
       <c r="D2">
-        <v>237</v>
+        <v>257</v>
       </c>
       <c r="E2">
-        <v>8221</v>
+        <v>8081</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -969,16 +969,16 @@
         <v>11</v>
       </c>
       <c r="B3">
-        <v>2381</v>
+        <v>2366</v>
       </c>
       <c r="C3">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="D3">
-        <v>210</v>
+        <v>236</v>
       </c>
       <c r="E3">
-        <v>1760</v>
+        <v>1711</v>
       </c>
       <c r="F3">
         <v>81</v>
@@ -992,13 +992,13 @@
         <v>1735</v>
       </c>
       <c r="C4">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="D4">
         <v>152</v>
       </c>
       <c r="E4">
-        <v>1328</v>
+        <v>1321</v>
       </c>
       <c r="F4">
         <v>19</v>
@@ -1009,16 +1009,16 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>1649</v>
+        <v>1632</v>
       </c>
       <c r="C5">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="D5">
-        <v>286</v>
+        <v>231</v>
       </c>
       <c r="E5">
-        <v>1088</v>
+        <v>1108</v>
       </c>
       <c r="F5">
         <v>11</v>
@@ -1029,16 +1029,16 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>1500</v>
+        <v>1498</v>
       </c>
       <c r="C6">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="D6">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E6">
-        <v>1009</v>
+        <v>999</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1049,16 +1049,16 @@
         <v>15</v>
       </c>
       <c r="B7">
-        <v>1280</v>
+        <v>1268</v>
       </c>
       <c r="C7">
         <v>266</v>
       </c>
       <c r="D7">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E7">
-        <v>939</v>
+        <v>929</v>
       </c>
       <c r="F7">
         <v>12</v>
@@ -1072,13 +1072,13 @@
         <v>1203</v>
       </c>
       <c r="C8">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D8">
         <v>44</v>
       </c>
       <c r="E8">
-        <v>1060</v>
+        <v>1055</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -1089,16 +1089,16 @@
         <v>17</v>
       </c>
       <c r="B9">
-        <v>1135</v>
+        <v>1127</v>
       </c>
       <c r="C9">
-        <v>218</v>
+        <v>270</v>
       </c>
       <c r="D9">
-        <v>356</v>
+        <v>341</v>
       </c>
       <c r="E9">
-        <v>552</v>
+        <v>507</v>
       </c>
       <c r="F9">
         <v>2</v>
@@ -1109,16 +1109,16 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>977</v>
+        <v>941</v>
       </c>
       <c r="C10">
-        <v>274</v>
+        <v>258</v>
       </c>
       <c r="D10">
-        <v>239</v>
+        <v>214</v>
       </c>
       <c r="E10">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1129,7 +1129,7 @@
         <v>19</v>
       </c>
       <c r="B11">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="C11">
         <v>73</v>
@@ -1138,7 +1138,7 @@
         <v>32</v>
       </c>
       <c r="E11">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1149,16 +1149,16 @@
         <v>20</v>
       </c>
       <c r="B12">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="C12">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12">
-        <v>790</v>
+        <v>781</v>
       </c>
       <c r="F12">
         <v>2</v>
@@ -1169,16 +1169,16 @@
         <v>21</v>
       </c>
       <c r="B13">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="C13">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D13">
         <v>69</v>
       </c>
       <c r="E13">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="F13">
         <v>101</v>
@@ -1192,16 +1192,16 @@
         <v>813</v>
       </c>
       <c r="C14">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="D14">
         <v>21</v>
       </c>
       <c r="E14">
-        <v>745</v>
+        <v>670</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1212,13 +1212,13 @@
         <v>811</v>
       </c>
       <c r="C15">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D15">
         <v>56</v>
       </c>
       <c r="E15">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -1229,16 +1229,16 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>790</v>
+        <v>783</v>
       </c>
       <c r="C16">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D16">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E16">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="F16">
         <v>84</v>
@@ -1252,13 +1252,13 @@
         <v>729</v>
       </c>
       <c r="C17">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D17">
         <v>8</v>
       </c>
       <c r="E17">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1289,16 +1289,16 @@
         <v>27</v>
       </c>
       <c r="B19">
-        <v>667</v>
+        <v>658</v>
       </c>
       <c r="C19">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="D19">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E19">
-        <v>463</v>
+        <v>432</v>
       </c>
       <c r="F19">
         <v>16</v>
@@ -1312,13 +1312,13 @@
         <v>646</v>
       </c>
       <c r="C20">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="D20">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="E20">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1329,16 +1329,16 @@
         <v>29</v>
       </c>
       <c r="B21">
-        <v>616</v>
+        <v>609</v>
       </c>
       <c r="C21">
-        <v>226</v>
+        <v>104</v>
       </c>
       <c r="D21">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="E21">
-        <v>345</v>
+        <v>465</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1349,19 +1349,19 @@
         <v>30</v>
       </c>
       <c r="B22">
-        <v>611</v>
+        <v>601</v>
       </c>
       <c r="C22">
-        <v>99</v>
+        <v>223</v>
       </c>
       <c r="D22">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="E22">
-        <v>493</v>
+        <v>333</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -1369,16 +1369,16 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C23">
         <v>93</v>
       </c>
       <c r="D23">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E23">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="F23">
         <v>17</v>
@@ -1389,16 +1389,16 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C24">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D24">
         <v>0</v>
       </c>
       <c r="E24">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1412,13 +1412,13 @@
         <v>495</v>
       </c>
       <c r="C25">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="D25">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E25">
-        <v>362</v>
+        <v>351</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1429,16 +1429,16 @@
         <v>34</v>
       </c>
       <c r="B26">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C26">
-        <v>103</v>
+        <v>58</v>
       </c>
       <c r="D26">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="E26">
-        <v>251</v>
+        <v>389</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -1449,16 +1449,16 @@
         <v>35</v>
       </c>
       <c r="B27">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="C27">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="E27">
-        <v>390</v>
+        <v>251</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -1472,16 +1472,16 @@
         <v>441</v>
       </c>
       <c r="C28">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D28">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E28">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F28">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -1492,13 +1492,13 @@
         <v>406</v>
       </c>
       <c r="C29">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D29">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E29">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="F29">
         <v>0</v>
@@ -1509,16 +1509,16 @@
         <v>38</v>
       </c>
       <c r="B30">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C30">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D30">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E30">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -1529,16 +1529,16 @@
         <v>39</v>
       </c>
       <c r="B31">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C31">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D31">
         <v>31</v>
       </c>
       <c r="E31">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F31">
         <v>24</v>
@@ -1549,16 +1549,16 @@
         <v>40</v>
       </c>
       <c r="B32">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C32">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D32">
         <v>0</v>
       </c>
       <c r="E32">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -1572,13 +1572,13 @@
         <v>316</v>
       </c>
       <c r="C33">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D33">
         <v>0</v>
       </c>
       <c r="E33">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -1589,16 +1589,16 @@
         <v>42</v>
       </c>
       <c r="B34">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="C34">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D34">
         <v>0</v>
       </c>
       <c r="E34">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F34">
         <v>0</v>
@@ -1609,16 +1609,16 @@
         <v>43</v>
       </c>
       <c r="B35">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C35">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D35">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E35">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -1629,16 +1629,16 @@
         <v>44</v>
       </c>
       <c r="B36">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="C36">
-        <v>90</v>
+        <v>51</v>
       </c>
       <c r="D36">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="E36">
-        <v>134</v>
+        <v>185</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -1649,16 +1649,16 @@
         <v>45</v>
       </c>
       <c r="B37">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C37">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="E37">
-        <v>193</v>
+        <v>125</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -1669,19 +1669,19 @@
         <v>46</v>
       </c>
       <c r="B38">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C38">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="D38">
-        <v>59</v>
+        <v>5</v>
       </c>
       <c r="E38">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="F38">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -1689,16 +1689,16 @@
         <v>47</v>
       </c>
       <c r="B39">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C39">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D39">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E39">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -1709,16 +1709,16 @@
         <v>48</v>
       </c>
       <c r="B40">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C40">
-        <v>66</v>
+        <v>21</v>
       </c>
       <c r="D40">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="E40">
-        <v>130</v>
+        <v>202</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -1729,16 +1729,16 @@
         <v>49</v>
       </c>
       <c r="B41">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C41">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="E41">
-        <v>202</v>
+        <v>124</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -1752,13 +1752,13 @@
         <v>207</v>
       </c>
       <c r="C42">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D42">
         <v>0</v>
       </c>
       <c r="E42">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="F42">
         <v>0</v>
@@ -1769,16 +1769,16 @@
         <v>51</v>
       </c>
       <c r="B43">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C43">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D43">
         <v>21</v>
       </c>
       <c r="E43">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F43">
         <v>0</v>
@@ -1832,16 +1832,16 @@
         <v>182</v>
       </c>
       <c r="C46">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D46">
         <v>0</v>
       </c>
       <c r="E46">
-        <v>175</v>
+        <v>159</v>
       </c>
       <c r="F46">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -1858,7 +1858,7 @@
         <v>1</v>
       </c>
       <c r="E47">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F47">
         <v>0</v>
@@ -1929,16 +1929,16 @@
         <v>59</v>
       </c>
       <c r="B51">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C51">
-        <v>83</v>
+        <v>12</v>
       </c>
       <c r="D51">
         <v>0</v>
       </c>
       <c r="E51">
-        <v>68</v>
+        <v>138</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -1958,7 +1958,7 @@
         <v>22</v>
       </c>
       <c r="E52">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F52">
         <v>0</v>
@@ -1969,16 +1969,16 @@
         <v>61</v>
       </c>
       <c r="B53">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C53">
-        <v>12</v>
+        <v>83</v>
       </c>
       <c r="D53">
         <v>0</v>
       </c>
       <c r="E53">
-        <v>138</v>
+        <v>65</v>
       </c>
       <c r="F53">
         <v>0</v>
@@ -2009,16 +2009,16 @@
         <v>63</v>
       </c>
       <c r="B55">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C55">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="D55">
         <v>0</v>
       </c>
       <c r="E55">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="F55">
         <v>0</v>
@@ -2029,10 +2029,10 @@
         <v>64</v>
       </c>
       <c r="B56">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="C56">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -2049,16 +2049,16 @@
         <v>65</v>
       </c>
       <c r="B57">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C57">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D57">
         <v>0</v>
       </c>
       <c r="E57">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="F57">
         <v>0</v>
@@ -2072,13 +2072,13 @@
         <v>127</v>
       </c>
       <c r="C58">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D58">
         <v>0</v>
       </c>
       <c r="E58">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F58">
         <v>0</v>
@@ -2092,13 +2092,13 @@
         <v>127</v>
       </c>
       <c r="C59">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="D59">
         <v>0</v>
       </c>
       <c r="E59">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="F59">
         <v>0</v>
@@ -2132,13 +2132,13 @@
         <v>123</v>
       </c>
       <c r="C61">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D61">
         <v>0</v>
       </c>
       <c r="E61">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="F61">
         <v>0</v>
@@ -2152,13 +2152,13 @@
         <v>118</v>
       </c>
       <c r="C62">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D62">
         <v>0</v>
       </c>
       <c r="E62">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="F62">
         <v>0</v>
@@ -2172,13 +2172,13 @@
         <v>111</v>
       </c>
       <c r="C63">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D63">
         <v>0</v>
       </c>
       <c r="E63">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F63">
         <v>0</v>
@@ -2232,13 +2232,13 @@
         <v>107</v>
       </c>
       <c r="C66">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D66">
         <v>0</v>
       </c>
       <c r="E66">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F66">
         <v>0</v>
@@ -2272,13 +2272,13 @@
         <v>103</v>
       </c>
       <c r="C68">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D68">
         <v>0</v>
       </c>
       <c r="E68">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F68">
         <v>0</v>
@@ -2332,13 +2332,13 @@
         <v>97</v>
       </c>
       <c r="C71">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D71">
         <v>0</v>
       </c>
       <c r="E71">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="F71">
         <v>0</v>
@@ -2352,13 +2352,13 @@
         <v>89</v>
       </c>
       <c r="C72">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D72">
         <v>0</v>
       </c>
       <c r="E72">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F72">
         <v>0</v>
@@ -2372,13 +2372,13 @@
         <v>88</v>
       </c>
       <c r="C73">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D73">
         <v>0</v>
       </c>
       <c r="E73">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="F73">
         <v>0</v>
@@ -2392,13 +2392,13 @@
         <v>86</v>
       </c>
       <c r="C74">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D74">
         <v>0</v>
       </c>
       <c r="E74">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="F74">
         <v>0</v>
@@ -2418,7 +2418,7 @@
         <v>0</v>
       </c>
       <c r="E75">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F75">
         <v>0</v>
@@ -2432,13 +2432,13 @@
         <v>81</v>
       </c>
       <c r="C76">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D76">
         <v>0</v>
       </c>
       <c r="E76">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="F76">
         <v>0</v>
@@ -2449,16 +2449,16 @@
         <v>85</v>
       </c>
       <c r="B77">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C77">
+        <v>36</v>
+      </c>
+      <c r="D77">
         <v>16</v>
       </c>
-      <c r="D77">
-        <v>20</v>
-      </c>
       <c r="E77">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="F77">
         <v>0</v>
@@ -2469,16 +2469,16 @@
         <v>86</v>
       </c>
       <c r="B78">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C78">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="D78">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E78">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="F78">
         <v>0</v>
@@ -2532,13 +2532,13 @@
         <v>76</v>
       </c>
       <c r="C81">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D81">
         <v>0</v>
       </c>
       <c r="E81">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F81">
         <v>0</v>
@@ -2572,13 +2572,13 @@
         <v>75</v>
       </c>
       <c r="C83">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D83">
         <v>0</v>
       </c>
       <c r="E83">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F83">
         <v>0</v>
@@ -2592,13 +2592,13 @@
         <v>74</v>
       </c>
       <c r="C84">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D84">
         <v>0</v>
       </c>
       <c r="E84">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F84">
         <v>2</v>
@@ -2632,13 +2632,13 @@
         <v>74</v>
       </c>
       <c r="C86">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D86">
         <v>0</v>
       </c>
       <c r="E86">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F86">
         <v>0</v>
@@ -2692,13 +2692,13 @@
         <v>67</v>
       </c>
       <c r="C89">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D89">
         <v>0</v>
       </c>
       <c r="E89">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F89">
         <v>0</v>
@@ -2772,13 +2772,13 @@
         <v>64</v>
       </c>
       <c r="C93">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D93">
         <v>0</v>
       </c>
       <c r="E93">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F93">
         <v>0</v>
@@ -2792,13 +2792,13 @@
         <v>64</v>
       </c>
       <c r="C94">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D94">
         <v>0</v>
       </c>
       <c r="E94">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F94">
         <v>0</v>
@@ -2852,13 +2852,13 @@
         <v>63</v>
       </c>
       <c r="C97">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D97">
         <v>0</v>
       </c>
       <c r="E97">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F97">
         <v>0</v>
@@ -2938,7 +2938,7 @@
         <v>0</v>
       </c>
       <c r="E101">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F101">
         <v>0</v>
@@ -2992,13 +2992,13 @@
         <v>54</v>
       </c>
       <c r="C104">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D104">
         <v>6</v>
       </c>
       <c r="E104">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F104">
         <v>1</v>
@@ -3078,7 +3078,7 @@
         <v>0</v>
       </c>
       <c r="E108">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F108">
         <v>0</v>
@@ -3172,13 +3172,13 @@
         <v>48</v>
       </c>
       <c r="C113">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D113">
         <v>0</v>
       </c>
       <c r="E113">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F113">
         <v>0</v>
@@ -3192,13 +3192,13 @@
         <v>47</v>
       </c>
       <c r="C114">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D114">
         <v>0</v>
       </c>
       <c r="E114">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F114">
         <v>0</v>
@@ -3209,10 +3209,10 @@
         <v>123</v>
       </c>
       <c r="B115">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C115">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D115">
         <v>0</v>
@@ -3232,13 +3232,13 @@
         <v>44</v>
       </c>
       <c r="C116">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D116">
         <v>0</v>
       </c>
       <c r="E116">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F116">
         <v>0</v>
@@ -3292,13 +3292,13 @@
         <v>43</v>
       </c>
       <c r="C119">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D119">
         <v>0</v>
       </c>
       <c r="E119">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F119">
         <v>0</v>
@@ -3458,7 +3458,7 @@
         <v>0</v>
       </c>
       <c r="E127">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F127">
         <v>0</v>
@@ -3492,13 +3492,13 @@
         <v>36</v>
       </c>
       <c r="C129">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D129">
         <v>0</v>
       </c>
       <c r="E129">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F129">
         <v>0</v>
@@ -3549,16 +3549,16 @@
         <v>140</v>
       </c>
       <c r="B132">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C132">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D132">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E132">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F132">
         <v>0</v>
@@ -3569,16 +3569,16 @@
         <v>141</v>
       </c>
       <c r="B133">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C133">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D133">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E133">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F133">
         <v>0</v>

--- a/resumo_busca_ativa_consolidado.xlsx
+++ b/resumo_busca_ativa_consolidado.xlsx
@@ -152,10 +152,10 @@
     <t>ITAPACI</t>
   </si>
   <si>
+    <t>ACREUNA</t>
+  </si>
+  <si>
     <t>BOM JESUS DE GOIAS</t>
-  </si>
-  <si>
-    <t>ACREUNA</t>
   </si>
   <si>
     <t>MARA ROSA</t>
@@ -859,19 +859,19 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>19014</v>
+        <v>19012</v>
       </c>
       <c r="C2">
-        <v>2881</v>
+        <v>2936</v>
       </c>
       <c r="D2">
-        <v>696</v>
+        <v>719</v>
       </c>
       <c r="E2">
-        <v>15294</v>
+        <v>15218</v>
       </c>
       <c r="F2">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -879,19 +879,19 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>16723</v>
+        <v>16724</v>
       </c>
       <c r="C3">
-        <v>2674</v>
+        <v>2736</v>
       </c>
       <c r="D3">
-        <v>1429</v>
+        <v>1423</v>
       </c>
       <c r="E3">
-        <v>12420</v>
+        <v>12375</v>
       </c>
       <c r="F3">
-        <v>162</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -899,19 +899,19 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>9404</v>
+        <v>9405</v>
       </c>
       <c r="C4">
-        <v>1262</v>
+        <v>1275</v>
       </c>
       <c r="D4">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="E4">
-        <v>7074</v>
+        <v>7062</v>
       </c>
       <c r="F4">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -949,16 +949,16 @@
         <v>10</v>
       </c>
       <c r="B2">
-        <v>9608</v>
+        <v>9606</v>
       </c>
       <c r="C2">
-        <v>1247</v>
+        <v>1265</v>
       </c>
       <c r="D2">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="E2">
-        <v>8081</v>
+        <v>8065</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -972,13 +972,13 @@
         <v>2366</v>
       </c>
       <c r="C3">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="D3">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="E3">
-        <v>1711</v>
+        <v>1700</v>
       </c>
       <c r="F3">
         <v>81</v>
@@ -992,13 +992,13 @@
         <v>1735</v>
       </c>
       <c r="C4">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D4">
         <v>152</v>
       </c>
       <c r="E4">
-        <v>1321</v>
+        <v>1318</v>
       </c>
       <c r="F4">
         <v>19</v>
@@ -1012,13 +1012,13 @@
         <v>1632</v>
       </c>
       <c r="C5">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="D5">
         <v>231</v>
       </c>
       <c r="E5">
-        <v>1108</v>
+        <v>1098</v>
       </c>
       <c r="F5">
         <v>11</v>
@@ -1032,13 +1032,13 @@
         <v>1498</v>
       </c>
       <c r="C6">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D6">
         <v>260</v>
       </c>
       <c r="E6">
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1052,13 +1052,13 @@
         <v>1268</v>
       </c>
       <c r="C7">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="D7">
         <v>57</v>
       </c>
       <c r="E7">
-        <v>929</v>
+        <v>922</v>
       </c>
       <c r="F7">
         <v>12</v>
@@ -1072,13 +1072,13 @@
         <v>1203</v>
       </c>
       <c r="C8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D8">
         <v>44</v>
       </c>
       <c r="E8">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -1092,13 +1092,13 @@
         <v>1127</v>
       </c>
       <c r="C9">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="D9">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E9">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="F9">
         <v>2</v>
@@ -1112,13 +1112,13 @@
         <v>941</v>
       </c>
       <c r="C10">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D10">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E10">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1132,13 +1132,13 @@
         <v>919</v>
       </c>
       <c r="C11">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D11">
         <v>32</v>
       </c>
       <c r="E11">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1152,13 +1152,13 @@
         <v>909</v>
       </c>
       <c r="C12">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="F12">
         <v>2</v>
@@ -1172,13 +1172,13 @@
         <v>840</v>
       </c>
       <c r="C13">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D13">
         <v>69</v>
       </c>
       <c r="E13">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="F13">
         <v>101</v>
@@ -1192,13 +1192,13 @@
         <v>813</v>
       </c>
       <c r="C14">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D14">
         <v>21</v>
       </c>
       <c r="E14">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="F14">
         <v>26</v>
@@ -1232,13 +1232,13 @@
         <v>783</v>
       </c>
       <c r="C16">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D16">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E16">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="F16">
         <v>84</v>
@@ -1252,13 +1252,13 @@
         <v>729</v>
       </c>
       <c r="C17">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D17">
         <v>8</v>
       </c>
       <c r="E17">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1272,13 +1272,13 @@
         <v>695</v>
       </c>
       <c r="C18">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D18">
         <v>35</v>
       </c>
       <c r="E18">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1292,16 +1292,16 @@
         <v>658</v>
       </c>
       <c r="C19">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="D19">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E19">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="F19">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1312,13 +1312,13 @@
         <v>646</v>
       </c>
       <c r="C20">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="D20">
         <v>22</v>
       </c>
       <c r="E20">
-        <v>557</v>
+        <v>567</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1332,7 +1332,7 @@
         <v>609</v>
       </c>
       <c r="C21">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D21">
         <v>34</v>
@@ -1352,13 +1352,13 @@
         <v>601</v>
       </c>
       <c r="C22">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D22">
         <v>40</v>
       </c>
       <c r="E22">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1392,13 +1392,13 @@
         <v>502</v>
       </c>
       <c r="C24">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D24">
         <v>0</v>
       </c>
       <c r="E24">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1449,16 +1449,16 @@
         <v>35</v>
       </c>
       <c r="B27">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C27">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D27">
         <v>95</v>
       </c>
       <c r="E27">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -1472,16 +1472,16 @@
         <v>441</v>
       </c>
       <c r="C28">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D28">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="E28">
-        <v>358</v>
+        <v>327</v>
       </c>
       <c r="F28">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -1492,13 +1492,13 @@
         <v>406</v>
       </c>
       <c r="C29">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D29">
         <v>69</v>
       </c>
       <c r="E29">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F29">
         <v>0</v>
@@ -1512,7 +1512,7 @@
         <v>401</v>
       </c>
       <c r="C30">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D30">
         <v>44</v>
@@ -1552,13 +1552,13 @@
         <v>388</v>
       </c>
       <c r="C32">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D32">
         <v>0</v>
       </c>
       <c r="E32">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -1612,13 +1612,13 @@
         <v>267</v>
       </c>
       <c r="C35">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D35">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E35">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -1632,16 +1632,16 @@
         <v>238</v>
       </c>
       <c r="C36">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D36">
         <v>0</v>
       </c>
       <c r="E36">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="F36">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -1649,19 +1649,19 @@
         <v>45</v>
       </c>
       <c r="B37">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C37">
-        <v>49</v>
+        <v>88</v>
       </c>
       <c r="D37">
-        <v>59</v>
+        <v>5</v>
       </c>
       <c r="E37">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -1672,16 +1672,16 @@
         <v>236</v>
       </c>
       <c r="C38">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="D38">
-        <v>5</v>
+        <v>59</v>
       </c>
       <c r="E38">
-        <v>144</v>
+        <v>125</v>
       </c>
       <c r="F38">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -1732,13 +1732,13 @@
         <v>221</v>
       </c>
       <c r="C41">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D41">
         <v>26</v>
       </c>
       <c r="E41">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -1832,7 +1832,7 @@
         <v>182</v>
       </c>
       <c r="C46">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -1841,7 +1841,7 @@
         <v>159</v>
       </c>
       <c r="F46">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -1878,7 +1878,7 @@
         <v>28</v>
       </c>
       <c r="E48">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F48">
         <v>0</v>
@@ -1912,13 +1912,13 @@
         <v>154</v>
       </c>
       <c r="C50">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D50">
         <v>0</v>
       </c>
       <c r="E50">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F50">
         <v>0</v>
@@ -2012,13 +2012,13 @@
         <v>137</v>
       </c>
       <c r="C55">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D55">
         <v>0</v>
       </c>
       <c r="E55">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F55">
         <v>0</v>
@@ -2092,13 +2092,13 @@
         <v>127</v>
       </c>
       <c r="C59">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="D59">
         <v>0</v>
       </c>
       <c r="E59">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="F59">
         <v>0</v>
@@ -2112,13 +2112,13 @@
         <v>124</v>
       </c>
       <c r="C60">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D60">
         <v>22</v>
       </c>
       <c r="E60">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -2452,13 +2452,13 @@
         <v>80</v>
       </c>
       <c r="C77">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D77">
         <v>16</v>
       </c>
       <c r="E77">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F77">
         <v>0</v>
@@ -2472,13 +2472,13 @@
         <v>79</v>
       </c>
       <c r="C78">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D78">
         <v>0</v>
       </c>
       <c r="E78">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F78">
         <v>0</v>
@@ -2492,13 +2492,13 @@
         <v>79</v>
       </c>
       <c r="C79">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D79">
         <v>0</v>
       </c>
       <c r="E79">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F79">
         <v>0</v>
@@ -2672,13 +2672,13 @@
         <v>68</v>
       </c>
       <c r="C88">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D88">
         <v>0</v>
       </c>
       <c r="E88">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F88">
         <v>0</v>
@@ -2792,13 +2792,13 @@
         <v>64</v>
       </c>
       <c r="C94">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D94">
         <v>0</v>
       </c>
       <c r="E94">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="F94">
         <v>0</v>
@@ -2872,13 +2872,13 @@
         <v>63</v>
       </c>
       <c r="C98">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D98">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E98">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F98">
         <v>0</v>
@@ -2998,10 +2998,10 @@
         <v>6</v>
       </c>
       <c r="E104">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F104">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105" spans="1:6">
@@ -3292,13 +3292,13 @@
         <v>43</v>
       </c>
       <c r="C119">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D119">
         <v>0</v>
       </c>
       <c r="E119">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="F119">
         <v>0</v>
@@ -3352,13 +3352,13 @@
         <v>39</v>
       </c>
       <c r="C122">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D122">
         <v>0</v>
       </c>
       <c r="E122">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F122">
         <v>0</v>

--- a/resumo_busca_ativa_consolidado.xlsx
+++ b/resumo_busca_ativa_consolidado.xlsx
@@ -859,19 +859,19 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>19012</v>
+        <v>19009</v>
       </c>
       <c r="C2">
-        <v>2936</v>
+        <v>3031</v>
       </c>
       <c r="D2">
-        <v>719</v>
+        <v>657</v>
       </c>
       <c r="E2">
-        <v>15218</v>
+        <v>15181</v>
       </c>
       <c r="F2">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -882,13 +882,13 @@
         <v>16724</v>
       </c>
       <c r="C3">
-        <v>2736</v>
+        <v>2737</v>
       </c>
       <c r="D3">
         <v>1423</v>
       </c>
       <c r="E3">
-        <v>12375</v>
+        <v>12374</v>
       </c>
       <c r="F3">
         <v>150</v>
@@ -902,16 +902,16 @@
         <v>9405</v>
       </c>
       <c r="C4">
-        <v>1275</v>
+        <v>1277</v>
       </c>
       <c r="D4">
         <v>787</v>
       </c>
       <c r="E4">
-        <v>7062</v>
+        <v>7061</v>
       </c>
       <c r="F4">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
   </sheetData>
@@ -949,16 +949,16 @@
         <v>10</v>
       </c>
       <c r="B2">
-        <v>9606</v>
+        <v>9603</v>
       </c>
       <c r="C2">
-        <v>1265</v>
+        <v>1317</v>
       </c>
       <c r="D2">
-        <v>252</v>
+        <v>229</v>
       </c>
       <c r="E2">
-        <v>8065</v>
+        <v>8033</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -1052,13 +1052,13 @@
         <v>1268</v>
       </c>
       <c r="C7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D7">
         <v>57</v>
       </c>
       <c r="E7">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="F7">
         <v>12</v>
@@ -1292,13 +1292,13 @@
         <v>658</v>
       </c>
       <c r="C19">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D19">
         <v>50</v>
       </c>
       <c r="E19">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="F19">
         <v>15</v>
@@ -1352,10 +1352,10 @@
         <v>601</v>
       </c>
       <c r="C22">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D22">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E22">
         <v>331</v>
@@ -1392,13 +1392,13 @@
         <v>502</v>
       </c>
       <c r="C24">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D24">
         <v>0</v>
       </c>
       <c r="E24">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1452,13 +1452,13 @@
         <v>443</v>
       </c>
       <c r="C27">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D27">
         <v>95</v>
       </c>
       <c r="E27">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -1472,13 +1472,13 @@
         <v>441</v>
       </c>
       <c r="C28">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="D28">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="E28">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -1612,13 +1612,13 @@
         <v>267</v>
       </c>
       <c r="C35">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D35">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E35">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -1772,13 +1772,13 @@
         <v>196</v>
       </c>
       <c r="C43">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D43">
         <v>21</v>
       </c>
       <c r="E43">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F43">
         <v>0</v>
@@ -1972,13 +1972,13 @@
         <v>148</v>
       </c>
       <c r="C53">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D53">
         <v>0</v>
       </c>
       <c r="E53">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F53">
         <v>0</v>
@@ -2132,16 +2132,16 @@
         <v>123</v>
       </c>
       <c r="C61">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D61">
         <v>0</v>
       </c>
       <c r="E61">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="F61">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -2452,13 +2452,13 @@
         <v>80</v>
       </c>
       <c r="C77">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D77">
         <v>16</v>
       </c>
       <c r="E77">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F77">
         <v>0</v>
@@ -2872,10 +2872,10 @@
         <v>63</v>
       </c>
       <c r="C98">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D98">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E98">
         <v>52</v>
@@ -2998,10 +2998,10 @@
         <v>6</v>
       </c>
       <c r="E104">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F104">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105" spans="1:6">
@@ -3292,13 +3292,13 @@
         <v>43</v>
       </c>
       <c r="C119">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D119">
         <v>0</v>
       </c>
       <c r="E119">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F119">
         <v>0</v>

--- a/resumo_busca_ativa_consolidado.xlsx
+++ b/resumo_busca_ativa_consolidado.xlsx
@@ -440,16 +440,16 @@
     <t>ALTO HORIZONTE</t>
   </si>
   <si>
+    <t>GUARINOS</t>
+  </si>
+  <si>
     <t>PILAR DE GOIAS</t>
   </si>
   <si>
-    <t>GUARINOS</t>
+    <t>EDEALINA</t>
   </si>
   <si>
     <t>MIMOSO DE GOIAS</t>
-  </si>
-  <si>
-    <t>EDEALINA</t>
   </si>
   <si>
     <t>GUARANI DE GOIAS</t>
@@ -859,19 +859,19 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>19009</v>
+        <v>19003</v>
       </c>
       <c r="C2">
-        <v>3031</v>
+        <v>3060</v>
       </c>
       <c r="D2">
-        <v>657</v>
+        <v>649</v>
       </c>
       <c r="E2">
-        <v>15181</v>
+        <v>15153</v>
       </c>
       <c r="F2">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -882,13 +882,13 @@
         <v>16724</v>
       </c>
       <c r="C3">
-        <v>2737</v>
+        <v>2746</v>
       </c>
       <c r="D3">
-        <v>1423</v>
+        <v>1426</v>
       </c>
       <c r="E3">
-        <v>12374</v>
+        <v>12362</v>
       </c>
       <c r="F3">
         <v>150</v>
@@ -899,16 +899,16 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>9405</v>
+        <v>9407</v>
       </c>
       <c r="C4">
-        <v>1277</v>
+        <v>1284</v>
       </c>
       <c r="D4">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="E4">
-        <v>7061</v>
+        <v>7056</v>
       </c>
       <c r="F4">
         <v>231</v>
@@ -949,16 +949,16 @@
         <v>10</v>
       </c>
       <c r="B2">
-        <v>9603</v>
+        <v>9600</v>
       </c>
       <c r="C2">
-        <v>1317</v>
+        <v>1331</v>
       </c>
       <c r="D2">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E2">
-        <v>8033</v>
+        <v>8019</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -972,13 +972,13 @@
         <v>2366</v>
       </c>
       <c r="C3">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D3">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="E3">
-        <v>1700</v>
+        <v>1692</v>
       </c>
       <c r="F3">
         <v>81</v>
@@ -992,13 +992,13 @@
         <v>1735</v>
       </c>
       <c r="C4">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D4">
         <v>152</v>
       </c>
       <c r="E4">
-        <v>1318</v>
+        <v>1316</v>
       </c>
       <c r="F4">
         <v>19</v>
@@ -1012,13 +1012,13 @@
         <v>1632</v>
       </c>
       <c r="C5">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D5">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E5">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="F5">
         <v>11</v>
@@ -1032,13 +1032,13 @@
         <v>1498</v>
       </c>
       <c r="C6">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D6">
         <v>260</v>
       </c>
       <c r="E6">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1049,16 +1049,16 @@
         <v>15</v>
       </c>
       <c r="B7">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="C7">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="D7">
         <v>57</v>
       </c>
       <c r="E7">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="F7">
         <v>12</v>
@@ -1072,13 +1072,13 @@
         <v>1203</v>
       </c>
       <c r="C8">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D8">
         <v>44</v>
       </c>
       <c r="E8">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -1092,10 +1092,10 @@
         <v>1127</v>
       </c>
       <c r="C9">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D9">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E9">
         <v>502</v>
@@ -1112,10 +1112,10 @@
         <v>941</v>
       </c>
       <c r="C10">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D10">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E10">
         <v>464</v>
@@ -1138,7 +1138,7 @@
         <v>32</v>
       </c>
       <c r="E11">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1172,10 +1172,10 @@
         <v>840</v>
       </c>
       <c r="C13">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D13">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E13">
         <v>540</v>
@@ -1229,10 +1229,10 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="C16">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D16">
         <v>64</v>
@@ -1292,13 +1292,13 @@
         <v>658</v>
       </c>
       <c r="C19">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D19">
         <v>50</v>
       </c>
       <c r="E19">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F19">
         <v>15</v>
@@ -1329,16 +1329,16 @@
         <v>29</v>
       </c>
       <c r="B21">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="C21">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="D21">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E21">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1352,13 +1352,13 @@
         <v>601</v>
       </c>
       <c r="C22">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D22">
         <v>38</v>
       </c>
       <c r="E22">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1372,13 +1372,13 @@
         <v>600</v>
       </c>
       <c r="C23">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D23">
         <v>70</v>
       </c>
       <c r="E23">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="F23">
         <v>17</v>
@@ -1398,7 +1398,7 @@
         <v>0</v>
       </c>
       <c r="E24">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1512,10 +1512,10 @@
         <v>401</v>
       </c>
       <c r="C30">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D30">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E30">
         <v>287</v>
@@ -1529,10 +1529,10 @@
         <v>39</v>
       </c>
       <c r="B31">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C31">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D31">
         <v>31</v>
@@ -1609,10 +1609,10 @@
         <v>43</v>
       </c>
       <c r="B35">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C35">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D35">
         <v>8</v>
@@ -1729,10 +1729,10 @@
         <v>49</v>
       </c>
       <c r="B41">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C41">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D41">
         <v>26</v>
@@ -1852,13 +1852,13 @@
         <v>167</v>
       </c>
       <c r="C47">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D47">
         <v>1</v>
       </c>
       <c r="E47">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F47">
         <v>0</v>
@@ -2089,7 +2089,7 @@
         <v>67</v>
       </c>
       <c r="B59">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C59">
         <v>18</v>
@@ -2098,7 +2098,7 @@
         <v>0</v>
       </c>
       <c r="E59">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F59">
         <v>0</v>
@@ -2132,16 +2132,16 @@
         <v>123</v>
       </c>
       <c r="C61">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E61">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F61">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -2372,13 +2372,13 @@
         <v>88</v>
       </c>
       <c r="C73">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D73">
         <v>0</v>
       </c>
       <c r="E73">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F73">
         <v>0</v>
@@ -2458,7 +2458,7 @@
         <v>16</v>
       </c>
       <c r="E77">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F77">
         <v>0</v>
@@ -3572,13 +3572,13 @@
         <v>33</v>
       </c>
       <c r="C133">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D133">
         <v>0</v>
       </c>
       <c r="E133">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F133">
         <v>0</v>
@@ -3589,16 +3589,16 @@
         <v>142</v>
       </c>
       <c r="B134">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C134">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D134">
         <v>0</v>
       </c>
       <c r="E134">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F134">
         <v>0</v>
@@ -3612,13 +3612,13 @@
         <v>32</v>
       </c>
       <c r="C135">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D135">
         <v>0</v>
       </c>
       <c r="E135">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F135">
         <v>0</v>
@@ -3632,13 +3632,13 @@
         <v>32</v>
       </c>
       <c r="C136">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D136">
         <v>0</v>
       </c>
       <c r="E136">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F136">
         <v>0</v>
